--- a/SHAPE-Lab-Website-Content.xlsx
+++ b/SHAPE-Lab-Website-Content.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bryan\Documents\GitHub\Website\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/byg5201_psu_edu/Documents/Documents/GitHub/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4358DB11-5B92-4F17-8511-6659BB54189A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{4358DB11-5B92-4F17-8511-6659BB54189A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5C65186-6CC4-4886-9A70-E8492214C0F6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site Copy" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="1169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="1170">
   <si>
     <t>Section</t>
   </si>
@@ -373,9 +373,6 @@
     <t>Guha Manogharan</t>
   </si>
   <si>
-    <t>Post-Doctorate and Graduate Researchers</t>
-  </si>
-  <si>
     <t>Aishwarya Deshpande, Ph.D.</t>
   </si>
   <si>
@@ -3536,6 +3533,12 @@
   </si>
   <si>
     <t>2444</t>
+  </si>
+  <si>
+    <t>Post-Doctorate</t>
+  </si>
+  <si>
+    <t>Ph.D.</t>
   </si>
 </sst>
 </file>
@@ -4449,842 +4452,842 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B1" t="s">
         <v>1042</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1043</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1044</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B2" t="s">
         <v>1046</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>1047</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>1048</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C3" t="s">
         <v>1050</v>
       </c>
-      <c r="B3" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1051</v>
-      </c>
       <c r="D3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C4" t="s">
         <v>1052</v>
       </c>
-      <c r="B4" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1053</v>
-      </c>
       <c r="D4" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C5" t="s">
         <v>1054</v>
       </c>
-      <c r="B5" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1055</v>
-      </c>
       <c r="D5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C6" t="s">
         <v>1056</v>
       </c>
-      <c r="B6" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1057</v>
-      </c>
       <c r="D6" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C7" t="s">
         <v>1058</v>
       </c>
-      <c r="B7" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1059</v>
-      </c>
       <c r="D7" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C8" t="s">
         <v>1060</v>
       </c>
-      <c r="B8" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1061</v>
-      </c>
       <c r="D8" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C9" t="s">
         <v>1062</v>
       </c>
-      <c r="B9" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1063</v>
-      </c>
       <c r="D9" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C10" t="s">
         <v>1064</v>
       </c>
-      <c r="B10" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1065</v>
-      </c>
       <c r="D10" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C11" t="s">
         <v>1066</v>
       </c>
-      <c r="B11" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1067</v>
-      </c>
       <c r="D11" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C12" t="s">
         <v>1068</v>
       </c>
-      <c r="B12" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1069</v>
-      </c>
       <c r="D12" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C13" t="s">
         <v>1070</v>
       </c>
-      <c r="B13" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1071</v>
-      </c>
       <c r="D13" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C14" t="s">
         <v>1072</v>
       </c>
-      <c r="B14" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1073</v>
-      </c>
       <c r="D14" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C15" t="s">
         <v>1074</v>
       </c>
-      <c r="B15" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1075</v>
-      </c>
       <c r="D15" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B16" t="s">
         <v>1076</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>1077</v>
       </c>
-      <c r="C16" t="s">
-        <v>1078</v>
-      </c>
       <c r="D16" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C17" t="s">
         <v>1079</v>
       </c>
-      <c r="B17" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1080</v>
-      </c>
       <c r="D17" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C18" t="s">
         <v>1081</v>
       </c>
-      <c r="B18" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1082</v>
-      </c>
       <c r="D18" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C19" t="s">
         <v>1083</v>
       </c>
-      <c r="B19" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1084</v>
-      </c>
       <c r="D19" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C20" t="s">
         <v>1085</v>
       </c>
-      <c r="B20" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1086</v>
-      </c>
       <c r="D20" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C21" t="s">
         <v>1087</v>
       </c>
-      <c r="B21" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1088</v>
-      </c>
       <c r="D21" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C22" t="s">
         <v>1089</v>
       </c>
-      <c r="B22" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1090</v>
-      </c>
       <c r="D22" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C23" t="s">
         <v>1091</v>
       </c>
-      <c r="B23" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1092</v>
-      </c>
       <c r="D23" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C24" t="s">
         <v>1093</v>
       </c>
-      <c r="B24" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1094</v>
-      </c>
       <c r="D24" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C25" t="s">
         <v>1095</v>
       </c>
-      <c r="B25" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1096</v>
-      </c>
       <c r="D25" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C26" t="s">
         <v>1097</v>
       </c>
-      <c r="B26" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1098</v>
-      </c>
       <c r="D26" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C27" t="s">
         <v>1099</v>
       </c>
-      <c r="B27" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1100</v>
-      </c>
       <c r="D27" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C28" t="s">
         <v>1101</v>
       </c>
-      <c r="B28" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1102</v>
-      </c>
       <c r="D28" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C29" t="s">
         <v>1103</v>
       </c>
-      <c r="B29" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1104</v>
-      </c>
       <c r="D29" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C30" t="s">
         <v>1105</v>
       </c>
-      <c r="B30" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1106</v>
-      </c>
       <c r="D30" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C31" t="s">
         <v>1107</v>
       </c>
-      <c r="B31" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1108</v>
-      </c>
       <c r="D31" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C32" t="s">
         <v>1109</v>
       </c>
-      <c r="B32" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1110</v>
-      </c>
       <c r="D32" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C33" t="s">
         <v>1111</v>
       </c>
-      <c r="B33" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1112</v>
-      </c>
       <c r="D33" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C34" t="s">
         <v>1113</v>
       </c>
-      <c r="B34" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1114</v>
-      </c>
       <c r="D34" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C35" t="s">
         <v>1115</v>
       </c>
-      <c r="B35" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1116</v>
-      </c>
       <c r="D35" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C36" t="s">
         <v>1117</v>
       </c>
-      <c r="B36" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1118</v>
-      </c>
       <c r="D36" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C37" t="s">
         <v>1119</v>
       </c>
-      <c r="B37" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1120</v>
-      </c>
       <c r="D37" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C38" t="s">
         <v>1121</v>
       </c>
-      <c r="B38" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1122</v>
-      </c>
       <c r="D38" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C39" t="s">
         <v>1123</v>
       </c>
-      <c r="B39" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1124</v>
-      </c>
       <c r="D39" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C40" t="s">
         <v>1125</v>
       </c>
-      <c r="B40" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C40" t="s">
-        <v>1126</v>
-      </c>
       <c r="D40" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C41" t="s">
         <v>1127</v>
       </c>
-      <c r="B41" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C41" t="s">
-        <v>1128</v>
-      </c>
       <c r="D41" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C42" t="s">
         <v>1129</v>
       </c>
-      <c r="B42" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1130</v>
-      </c>
       <c r="D42" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C43" t="s">
         <v>1131</v>
       </c>
-      <c r="B43" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1132</v>
-      </c>
       <c r="D43" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C44" t="s">
         <v>1133</v>
       </c>
-      <c r="B44" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1134</v>
-      </c>
       <c r="D44" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C45" t="s">
         <v>1135</v>
       </c>
-      <c r="B45" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C45" t="s">
-        <v>1136</v>
-      </c>
       <c r="D45" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C46" t="s">
         <v>1137</v>
       </c>
-      <c r="B46" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1138</v>
-      </c>
       <c r="D46" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C47" t="s">
         <v>1139</v>
       </c>
-      <c r="B47" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1140</v>
-      </c>
       <c r="D47" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B48" t="s">
         <v>1141</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>1142</v>
       </c>
-      <c r="C48" t="s">
-        <v>1143</v>
-      </c>
       <c r="D48" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C49" t="s">
         <v>1144</v>
       </c>
-      <c r="B49" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1145</v>
-      </c>
       <c r="D49" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C50" t="s">
         <v>1146</v>
       </c>
-      <c r="B50" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1147</v>
-      </c>
       <c r="D50" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C51" t="s">
         <v>1148</v>
       </c>
-      <c r="B51" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1149</v>
-      </c>
       <c r="D51" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C52" t="s">
         <v>1150</v>
       </c>
-      <c r="B52" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C52" t="s">
-        <v>1151</v>
-      </c>
       <c r="D52" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C53" t="s">
         <v>1152</v>
       </c>
-      <c r="B53" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1153</v>
-      </c>
       <c r="D53" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C54" t="s">
         <v>1154</v>
       </c>
-      <c r="B54" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1155</v>
-      </c>
       <c r="D54" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C55" t="s">
         <v>1156</v>
       </c>
-      <c r="B55" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C55" t="s">
-        <v>1157</v>
-      </c>
       <c r="D55" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C56" t="s">
         <v>1158</v>
       </c>
-      <c r="B56" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C56" t="s">
-        <v>1159</v>
-      </c>
       <c r="D56" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C57" t="s">
         <v>1160</v>
       </c>
-      <c r="B57" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1161</v>
-      </c>
       <c r="D57" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C58" t="s">
         <v>1162</v>
       </c>
-      <c r="B58" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C58" t="s">
-        <v>1163</v>
-      </c>
       <c r="D58" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C59" t="s">
         <v>1164</v>
       </c>
-      <c r="B59" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1165</v>
-      </c>
       <c r="D59" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B60" t="s">
         <v>1166</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>1167</v>
       </c>
-      <c r="C60" t="s">
-        <v>1168</v>
-      </c>
       <c r="D60" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
   </sheetData>
@@ -5534,278 +5537,278 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B3" t="s">
         <v>114</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
         <v>115</v>
       </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>116</v>
-      </c>
-      <c r="G3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>1169</v>
       </c>
       <c r="B4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
         <v>118</v>
       </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>119</v>
-      </c>
       <c r="G4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>1169</v>
       </c>
       <c r="B5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
         <v>120</v>
       </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>121</v>
-      </c>
       <c r="G5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>1169</v>
       </c>
       <c r="B6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
         <v>122</v>
       </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>123</v>
-      </c>
       <c r="G6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>1169</v>
       </c>
       <c r="B7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
         <v>124</v>
       </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>125</v>
-      </c>
       <c r="G7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>1169</v>
       </c>
       <c r="B8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
         <v>126</v>
       </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>127</v>
-      </c>
       <c r="G8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>1169</v>
       </c>
       <c r="B9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
         <v>128</v>
       </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>129</v>
-      </c>
       <c r="G9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>1169</v>
       </c>
       <c r="B10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
         <v>130</v>
       </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>131</v>
-      </c>
       <c r="G10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" t="s">
         <v>132</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
         <v>133</v>
       </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>134</v>
-      </c>
       <c r="G11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
         <v>135</v>
       </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>136</v>
-      </c>
       <c r="G12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
         <v>137</v>
       </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>138</v>
-      </c>
       <c r="G13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
         <v>139</v>
       </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>140</v>
-      </c>
       <c r="G14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -5827,13 +5830,13 @@
         <v>28</v>
       </c>
       <c r="C1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" t="s">
         <v>141</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>142</v>
-      </c>
-      <c r="E1" t="s">
-        <v>143</v>
       </c>
       <c r="F1" t="s">
         <v>6</v>
@@ -5841,2442 +5844,2442 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" t="s">
         <v>144</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>145</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>146</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>147</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>148</v>
-      </c>
-      <c r="F2" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" t="s">
         <v>150</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>151</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>152</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>153</v>
-      </c>
-      <c r="F3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" t="s">
         <v>155</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>156</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>157</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>158</v>
-      </c>
-      <c r="F4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" t="s">
         <v>160</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>161</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>162</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>163</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>164</v>
-      </c>
-      <c r="F5" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" t="s">
         <v>166</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>167</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>168</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>169</v>
-      </c>
-      <c r="F6" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" t="s">
         <v>171</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E7" t="s">
         <v>172</v>
       </c>
-      <c r="D7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>173</v>
-      </c>
-      <c r="F7" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" t="s">
         <v>175</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>176</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>177</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>178</v>
-      </c>
-      <c r="F8" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" t="s">
         <v>180</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>181</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>182</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>183</v>
-      </c>
-      <c r="F9" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" t="s">
         <v>185</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>186</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>187</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>188</v>
-      </c>
-      <c r="F10" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" t="s">
         <v>190</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>191</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>192</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>193</v>
-      </c>
-      <c r="F11" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C12" t="s">
         <v>195</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>196</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>197</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>198</v>
-      </c>
-      <c r="F12" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" t="s">
         <v>200</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>201</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>202</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>203</v>
-      </c>
-      <c r="F13" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" t="s">
         <v>205</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>206</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>207</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>208</v>
-      </c>
-      <c r="F14" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" t="s">
         <v>210</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>211</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>212</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>213</v>
-      </c>
-      <c r="F15" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B16" t="s">
+        <v>214</v>
+      </c>
+      <c r="C16" t="s">
         <v>215</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>216</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>217</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>218</v>
-      </c>
-      <c r="F16" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B17" t="s">
+        <v>219</v>
+      </c>
+      <c r="C17" t="s">
         <v>220</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>221</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>222</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>223</v>
-      </c>
-      <c r="F17" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B18" t="s">
+        <v>224</v>
+      </c>
+      <c r="C18" t="s">
         <v>225</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>226</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>227</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>228</v>
-      </c>
-      <c r="F18" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C19" t="s">
         <v>230</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>231</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>232</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>233</v>
-      </c>
-      <c r="F19" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B20" t="s">
         <v>235</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>236</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E20" t="s">
         <v>237</v>
       </c>
-      <c r="D20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>238</v>
-      </c>
-      <c r="F20" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s">
+        <v>239</v>
+      </c>
+      <c r="C21" t="s">
         <v>240</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>241</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>242</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>243</v>
-      </c>
-      <c r="F21" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s">
+        <v>244</v>
+      </c>
+      <c r="C22" t="s">
         <v>245</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>246</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>247</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>248</v>
-      </c>
-      <c r="F22" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" t="s">
         <v>250</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>251</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>252</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>253</v>
-      </c>
-      <c r="F23" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s">
+        <v>254</v>
+      </c>
+      <c r="C24" t="s">
         <v>255</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>256</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>257</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>258</v>
-      </c>
-      <c r="F24" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s">
+        <v>259</v>
+      </c>
+      <c r="C25" t="s">
         <v>260</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>261</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>262</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>263</v>
-      </c>
-      <c r="F25" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s">
+        <v>264</v>
+      </c>
+      <c r="C26" t="s">
         <v>265</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>266</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>267</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>268</v>
-      </c>
-      <c r="F26" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s">
+        <v>269</v>
+      </c>
+      <c r="C27" t="s">
         <v>270</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>271</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>272</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>273</v>
-      </c>
-      <c r="F27" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B28" t="s">
+        <v>274</v>
+      </c>
+      <c r="C28" t="s">
         <v>275</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>276</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>277</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>278</v>
-      </c>
-      <c r="F28" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>279</v>
+      </c>
+      <c r="B29" t="s">
         <v>280</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>281</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>282</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>283</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>284</v>
-      </c>
-      <c r="F29" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s">
+        <v>285</v>
+      </c>
+      <c r="C30" t="s">
         <v>286</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>287</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>288</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>289</v>
-      </c>
-      <c r="F30" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s">
+        <v>290</v>
+      </c>
+      <c r="C31" t="s">
         <v>291</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>292</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>293</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>294</v>
-      </c>
-      <c r="F31" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B32" t="s">
+        <v>295</v>
+      </c>
+      <c r="C32" t="s">
         <v>296</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>297</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>298</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>299</v>
-      </c>
-      <c r="F32" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B33" t="s">
+        <v>300</v>
+      </c>
+      <c r="C33" t="s">
         <v>301</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>302</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>303</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>304</v>
-      </c>
-      <c r="F33" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s">
+        <v>305</v>
+      </c>
+      <c r="C34" t="s">
         <v>306</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>221</v>
+      </c>
+      <c r="E34" t="s">
         <v>307</v>
       </c>
-      <c r="D34" t="s">
-        <v>222</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>308</v>
-      </c>
-      <c r="F34" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s">
+        <v>309</v>
+      </c>
+      <c r="C35" t="s">
         <v>310</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>311</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>312</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>313</v>
-      </c>
-      <c r="F35" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B36" t="s">
+        <v>314</v>
+      </c>
+      <c r="C36" t="s">
         <v>315</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
+        <v>226</v>
+      </c>
+      <c r="E36" t="s">
         <v>316</v>
       </c>
-      <c r="D36" t="s">
-        <v>227</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>317</v>
-      </c>
-      <c r="F36" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B37" t="s">
+        <v>318</v>
+      </c>
+      <c r="C37" t="s">
+        <v>306</v>
+      </c>
+      <c r="D37" t="s">
         <v>319</v>
       </c>
-      <c r="C37" t="s">
-        <v>307</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>320</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>321</v>
-      </c>
-      <c r="F37" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B38" t="s">
+        <v>322</v>
+      </c>
+      <c r="C38" t="s">
         <v>323</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>324</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>325</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>326</v>
-      </c>
-      <c r="F38" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B39" t="s">
+        <v>327</v>
+      </c>
+      <c r="C39" t="s">
         <v>328</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>329</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>330</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>331</v>
-      </c>
-      <c r="F39" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s">
+        <v>332</v>
+      </c>
+      <c r="C40" t="s">
         <v>333</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>334</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>335</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>336</v>
-      </c>
-      <c r="F40" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B41" t="s">
+        <v>337</v>
+      </c>
+      <c r="C41" t="s">
         <v>338</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>339</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>340</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>341</v>
-      </c>
-      <c r="F41" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>342</v>
+      </c>
+      <c r="B42" t="s">
         <v>343</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>344</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>345</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>346</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>347</v>
-      </c>
-      <c r="F42" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B43" t="s">
+        <v>348</v>
+      </c>
+      <c r="C43" t="s">
         <v>349</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
+        <v>151</v>
+      </c>
+      <c r="E43" t="s">
         <v>350</v>
       </c>
-      <c r="D43" t="s">
-        <v>152</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>351</v>
-      </c>
-      <c r="F43" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B44" t="s">
+        <v>352</v>
+      </c>
+      <c r="C44" t="s">
         <v>353</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>354</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>355</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>356</v>
-      </c>
-      <c r="F44" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s">
+        <v>357</v>
+      </c>
+      <c r="C45" t="s">
         <v>358</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>359</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>360</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>361</v>
-      </c>
-      <c r="F45" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s">
+        <v>362</v>
+      </c>
+      <c r="C46" t="s">
         <v>363</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>364</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>365</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>366</v>
-      </c>
-      <c r="F46" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B47" t="s">
+        <v>367</v>
+      </c>
+      <c r="C47" t="s">
         <v>368</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>369</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>370</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>371</v>
-      </c>
-      <c r="F47" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s">
+        <v>372</v>
+      </c>
+      <c r="C48" t="s">
         <v>373</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>374</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>375</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>376</v>
-      </c>
-      <c r="F48" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s">
+        <v>377</v>
+      </c>
+      <c r="C49" t="s">
         <v>378</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>379</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>380</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>381</v>
-      </c>
-      <c r="F49" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s">
+        <v>382</v>
+      </c>
+      <c r="C50" t="s">
         <v>383</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>384</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>385</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>386</v>
-      </c>
-      <c r="F50" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B51" t="s">
+        <v>387</v>
+      </c>
+      <c r="C51" t="s">
         <v>388</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>389</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>390</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>391</v>
-      </c>
-      <c r="F51" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B52" t="s">
+        <v>392</v>
+      </c>
+      <c r="C52" t="s">
         <v>393</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>394</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>395</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>396</v>
-      </c>
-      <c r="F52" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B53" t="s">
+        <v>397</v>
+      </c>
+      <c r="C53" t="s">
         <v>398</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>399</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>400</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>401</v>
-      </c>
-      <c r="F53" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B54" t="s">
+        <v>402</v>
+      </c>
+      <c r="C54" t="s">
         <v>403</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>404</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>405</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>406</v>
-      </c>
-      <c r="F54" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B55" t="s">
+        <v>407</v>
+      </c>
+      <c r="C55" t="s">
         <v>408</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>409</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>410</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>411</v>
-      </c>
-      <c r="F55" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B56" t="s">
+        <v>412</v>
+      </c>
+      <c r="C56" t="s">
         <v>413</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>414</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>415</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>416</v>
-      </c>
-      <c r="F56" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B57" t="s">
+        <v>417</v>
+      </c>
+      <c r="C57" t="s">
         <v>418</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>419</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>420</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>421</v>
-      </c>
-      <c r="F57" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s">
+        <v>422</v>
+      </c>
+      <c r="C58" t="s">
         <v>423</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>424</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>425</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>426</v>
-      </c>
-      <c r="F58" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B59" t="s">
+        <v>427</v>
+      </c>
+      <c r="C59" t="s">
         <v>428</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>429</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>430</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>431</v>
-      </c>
-      <c r="F59" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B60" t="s">
+        <v>432</v>
+      </c>
+      <c r="C60" t="s">
         <v>433</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>434</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>435</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>436</v>
-      </c>
-      <c r="F60" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B61" t="s">
+        <v>437</v>
+      </c>
+      <c r="C61" t="s">
         <v>438</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>439</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>440</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>441</v>
-      </c>
-      <c r="F61" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B62" t="s">
+        <v>442</v>
+      </c>
+      <c r="C62" t="s">
         <v>443</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>444</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>445</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>446</v>
-      </c>
-      <c r="F62" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B63" t="s">
+        <v>447</v>
+      </c>
+      <c r="C63" t="s">
         <v>448</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
+        <v>444</v>
+      </c>
+      <c r="E63" t="s">
         <v>449</v>
       </c>
-      <c r="D63" t="s">
-        <v>445</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>450</v>
-      </c>
-      <c r="F63" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B64" t="s">
+        <v>451</v>
+      </c>
+      <c r="C64" t="s">
         <v>452</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>453</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>454</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>455</v>
-      </c>
-      <c r="F64" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B65" t="s">
+        <v>456</v>
+      </c>
+      <c r="C65" t="s">
         <v>457</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>458</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>459</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>460</v>
-      </c>
-      <c r="F65" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B66" t="s">
+        <v>461</v>
+      </c>
+      <c r="C66" t="s">
         <v>462</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>463</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>464</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>465</v>
-      </c>
-      <c r="F66" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B67" t="s">
+        <v>466</v>
+      </c>
+      <c r="C67" t="s">
         <v>467</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>468</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>469</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>470</v>
-      </c>
-      <c r="F67" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
+        <v>471</v>
+      </c>
+      <c r="B68" t="s">
         <v>472</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>473</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>474</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>475</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>476</v>
-      </c>
-      <c r="F68" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
+        <v>477</v>
+      </c>
+      <c r="B69" t="s">
         <v>478</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>479</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>480</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>481</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>482</v>
-      </c>
-      <c r="F69" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B70" t="s">
+        <v>483</v>
+      </c>
+      <c r="C70" t="s">
         <v>484</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>485</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>486</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>487</v>
-      </c>
-      <c r="F70" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B71" t="s">
+        <v>488</v>
+      </c>
+      <c r="C71" t="s">
         <v>489</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>490</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>491</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>492</v>
-      </c>
-      <c r="F71" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B72" t="s">
+        <v>493</v>
+      </c>
+      <c r="C72" t="s">
         <v>494</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>495</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>496</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>497</v>
-      </c>
-      <c r="F72" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B73" t="s">
+        <v>498</v>
+      </c>
+      <c r="C73" t="s">
         <v>499</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>500</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>501</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>502</v>
-      </c>
-      <c r="F73" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B74" t="s">
+        <v>503</v>
+      </c>
+      <c r="C74" t="s">
         <v>504</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>505</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>506</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>507</v>
-      </c>
-      <c r="F74" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B75" t="s">
+        <v>508</v>
+      </c>
+      <c r="C75" t="s">
         <v>509</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
+        <v>500</v>
+      </c>
+      <c r="E75" t="s">
         <v>510</v>
       </c>
-      <c r="D75" t="s">
-        <v>501</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>511</v>
-      </c>
-      <c r="F75" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B76" t="s">
+        <v>512</v>
+      </c>
+      <c r="C76" t="s">
         <v>513</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>514</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" t="s">
         <v>515</v>
-      </c>
-      <c r="E76" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B77" t="s">
+        <v>516</v>
+      </c>
+      <c r="C77" t="s">
         <v>517</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>518</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>519</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>520</v>
-      </c>
-      <c r="F77" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B78" t="s">
+        <v>521</v>
+      </c>
+      <c r="C78" t="s">
         <v>522</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>523</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>524</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>525</v>
-      </c>
-      <c r="F78" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B79" t="s">
+        <v>526</v>
+      </c>
+      <c r="C79" t="s">
         <v>527</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>528</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>529</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>530</v>
-      </c>
-      <c r="F79" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B80" t="s">
+        <v>531</v>
+      </c>
+      <c r="C80" t="s">
         <v>532</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>533</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>534</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>535</v>
-      </c>
-      <c r="F80" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B81" t="s">
+        <v>536</v>
+      </c>
+      <c r="C81" t="s">
         <v>537</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>538</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>539</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>540</v>
-      </c>
-      <c r="F81" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B82" t="s">
+        <v>541</v>
+      </c>
+      <c r="C82" t="s">
         <v>542</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>543</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>544</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>545</v>
-      </c>
-      <c r="F82" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B83" t="s">
+        <v>546</v>
+      </c>
+      <c r="C83" t="s">
         <v>547</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>548</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>549</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>550</v>
-      </c>
-      <c r="F83" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B84" t="s">
+        <v>551</v>
+      </c>
+      <c r="C84" t="s">
         <v>552</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>553</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>554</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>555</v>
-      </c>
-      <c r="F84" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B85" t="s">
+        <v>556</v>
+      </c>
+      <c r="C85" t="s">
         <v>557</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>558</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>559</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>560</v>
-      </c>
-      <c r="F85" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B86" t="s">
+        <v>561</v>
+      </c>
+      <c r="C86" t="s">
         <v>562</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>563</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F86" t="s">
         <v>564</v>
-      </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B87" t="s">
+        <v>565</v>
+      </c>
+      <c r="C87" t="s">
         <v>566</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>567</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87" t="s">
         <v>568</v>
-      </c>
-      <c r="E87" t="s">
-        <v>10</v>
-      </c>
-      <c r="F87" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B88" t="s">
+        <v>569</v>
+      </c>
+      <c r="C88" t="s">
         <v>570</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>571</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" t="s">
         <v>572</v>
-      </c>
-      <c r="E88" t="s">
-        <v>10</v>
-      </c>
-      <c r="F88" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B89" t="s">
+        <v>573</v>
+      </c>
+      <c r="C89" t="s">
         <v>574</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>575</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" t="s">
         <v>576</v>
-      </c>
-      <c r="E89" t="s">
-        <v>10</v>
-      </c>
-      <c r="F89" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B90" t="s">
+        <v>577</v>
+      </c>
+      <c r="C90" t="s">
         <v>578</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
+        <v>575</v>
+      </c>
+      <c r="E90" t="s">
+        <v>10</v>
+      </c>
+      <c r="F90" t="s">
         <v>579</v>
-      </c>
-      <c r="D90" t="s">
-        <v>576</v>
-      </c>
-      <c r="E90" t="s">
-        <v>10</v>
-      </c>
-      <c r="F90" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B91" t="s">
+        <v>580</v>
+      </c>
+      <c r="C91" t="s">
         <v>581</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>582</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" t="s">
         <v>583</v>
-      </c>
-      <c r="E91" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B92" t="s">
+        <v>584</v>
+      </c>
+      <c r="C92" t="s">
         <v>585</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
+        <v>575</v>
+      </c>
+      <c r="E92" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" t="s">
         <v>586</v>
-      </c>
-      <c r="D92" t="s">
-        <v>576</v>
-      </c>
-      <c r="E92" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B93" t="s">
+        <v>587</v>
+      </c>
+      <c r="C93" t="s">
         <v>588</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
+        <v>575</v>
+      </c>
+      <c r="E93" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93" t="s">
         <v>589</v>
-      </c>
-      <c r="D93" t="s">
-        <v>576</v>
-      </c>
-      <c r="E93" t="s">
-        <v>10</v>
-      </c>
-      <c r="F93" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B94" t="s">
+        <v>590</v>
+      </c>
+      <c r="C94" t="s">
         <v>591</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>592</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" t="s">
         <v>593</v>
-      </c>
-      <c r="E94" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B95" t="s">
+        <v>337</v>
+      </c>
+      <c r="C95" t="s">
         <v>338</v>
       </c>
-      <c r="C95" t="s">
-        <v>339</v>
-      </c>
       <c r="D95" t="s">
+        <v>594</v>
+      </c>
+      <c r="E95" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95" t="s">
         <v>595</v>
-      </c>
-      <c r="E95" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B96" t="s">
+        <v>596</v>
+      </c>
+      <c r="C96" t="s">
         <v>597</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>598</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" t="s">
         <v>599</v>
-      </c>
-      <c r="E96" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B97" t="s">
+        <v>600</v>
+      </c>
+      <c r="C97" t="s">
         <v>601</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>602</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
+        <v>10</v>
+      </c>
+      <c r="F97" t="s">
         <v>603</v>
-      </c>
-      <c r="E97" t="s">
-        <v>10</v>
-      </c>
-      <c r="F97" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B98" t="s">
+        <v>604</v>
+      </c>
+      <c r="C98" t="s">
         <v>605</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>606</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
+        <v>10</v>
+      </c>
+      <c r="F98" t="s">
         <v>607</v>
-      </c>
-      <c r="E98" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B99" t="s">
+        <v>608</v>
+      </c>
+      <c r="C99" t="s">
         <v>609</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
+        <v>606</v>
+      </c>
+      <c r="E99" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99" t="s">
         <v>610</v>
-      </c>
-      <c r="D99" t="s">
-        <v>607</v>
-      </c>
-      <c r="E99" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B100" t="s">
+        <v>611</v>
+      </c>
+      <c r="C100" t="s">
         <v>612</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>613</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" t="s">
         <v>614</v>
-      </c>
-      <c r="E100" t="s">
-        <v>10</v>
-      </c>
-      <c r="F100" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B101" t="s">
+        <v>615</v>
+      </c>
+      <c r="C101" t="s">
         <v>616</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>617</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" t="s">
         <v>618</v>
-      </c>
-      <c r="E101" t="s">
-        <v>10</v>
-      </c>
-      <c r="F101" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B102" t="s">
+        <v>619</v>
+      </c>
+      <c r="C102" t="s">
         <v>620</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
+        <v>613</v>
+      </c>
+      <c r="E102" t="s">
+        <v>10</v>
+      </c>
+      <c r="F102" t="s">
         <v>621</v>
-      </c>
-      <c r="D102" t="s">
-        <v>614</v>
-      </c>
-      <c r="E102" t="s">
-        <v>10</v>
-      </c>
-      <c r="F102" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B103" t="s">
+        <v>622</v>
+      </c>
+      <c r="C103" t="s">
         <v>623</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>624</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
+        <v>10</v>
+      </c>
+      <c r="F103" t="s">
         <v>625</v>
-      </c>
-      <c r="E103" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B104" t="s">
+        <v>626</v>
+      </c>
+      <c r="C104" t="s">
         <v>627</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
+        <v>617</v>
+      </c>
+      <c r="E104" t="s">
+        <v>10</v>
+      </c>
+      <c r="F104" t="s">
         <v>628</v>
-      </c>
-      <c r="D104" t="s">
-        <v>618</v>
-      </c>
-      <c r="E104" t="s">
-        <v>10</v>
-      </c>
-      <c r="F104" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B105" t="s">
+        <v>629</v>
+      </c>
+      <c r="C105" t="s">
         <v>630</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>631</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
+        <v>10</v>
+      </c>
+      <c r="F105" t="s">
         <v>632</v>
-      </c>
-      <c r="E105" t="s">
-        <v>10</v>
-      </c>
-      <c r="F105" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B106" t="s">
+        <v>633</v>
+      </c>
+      <c r="C106" t="s">
         <v>634</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>635</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
+        <v>10</v>
+      </c>
+      <c r="F106" t="s">
         <v>636</v>
-      </c>
-      <c r="E106" t="s">
-        <v>10</v>
-      </c>
-      <c r="F106" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
+        <v>637</v>
+      </c>
+      <c r="B107" t="s">
         <v>638</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>639</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>640</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107" t="s">
         <v>641</v>
-      </c>
-      <c r="E107" t="s">
-        <v>10</v>
-      </c>
-      <c r="F107" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B108" t="s">
+        <v>642</v>
+      </c>
+      <c r="C108" t="s">
+        <v>195</v>
+      </c>
+      <c r="D108" t="s">
+        <v>640</v>
+      </c>
+      <c r="E108" t="s">
+        <v>10</v>
+      </c>
+      <c r="F108" t="s">
         <v>643</v>
-      </c>
-      <c r="C108" t="s">
-        <v>196</v>
-      </c>
-      <c r="D108" t="s">
-        <v>641</v>
-      </c>
-      <c r="E108" t="s">
-        <v>10</v>
-      </c>
-      <c r="F108" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B109" t="s">
+        <v>644</v>
+      </c>
+      <c r="C109" t="s">
         <v>645</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>646</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
+        <v>10</v>
+      </c>
+      <c r="F109" t="s">
         <v>647</v>
-      </c>
-      <c r="E109" t="s">
-        <v>10</v>
-      </c>
-      <c r="F109" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B110" t="s">
+        <v>648</v>
+      </c>
+      <c r="C110" t="s">
         <v>649</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>650</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
+        <v>10</v>
+      </c>
+      <c r="F110" t="s">
         <v>651</v>
-      </c>
-      <c r="E110" t="s">
-        <v>10</v>
-      </c>
-      <c r="F110" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B111" t="s">
+        <v>652</v>
+      </c>
+      <c r="C111" t="s">
         <v>653</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>654</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
+        <v>10</v>
+      </c>
+      <c r="F111" t="s">
         <v>655</v>
-      </c>
-      <c r="E111" t="s">
-        <v>10</v>
-      </c>
-      <c r="F111" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B112" t="s">
+        <v>656</v>
+      </c>
+      <c r="C112" t="s">
         <v>657</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>658</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
+        <v>10</v>
+      </c>
+      <c r="F112" t="s">
         <v>659</v>
-      </c>
-      <c r="E112" t="s">
-        <v>10</v>
-      </c>
-      <c r="F112" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B113" t="s">
+        <v>660</v>
+      </c>
+      <c r="C113" t="s">
         <v>661</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
         <v>662</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113" t="s">
         <v>663</v>
-      </c>
-      <c r="E113" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B114" t="s">
+        <v>664</v>
+      </c>
+      <c r="C114" t="s">
         <v>665</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
+        <v>662</v>
+      </c>
+      <c r="E114" t="s">
+        <v>10</v>
+      </c>
+      <c r="F114" t="s">
         <v>666</v>
-      </c>
-      <c r="D114" t="s">
-        <v>663</v>
-      </c>
-      <c r="E114" t="s">
-        <v>10</v>
-      </c>
-      <c r="F114" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B115" t="s">
+        <v>667</v>
+      </c>
+      <c r="C115" t="s">
         <v>668</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
+        <v>662</v>
+      </c>
+      <c r="E115" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115" t="s">
         <v>669</v>
-      </c>
-      <c r="D115" t="s">
-        <v>663</v>
-      </c>
-      <c r="E115" t="s">
-        <v>10</v>
-      </c>
-      <c r="F115" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B116" t="s">
+        <v>670</v>
+      </c>
+      <c r="C116" t="s">
         <v>671</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
+        <v>662</v>
+      </c>
+      <c r="E116" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116" t="s">
         <v>672</v>
-      </c>
-      <c r="D116" t="s">
-        <v>663</v>
-      </c>
-      <c r="E116" t="s">
-        <v>10</v>
-      </c>
-      <c r="F116" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B117" t="s">
+        <v>673</v>
+      </c>
+      <c r="C117" t="s">
         <v>674</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>675</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
+        <v>10</v>
+      </c>
+      <c r="F117" t="s">
         <v>676</v>
-      </c>
-      <c r="E117" t="s">
-        <v>10</v>
-      </c>
-      <c r="F117" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B118" t="s">
+        <v>677</v>
+      </c>
+      <c r="C118" t="s">
         <v>678</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>679</v>
       </c>
-      <c r="D118" t="s">
+      <c r="E118" t="s">
+        <v>10</v>
+      </c>
+      <c r="F118" t="s">
         <v>680</v>
-      </c>
-      <c r="E118" t="s">
-        <v>10</v>
-      </c>
-      <c r="F118" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B119" t="s">
+        <v>681</v>
+      </c>
+      <c r="C119" t="s">
         <v>682</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>683</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
+        <v>10</v>
+      </c>
+      <c r="F119" t="s">
         <v>684</v>
-      </c>
-      <c r="E119" t="s">
-        <v>10</v>
-      </c>
-      <c r="F119" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B120" t="s">
+        <v>685</v>
+      </c>
+      <c r="C120" t="s">
         <v>686</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
+        <v>683</v>
+      </c>
+      <c r="E120" t="s">
+        <v>10</v>
+      </c>
+      <c r="F120" t="s">
         <v>687</v>
-      </c>
-      <c r="D120" t="s">
-        <v>684</v>
-      </c>
-      <c r="E120" t="s">
-        <v>10</v>
-      </c>
-      <c r="F120" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B121" t="s">
+        <v>688</v>
+      </c>
+      <c r="C121" t="s">
         <v>689</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
+        <v>606</v>
+      </c>
+      <c r="E121" t="s">
+        <v>10</v>
+      </c>
+      <c r="F121" t="s">
         <v>690</v>
-      </c>
-      <c r="D121" t="s">
-        <v>607</v>
-      </c>
-      <c r="E121" t="s">
-        <v>10</v>
-      </c>
-      <c r="F121" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B122" t="s">
+        <v>691</v>
+      </c>
+      <c r="C122" t="s">
         <v>692</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>693</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122" t="s">
         <v>694</v>
-      </c>
-      <c r="E122" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B123" t="s">
+        <v>695</v>
+      </c>
+      <c r="C123" t="s">
         <v>696</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
         <v>697</v>
       </c>
-      <c r="D123" t="s">
+      <c r="E123" t="s">
+        <v>10</v>
+      </c>
+      <c r="F123" t="s">
         <v>698</v>
-      </c>
-      <c r="E123" t="s">
-        <v>10</v>
-      </c>
-      <c r="F123" t="s">
-        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -8292,7 +8295,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B1" t="s">
         <v>65</v>
@@ -8309,53 +8312,53 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B2" t="s">
         <v>701</v>
-      </c>
-      <c r="B2" t="s">
-        <v>702</v>
       </c>
       <c r="C2" t="s">
         <v>88</v>
       </c>
       <c r="D2" t="s">
+        <v>702</v>
+      </c>
+      <c r="E2" t="s">
         <v>703</v>
-      </c>
-      <c r="E2" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>704</v>
+      </c>
+      <c r="B3" t="s">
         <v>705</v>
-      </c>
-      <c r="B3" t="s">
-        <v>706</v>
       </c>
       <c r="C3" t="s">
         <v>71</v>
       </c>
       <c r="D3" t="s">
+        <v>706</v>
+      </c>
+      <c r="E3" t="s">
         <v>707</v>
-      </c>
-      <c r="E3" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>708</v>
+      </c>
+      <c r="B4" t="s">
         <v>709</v>
-      </c>
-      <c r="B4" t="s">
-        <v>710</v>
       </c>
       <c r="C4" t="s">
         <v>94</v>
       </c>
       <c r="D4" t="s">
+        <v>710</v>
+      </c>
+      <c r="E4" t="s">
         <v>711</v>
-      </c>
-      <c r="E4" t="s">
-        <v>712</v>
       </c>
     </row>
   </sheetData>
@@ -8371,22 +8374,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B1" t="s">
         <v>103</v>
       </c>
       <c r="C1" t="s">
+        <v>713</v>
+      </c>
+      <c r="D1" t="s">
         <v>714</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>715</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>716</v>
-      </c>
-      <c r="F1" t="s">
-        <v>717</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
@@ -8394,347 +8397,347 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B2" t="s">
         <v>718</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>719</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>720</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>721</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>722</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>723</v>
-      </c>
-      <c r="G2" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B3" t="s">
+        <v>724</v>
+      </c>
+      <c r="C3" t="s">
         <v>725</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>726</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>727</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>728</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>729</v>
-      </c>
-      <c r="G3" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B4" t="s">
+        <v>730</v>
+      </c>
+      <c r="C4" t="s">
+        <v>719</v>
+      </c>
+      <c r="D4" t="s">
         <v>731</v>
       </c>
-      <c r="C4" t="s">
-        <v>720</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>732</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>733</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>734</v>
-      </c>
-      <c r="G4" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B5" t="s">
+        <v>735</v>
+      </c>
+      <c r="C5" t="s">
+        <v>719</v>
+      </c>
+      <c r="D5" t="s">
         <v>736</v>
       </c>
-      <c r="C5" t="s">
-        <v>720</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>737</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>738</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>739</v>
-      </c>
-      <c r="G5" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B6" t="s">
+        <v>740</v>
+      </c>
+      <c r="C6" t="s">
         <v>741</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>742</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>743</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>744</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>745</v>
-      </c>
-      <c r="G6" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B7" t="s">
+        <v>746</v>
+      </c>
+      <c r="C7" t="s">
+        <v>719</v>
+      </c>
+      <c r="D7" t="s">
         <v>747</v>
       </c>
-      <c r="C7" t="s">
-        <v>720</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>748</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>749</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>750</v>
-      </c>
-      <c r="G7" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B8" t="s">
+        <v>751</v>
+      </c>
+      <c r="C8" t="s">
+        <v>719</v>
+      </c>
+      <c r="D8" t="s">
         <v>752</v>
       </c>
-      <c r="C8" t="s">
-        <v>720</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>753</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>754</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>755</v>
-      </c>
-      <c r="G8" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B9" t="s">
+        <v>756</v>
+      </c>
+      <c r="C9" t="s">
+        <v>741</v>
+      </c>
+      <c r="D9" t="s">
+        <v>742</v>
+      </c>
+      <c r="E9" t="s">
         <v>757</v>
       </c>
-      <c r="C9" t="s">
-        <v>742</v>
-      </c>
-      <c r="D9" t="s">
-        <v>743</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>758</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>759</v>
-      </c>
-      <c r="G9" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C10" t="s">
+        <v>725</v>
+      </c>
+      <c r="D10" t="s">
         <v>761</v>
       </c>
-      <c r="C10" t="s">
-        <v>726</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>762</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>763</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>764</v>
-      </c>
-      <c r="G10" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B11" t="s">
+        <v>765</v>
+      </c>
+      <c r="C11" t="s">
+        <v>719</v>
+      </c>
+      <c r="D11" t="s">
         <v>766</v>
       </c>
-      <c r="C11" t="s">
-        <v>720</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>767</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>768</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>769</v>
-      </c>
-      <c r="G11" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>770</v>
+      </c>
+      <c r="B12" t="s">
         <v>771</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D12" t="s">
         <v>772</v>
       </c>
-      <c r="C12" t="s">
-        <v>726</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>773</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>774</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>775</v>
-      </c>
-      <c r="G12" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B13" t="s">
+        <v>776</v>
+      </c>
+      <c r="C13" t="s">
+        <v>725</v>
+      </c>
+      <c r="D13" t="s">
+        <v>742</v>
+      </c>
+      <c r="E13" t="s">
         <v>777</v>
       </c>
-      <c r="C13" t="s">
-        <v>726</v>
-      </c>
-      <c r="D13" t="s">
-        <v>743</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>778</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>779</v>
-      </c>
-      <c r="G13" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B14" t="s">
+        <v>780</v>
+      </c>
+      <c r="C14" t="s">
+        <v>725</v>
+      </c>
+      <c r="D14" t="s">
+        <v>742</v>
+      </c>
+      <c r="E14" t="s">
         <v>781</v>
       </c>
-      <c r="C14" t="s">
-        <v>726</v>
-      </c>
-      <c r="D14" t="s">
-        <v>743</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
+        <v>778</v>
+      </c>
+      <c r="G14" t="s">
         <v>782</v>
-      </c>
-      <c r="F14" t="s">
-        <v>779</v>
-      </c>
-      <c r="G14" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B15" t="s">
+        <v>783</v>
+      </c>
+      <c r="C15" t="s">
         <v>784</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>785</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>786</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>787</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>788</v>
-      </c>
-      <c r="G15" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B16" t="s">
+        <v>789</v>
+      </c>
+      <c r="C16" t="s">
+        <v>725</v>
+      </c>
+      <c r="D16" t="s">
         <v>790</v>
       </c>
-      <c r="C16" t="s">
-        <v>726</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>791</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>792</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>793</v>
-      </c>
-      <c r="G16" t="s">
-        <v>794</v>
       </c>
     </row>
   </sheetData>
@@ -8750,24 +8753,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -8783,46 +8786,46 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>797</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>798</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>799</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
         <v>800</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>801</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
         <v>802</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>803</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
         <v>804</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>805</v>
       </c>
     </row>
   </sheetData>
@@ -8838,16 +8841,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>805</v>
+      </c>
+      <c r="B1" t="s">
         <v>806</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>807</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>808</v>
-      </c>
-      <c r="D1" t="s">
-        <v>809</v>
       </c>
       <c r="E1" t="s">
         <v>6</v>
@@ -8855,19 +8858,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B2" t="s">
         <v>810</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>811</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
         <v>812</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -8875,33 +8878,33 @@
         <v>94</v>
       </c>
       <c r="B3" t="s">
+        <v>813</v>
+      </c>
+      <c r="C3" t="s">
+        <v>811</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
         <v>814</v>
-      </c>
-      <c r="C3" t="s">
-        <v>812</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>809</v>
+      </c>
+      <c r="B4" t="s">
         <v>810</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>811</v>
       </c>
-      <c r="C4" t="s">
-        <v>812</v>
-      </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -8912,13 +8915,13 @@
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -8929,13 +8932,13 @@
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -8946,13 +8949,13 @@
         <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -8963,13 +8966,13 @@
         <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -8980,13 +8983,13 @@
         <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -8997,13 +9000,13 @@
         <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -9014,217 +9017,217 @@
         <v>113</v>
       </c>
       <c r="C11" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" t="s">
         <v>116</v>
       </c>
-      <c r="B12" t="s">
-        <v>117</v>
-      </c>
       <c r="C12" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C15" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C18" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
       </c>
       <c r="E18" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C19" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
       </c>
       <c r="E19" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C20" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
       </c>
       <c r="E20" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C22" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -9232,16 +9235,16 @@
         <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C24" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
       </c>
       <c r="E24" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -9249,16 +9252,16 @@
         <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -9266,271 +9269,271 @@
         <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C26" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
       </c>
       <c r="E26" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>721</v>
+      </c>
+      <c r="B27" t="s">
         <v>722</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>838</v>
+      </c>
+      <c r="D27" t="s">
+        <v>839</v>
+      </c>
+      <c r="E27" t="s">
         <v>723</v>
-      </c>
-      <c r="C27" t="s">
-        <v>839</v>
-      </c>
-      <c r="D27" t="s">
-        <v>840</v>
-      </c>
-      <c r="E27" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>727</v>
+      </c>
+      <c r="B28" t="s">
         <v>728</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>838</v>
+      </c>
+      <c r="D28" t="s">
+        <v>839</v>
+      </c>
+      <c r="E28" t="s">
         <v>729</v>
-      </c>
-      <c r="C28" t="s">
-        <v>839</v>
-      </c>
-      <c r="D28" t="s">
-        <v>840</v>
-      </c>
-      <c r="E28" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>732</v>
+      </c>
+      <c r="B29" t="s">
         <v>733</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
+        <v>838</v>
+      </c>
+      <c r="D29" t="s">
+        <v>839</v>
+      </c>
+      <c r="E29" t="s">
         <v>734</v>
-      </c>
-      <c r="C29" t="s">
-        <v>839</v>
-      </c>
-      <c r="D29" t="s">
-        <v>840</v>
-      </c>
-      <c r="E29" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>737</v>
+      </c>
+      <c r="B30" t="s">
         <v>738</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>838</v>
+      </c>
+      <c r="D30" t="s">
+        <v>839</v>
+      </c>
+      <c r="E30" t="s">
         <v>739</v>
-      </c>
-      <c r="C30" t="s">
-        <v>839</v>
-      </c>
-      <c r="D30" t="s">
-        <v>840</v>
-      </c>
-      <c r="E30" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>743</v>
+      </c>
+      <c r="B31" t="s">
         <v>744</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>838</v>
+      </c>
+      <c r="D31" t="s">
+        <v>839</v>
+      </c>
+      <c r="E31" t="s">
         <v>745</v>
-      </c>
-      <c r="C31" t="s">
-        <v>839</v>
-      </c>
-      <c r="D31" t="s">
-        <v>840</v>
-      </c>
-      <c r="E31" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>748</v>
+      </c>
+      <c r="B32" t="s">
         <v>749</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>838</v>
+      </c>
+      <c r="D32" t="s">
+        <v>839</v>
+      </c>
+      <c r="E32" t="s">
         <v>750</v>
-      </c>
-      <c r="C32" t="s">
-        <v>839</v>
-      </c>
-      <c r="D32" t="s">
-        <v>840</v>
-      </c>
-      <c r="E32" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>753</v>
+      </c>
+      <c r="B33" t="s">
         <v>754</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>838</v>
+      </c>
+      <c r="D33" t="s">
+        <v>839</v>
+      </c>
+      <c r="E33" t="s">
         <v>755</v>
-      </c>
-      <c r="C33" t="s">
-        <v>839</v>
-      </c>
-      <c r="D33" t="s">
-        <v>840</v>
-      </c>
-      <c r="E33" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>757</v>
+      </c>
+      <c r="B34" t="s">
         <v>758</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
+        <v>838</v>
+      </c>
+      <c r="D34" t="s">
+        <v>839</v>
+      </c>
+      <c r="E34" t="s">
         <v>759</v>
-      </c>
-      <c r="C34" t="s">
-        <v>839</v>
-      </c>
-      <c r="D34" t="s">
-        <v>840</v>
-      </c>
-      <c r="E34" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>762</v>
+      </c>
+      <c r="B35" t="s">
         <v>763</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
+        <v>838</v>
+      </c>
+      <c r="D35" t="s">
+        <v>839</v>
+      </c>
+      <c r="E35" t="s">
         <v>764</v>
-      </c>
-      <c r="C35" t="s">
-        <v>839</v>
-      </c>
-      <c r="D35" t="s">
-        <v>840</v>
-      </c>
-      <c r="E35" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>767</v>
+      </c>
+      <c r="B36" t="s">
         <v>768</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>838</v>
+      </c>
+      <c r="D36" t="s">
+        <v>839</v>
+      </c>
+      <c r="E36" t="s">
         <v>769</v>
-      </c>
-      <c r="C36" t="s">
-        <v>839</v>
-      </c>
-      <c r="D36" t="s">
-        <v>840</v>
-      </c>
-      <c r="E36" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>773</v>
+      </c>
+      <c r="B37" t="s">
         <v>774</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>838</v>
+      </c>
+      <c r="D37" t="s">
+        <v>839</v>
+      </c>
+      <c r="E37" t="s">
         <v>775</v>
-      </c>
-      <c r="C37" t="s">
-        <v>839</v>
-      </c>
-      <c r="D37" t="s">
-        <v>840</v>
-      </c>
-      <c r="E37" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>777</v>
+      </c>
+      <c r="B38" t="s">
         <v>778</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
+        <v>838</v>
+      </c>
+      <c r="D38" t="s">
+        <v>839</v>
+      </c>
+      <c r="E38" t="s">
         <v>779</v>
-      </c>
-      <c r="C38" t="s">
-        <v>839</v>
-      </c>
-      <c r="D38" t="s">
-        <v>840</v>
-      </c>
-      <c r="E38" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>781</v>
+      </c>
+      <c r="B39" t="s">
+        <v>778</v>
+      </c>
+      <c r="C39" t="s">
+        <v>838</v>
+      </c>
+      <c r="D39" t="s">
+        <v>839</v>
+      </c>
+      <c r="E39" t="s">
         <v>782</v>
-      </c>
-      <c r="B39" t="s">
-        <v>779</v>
-      </c>
-      <c r="C39" t="s">
-        <v>839</v>
-      </c>
-      <c r="D39" t="s">
-        <v>840</v>
-      </c>
-      <c r="E39" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>786</v>
+      </c>
+      <c r="B40" t="s">
         <v>787</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
+        <v>838</v>
+      </c>
+      <c r="D40" t="s">
+        <v>839</v>
+      </c>
+      <c r="E40" t="s">
         <v>788</v>
-      </c>
-      <c r="C40" t="s">
-        <v>839</v>
-      </c>
-      <c r="D40" t="s">
-        <v>840</v>
-      </c>
-      <c r="E40" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>791</v>
+      </c>
+      <c r="B41" t="s">
         <v>792</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
+        <v>838</v>
+      </c>
+      <c r="D41" t="s">
+        <v>839</v>
+      </c>
+      <c r="E41" t="s">
         <v>793</v>
-      </c>
-      <c r="C41" t="s">
-        <v>839</v>
-      </c>
-      <c r="D41" t="s">
-        <v>840</v>
-      </c>
-      <c r="E41" t="s">
-        <v>794</v>
       </c>
     </row>
   </sheetData>
@@ -9546,13 +9549,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>840</v>
+      </c>
+      <c r="B1" t="s">
         <v>841</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>842</v>
-      </c>
-      <c r="C1" t="s">
-        <v>843</v>
       </c>
       <c r="D1" t="s">
         <v>6</v>
@@ -9560,16 +9563,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>844</v>
+      </c>
+      <c r="D2" t="s">
         <v>845</v>
-      </c>
-      <c r="D2" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -9583,7 +9586,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -9597,7 +9600,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -9611,7 +9614,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -9625,7 +9628,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -9639,7 +9642,7 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -9653,7 +9656,7 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -9667,1379 +9670,1379 @@
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>853</v>
+      </c>
+      <c r="B10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" t="s">
         <v>854</v>
       </c>
-      <c r="B10" t="s">
-        <v>148</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>855</v>
-      </c>
-      <c r="D10" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C11" t="s">
+        <v>856</v>
+      </c>
+      <c r="D11" t="s">
         <v>857</v>
-      </c>
-      <c r="D11" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C12" t="s">
+        <v>858</v>
+      </c>
+      <c r="D12" t="s">
         <v>859</v>
-      </c>
-      <c r="D12" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" t="s">
+        <v>860</v>
+      </c>
+      <c r="D13" t="s">
         <v>861</v>
-      </c>
-      <c r="D13" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C14" t="s">
+        <v>862</v>
+      </c>
+      <c r="D14" t="s">
         <v>863</v>
-      </c>
-      <c r="D14" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
+        <v>864</v>
+      </c>
+      <c r="D15" t="s">
         <v>865</v>
-      </c>
-      <c r="D15" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C16" t="s">
+        <v>866</v>
+      </c>
+      <c r="D16" t="s">
         <v>867</v>
-      </c>
-      <c r="D16" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C17" t="s">
+        <v>868</v>
+      </c>
+      <c r="D17" t="s">
         <v>869</v>
-      </c>
-      <c r="D17" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C18" t="s">
+        <v>870</v>
+      </c>
+      <c r="D18" t="s">
         <v>871</v>
-      </c>
-      <c r="D18" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C19" t="s">
+        <v>872</v>
+      </c>
+      <c r="D19" t="s">
         <v>873</v>
-      </c>
-      <c r="D19" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C20" t="s">
+        <v>874</v>
+      </c>
+      <c r="D20" t="s">
         <v>875</v>
-      </c>
-      <c r="D20" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C21" t="s">
+        <v>876</v>
+      </c>
+      <c r="D21" t="s">
         <v>877</v>
-      </c>
-      <c r="D21" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C22" t="s">
+        <v>878</v>
+      </c>
+      <c r="D22" t="s">
         <v>879</v>
-      </c>
-      <c r="D22" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C23" t="s">
+        <v>880</v>
+      </c>
+      <c r="D23" t="s">
         <v>881</v>
-      </c>
-      <c r="D23" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C24" t="s">
+        <v>882</v>
+      </c>
+      <c r="D24" t="s">
         <v>883</v>
-      </c>
-      <c r="D24" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B25" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C25" t="s">
+        <v>884</v>
+      </c>
+      <c r="D25" t="s">
         <v>885</v>
-      </c>
-      <c r="D25" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C26" t="s">
+        <v>886</v>
+      </c>
+      <c r="D26" t="s">
         <v>887</v>
-      </c>
-      <c r="D26" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B27" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C27" t="s">
+        <v>888</v>
+      </c>
+      <c r="D27" t="s">
         <v>889</v>
-      </c>
-      <c r="D27" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s">
+        <v>890</v>
+      </c>
+      <c r="D28" t="s">
         <v>891</v>
-      </c>
-      <c r="D28" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C29" t="s">
+        <v>892</v>
+      </c>
+      <c r="D29" t="s">
         <v>893</v>
-      </c>
-      <c r="D29" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C30" t="s">
+        <v>894</v>
+      </c>
+      <c r="D30" t="s">
         <v>895</v>
-      </c>
-      <c r="D30" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C31" t="s">
+        <v>896</v>
+      </c>
+      <c r="D31" t="s">
         <v>897</v>
-      </c>
-      <c r="D31" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B32" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C32" t="s">
+        <v>898</v>
+      </c>
+      <c r="D32" t="s">
         <v>899</v>
-      </c>
-      <c r="D32" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B33" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C33" t="s">
+        <v>900</v>
+      </c>
+      <c r="D33" t="s">
         <v>901</v>
-      </c>
-      <c r="D33" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C34" t="s">
+        <v>902</v>
+      </c>
+      <c r="D34" t="s">
         <v>903</v>
-      </c>
-      <c r="D34" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B35" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C35" t="s">
+        <v>904</v>
+      </c>
+      <c r="D35" t="s">
         <v>905</v>
-      </c>
-      <c r="D35" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B36" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C36" t="s">
+        <v>906</v>
+      </c>
+      <c r="D36" t="s">
         <v>907</v>
-      </c>
-      <c r="D36" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B37" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C37" t="s">
+        <v>908</v>
+      </c>
+      <c r="D37" t="s">
         <v>909</v>
-      </c>
-      <c r="D37" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B38" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C38" t="s">
+        <v>910</v>
+      </c>
+      <c r="D38" t="s">
         <v>911</v>
-      </c>
-      <c r="D38" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B39" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C39" t="s">
+        <v>912</v>
+      </c>
+      <c r="D39" t="s">
         <v>913</v>
-      </c>
-      <c r="D39" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B40" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C40" t="s">
+        <v>914</v>
+      </c>
+      <c r="D40" t="s">
         <v>915</v>
-      </c>
-      <c r="D40" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B41" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C41" t="s">
+        <v>916</v>
+      </c>
+      <c r="D41" t="s">
         <v>917</v>
-      </c>
-      <c r="D41" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B42" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C42" t="s">
+        <v>918</v>
+      </c>
+      <c r="D42" t="s">
         <v>919</v>
-      </c>
-      <c r="D42" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C43" t="s">
+        <v>920</v>
+      </c>
+      <c r="D43" t="s">
         <v>921</v>
-      </c>
-      <c r="D43" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B44" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C44" t="s">
+        <v>922</v>
+      </c>
+      <c r="D44" t="s">
         <v>923</v>
-      </c>
-      <c r="D44" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B45" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C45" t="s">
+        <v>924</v>
+      </c>
+      <c r="D45" t="s">
         <v>925</v>
-      </c>
-      <c r="D45" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B46" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C46" t="s">
+        <v>926</v>
+      </c>
+      <c r="D46" t="s">
         <v>927</v>
-      </c>
-      <c r="D46" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B47" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C47" t="s">
+        <v>928</v>
+      </c>
+      <c r="D47" t="s">
         <v>929</v>
-      </c>
-      <c r="D47" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B48" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C48" t="s">
+        <v>930</v>
+      </c>
+      <c r="D48" t="s">
         <v>931</v>
-      </c>
-      <c r="D48" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B49" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C49" t="s">
+        <v>932</v>
+      </c>
+      <c r="D49" t="s">
         <v>933</v>
-      </c>
-      <c r="D49" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B50" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C50" t="s">
+        <v>934</v>
+      </c>
+      <c r="D50" t="s">
         <v>935</v>
-      </c>
-      <c r="D50" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B51" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C51" t="s">
+        <v>936</v>
+      </c>
+      <c r="D51" t="s">
         <v>937</v>
-      </c>
-      <c r="D51" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B52" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C52" t="s">
+        <v>938</v>
+      </c>
+      <c r="D52" t="s">
         <v>939</v>
-      </c>
-      <c r="D52" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B53" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C53" t="s">
+        <v>940</v>
+      </c>
+      <c r="D53" t="s">
         <v>941</v>
-      </c>
-      <c r="D53" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C54" t="s">
+        <v>942</v>
+      </c>
+      <c r="D54" t="s">
         <v>943</v>
-      </c>
-      <c r="D54" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B55" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C55" t="s">
+        <v>944</v>
+      </c>
+      <c r="D55" t="s">
         <v>945</v>
-      </c>
-      <c r="D55" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B56" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C56" t="s">
+        <v>946</v>
+      </c>
+      <c r="D56" t="s">
         <v>947</v>
-      </c>
-      <c r="D56" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B57" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C57" t="s">
+        <v>948</v>
+      </c>
+      <c r="D57" t="s">
         <v>949</v>
-      </c>
-      <c r="D57" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B58" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C58" t="s">
+        <v>950</v>
+      </c>
+      <c r="D58" t="s">
         <v>951</v>
-      </c>
-      <c r="D58" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B59" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C59" t="s">
+        <v>952</v>
+      </c>
+      <c r="D59" t="s">
         <v>953</v>
-      </c>
-      <c r="D59" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B60" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C60" t="s">
+        <v>954</v>
+      </c>
+      <c r="D60" t="s">
         <v>955</v>
-      </c>
-      <c r="D60" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B61" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C61" t="s">
+        <v>956</v>
+      </c>
+      <c r="D61" t="s">
         <v>957</v>
-      </c>
-      <c r="D61" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B62" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C62" t="s">
+        <v>958</v>
+      </c>
+      <c r="D62" t="s">
         <v>959</v>
-      </c>
-      <c r="D62" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B63" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C63" t="s">
+        <v>960</v>
+      </c>
+      <c r="D63" t="s">
         <v>961</v>
-      </c>
-      <c r="D63" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B64" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C64" t="s">
+        <v>962</v>
+      </c>
+      <c r="D64" t="s">
         <v>963</v>
-      </c>
-      <c r="D64" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B65" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C65" t="s">
+        <v>964</v>
+      </c>
+      <c r="D65" t="s">
         <v>965</v>
-      </c>
-      <c r="D65" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B66" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C66" t="s">
+        <v>966</v>
+      </c>
+      <c r="D66" t="s">
         <v>967</v>
-      </c>
-      <c r="D66" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B67" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C67" t="s">
+        <v>968</v>
+      </c>
+      <c r="D67" t="s">
         <v>969</v>
-      </c>
-      <c r="D67" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B68" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C68" t="s">
+        <v>970</v>
+      </c>
+      <c r="D68" t="s">
         <v>971</v>
-      </c>
-      <c r="D68" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B69" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C69" t="s">
+        <v>972</v>
+      </c>
+      <c r="D69" t="s">
         <v>973</v>
-      </c>
-      <c r="D69" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B70" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C70" t="s">
+        <v>974</v>
+      </c>
+      <c r="D70" t="s">
         <v>975</v>
-      </c>
-      <c r="D70" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B71" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C71" t="s">
+        <v>976</v>
+      </c>
+      <c r="D71" t="s">
         <v>977</v>
-      </c>
-      <c r="D71" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B72" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C72" t="s">
+        <v>978</v>
+      </c>
+      <c r="D72" t="s">
         <v>979</v>
-      </c>
-      <c r="D72" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B73" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C73" t="s">
+        <v>980</v>
+      </c>
+      <c r="D73" t="s">
         <v>981</v>
-      </c>
-      <c r="D73" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B74" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C74" t="s">
+        <v>982</v>
+      </c>
+      <c r="D74" t="s">
         <v>983</v>
-      </c>
-      <c r="D74" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B75" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C75" t="s">
+        <v>984</v>
+      </c>
+      <c r="D75" t="s">
         <v>985</v>
-      </c>
-      <c r="D75" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B76" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C76" t="s">
+        <v>986</v>
+      </c>
+      <c r="D76" t="s">
         <v>987</v>
-      </c>
-      <c r="D76" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B77" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C77" t="s">
+        <v>988</v>
+      </c>
+      <c r="D77" t="s">
         <v>989</v>
-      </c>
-      <c r="D77" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B78" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C78" t="s">
+        <v>990</v>
+      </c>
+      <c r="D78" t="s">
         <v>991</v>
-      </c>
-      <c r="D78" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B79" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C79" t="s">
+        <v>992</v>
+      </c>
+      <c r="D79" t="s">
         <v>993</v>
-      </c>
-      <c r="D79" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B80" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C80" t="s">
+        <v>994</v>
+      </c>
+      <c r="D80" t="s">
         <v>995</v>
-      </c>
-      <c r="D80" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B81" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C81" t="s">
+        <v>996</v>
+      </c>
+      <c r="D81" t="s">
         <v>997</v>
-      </c>
-      <c r="D81" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B82" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C82" t="s">
+        <v>998</v>
+      </c>
+      <c r="D82" t="s">
         <v>999</v>
-      </c>
-      <c r="D82" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B83" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C83" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D83" t="s">
         <v>1001</v>
-      </c>
-      <c r="D83" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B84" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C84" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D84" t="s">
         <v>1003</v>
-      </c>
-      <c r="D84" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B85" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C85" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D85" t="s">
         <v>1005</v>
-      </c>
-      <c r="D85" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B86" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C86" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D86" t="s">
         <v>1007</v>
-      </c>
-      <c r="D86" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B87" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C87" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D87" t="s">
         <v>1009</v>
-      </c>
-      <c r="D87" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B88" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C88" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D88" t="s">
         <v>1011</v>
-      </c>
-      <c r="D88" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B89" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C89" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D89" t="s">
         <v>1013</v>
-      </c>
-      <c r="D89" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B90" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C90" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D90" t="s">
         <v>1015</v>
-      </c>
-      <c r="D90" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B91" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C91" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D91" t="s">
         <v>1017</v>
-      </c>
-      <c r="D91" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B92" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C92" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D92" t="s">
         <v>1019</v>
-      </c>
-      <c r="D92" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B93" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C93" t="s">
         <v>10</v>
       </c>
       <c r="D93" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B94" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C94" t="s">
         <v>10</v>
       </c>
       <c r="D94" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B95" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C95" t="s">
         <v>10</v>
       </c>
       <c r="D95" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B96" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C96" t="s">
         <v>10</v>
       </c>
       <c r="D96" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B97" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C97" t="s">
         <v>10</v>
       </c>
       <c r="D97" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B98" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C98" t="s">
         <v>10</v>
       </c>
       <c r="D98" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B99" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C99" t="s">
         <v>10</v>
       </c>
       <c r="D99" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B100" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C100" t="s">
         <v>10</v>
       </c>
       <c r="D100" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B101" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C101" t="s">
         <v>10</v>
       </c>
       <c r="D101" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B102" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C102" t="s">
         <v>10</v>
       </c>
       <c r="D102" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B103" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C103" t="s">
         <v>10</v>
       </c>
       <c r="D103" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B104" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C104" t="s">
         <v>10</v>
       </c>
       <c r="D104" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B105" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C105" t="s">
         <v>10</v>
       </c>
       <c r="D105" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B106" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C106" t="s">
         <v>10</v>
       </c>
       <c r="D106" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B107" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C107" t="s">
         <v>10</v>
       </c>
       <c r="D107" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
@@ -11053,7 +11056,7 @@
         <v>10</v>
       </c>
       <c r="D108" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
@@ -11067,7 +11070,7 @@
         <v>10</v>
       </c>
       <c r="D109" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
@@ -11081,7 +11084,7 @@
         <v>10</v>
       </c>
       <c r="D110" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
@@ -11095,7 +11098,7 @@
         <v>10</v>
       </c>
       <c r="D111" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
@@ -11109,7 +11112,7 @@
         <v>10</v>
       </c>
       <c r="D112" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
@@ -11123,11 +11126,17 @@
         <v>10</v>
       </c>
       <c r="D113" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Z1" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{7cf48d45-3ddb-4389-a9c1-c115526eb52e}" enabled="0" method="" siteId="{7cf48d45-3ddb-4389-a9c1-c115526eb52e}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/SHAPE-Lab-Website-Content.xlsx
+++ b/SHAPE-Lab-Website-Content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/byg5201_psu_edu/Documents/Documents/GitHub/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{4358DB11-5B92-4F17-8511-6659BB54189A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5C65186-6CC4-4886-9A70-E8492214C0F6}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{4358DB11-5B92-4F17-8511-6659BB54189A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68D472D3-A90E-4767-B534-8AD14202E44E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="42075" yWindow="1620" windowWidth="9465" windowHeight="6420" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site Copy" sheetId="1" r:id="rId1"/>
@@ -3588,6 +3588,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8371,6 +8375,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="47.81640625" customWidth="1"/>
+    <col min="5" max="5" width="78.08984375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">

--- a/SHAPE-Lab-Website-Content.xlsx
+++ b/SHAPE-Lab-Website-Content.xlsx
@@ -8,28 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/byg5201_psu_edu/Documents/Documents/GitHub/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{4358DB11-5B92-4F17-8511-6659BB54189A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68D472D3-A90E-4767-B534-8AD14202E44E}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{4358DB11-5B92-4F17-8511-6659BB54189A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E00C963-8A44-413D-881A-0AC7F5565D97}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="42075" yWindow="1620" windowWidth="9465" windowHeight="6420" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site Copy" sheetId="1" r:id="rId1"/>
     <sheet name="Research" sheetId="2" r:id="rId2"/>
     <sheet name="Team" sheetId="3" r:id="rId3"/>
-    <sheet name="Publications" sheetId="4" r:id="rId4"/>
-    <sheet name="News" sheetId="5" r:id="rId5"/>
-    <sheet name="Sponsors Partners" sheetId="6" r:id="rId6"/>
-    <sheet name="Contact" sheetId="7" r:id="rId7"/>
-    <sheet name="Images Referenced" sheetId="8" r:id="rId8"/>
-    <sheet name="Links Referenced" sheetId="9" r:id="rId9"/>
-    <sheet name="Photo Library" sheetId="10" r:id="rId10"/>
+    <sheet name="Alumni" sheetId="11" r:id="rId4"/>
+    <sheet name="Publications" sheetId="4" r:id="rId5"/>
+    <sheet name="News" sheetId="5" r:id="rId6"/>
+    <sheet name="Sponsors Partners" sheetId="6" r:id="rId7"/>
+    <sheet name="Contact" sheetId="7" r:id="rId8"/>
+    <sheet name="Images Referenced" sheetId="8" r:id="rId9"/>
+    <sheet name="Links Referenced" sheetId="9" r:id="rId10"/>
+    <sheet name="Photo Library" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="1170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="1270">
   <si>
     <t>Section</t>
   </si>
@@ -3539,24 +3540,378 @@
   </si>
   <si>
     <t>Ph.D.</t>
+  </si>
+  <si>
+    <t>Google Scholar</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
+  </si>
+  <si>
+    <t>Degree</t>
+  </si>
+  <si>
+    <t>Post-Doctoral</t>
+  </si>
+  <si>
+    <t>Masters</t>
+  </si>
+  <si>
+    <t>Undergraduate</t>
+  </si>
+  <si>
+    <t>Sagar Jalui</t>
+  </si>
+  <si>
+    <t>Ph.D., Mechanical Engineering, 2024</t>
+  </si>
+  <si>
+    <t>Alan Burl</t>
+  </si>
+  <si>
+    <t>Ph.D., Mechanical Engineering, 2025</t>
+  </si>
+  <si>
+    <t>Thesis</t>
+  </si>
+  <si>
+    <t> Ph.D., Mechanical Engineering, 2024</t>
+  </si>
+  <si>
+    <t>AM-driven design innovation: DfAM constraints in adjoint shape optimization for gas turbine applications</t>
+  </si>
+  <si>
+    <t>Ankit Saxena</t>
+  </si>
+  <si>
+    <t>Systematic design of pressure-actuated adaptive structural cells enabling adaptive mechanical properties in mechanical structures</t>
+  </si>
+  <si>
+    <t>Philip King</t>
+  </si>
+  <si>
+    <t>Ph.D., Mechanical Engineering, 2023</t>
+  </si>
+  <si>
+    <t>Bridging the oldest and newest manufacturing technologies: Additive Manufacturing, Metal Casting, and Internet of Things.</t>
+  </si>
+  <si>
+    <t>Foxian Fan</t>
+  </si>
+  <si>
+    <t>Ph.D., Industrial &amp; Manufacturing Engineering, 2023</t>
+  </si>
+  <si>
+    <t>Evolution of Additive Manufacturing surface morphology during Centrifugal Disc Finishing.</t>
+  </si>
+  <si>
+    <t>Md Moinuddin Shuvo</t>
+  </si>
+  <si>
+    <t>Improving sustainability of Sand-Casting Processes via novel 3D Mold Designs.</t>
+  </si>
+  <si>
+    <t>Xi Gong</t>
+  </si>
+  <si>
+    <t>Ph.D., Mechanical Engineering, 2020</t>
+  </si>
+  <si>
+    <t>Machining Behavior and Material Properties in Additive Manufacturing of TI-6AL-4V Parts</t>
+  </si>
+  <si>
+    <t>Maryam Tilton</t>
+  </si>
+  <si>
+    <t>Multi-Objective Design and Characterization of Orthopaedic Implants and Meta-Biomaterials Fabricated via Additive Manufacturing</t>
+  </si>
+  <si>
+    <t>Kaitlyn Hartman</t>
+  </si>
+  <si>
+    <t>M.S. Mechanical Engineering, 2025</t>
+  </si>
+  <si>
+    <t>Functionally Graded TPMS Lattice Structures Optimized to Improve Mechanical Strength</t>
+  </si>
+  <si>
+    <t>Mychal Taylor</t>
+  </si>
+  <si>
+    <t>M.S. Mechanical Engineering, 2024</t>
+  </si>
+  <si>
+    <t>Power cell packaging using a structural electronics approach</t>
+  </si>
+  <si>
+    <t>Buket Yilmaz</t>
+  </si>
+  <si>
+    <t>A review of the interface design in multi-material laser powder bed fusion of metals</t>
+  </si>
+  <si>
+    <r>
+      <t>Matthew</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF777777"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF777777"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Williams</t>
+    </r>
+  </si>
+  <si>
+    <t>Multi-axis routing of syringe deposited conductive traces over topology-optimized multi-functional structures</t>
+  </si>
+  <si>
+    <t> Serah Hatch</t>
+  </si>
+  <si>
+    <t>A microstructure based machine learning model to predict mechanical properties of LPBF-manufactured 15-5PH stainless steel.</t>
+  </si>
+  <si>
+    <t>Carson Vath</t>
+  </si>
+  <si>
+    <t>Development and testing of novel multi-material additive manufacturing systems for embedding wire electronic.</t>
+  </si>
+  <si>
+    <t>Sandy Karam</t>
+  </si>
+  <si>
+    <t>M.S. Mechanical Engineering, 2023</t>
+  </si>
+  <si>
+    <t>Additive Manufacturing of patient-specific high-fidelity and thickness-controlled cerebral aneurysm geometries</t>
+  </si>
+  <si>
+    <t>Willem Groeneveld-Meijer</t>
+  </si>
+  <si>
+    <t>Does Finer Powder get deposited first in Powder Bed? – A Comparative Study using Simulation and Experimental Techniques.</t>
+  </si>
+  <si>
+    <t>Ryan Stebbins</t>
+  </si>
+  <si>
+    <t>M.S. Mechanical Engineering, 2022</t>
+  </si>
+  <si>
+    <t>Novel Runner Extension Designs via 3D Sand-printing to Improve Casting Performance</t>
+  </si>
+  <si>
+    <t>Paula Clares</t>
+  </si>
+  <si>
+    <t>M.S. Additive Manufacturing &amp; Design, 2022</t>
+  </si>
+  <si>
+    <t>Fundamental Understanding into Bimodal Powder Size Distributions in Binder Jetting Additive Manufacturing Process</t>
+  </si>
+  <si>
+    <t>Erik Jacobs</t>
+  </si>
+  <si>
+    <t>M.S. Additive Manufacturing &amp; Design, 2021</t>
+  </si>
+  <si>
+    <t>Influence of Anti-Counterfeiting Taggants on the Tensile Properties of STEP Additively Manufactured Polymer</t>
+  </si>
+  <si>
+    <t>Nicholas Soares</t>
+  </si>
+  <si>
+    <t>M.S. Mechanical Engineering, 2021</t>
+  </si>
+  <si>
+    <t>Incorporating Novel Sprue Design and Additive Manufacturing Techniques to Improve Nickel Aluminum Bronze Castings</t>
+  </si>
+  <si>
+    <t>Daniel Martinez</t>
+  </si>
+  <si>
+    <t>M.S. Additive Manufacturing, 2019</t>
+  </si>
+  <si>
+    <t>Indirect Hybrid Manufacturing – Integrating 3D Sand-Printing for Metal Casting</t>
+  </si>
+  <si>
+    <t>Casey Bate</t>
+  </si>
+  <si>
+    <t>M.S. Mechanical Engineering, 2019</t>
+  </si>
+  <si>
+    <t>Fundamental Study on 3D Sand-Printed Molds: Metal Flow and Thermal Properties</t>
+  </si>
+  <si>
+    <t>Gregory Bicknell</t>
+  </si>
+  <si>
+    <t>Electrical Discharge Machining Process Design for Post-Processing Stainless Steel 316L Additively Manufactured Parts</t>
+  </si>
+  <si>
+    <t>Santosh Reddy Sama</t>
+  </si>
+  <si>
+    <t>M.S. Mechanical Engineering, 2018</t>
+  </si>
+  <si>
+    <t>Investigation into Non-Conventional Mold Design Using 3D Sand-Printing in Castings</t>
+  </si>
+  <si>
+    <t>Jiayi Wang</t>
+  </si>
+  <si>
+    <t>M.S. Engineering Design, 2017</t>
+  </si>
+  <si>
+    <t>Part Design and Topology Optimization for Rapid Sand and Investment Casting</t>
+  </si>
+  <si>
+    <t>Joe Borst, Visiting student from Clarkson University</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF777777"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>B.S. Mechanical Engineering, 2026</t>
+    </r>
+  </si>
+  <si>
+    <t>Joseph Daghir</t>
+  </si>
+  <si>
+    <t>B.S. Mechanical Engineering, 2025</t>
+  </si>
+  <si>
+    <t>Thomas Molnar</t>
+  </si>
+  <si>
+    <t>B.S. Mechanical Engineering, 2024</t>
+  </si>
+  <si>
+    <t>Avah Cherry, Visiting student from University of Tennessee</t>
+  </si>
+  <si>
+    <t>B.E. Aerospace Engineering, 2026</t>
+  </si>
+  <si>
+    <t>Rachel Bonfini</t>
+  </si>
+  <si>
+    <t>B.S. Biomedical and Mechanical Engineering, 2024</t>
+  </si>
+  <si>
+    <t>Valerie Fu</t>
+  </si>
+  <si>
+    <t>B.S. Mechanical Engineering, 2023</t>
+  </si>
+  <si>
+    <t>Christine Gabriele</t>
+  </si>
+  <si>
+    <t>Jay Sim</t>
+  </si>
+  <si>
+    <t>B.S. Mechanical Engineering, 2022</t>
+  </si>
+  <si>
+    <t>Shelby Bauer</t>
+  </si>
+  <si>
+    <t>Nick Vitagliano</t>
+  </si>
+  <si>
+    <t>B.S. Mechanical Engineering, 2021</t>
+  </si>
+  <si>
+    <t>Alex Cayley</t>
+  </si>
+  <si>
+    <t>Brianna Wilson</t>
+  </si>
+  <si>
+    <t>B.S. Industrial and Manufacturing Engineering, 2021</t>
+  </si>
+  <si>
+    <t>Israel Monroy</t>
+  </si>
+  <si>
+    <t>Hunter Snyder</t>
+  </si>
+  <si>
+    <t>B.S. Mechanical Engineering, 2019</t>
+  </si>
+  <si>
+    <t>Michael Szczesniak</t>
+  </si>
+  <si>
+    <t>B.S. Mechanical Engineering, 2018</t>
+  </si>
+  <si>
+    <t>James Lauer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF777777"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF777777"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3571,8 +3926,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4450,6 +4813,1599 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:D113"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>840</v>
+      </c>
+      <c r="B1" t="s">
+        <v>841</v>
+      </c>
+      <c r="C1" t="s">
+        <v>842</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>844</v>
+      </c>
+      <c r="D2" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>853</v>
+      </c>
+      <c r="B10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" t="s">
+        <v>854</v>
+      </c>
+      <c r="D10" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>853</v>
+      </c>
+      <c r="B11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" t="s">
+        <v>856</v>
+      </c>
+      <c r="D11" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>853</v>
+      </c>
+      <c r="B12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" t="s">
+        <v>858</v>
+      </c>
+      <c r="D12" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>853</v>
+      </c>
+      <c r="B13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" t="s">
+        <v>860</v>
+      </c>
+      <c r="D13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>853</v>
+      </c>
+      <c r="B14" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" t="s">
+        <v>862</v>
+      </c>
+      <c r="D14" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>853</v>
+      </c>
+      <c r="B15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" t="s">
+        <v>864</v>
+      </c>
+      <c r="D15" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>853</v>
+      </c>
+      <c r="B16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" t="s">
+        <v>866</v>
+      </c>
+      <c r="D16" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>853</v>
+      </c>
+      <c r="B17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" t="s">
+        <v>868</v>
+      </c>
+      <c r="D17" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>853</v>
+      </c>
+      <c r="B18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" t="s">
+        <v>870</v>
+      </c>
+      <c r="D18" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>853</v>
+      </c>
+      <c r="B19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C19" t="s">
+        <v>872</v>
+      </c>
+      <c r="D19" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>853</v>
+      </c>
+      <c r="B20" t="s">
+        <v>197</v>
+      </c>
+      <c r="C20" t="s">
+        <v>874</v>
+      </c>
+      <c r="D20" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>853</v>
+      </c>
+      <c r="B21" t="s">
+        <v>202</v>
+      </c>
+      <c r="C21" t="s">
+        <v>876</v>
+      </c>
+      <c r="D21" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>853</v>
+      </c>
+      <c r="B22" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" t="s">
+        <v>878</v>
+      </c>
+      <c r="D22" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>853</v>
+      </c>
+      <c r="B23" t="s">
+        <v>212</v>
+      </c>
+      <c r="C23" t="s">
+        <v>880</v>
+      </c>
+      <c r="D23" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>853</v>
+      </c>
+      <c r="B24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C24" t="s">
+        <v>882</v>
+      </c>
+      <c r="D24" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>853</v>
+      </c>
+      <c r="B25" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" t="s">
+        <v>884</v>
+      </c>
+      <c r="D25" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>853</v>
+      </c>
+      <c r="B26" t="s">
+        <v>227</v>
+      </c>
+      <c r="C26" t="s">
+        <v>886</v>
+      </c>
+      <c r="D26" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>853</v>
+      </c>
+      <c r="B27" t="s">
+        <v>232</v>
+      </c>
+      <c r="C27" t="s">
+        <v>888</v>
+      </c>
+      <c r="D27" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>853</v>
+      </c>
+      <c r="B28" t="s">
+        <v>237</v>
+      </c>
+      <c r="C28" t="s">
+        <v>890</v>
+      </c>
+      <c r="D28" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>853</v>
+      </c>
+      <c r="B29" t="s">
+        <v>242</v>
+      </c>
+      <c r="C29" t="s">
+        <v>892</v>
+      </c>
+      <c r="D29" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>853</v>
+      </c>
+      <c r="B30" t="s">
+        <v>247</v>
+      </c>
+      <c r="C30" t="s">
+        <v>894</v>
+      </c>
+      <c r="D30" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>853</v>
+      </c>
+      <c r="B31" t="s">
+        <v>252</v>
+      </c>
+      <c r="C31" t="s">
+        <v>896</v>
+      </c>
+      <c r="D31" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>853</v>
+      </c>
+      <c r="B32" t="s">
+        <v>257</v>
+      </c>
+      <c r="C32" t="s">
+        <v>898</v>
+      </c>
+      <c r="D32" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>853</v>
+      </c>
+      <c r="B33" t="s">
+        <v>262</v>
+      </c>
+      <c r="C33" t="s">
+        <v>900</v>
+      </c>
+      <c r="D33" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>853</v>
+      </c>
+      <c r="B34" t="s">
+        <v>267</v>
+      </c>
+      <c r="C34" t="s">
+        <v>902</v>
+      </c>
+      <c r="D34" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>853</v>
+      </c>
+      <c r="B35" t="s">
+        <v>272</v>
+      </c>
+      <c r="C35" t="s">
+        <v>904</v>
+      </c>
+      <c r="D35" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>853</v>
+      </c>
+      <c r="B36" t="s">
+        <v>277</v>
+      </c>
+      <c r="C36" t="s">
+        <v>906</v>
+      </c>
+      <c r="D36" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>853</v>
+      </c>
+      <c r="B37" t="s">
+        <v>283</v>
+      </c>
+      <c r="C37" t="s">
+        <v>908</v>
+      </c>
+      <c r="D37" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>853</v>
+      </c>
+      <c r="B38" t="s">
+        <v>288</v>
+      </c>
+      <c r="C38" t="s">
+        <v>910</v>
+      </c>
+      <c r="D38" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>853</v>
+      </c>
+      <c r="B39" t="s">
+        <v>293</v>
+      </c>
+      <c r="C39" t="s">
+        <v>912</v>
+      </c>
+      <c r="D39" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>853</v>
+      </c>
+      <c r="B40" t="s">
+        <v>298</v>
+      </c>
+      <c r="C40" t="s">
+        <v>914</v>
+      </c>
+      <c r="D40" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>853</v>
+      </c>
+      <c r="B41" t="s">
+        <v>303</v>
+      </c>
+      <c r="C41" t="s">
+        <v>916</v>
+      </c>
+      <c r="D41" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>853</v>
+      </c>
+      <c r="B42" t="s">
+        <v>307</v>
+      </c>
+      <c r="C42" t="s">
+        <v>918</v>
+      </c>
+      <c r="D42" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>853</v>
+      </c>
+      <c r="B43" t="s">
+        <v>312</v>
+      </c>
+      <c r="C43" t="s">
+        <v>920</v>
+      </c>
+      <c r="D43" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>853</v>
+      </c>
+      <c r="B44" t="s">
+        <v>316</v>
+      </c>
+      <c r="C44" t="s">
+        <v>922</v>
+      </c>
+      <c r="D44" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>853</v>
+      </c>
+      <c r="B45" t="s">
+        <v>320</v>
+      </c>
+      <c r="C45" t="s">
+        <v>924</v>
+      </c>
+      <c r="D45" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>853</v>
+      </c>
+      <c r="B46" t="s">
+        <v>325</v>
+      </c>
+      <c r="C46" t="s">
+        <v>926</v>
+      </c>
+      <c r="D46" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>853</v>
+      </c>
+      <c r="B47" t="s">
+        <v>330</v>
+      </c>
+      <c r="C47" t="s">
+        <v>928</v>
+      </c>
+      <c r="D47" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>853</v>
+      </c>
+      <c r="B48" t="s">
+        <v>335</v>
+      </c>
+      <c r="C48" t="s">
+        <v>930</v>
+      </c>
+      <c r="D48" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>853</v>
+      </c>
+      <c r="B49" t="s">
+        <v>340</v>
+      </c>
+      <c r="C49" t="s">
+        <v>932</v>
+      </c>
+      <c r="D49" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>853</v>
+      </c>
+      <c r="B50" t="s">
+        <v>346</v>
+      </c>
+      <c r="C50" t="s">
+        <v>934</v>
+      </c>
+      <c r="D50" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>853</v>
+      </c>
+      <c r="B51" t="s">
+        <v>350</v>
+      </c>
+      <c r="C51" t="s">
+        <v>936</v>
+      </c>
+      <c r="D51" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>853</v>
+      </c>
+      <c r="B52" t="s">
+        <v>355</v>
+      </c>
+      <c r="C52" t="s">
+        <v>938</v>
+      </c>
+      <c r="D52" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>853</v>
+      </c>
+      <c r="B53" t="s">
+        <v>360</v>
+      </c>
+      <c r="C53" t="s">
+        <v>940</v>
+      </c>
+      <c r="D53" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>853</v>
+      </c>
+      <c r="B54" t="s">
+        <v>365</v>
+      </c>
+      <c r="C54" t="s">
+        <v>942</v>
+      </c>
+      <c r="D54" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>853</v>
+      </c>
+      <c r="B55" t="s">
+        <v>370</v>
+      </c>
+      <c r="C55" t="s">
+        <v>944</v>
+      </c>
+      <c r="D55" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>853</v>
+      </c>
+      <c r="B56" t="s">
+        <v>375</v>
+      </c>
+      <c r="C56" t="s">
+        <v>946</v>
+      </c>
+      <c r="D56" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>853</v>
+      </c>
+      <c r="B57" t="s">
+        <v>380</v>
+      </c>
+      <c r="C57" t="s">
+        <v>948</v>
+      </c>
+      <c r="D57" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>853</v>
+      </c>
+      <c r="B58" t="s">
+        <v>385</v>
+      </c>
+      <c r="C58" t="s">
+        <v>950</v>
+      </c>
+      <c r="D58" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>853</v>
+      </c>
+      <c r="B59" t="s">
+        <v>390</v>
+      </c>
+      <c r="C59" t="s">
+        <v>952</v>
+      </c>
+      <c r="D59" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>853</v>
+      </c>
+      <c r="B60" t="s">
+        <v>395</v>
+      </c>
+      <c r="C60" t="s">
+        <v>954</v>
+      </c>
+      <c r="D60" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>853</v>
+      </c>
+      <c r="B61" t="s">
+        <v>400</v>
+      </c>
+      <c r="C61" t="s">
+        <v>956</v>
+      </c>
+      <c r="D61" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>853</v>
+      </c>
+      <c r="B62" t="s">
+        <v>405</v>
+      </c>
+      <c r="C62" t="s">
+        <v>958</v>
+      </c>
+      <c r="D62" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>853</v>
+      </c>
+      <c r="B63" t="s">
+        <v>410</v>
+      </c>
+      <c r="C63" t="s">
+        <v>960</v>
+      </c>
+      <c r="D63" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>853</v>
+      </c>
+      <c r="B64" t="s">
+        <v>415</v>
+      </c>
+      <c r="C64" t="s">
+        <v>962</v>
+      </c>
+      <c r="D64" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>853</v>
+      </c>
+      <c r="B65" t="s">
+        <v>420</v>
+      </c>
+      <c r="C65" t="s">
+        <v>964</v>
+      </c>
+      <c r="D65" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>853</v>
+      </c>
+      <c r="B66" t="s">
+        <v>425</v>
+      </c>
+      <c r="C66" t="s">
+        <v>966</v>
+      </c>
+      <c r="D66" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>853</v>
+      </c>
+      <c r="B67" t="s">
+        <v>430</v>
+      </c>
+      <c r="C67" t="s">
+        <v>968</v>
+      </c>
+      <c r="D67" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>853</v>
+      </c>
+      <c r="B68" t="s">
+        <v>435</v>
+      </c>
+      <c r="C68" t="s">
+        <v>970</v>
+      </c>
+      <c r="D68" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>853</v>
+      </c>
+      <c r="B69" t="s">
+        <v>440</v>
+      </c>
+      <c r="C69" t="s">
+        <v>972</v>
+      </c>
+      <c r="D69" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>853</v>
+      </c>
+      <c r="B70" t="s">
+        <v>445</v>
+      </c>
+      <c r="C70" t="s">
+        <v>974</v>
+      </c>
+      <c r="D70" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>853</v>
+      </c>
+      <c r="B71" t="s">
+        <v>449</v>
+      </c>
+      <c r="C71" t="s">
+        <v>976</v>
+      </c>
+      <c r="D71" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>853</v>
+      </c>
+      <c r="B72" t="s">
+        <v>454</v>
+      </c>
+      <c r="C72" t="s">
+        <v>978</v>
+      </c>
+      <c r="D72" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>853</v>
+      </c>
+      <c r="B73" t="s">
+        <v>459</v>
+      </c>
+      <c r="C73" t="s">
+        <v>980</v>
+      </c>
+      <c r="D73" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>853</v>
+      </c>
+      <c r="B74" t="s">
+        <v>464</v>
+      </c>
+      <c r="C74" t="s">
+        <v>982</v>
+      </c>
+      <c r="D74" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>853</v>
+      </c>
+      <c r="B75" t="s">
+        <v>469</v>
+      </c>
+      <c r="C75" t="s">
+        <v>984</v>
+      </c>
+      <c r="D75" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>853</v>
+      </c>
+      <c r="B76" t="s">
+        <v>475</v>
+      </c>
+      <c r="C76" t="s">
+        <v>986</v>
+      </c>
+      <c r="D76" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>853</v>
+      </c>
+      <c r="B77" t="s">
+        <v>481</v>
+      </c>
+      <c r="C77" t="s">
+        <v>988</v>
+      </c>
+      <c r="D77" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>853</v>
+      </c>
+      <c r="B78" t="s">
+        <v>486</v>
+      </c>
+      <c r="C78" t="s">
+        <v>990</v>
+      </c>
+      <c r="D78" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>853</v>
+      </c>
+      <c r="B79" t="s">
+        <v>491</v>
+      </c>
+      <c r="C79" t="s">
+        <v>992</v>
+      </c>
+      <c r="D79" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>853</v>
+      </c>
+      <c r="B80" t="s">
+        <v>496</v>
+      </c>
+      <c r="C80" t="s">
+        <v>994</v>
+      </c>
+      <c r="D80" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>853</v>
+      </c>
+      <c r="B81" t="s">
+        <v>501</v>
+      </c>
+      <c r="C81" t="s">
+        <v>996</v>
+      </c>
+      <c r="D81" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>853</v>
+      </c>
+      <c r="B82" t="s">
+        <v>506</v>
+      </c>
+      <c r="C82" t="s">
+        <v>998</v>
+      </c>
+      <c r="D82" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>853</v>
+      </c>
+      <c r="B83" t="s">
+        <v>510</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D83" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>853</v>
+      </c>
+      <c r="B84" t="s">
+        <v>519</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D84" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>853</v>
+      </c>
+      <c r="B85" t="s">
+        <v>524</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D85" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>853</v>
+      </c>
+      <c r="B86" t="s">
+        <v>529</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D86" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>853</v>
+      </c>
+      <c r="B87" t="s">
+        <v>534</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D87" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>853</v>
+      </c>
+      <c r="B88" t="s">
+        <v>539</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D88" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>853</v>
+      </c>
+      <c r="B89" t="s">
+        <v>544</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D89" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>853</v>
+      </c>
+      <c r="B90" t="s">
+        <v>549</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D90" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>853</v>
+      </c>
+      <c r="B91" t="s">
+        <v>554</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D91" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>853</v>
+      </c>
+      <c r="B92" t="s">
+        <v>559</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D92" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B93" t="s">
+        <v>720</v>
+      </c>
+      <c r="C93" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B94" t="s">
+        <v>726</v>
+      </c>
+      <c r="C94" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B95" t="s">
+        <v>731</v>
+      </c>
+      <c r="C95" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B96" t="s">
+        <v>736</v>
+      </c>
+      <c r="C96" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B97" t="s">
+        <v>742</v>
+      </c>
+      <c r="C97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B98" t="s">
+        <v>747</v>
+      </c>
+      <c r="C98" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B99" t="s">
+        <v>752</v>
+      </c>
+      <c r="C99" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B100" t="s">
+        <v>742</v>
+      </c>
+      <c r="C100" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B101" t="s">
+        <v>761</v>
+      </c>
+      <c r="C101" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B102" t="s">
+        <v>766</v>
+      </c>
+      <c r="C102" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B103" t="s">
+        <v>772</v>
+      </c>
+      <c r="C103" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B104" t="s">
+        <v>742</v>
+      </c>
+      <c r="C104" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B105" t="s">
+        <v>742</v>
+      </c>
+      <c r="C105" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B106" t="s">
+        <v>785</v>
+      </c>
+      <c r="C106" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B107" t="s">
+        <v>790</v>
+      </c>
+      <c r="C107" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>8</v>
+      </c>
+      <c r="B108" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>12</v>
+      </c>
+      <c r="B109" t="s">
+        <v>13</v>
+      </c>
+      <c r="C109" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>17</v>
+      </c>
+      <c r="B111" t="s">
+        <v>18</v>
+      </c>
+      <c r="C111" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>20</v>
+      </c>
+      <c r="B112" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>22</v>
+      </c>
+      <c r="B113" t="s">
+        <v>23</v>
+      </c>
+      <c r="C113" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Z1" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5483,7 +7439,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.90625" customWidth="1"/>
@@ -5493,7 +7449,7 @@
     <col min="5" max="5" width="29.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>63</v>
       </c>
@@ -5515,8 +7471,17 @@
       <c r="G1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>107</v>
       </c>
@@ -5539,7 +7504,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1168</v>
       </c>
@@ -5562,7 +7527,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1169</v>
       </c>
@@ -5585,7 +7550,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1169</v>
       </c>
@@ -5608,7 +7573,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1169</v>
       </c>
@@ -5631,7 +7596,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>1169</v>
       </c>
@@ -5654,7 +7619,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>1169</v>
       </c>
@@ -5677,7 +7642,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>1169</v>
       </c>
@@ -5700,7 +7665,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>1169</v>
       </c>
@@ -5723,7 +7688,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>131</v>
       </c>
@@ -5746,7 +7711,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>131</v>
       </c>
@@ -5769,7 +7734,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>131</v>
       </c>
@@ -5792,7 +7757,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>131</v>
       </c>
@@ -5822,6 +7787,566 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC777CA-632C-4876-8BA8-C36A1361E85B}">
+  <dimension ref="A1:D43"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" ht="169" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="208" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="208" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="143" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="104" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="143" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="221" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="117" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="91" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="130" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="156" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="195" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="182" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="169" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="221" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="143" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="195" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="156" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="195" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="117" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="130" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="156" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="130" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="130" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="78" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="104" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="91" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="65" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="65" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="65" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="65" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="65" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="65" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="91" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="65" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="65" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="65" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="65" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F123"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8292,7 +10817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8371,7 +10896,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8754,7 +11279,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8842,7 +11367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -9546,1599 +12071,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:Z1" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:D113"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>840</v>
-      </c>
-      <c r="B1" t="s">
-        <v>841</v>
-      </c>
-      <c r="C1" t="s">
-        <v>842</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>843</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>844</v>
-      </c>
-      <c r="D2" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>853</v>
-      </c>
-      <c r="B10" t="s">
-        <v>147</v>
-      </c>
-      <c r="C10" t="s">
-        <v>854</v>
-      </c>
-      <c r="D10" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>853</v>
-      </c>
-      <c r="B11" t="s">
-        <v>152</v>
-      </c>
-      <c r="C11" t="s">
-        <v>856</v>
-      </c>
-      <c r="D11" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>853</v>
-      </c>
-      <c r="B12" t="s">
-        <v>157</v>
-      </c>
-      <c r="C12" t="s">
-        <v>858</v>
-      </c>
-      <c r="D12" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>853</v>
-      </c>
-      <c r="B13" t="s">
-        <v>163</v>
-      </c>
-      <c r="C13" t="s">
-        <v>860</v>
-      </c>
-      <c r="D13" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>853</v>
-      </c>
-      <c r="B14" t="s">
-        <v>168</v>
-      </c>
-      <c r="C14" t="s">
-        <v>862</v>
-      </c>
-      <c r="D14" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>853</v>
-      </c>
-      <c r="B15" t="s">
-        <v>172</v>
-      </c>
-      <c r="C15" t="s">
-        <v>864</v>
-      </c>
-      <c r="D15" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>853</v>
-      </c>
-      <c r="B16" t="s">
-        <v>177</v>
-      </c>
-      <c r="C16" t="s">
-        <v>866</v>
-      </c>
-      <c r="D16" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>853</v>
-      </c>
-      <c r="B17" t="s">
-        <v>182</v>
-      </c>
-      <c r="C17" t="s">
-        <v>868</v>
-      </c>
-      <c r="D17" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>853</v>
-      </c>
-      <c r="B18" t="s">
-        <v>187</v>
-      </c>
-      <c r="C18" t="s">
-        <v>870</v>
-      </c>
-      <c r="D18" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>853</v>
-      </c>
-      <c r="B19" t="s">
-        <v>192</v>
-      </c>
-      <c r="C19" t="s">
-        <v>872</v>
-      </c>
-      <c r="D19" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>853</v>
-      </c>
-      <c r="B20" t="s">
-        <v>197</v>
-      </c>
-      <c r="C20" t="s">
-        <v>874</v>
-      </c>
-      <c r="D20" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>853</v>
-      </c>
-      <c r="B21" t="s">
-        <v>202</v>
-      </c>
-      <c r="C21" t="s">
-        <v>876</v>
-      </c>
-      <c r="D21" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>853</v>
-      </c>
-      <c r="B22" t="s">
-        <v>207</v>
-      </c>
-      <c r="C22" t="s">
-        <v>878</v>
-      </c>
-      <c r="D22" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>853</v>
-      </c>
-      <c r="B23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C23" t="s">
-        <v>880</v>
-      </c>
-      <c r="D23" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>853</v>
-      </c>
-      <c r="B24" t="s">
-        <v>217</v>
-      </c>
-      <c r="C24" t="s">
-        <v>882</v>
-      </c>
-      <c r="D24" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>853</v>
-      </c>
-      <c r="B25" t="s">
-        <v>222</v>
-      </c>
-      <c r="C25" t="s">
-        <v>884</v>
-      </c>
-      <c r="D25" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>853</v>
-      </c>
-      <c r="B26" t="s">
-        <v>227</v>
-      </c>
-      <c r="C26" t="s">
-        <v>886</v>
-      </c>
-      <c r="D26" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>853</v>
-      </c>
-      <c r="B27" t="s">
-        <v>232</v>
-      </c>
-      <c r="C27" t="s">
-        <v>888</v>
-      </c>
-      <c r="D27" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>853</v>
-      </c>
-      <c r="B28" t="s">
-        <v>237</v>
-      </c>
-      <c r="C28" t="s">
-        <v>890</v>
-      </c>
-      <c r="D28" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>853</v>
-      </c>
-      <c r="B29" t="s">
-        <v>242</v>
-      </c>
-      <c r="C29" t="s">
-        <v>892</v>
-      </c>
-      <c r="D29" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>853</v>
-      </c>
-      <c r="B30" t="s">
-        <v>247</v>
-      </c>
-      <c r="C30" t="s">
-        <v>894</v>
-      </c>
-      <c r="D30" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>853</v>
-      </c>
-      <c r="B31" t="s">
-        <v>252</v>
-      </c>
-      <c r="C31" t="s">
-        <v>896</v>
-      </c>
-      <c r="D31" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>853</v>
-      </c>
-      <c r="B32" t="s">
-        <v>257</v>
-      </c>
-      <c r="C32" t="s">
-        <v>898</v>
-      </c>
-      <c r="D32" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>853</v>
-      </c>
-      <c r="B33" t="s">
-        <v>262</v>
-      </c>
-      <c r="C33" t="s">
-        <v>900</v>
-      </c>
-      <c r="D33" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>853</v>
-      </c>
-      <c r="B34" t="s">
-        <v>267</v>
-      </c>
-      <c r="C34" t="s">
-        <v>902</v>
-      </c>
-      <c r="D34" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>853</v>
-      </c>
-      <c r="B35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C35" t="s">
-        <v>904</v>
-      </c>
-      <c r="D35" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>853</v>
-      </c>
-      <c r="B36" t="s">
-        <v>277</v>
-      </c>
-      <c r="C36" t="s">
-        <v>906</v>
-      </c>
-      <c r="D36" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>853</v>
-      </c>
-      <c r="B37" t="s">
-        <v>283</v>
-      </c>
-      <c r="C37" t="s">
-        <v>908</v>
-      </c>
-      <c r="D37" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>853</v>
-      </c>
-      <c r="B38" t="s">
-        <v>288</v>
-      </c>
-      <c r="C38" t="s">
-        <v>910</v>
-      </c>
-      <c r="D38" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>853</v>
-      </c>
-      <c r="B39" t="s">
-        <v>293</v>
-      </c>
-      <c r="C39" t="s">
-        <v>912</v>
-      </c>
-      <c r="D39" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>853</v>
-      </c>
-      <c r="B40" t="s">
-        <v>298</v>
-      </c>
-      <c r="C40" t="s">
-        <v>914</v>
-      </c>
-      <c r="D40" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>853</v>
-      </c>
-      <c r="B41" t="s">
-        <v>303</v>
-      </c>
-      <c r="C41" t="s">
-        <v>916</v>
-      </c>
-      <c r="D41" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>853</v>
-      </c>
-      <c r="B42" t="s">
-        <v>307</v>
-      </c>
-      <c r="C42" t="s">
-        <v>918</v>
-      </c>
-      <c r="D42" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>853</v>
-      </c>
-      <c r="B43" t="s">
-        <v>312</v>
-      </c>
-      <c r="C43" t="s">
-        <v>920</v>
-      </c>
-      <c r="D43" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>853</v>
-      </c>
-      <c r="B44" t="s">
-        <v>316</v>
-      </c>
-      <c r="C44" t="s">
-        <v>922</v>
-      </c>
-      <c r="D44" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>853</v>
-      </c>
-      <c r="B45" t="s">
-        <v>320</v>
-      </c>
-      <c r="C45" t="s">
-        <v>924</v>
-      </c>
-      <c r="D45" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>853</v>
-      </c>
-      <c r="B46" t="s">
-        <v>325</v>
-      </c>
-      <c r="C46" t="s">
-        <v>926</v>
-      </c>
-      <c r="D46" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>853</v>
-      </c>
-      <c r="B47" t="s">
-        <v>330</v>
-      </c>
-      <c r="C47" t="s">
-        <v>928</v>
-      </c>
-      <c r="D47" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>853</v>
-      </c>
-      <c r="B48" t="s">
-        <v>335</v>
-      </c>
-      <c r="C48" t="s">
-        <v>930</v>
-      </c>
-      <c r="D48" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>853</v>
-      </c>
-      <c r="B49" t="s">
-        <v>340</v>
-      </c>
-      <c r="C49" t="s">
-        <v>932</v>
-      </c>
-      <c r="D49" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>853</v>
-      </c>
-      <c r="B50" t="s">
-        <v>346</v>
-      </c>
-      <c r="C50" t="s">
-        <v>934</v>
-      </c>
-      <c r="D50" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>853</v>
-      </c>
-      <c r="B51" t="s">
-        <v>350</v>
-      </c>
-      <c r="C51" t="s">
-        <v>936</v>
-      </c>
-      <c r="D51" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>853</v>
-      </c>
-      <c r="B52" t="s">
-        <v>355</v>
-      </c>
-      <c r="C52" t="s">
-        <v>938</v>
-      </c>
-      <c r="D52" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>853</v>
-      </c>
-      <c r="B53" t="s">
-        <v>360</v>
-      </c>
-      <c r="C53" t="s">
-        <v>940</v>
-      </c>
-      <c r="D53" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>853</v>
-      </c>
-      <c r="B54" t="s">
-        <v>365</v>
-      </c>
-      <c r="C54" t="s">
-        <v>942</v>
-      </c>
-      <c r="D54" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>853</v>
-      </c>
-      <c r="B55" t="s">
-        <v>370</v>
-      </c>
-      <c r="C55" t="s">
-        <v>944</v>
-      </c>
-      <c r="D55" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>853</v>
-      </c>
-      <c r="B56" t="s">
-        <v>375</v>
-      </c>
-      <c r="C56" t="s">
-        <v>946</v>
-      </c>
-      <c r="D56" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>853</v>
-      </c>
-      <c r="B57" t="s">
-        <v>380</v>
-      </c>
-      <c r="C57" t="s">
-        <v>948</v>
-      </c>
-      <c r="D57" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>853</v>
-      </c>
-      <c r="B58" t="s">
-        <v>385</v>
-      </c>
-      <c r="C58" t="s">
-        <v>950</v>
-      </c>
-      <c r="D58" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>853</v>
-      </c>
-      <c r="B59" t="s">
-        <v>390</v>
-      </c>
-      <c r="C59" t="s">
-        <v>952</v>
-      </c>
-      <c r="D59" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>853</v>
-      </c>
-      <c r="B60" t="s">
-        <v>395</v>
-      </c>
-      <c r="C60" t="s">
-        <v>954</v>
-      </c>
-      <c r="D60" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>853</v>
-      </c>
-      <c r="B61" t="s">
-        <v>400</v>
-      </c>
-      <c r="C61" t="s">
-        <v>956</v>
-      </c>
-      <c r="D61" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>853</v>
-      </c>
-      <c r="B62" t="s">
-        <v>405</v>
-      </c>
-      <c r="C62" t="s">
-        <v>958</v>
-      </c>
-      <c r="D62" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>853</v>
-      </c>
-      <c r="B63" t="s">
-        <v>410</v>
-      </c>
-      <c r="C63" t="s">
-        <v>960</v>
-      </c>
-      <c r="D63" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>853</v>
-      </c>
-      <c r="B64" t="s">
-        <v>415</v>
-      </c>
-      <c r="C64" t="s">
-        <v>962</v>
-      </c>
-      <c r="D64" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>853</v>
-      </c>
-      <c r="B65" t="s">
-        <v>420</v>
-      </c>
-      <c r="C65" t="s">
-        <v>964</v>
-      </c>
-      <c r="D65" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>853</v>
-      </c>
-      <c r="B66" t="s">
-        <v>425</v>
-      </c>
-      <c r="C66" t="s">
-        <v>966</v>
-      </c>
-      <c r="D66" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>853</v>
-      </c>
-      <c r="B67" t="s">
-        <v>430</v>
-      </c>
-      <c r="C67" t="s">
-        <v>968</v>
-      </c>
-      <c r="D67" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>853</v>
-      </c>
-      <c r="B68" t="s">
-        <v>435</v>
-      </c>
-      <c r="C68" t="s">
-        <v>970</v>
-      </c>
-      <c r="D68" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>853</v>
-      </c>
-      <c r="B69" t="s">
-        <v>440</v>
-      </c>
-      <c r="C69" t="s">
-        <v>972</v>
-      </c>
-      <c r="D69" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>853</v>
-      </c>
-      <c r="B70" t="s">
-        <v>445</v>
-      </c>
-      <c r="C70" t="s">
-        <v>974</v>
-      </c>
-      <c r="D70" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>853</v>
-      </c>
-      <c r="B71" t="s">
-        <v>449</v>
-      </c>
-      <c r="C71" t="s">
-        <v>976</v>
-      </c>
-      <c r="D71" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>853</v>
-      </c>
-      <c r="B72" t="s">
-        <v>454</v>
-      </c>
-      <c r="C72" t="s">
-        <v>978</v>
-      </c>
-      <c r="D72" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>853</v>
-      </c>
-      <c r="B73" t="s">
-        <v>459</v>
-      </c>
-      <c r="C73" t="s">
-        <v>980</v>
-      </c>
-      <c r="D73" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>853</v>
-      </c>
-      <c r="B74" t="s">
-        <v>464</v>
-      </c>
-      <c r="C74" t="s">
-        <v>982</v>
-      </c>
-      <c r="D74" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>853</v>
-      </c>
-      <c r="B75" t="s">
-        <v>469</v>
-      </c>
-      <c r="C75" t="s">
-        <v>984</v>
-      </c>
-      <c r="D75" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>853</v>
-      </c>
-      <c r="B76" t="s">
-        <v>475</v>
-      </c>
-      <c r="C76" t="s">
-        <v>986</v>
-      </c>
-      <c r="D76" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>853</v>
-      </c>
-      <c r="B77" t="s">
-        <v>481</v>
-      </c>
-      <c r="C77" t="s">
-        <v>988</v>
-      </c>
-      <c r="D77" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>853</v>
-      </c>
-      <c r="B78" t="s">
-        <v>486</v>
-      </c>
-      <c r="C78" t="s">
-        <v>990</v>
-      </c>
-      <c r="D78" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>853</v>
-      </c>
-      <c r="B79" t="s">
-        <v>491</v>
-      </c>
-      <c r="C79" t="s">
-        <v>992</v>
-      </c>
-      <c r="D79" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>853</v>
-      </c>
-      <c r="B80" t="s">
-        <v>496</v>
-      </c>
-      <c r="C80" t="s">
-        <v>994</v>
-      </c>
-      <c r="D80" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>853</v>
-      </c>
-      <c r="B81" t="s">
-        <v>501</v>
-      </c>
-      <c r="C81" t="s">
-        <v>996</v>
-      </c>
-      <c r="D81" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>853</v>
-      </c>
-      <c r="B82" t="s">
-        <v>506</v>
-      </c>
-      <c r="C82" t="s">
-        <v>998</v>
-      </c>
-      <c r="D82" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>853</v>
-      </c>
-      <c r="B83" t="s">
-        <v>510</v>
-      </c>
-      <c r="C83" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D83" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>853</v>
-      </c>
-      <c r="B84" t="s">
-        <v>519</v>
-      </c>
-      <c r="C84" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D84" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>853</v>
-      </c>
-      <c r="B85" t="s">
-        <v>524</v>
-      </c>
-      <c r="C85" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D85" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>853</v>
-      </c>
-      <c r="B86" t="s">
-        <v>529</v>
-      </c>
-      <c r="C86" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D86" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>853</v>
-      </c>
-      <c r="B87" t="s">
-        <v>534</v>
-      </c>
-      <c r="C87" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D87" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>853</v>
-      </c>
-      <c r="B88" t="s">
-        <v>539</v>
-      </c>
-      <c r="C88" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D88" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>853</v>
-      </c>
-      <c r="B89" t="s">
-        <v>544</v>
-      </c>
-      <c r="C89" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D89" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>853</v>
-      </c>
-      <c r="B90" t="s">
-        <v>549</v>
-      </c>
-      <c r="C90" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D90" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>853</v>
-      </c>
-      <c r="B91" t="s">
-        <v>554</v>
-      </c>
-      <c r="C91" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D91" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>853</v>
-      </c>
-      <c r="B92" t="s">
-        <v>559</v>
-      </c>
-      <c r="C92" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D92" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B93" t="s">
-        <v>720</v>
-      </c>
-      <c r="C93" t="s">
-        <v>10</v>
-      </c>
-      <c r="D93" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B94" t="s">
-        <v>726</v>
-      </c>
-      <c r="C94" t="s">
-        <v>10</v>
-      </c>
-      <c r="D94" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B95" t="s">
-        <v>731</v>
-      </c>
-      <c r="C95" t="s">
-        <v>10</v>
-      </c>
-      <c r="D95" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B96" t="s">
-        <v>736</v>
-      </c>
-      <c r="C96" t="s">
-        <v>10</v>
-      </c>
-      <c r="D96" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B97" t="s">
-        <v>742</v>
-      </c>
-      <c r="C97" t="s">
-        <v>10</v>
-      </c>
-      <c r="D97" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B98" t="s">
-        <v>747</v>
-      </c>
-      <c r="C98" t="s">
-        <v>10</v>
-      </c>
-      <c r="D98" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B99" t="s">
-        <v>752</v>
-      </c>
-      <c r="C99" t="s">
-        <v>10</v>
-      </c>
-      <c r="D99" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B100" t="s">
-        <v>742</v>
-      </c>
-      <c r="C100" t="s">
-        <v>10</v>
-      </c>
-      <c r="D100" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B101" t="s">
-        <v>761</v>
-      </c>
-      <c r="C101" t="s">
-        <v>10</v>
-      </c>
-      <c r="D101" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B102" t="s">
-        <v>766</v>
-      </c>
-      <c r="C102" t="s">
-        <v>10</v>
-      </c>
-      <c r="D102" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B103" t="s">
-        <v>772</v>
-      </c>
-      <c r="C103" t="s">
-        <v>10</v>
-      </c>
-      <c r="D103" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B104" t="s">
-        <v>742</v>
-      </c>
-      <c r="C104" t="s">
-        <v>10</v>
-      </c>
-      <c r="D104" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B105" t="s">
-        <v>742</v>
-      </c>
-      <c r="C105" t="s">
-        <v>10</v>
-      </c>
-      <c r="D105" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B106" t="s">
-        <v>785</v>
-      </c>
-      <c r="C106" t="s">
-        <v>10</v>
-      </c>
-      <c r="D106" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B107" t="s">
-        <v>790</v>
-      </c>
-      <c r="C107" t="s">
-        <v>10</v>
-      </c>
-      <c r="D107" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>8</v>
-      </c>
-      <c r="B108" t="s">
-        <v>9</v>
-      </c>
-      <c r="C108" t="s">
-        <v>10</v>
-      </c>
-      <c r="D108" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>12</v>
-      </c>
-      <c r="B109" t="s">
-        <v>13</v>
-      </c>
-      <c r="C109" t="s">
-        <v>10</v>
-      </c>
-      <c r="D109" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="s">
-        <v>10</v>
-      </c>
-      <c r="D110" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>17</v>
-      </c>
-      <c r="B111" t="s">
-        <v>18</v>
-      </c>
-      <c r="C111" t="s">
-        <v>10</v>
-      </c>
-      <c r="D111" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>20</v>
-      </c>
-      <c r="B112" t="s">
-        <v>21</v>
-      </c>
-      <c r="C112" t="s">
-        <v>10</v>
-      </c>
-      <c r="D112" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>22</v>
-      </c>
-      <c r="B113" t="s">
-        <v>23</v>
-      </c>
-      <c r="C113" t="s">
-        <v>10</v>
-      </c>
-      <c r="D113" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:Z1" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/SHAPE-Lab-Website-Content.xlsx
+++ b/SHAPE-Lab-Website-Content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/byg5201_psu_edu/Documents/Documents/GitHub/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{4358DB11-5B92-4F17-8511-6659BB54189A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E00C963-8A44-413D-881A-0AC7F5565D97}"/>
+  <xr:revisionPtr revIDLastSave="199" documentId="13_ncr:1_{4358DB11-5B92-4F17-8511-6659BB54189A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA3639D8-7A6C-40BB-AD6E-BD82F92073D8}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="1270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="1310">
   <si>
     <t>Section</t>
   </si>
@@ -3648,29 +3648,6 @@
   </si>
   <si>
     <t>A review of the interface design in multi-material laser powder bed fusion of metals</t>
-  </si>
-  <si>
-    <r>
-      <t>Matthew</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF777777"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Williams</t>
-    </r>
   </si>
   <si>
     <t>Multi-axis routing of syringe deposited conductive traces over topology-optimized multi-functional structures</t>
@@ -3872,12 +3849,135 @@
   <si>
     <t>James Lauer</t>
   </si>
+  <si>
+    <t>KC Majewski</t>
+  </si>
+  <si>
+    <t>Andres Bujanda</t>
+  </si>
+  <si>
+    <t>Kirshna Vistarakula</t>
+  </si>
+  <si>
+    <t>Eklou Eric Hiheglo</t>
+  </si>
+  <si>
+    <t>James Sprague IV</t>
+  </si>
+  <si>
+    <t>Timothy Sheffield</t>
+  </si>
+  <si>
+    <t>‪Guha Manogharan‬ - ‪Google Scholar‬</t>
+  </si>
+  <si>
+    <t>Guha Manogharan | LinkedIn</t>
+  </si>
+  <si>
+    <t>aad6034@psu.edu</t>
+  </si>
+  <si>
+    <t>kxs6079@psu.edu</t>
+  </si>
+  <si>
+    <t>aas6636@psu.edu</t>
+  </si>
+  <si>
+    <t>akj5512@psu.edu</t>
+  </si>
+  <si>
+    <t>bygong@psu.edu</t>
+  </si>
+  <si>
+    <t>teh5427@psu.edu</t>
+  </si>
+  <si>
+    <t>Luis Rodriguez</t>
+  </si>
+  <si>
+    <t>kmajewski@blueorigin.com</t>
+  </si>
+  <si>
+    <t>aab206@psu.edu</t>
+  </si>
+  <si>
+    <t>kcv5092@psu.edu</t>
+  </si>
+  <si>
+    <t>eeh93@psu.edu</t>
+  </si>
+  <si>
+    <t>jes6847@psu.edu</t>
+  </si>
+  <si>
+    <t>tss5561@psu.edu</t>
+  </si>
+  <si>
+    <t>shapelab_photos/shapelab_photos/james_sprague.jpg</t>
+  </si>
+  <si>
+    <t>shapelab_photos/shapelab_photos/eric-aaa2219df26cd818.jpg</t>
+  </si>
+  <si>
+    <t>shapelab_photos/shapelab_photos/IMG_070541-225x300.jpg</t>
+  </si>
+  <si>
+    <t>shapelab_photos/shapelab_photos/IMG_4585-e1668446043331-202x300.jpg</t>
+  </si>
+  <si>
+    <t>shapelab_photos/shapelab_photos/IMG_1473-225x300.jpg</t>
+  </si>
+  <si>
+    <t>Ella Fuener</t>
+  </si>
+  <si>
+    <t>Mackenzie Cherry</t>
+  </si>
+  <si>
+    <t>Paige Cole</t>
+  </si>
+  <si>
+    <t>Joseph Northcote</t>
+  </si>
+  <si>
+    <t>George Kuney</t>
+  </si>
+  <si>
+    <t>Ahmed Elmanzalawi</t>
+  </si>
+  <si>
+    <t>B.S Mechanical Engineering, 2026</t>
+  </si>
+  <si>
+    <t>Ph.D. Mechanical Engineering, 2026</t>
+  </si>
+  <si>
+    <t>Matthew Williams</t>
+  </si>
+  <si>
+    <t>Interfaces in Multi-Material Laser Powder Bed Fusion: Defect Formation and Mitigation</t>
+  </si>
+  <si>
+    <t>erf5323@psu.edu</t>
+  </si>
+  <si>
+    <t>jjn5654@psu.edu</t>
+  </si>
+  <si>
+    <t>gmk5561@psu.edu</t>
+  </si>
+  <si>
+    <t>aye5163@psu.edu</t>
+  </si>
+  <si>
+    <t>B.S. Mechanical Engineering, 2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3899,6 +3999,31 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF777777"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3914,7 +4039,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -3922,22 +4047,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -7439,7 +7590,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.90625" customWidth="1"/>
@@ -7447,6 +7598,11 @@
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="22.453125" customWidth="1"/>
     <col min="5" max="5" width="29.36328125" customWidth="1"/>
+    <col min="6" max="6" width="16.08984375" customWidth="1"/>
+    <col min="7" max="7" width="24.453125" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" customWidth="1"/>
+    <col min="9" max="9" width="18.54296875" customWidth="1"/>
+    <col min="10" max="10" width="15.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -7503,6 +7659,15 @@
       <c r="G2" t="s">
         <v>113</v>
       </c>
+      <c r="H2" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>1276</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -7526,6 +7691,9 @@
       <c r="G3" t="s">
         <v>116</v>
       </c>
+      <c r="H3" t="s">
+        <v>1277</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -7549,13 +7717,16 @@
       <c r="G4" t="s">
         <v>117</v>
       </c>
+      <c r="H4" t="s">
+        <v>1278</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1169</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -7567,10 +7738,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G5" t="s">
-        <v>119</v>
+        <v>121</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1279</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -7578,7 +7752,7 @@
         <v>1169</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -7590,10 +7764,13 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G6" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1280</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -7601,7 +7778,7 @@
         <v>1169</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -7613,10 +7790,13 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G7" t="s">
-        <v>123</v>
+        <v>125</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>1281</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -7624,7 +7804,7 @@
         <v>1169</v>
       </c>
       <c r="B8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -7636,18 +7816,21 @@
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G8" t="s">
-        <v>125</v>
+        <v>127</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>1282</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>1169</v>
       </c>
-      <c r="B9" t="s">
-        <v>127</v>
+      <c r="B9" s="1" t="s">
+        <v>1283</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7659,18 +7842,18 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>1169</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -7682,10 +7865,10 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G10" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -7693,7 +7876,7 @@
         <v>131</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -7704,11 +7887,11 @@
       <c r="E11" t="s">
         <v>10</v>
       </c>
-      <c r="F11" t="s">
-        <v>133</v>
+      <c r="F11" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="G11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -7716,7 +7899,7 @@
         <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -7728,618 +7911,790 @@
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>131</v>
+        <v>1169</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G13" t="s">
-        <v>136</v>
+        <v>1269</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1284</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H18" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>131</v>
       </c>
-      <c r="B14" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G14" t="s">
-        <v>138</v>
+      <c r="B19" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H20" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1308</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Z1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" display="https://scholar.google.com/citations?user=KcYleckAAAAJ&amp;hl=en" xr:uid="{DD0E5204-590B-4947-8690-B27B3E859B8E}"/>
+    <hyperlink ref="J2" r:id="rId2" display="https://www.linkedin.com/in/guhamanogharan/" xr:uid="{4758B6A3-14F4-4259-9611-25878CF7F11E}"/>
+    <hyperlink ref="H7" r:id="rId3" xr:uid="{F94E3F68-BE76-495F-B30A-D239F7061A3F}"/>
+    <hyperlink ref="H8" r:id="rId4" xr:uid="{818A03B0-AA1D-4978-9AB8-A482133D4F22}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC777CA-632C-4876-8BA8-C36A1361E85B}">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.81640625" customWidth="1"/>
+    <col min="4" max="4" width="84.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>1172</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>1180</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>1173</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>1176</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>1177</v>
       </c>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1173</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>1178</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>1179</v>
       </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" ht="169" x14ac:dyDescent="0.35">
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="1:4" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>1169</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>1176</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>1181</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>1182</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="208" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:4" ht="261" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
         <v>1169</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>1183</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="5" t="s">
         <v>1181</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="5" t="s">
         <v>1184</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="208" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:4" ht="261" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>1169</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>1185</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>1186</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="5" t="s">
         <v>1187</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="143" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:4" ht="174" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>1169</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>1188</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="5" t="s">
         <v>1189</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="5" t="s">
         <v>1190</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="104" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>1169</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="5" t="s">
         <v>1191</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="5" t="s">
         <v>1186</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="5" t="s">
         <v>1192</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="143" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:4" ht="174" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
         <v>1169</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>1193</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="5" t="s">
         <v>1194</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="5" t="s">
         <v>1195</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="221" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:4" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>1169</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="5" t="s">
         <v>1196</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="5" t="s">
         <v>1194</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="5" t="s">
         <v>1197</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="117" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>1198</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>1199</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="5" t="s">
         <v>1200</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="91" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:4" ht="145" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>1201</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="5" t="s">
         <v>1202</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="5" t="s">
         <v>1203</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="130" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="5" t="s">
         <v>1204</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="5" t="s">
         <v>1202</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="5" t="s">
         <v>1205</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="156" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="14" spans="1:4" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>1206</v>
       </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:4" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>1202</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="195" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="D15" s="5" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="232" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>1208</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="B16" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>1202</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="182" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="D16" s="5" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="232" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>1210</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="B17" s="5" t="s">
         <v>1211</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="169" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="C17" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="261" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B18" s="5" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>1212</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="221" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="D18" s="5" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="B19" s="5" t="s">
         <v>1216</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="143" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="C19" s="5" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="232" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1218</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="B20" s="5" t="s">
         <v>1219</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="195" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="C20" s="5" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>1220</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="B21" s="5" t="s">
         <v>1222</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="156" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="C21" s="5" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="B22" s="5" t="s">
         <v>1225</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="195" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="C22" s="5" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="145" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>1226</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="B23" s="5" t="s">
         <v>1228</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="117" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="C23" s="5" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1230</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="B24" s="5" t="s">
         <v>1231</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="130" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="C24" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B25" s="5" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>1232</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="156" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="D25" s="5" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="174" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="B26" s="5" t="s">
         <v>1236</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="130" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="C26" s="5" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1238</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="B27" s="5" t="s">
         <v>1239</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="130" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="5" t="s">
         <v>1240</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="5" t="s">
         <v>1241</v>
       </c>
-      <c r="D27" s="2" t="s">
+    </row>
+    <row r="28" spans="1:4" ht="78" x14ac:dyDescent="0.35">
+      <c r="A28" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>1242</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="78" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
+      <c r="C28" s="9" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D28" s="10"/>
+    </row>
+    <row r="29" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="B29" s="8" t="s">
         <v>1244</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="C29" s="8" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D29" s="10"/>
+    </row>
+    <row r="30" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A30" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="B30" s="8" t="s">
         <v>1246</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="C30" s="8" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D30" s="10"/>
+    </row>
+    <row r="31" spans="1:4" ht="104" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="B31" s="8" t="s">
         <v>1248</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="104" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="C31" s="8" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D31" s="10"/>
+    </row>
+    <row r="32" spans="1:4" ht="91" x14ac:dyDescent="0.35">
+      <c r="A32" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>1249</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="B32" s="8" t="s">
         <v>1250</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="91" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="C32" s="8" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D32" s="10"/>
+    </row>
+    <row r="33" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A33" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>1251</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="B33" s="8" t="s">
         <v>1252</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="65" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="C33" s="8" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D33" s="10"/>
+    </row>
+    <row r="34" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A34" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B34" s="8" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>1253</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="65" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="D34" s="10"/>
+    </row>
+    <row r="35" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A35" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B35" s="8" t="s">
         <v>1255</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="65" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="C35" s="8" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D35" s="10"/>
+    </row>
+    <row r="36" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A36" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B36" s="8" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>1256</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="65" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="D36" s="10"/>
+    </row>
+    <row r="37" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A37" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B37" s="8" t="s">
         <v>1258</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="65" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="C37" s="8" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D37" s="10"/>
+    </row>
+    <row r="38" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A38" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B38" s="8" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>1259</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="65" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="D38" s="10"/>
+    </row>
+    <row r="39" spans="1:4" ht="91" x14ac:dyDescent="0.35">
+      <c r="A39" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B39" s="8" t="s">
         <v>1261</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="91" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="C39" s="8" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D39" s="10"/>
+    </row>
+    <row r="40" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A40" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="B40" s="8" t="s">
         <v>1263</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="65" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="C40" s="8" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D40" s="10"/>
+    </row>
+    <row r="41" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A41" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B41" s="8" t="s">
         <v>1264</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="65" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+      <c r="C41" s="8" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D41" s="10"/>
+    </row>
+    <row r="42" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A42" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="B42" s="8" t="s">
         <v>1266</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="65" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+      <c r="C42" s="8" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D42" s="10"/>
+    </row>
+    <row r="43" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A43" s="10" t="s">
         <v>1175</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B43" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>1267</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="65" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="D43" s="10"/>
+    </row>
+    <row r="44" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A44" s="7" t="s">
         <v>1175</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>1269</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>1268</v>
-      </c>
+      <c r="B44" s="7" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D44" s="10"/>
+    </row>
+    <row r="45" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A45" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D45" s="10"/>
+    </row>
+    <row r="46" spans="1:4" ht="65" x14ac:dyDescent="0.4">
+      <c r="A46" s="7" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A47" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D47" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SHAPE-Lab-Website-Content.xlsx
+++ b/SHAPE-Lab-Website-Content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/byg5201_psu_edu/Documents/Documents/GitHub/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="199" documentId="13_ncr:1_{4358DB11-5B92-4F17-8511-6659BB54189A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA3639D8-7A6C-40BB-AD6E-BD82F92073D8}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="13_ncr:1_{4358DB11-5B92-4F17-8511-6659BB54189A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D84527D2-81FB-4F15-836F-AAAD882AA0D9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site Copy" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="1310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2328" uniqueCount="1337">
   <si>
     <t>Section</t>
   </si>
@@ -3761,20 +3761,6 @@
     <t>Joe Borst, Visiting student from Clarkson University</t>
   </si>
   <si>
-    <r>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF777777"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>B.S. Mechanical Engineering, 2026</t>
-    </r>
-  </si>
-  <si>
     <t>Joseph Daghir</t>
   </si>
   <si>
@@ -3868,12 +3854,6 @@
     <t>Timothy Sheffield</t>
   </si>
   <si>
-    <t>‪Guha Manogharan‬ - ‪Google Scholar‬</t>
-  </si>
-  <si>
-    <t>Guha Manogharan | LinkedIn</t>
-  </si>
-  <si>
     <t>aad6034@psu.edu</t>
   </si>
   <si>
@@ -3971,28 +3951,106 @@
   </si>
   <si>
     <t>B.S. Mechanical Engineering, 2026</t>
+  </si>
+  <si>
+    <t> B.S. Mechanical Engineering, 2026</t>
+  </si>
+  <si>
+    <t>oia5149@psu.edu</t>
+  </si>
+  <si>
+    <t>mrb6723@psu.edu</t>
+  </si>
+  <si>
+    <t>tbm5711@psu.edu</t>
+  </si>
+  <si>
+    <t>ler5605@psu.edu</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?hl=en&amp;user=KcYleckAAAAJ</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?hl=en&amp;user=ef_GbGwAAAAJ</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/aishwarya-deshpande-504b33177/</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?hl=en&amp;user=soPw1QIAAAAJ</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kazi-safowan-shahed-5255a512a/</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?hl=en&amp;user=9gPZgy4AAAAJ</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/avez-shaikh</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?hl=en&amp;user=cxenzngAAAAJ</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ashish-jacob-397362a0/</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?hl=en&amp;user=94cfIs0AAAAJ</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/bryan-gong-512228225/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/thomashanlon08/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/luis-rodriguez-5763a516/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/oreoluwa-adegbite/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/maxwell-bacon-me/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kc-majewski-18763584/</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?hl=en&amp;user=DCjpricAAAAJ</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/krishna-vistarakula-a2023b13/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/eklou-eric-h-a1921672</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/james-sprague-386846a8/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/tim-sheffield/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ella-fuener-a3a327290/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/josephnorthcote/</t>
+  </si>
+  <si>
+    <t>http://www.linkedin.com/in/georgekuney888</t>
+  </si>
+  <si>
+    <t>http://www.linkedin.com/in/ahmed-elmanzalawi-75b83a382</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF777777"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF777777"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4065,27 +4123,21 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7663,11 +7715,9 @@
         <v>804</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>1275</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>1276</v>
-      </c>
+        <v>1312</v>
+      </c>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -7692,7 +7742,13 @@
         <v>116</v>
       </c>
       <c r="H3" t="s">
-        <v>1277</v>
+        <v>1274</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1314</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -7718,7 +7774,13 @@
         <v>117</v>
       </c>
       <c r="H4" t="s">
-        <v>1278</v>
+        <v>1275</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1316</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -7744,7 +7806,13 @@
         <v>121</v>
       </c>
       <c r="H5" t="s">
-        <v>1279</v>
+        <v>1276</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1317</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1318</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -7770,7 +7838,13 @@
         <v>123</v>
       </c>
       <c r="H6" t="s">
-        <v>1280</v>
+        <v>1277</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1319</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1320</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -7796,7 +7870,13 @@
         <v>125</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1281</v>
+        <v>1278</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1321</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1322</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -7822,7 +7902,10 @@
         <v>127</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1282</v>
+        <v>1279</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1323</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -7830,7 +7913,7 @@
         <v>1169</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -7846,6 +7929,12 @@
       </c>
       <c r="G9" t="s">
         <v>129</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1324</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -7870,6 +7959,12 @@
       <c r="G10" t="s">
         <v>134</v>
       </c>
+      <c r="H10" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1325</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -7893,6 +7988,12 @@
       <c r="G11" t="s">
         <v>136</v>
       </c>
+      <c r="H11" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1326</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -7916,19 +8017,25 @@
       <c r="G12" t="s">
         <v>138</v>
       </c>
+      <c r="H12" t="s">
+        <v>1310</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>1169</v>
       </c>
       <c r="B13" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="H13" t="s">
-        <v>1284</v>
+        <v>1281</v>
+      </c>
+      <c r="J13" t="s">
+        <v>1327</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
@@ -7936,13 +8043,13 @@
         <v>1169</v>
       </c>
       <c r="B14" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="H14" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
@@ -7950,13 +8057,19 @@
         <v>1169</v>
       </c>
       <c r="B15" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="H15" t="s">
-        <v>1286</v>
+        <v>1283</v>
+      </c>
+      <c r="I15" t="s">
+        <v>1328</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1329</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -7964,106 +8077,125 @@
         <v>1169</v>
       </c>
       <c r="B16" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="H16" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1284</v>
+      </c>
+      <c r="J16" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>1169</v>
       </c>
       <c r="B17" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="H17" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1285</v>
+      </c>
+      <c r="J17" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>1174</v>
       </c>
       <c r="B18" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>1157</v>
       </c>
       <c r="H18" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1286</v>
+      </c>
+      <c r="J18" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>131</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>1136</v>
       </c>
       <c r="H19" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1302</v>
+      </c>
+      <c r="J19" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>1090</v>
       </c>
       <c r="H20" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1303</v>
+      </c>
+      <c r="J20" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>131</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>1071</v>
       </c>
       <c r="H21" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+        <v>1304</v>
+      </c>
+      <c r="J21" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>1138</v>
       </c>
       <c r="H22" t="s">
-        <v>1308</v>
+        <v>1305</v>
+      </c>
+      <c r="J22" t="s">
+        <v>1336</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Z1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" display="https://scholar.google.com/citations?user=KcYleckAAAAJ&amp;hl=en" xr:uid="{DD0E5204-590B-4947-8690-B27B3E859B8E}"/>
-    <hyperlink ref="J2" r:id="rId2" display="https://www.linkedin.com/in/guhamanogharan/" xr:uid="{4758B6A3-14F4-4259-9611-25878CF7F11E}"/>
-    <hyperlink ref="H7" r:id="rId3" xr:uid="{F94E3F68-BE76-495F-B30A-D239F7061A3F}"/>
-    <hyperlink ref="H8" r:id="rId4" xr:uid="{818A03B0-AA1D-4978-9AB8-A482133D4F22}"/>
+    <hyperlink ref="H7" r:id="rId1" xr:uid="{F94E3F68-BE76-495F-B30A-D239F7061A3F}"/>
+    <hyperlink ref="H8" r:id="rId2" xr:uid="{818A03B0-AA1D-4978-9AB8-A482133D4F22}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8094,7 +8226,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>1173</v>
       </c>
@@ -8106,7 +8238,7 @@
       </c>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1173</v>
       </c>
@@ -8118,7 +8250,7 @@
       </c>
       <c r="D3" s="6"/>
     </row>
-    <row r="4" spans="1:4" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>1169</v>
       </c>
@@ -8132,7 +8264,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="261" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>1169</v>
       </c>
@@ -8146,7 +8278,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="261" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>1169</v>
       </c>
@@ -8160,7 +8292,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="174" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>1169</v>
       </c>
@@ -8174,7 +8306,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>1169</v>
       </c>
@@ -8188,7 +8320,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="174" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>1169</v>
       </c>
@@ -8202,7 +8334,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>1169</v>
       </c>
@@ -8216,7 +8348,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8230,7 +8362,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="145" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8244,7 +8376,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8258,12 +8390,12 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>1174</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>1202</v>
@@ -8272,7 +8404,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8286,7 +8418,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="232" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8300,7 +8432,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="232" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8314,7 +8446,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="261" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8328,7 +8460,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8342,7 +8474,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="232" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8356,7 +8488,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8370,7 +8502,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8384,7 +8516,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="145" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8398,7 +8530,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8412,7 +8544,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8426,7 +8558,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="174" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8440,7 +8572,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>1174</v>
       </c>
@@ -8454,247 +8586,247 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="78" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>1175</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="5" t="s">
         <v>1242</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="8" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>1243</v>
       </c>
-      <c r="D28" s="10"/>
-    </row>
-    <row r="29" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A29" s="10" t="s">
+      <c r="C29" s="5" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>1244</v>
-      </c>
-      <c r="C29" s="8" t="s">
+      <c r="B30" s="5" t="s">
         <v>1245</v>
       </c>
-      <c r="D29" s="10"/>
-    </row>
-    <row r="30" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A30" s="10" t="s">
+      <c r="C30" s="5" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D30" s="8"/>
+    </row>
+    <row r="31" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>1246</v>
-      </c>
-      <c r="C30" s="8" t="s">
+      <c r="B31" s="5" t="s">
         <v>1247</v>
       </c>
-      <c r="D30" s="10"/>
-    </row>
-    <row r="31" spans="1:4" ht="104" x14ac:dyDescent="0.35">
-      <c r="A31" s="10" t="s">
+      <c r="C31" s="5" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D31" s="8"/>
+    </row>
+    <row r="32" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>1248</v>
-      </c>
-      <c r="C31" s="8" t="s">
+      <c r="B32" s="5" t="s">
         <v>1249</v>
       </c>
-      <c r="D31" s="10"/>
-    </row>
-    <row r="32" spans="1:4" ht="91" x14ac:dyDescent="0.35">
-      <c r="A32" s="10" t="s">
+      <c r="C32" s="5" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D32" s="8"/>
+    </row>
+    <row r="33" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A33" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C32" s="8" t="s">
+      <c r="B33" s="5" t="s">
         <v>1251</v>
       </c>
-      <c r="D32" s="10"/>
-    </row>
-    <row r="33" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A33" s="10" t="s">
+      <c r="C33" s="5" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D33" s="8"/>
+    </row>
+    <row r="34" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A34" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B34" s="5" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>1252</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>1253</v>
-      </c>
-      <c r="D33" s="10"/>
-    </row>
-    <row r="34" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A34" s="10" t="s">
+      <c r="D34" s="8"/>
+    </row>
+    <row r="35" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A35" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B35" s="5" t="s">
         <v>1254</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>1253</v>
-      </c>
-      <c r="D34" s="10"/>
-    </row>
-    <row r="35" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A35" s="10" t="s">
+      <c r="C35" s="5" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B36" s="5" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>1255</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D35" s="10"/>
-    </row>
-    <row r="36" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A36" s="10" t="s">
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B37" s="5" t="s">
         <v>1257</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D36" s="10"/>
-    </row>
-    <row r="37" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A37" s="10" t="s">
+      <c r="C37" s="5" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D37" s="8"/>
+    </row>
+    <row r="38" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A38" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B38" s="5" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>1258</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>1259</v>
-      </c>
-      <c r="D37" s="10"/>
-    </row>
-    <row r="38" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A38" s="10" t="s">
+      <c r="D38" s="8"/>
+    </row>
+    <row r="39" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B39" s="5" t="s">
         <v>1260</v>
       </c>
-      <c r="C38" s="8" t="s">
-        <v>1259</v>
-      </c>
-      <c r="D38" s="10"/>
-    </row>
-    <row r="39" spans="1:4" ht="91" x14ac:dyDescent="0.35">
-      <c r="A39" s="10" t="s">
+      <c r="C39" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D39" s="8"/>
+    </row>
+    <row r="40" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>1261</v>
-      </c>
-      <c r="C39" s="8" t="s">
+      <c r="B40" s="5" t="s">
         <v>1262</v>
       </c>
-      <c r="D39" s="10"/>
-    </row>
-    <row r="40" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A40" s="10" t="s">
+      <c r="C40" s="5" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D40" s="8"/>
+    </row>
+    <row r="41" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A41" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B41" s="5" t="s">
         <v>1263</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>1259</v>
-      </c>
-      <c r="D40" s="10"/>
-    </row>
-    <row r="41" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A41" s="10" t="s">
+      <c r="C41" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D41" s="8"/>
+    </row>
+    <row r="42" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A42" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>1264</v>
-      </c>
-      <c r="C41" s="8" t="s">
+      <c r="B42" s="5" t="s">
         <v>1265</v>
       </c>
-      <c r="D41" s="10"/>
-    </row>
-    <row r="42" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A42" s="10" t="s">
+      <c r="C42" s="5" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D42" s="8"/>
+    </row>
+    <row r="43" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A43" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B43" s="5" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>1266</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>1267</v>
-      </c>
-      <c r="D42" s="10"/>
-    </row>
-    <row r="43" spans="1:4" ht="65" x14ac:dyDescent="0.35">
-      <c r="A43" s="10" t="s">
-        <v>1175</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>1267</v>
-      </c>
-      <c r="D43" s="10"/>
-    </row>
-    <row r="44" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="D43" s="8"/>
+    </row>
+    <row r="44" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>1175</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>1296</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>1301</v>
-      </c>
-      <c r="D44" s="10"/>
-    </row>
-    <row r="45" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="B44" s="4" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D44" s="8"/>
+    </row>
+    <row r="45" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>1175</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>1297</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>1301</v>
-      </c>
-      <c r="D45" s="10"/>
-    </row>
-    <row r="46" spans="1:4" ht="65" x14ac:dyDescent="0.4">
+      <c r="B45" s="4" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D45" s="8"/>
+    </row>
+    <row r="46" spans="1:4" ht="29" x14ac:dyDescent="0.4">
       <c r="A46" s="7" t="s">
         <v>1169</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>1302</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="C46" s="5" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>1175</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>1309</v>
-      </c>
-      <c r="D47" s="10"/>
+      <c r="C47" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D47" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SHAPE-Lab-Website-Content.xlsx
+++ b/SHAPE-Lab-Website-Content.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305</t>
+          <t xml:space="preserve">1310</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305</t>
+          <t xml:space="preserve">1310</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375</t>
+          <t xml:space="preserve">1380</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1518</t>
+          <t xml:space="preserve">1523</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631</t>
+          <t xml:space="preserve">1636</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631</t>
+          <t xml:space="preserve">1636</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662</t>
+          <t xml:space="preserve">1663</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662</t>
+          <t xml:space="preserve">1663</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2879</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2879</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2921</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2921</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2941</t>
+          <t xml:space="preserve">2942</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2941</t>
+          <t xml:space="preserve">2942</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1316</t>
+          <t xml:space="preserve">1321</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1324</t>
+          <t xml:space="preserve">1329</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1332</t>
+          <t xml:space="preserve">1337</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1346</t>
+          <t xml:space="preserve">1351</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1354</t>
+          <t xml:space="preserve">1359</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1362</t>
+          <t xml:space="preserve">1367</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1673</t>
+          <t xml:space="preserve">1674</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683</t>
+          <t xml:space="preserve">1684</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1693</t>
+          <t xml:space="preserve">1694</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1708</t>
+          <t xml:space="preserve">1709</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718</t>
+          <t xml:space="preserve">1719</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728</t>
+          <t xml:space="preserve">1729</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1738</t>
+          <t xml:space="preserve">1739</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1748</t>
+          <t xml:space="preserve">1749</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1758</t>
+          <t xml:space="preserve">1759</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1768</t>
+          <t xml:space="preserve">1769</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778</t>
+          <t xml:space="preserve">1779</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1788</t>
+          <t xml:space="preserve">1789</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1798</t>
+          <t xml:space="preserve">1799</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808</t>
+          <t xml:space="preserve">1809</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818</t>
+          <t xml:space="preserve">1819</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828</t>
+          <t xml:space="preserve">1829</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1838</t>
+          <t xml:space="preserve">1839</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848</t>
+          <t xml:space="preserve">1849</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1863</t>
+          <t xml:space="preserve">1864</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1873</t>
+          <t xml:space="preserve">1874</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1883</t>
+          <t xml:space="preserve">1884</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1893</t>
+          <t xml:space="preserve">1894</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">1904</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1913</t>
+          <t xml:space="preserve">1914</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1923</t>
+          <t xml:space="preserve">1924</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1933</t>
+          <t xml:space="preserve">1934</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943</t>
+          <t xml:space="preserve">1944</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1958</t>
+          <t xml:space="preserve">1959</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1968</t>
+          <t xml:space="preserve">1969</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1978</t>
+          <t xml:space="preserve">1979</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1988</t>
+          <t xml:space="preserve">1989</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998</t>
+          <t xml:space="preserve">1999</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008</t>
+          <t xml:space="preserve">2009</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018</t>
+          <t xml:space="preserve">2019</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028</t>
+          <t xml:space="preserve">2029</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2038</t>
+          <t xml:space="preserve">2039</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2048</t>
+          <t xml:space="preserve">2049</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2058</t>
+          <t xml:space="preserve">2059</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068</t>
+          <t xml:space="preserve">2069</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2078</t>
+          <t xml:space="preserve">2079</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2093</t>
+          <t xml:space="preserve">2094</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103</t>
+          <t xml:space="preserve">2104</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2113</t>
+          <t xml:space="preserve">2114</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2123</t>
+          <t xml:space="preserve">2124</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2133</t>
+          <t xml:space="preserve">2134</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2143</t>
+          <t xml:space="preserve">2144</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2153</t>
+          <t xml:space="preserve">2154</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163</t>
+          <t xml:space="preserve">2164</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173</t>
+          <t xml:space="preserve">2174</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2183</t>
+          <t xml:space="preserve">2184</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2193</t>
+          <t xml:space="preserve">2194</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203</t>
+          <t xml:space="preserve">2204</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213</t>
+          <t xml:space="preserve">2214</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223</t>
+          <t xml:space="preserve">2224</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2233</t>
+          <t xml:space="preserve">2234</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2243</t>
+          <t xml:space="preserve">2244</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2253</t>
+          <t xml:space="preserve">2254</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263</t>
+          <t xml:space="preserve">2264</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2273</t>
+          <t xml:space="preserve">2274</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2283</t>
+          <t xml:space="preserve">2284</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2293</t>
+          <t xml:space="preserve">2294</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303</t>
+          <t xml:space="preserve">2304</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2313</t>
+          <t xml:space="preserve">2314</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323</t>
+          <t xml:space="preserve">2324</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2333</t>
+          <t xml:space="preserve">2334</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2343</t>
+          <t xml:space="preserve">2344</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2358</t>
+          <t xml:space="preserve">2359</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2373</t>
+          <t xml:space="preserve">2374</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2383</t>
+          <t xml:space="preserve">2384</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393</t>
+          <t xml:space="preserve">2394</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2403</t>
+          <t xml:space="preserve">2404</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2413</t>
+          <t xml:space="preserve">2414</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2423</t>
+          <t xml:space="preserve">2424</t>
         </is>
       </c>
     </row>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2433</t>
+          <t xml:space="preserve">2434</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2443</t>
+          <t xml:space="preserve">2444</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2452</t>
+          <t xml:space="preserve">2453</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2462</t>
+          <t xml:space="preserve">2463</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2472</t>
+          <t xml:space="preserve">2473</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2482</t>
+          <t xml:space="preserve">2483</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492</t>
+          <t xml:space="preserve">2493</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2502</t>
+          <t xml:space="preserve">2503</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2512</t>
+          <t xml:space="preserve">2513</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2522</t>
+          <t xml:space="preserve">2523</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2532</t>
+          <t xml:space="preserve">2533</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2542</t>
+          <t xml:space="preserve">2543</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2551</t>
+          <t xml:space="preserve">2552</t>
         </is>
       </c>
     </row>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2560</t>
+          <t xml:space="preserve">2561</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2569</t>
+          <t xml:space="preserve">2570</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2578</t>
+          <t xml:space="preserve">2579</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2587</t>
+          <t xml:space="preserve">2588</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2596</t>
+          <t xml:space="preserve">2597</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2606</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2614</t>
+          <t xml:space="preserve">2615</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2623</t>
+          <t xml:space="preserve">2624</t>
         </is>
       </c>
     </row>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2632</t>
+          <t xml:space="preserve">2633</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2641</t>
+          <t xml:space="preserve">2642</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8324,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">2651</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2659</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2668</t>
+          <t xml:space="preserve">2669</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8420,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2677</t>
+          <t xml:space="preserve">2678</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8452,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2686</t>
+          <t xml:space="preserve">2687</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2695</t>
+          <t xml:space="preserve">2696</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2704</t>
+          <t xml:space="preserve">2705</t>
         </is>
       </c>
     </row>
@@ -8548,7 +8548,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2713</t>
+          <t xml:space="preserve">2714</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2722</t>
+          <t xml:space="preserve">2723</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2736</t>
+          <t xml:space="preserve">2737</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2744</t>
+          <t xml:space="preserve">2745</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2752</t>
+          <t xml:space="preserve">2753</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2760</t>
+          <t xml:space="preserve">2761</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2768</t>
+          <t xml:space="preserve">2769</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2776</t>
+          <t xml:space="preserve">2777</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2784</t>
+          <t xml:space="preserve">2785</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2792</t>
+          <t xml:space="preserve">2793</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2801</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2808</t>
+          <t xml:space="preserve">2809</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2816</t>
+          <t xml:space="preserve">2817</t>
         </is>
       </c>
     </row>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2824</t>
+          <t xml:space="preserve">2825</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2832</t>
+          <t xml:space="preserve">2833</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2840</t>
+          <t xml:space="preserve">2841</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2848</t>
+          <t xml:space="preserve">2849</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2856</t>
+          <t xml:space="preserve">2857</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2864</t>
+          <t xml:space="preserve">2865</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1524</t>
+          <t xml:space="preserve">1529</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1528</t>
+          <t xml:space="preserve">1533</t>
         </is>
       </c>
     </row>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1532</t>
+          <t xml:space="preserve">1537</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1536</t>
+          <t xml:space="preserve">1541</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544</t>
+          <t xml:space="preserve">1549</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1545</t>
+          <t xml:space="preserve">1550</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1546</t>
+          <t xml:space="preserve">1551</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547</t>
+          <t xml:space="preserve">1552</t>
         </is>
       </c>
     </row>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1548</t>
+          <t xml:space="preserve">1553</t>
         </is>
       </c>
     </row>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1549</t>
+          <t xml:space="preserve">1554</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1550</t>
+          <t xml:space="preserve">1555</t>
         </is>
       </c>
     </row>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551</t>
+          <t xml:space="preserve">1556</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9652,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1552</t>
+          <t xml:space="preserve">1557</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553</t>
+          <t xml:space="preserve">1558</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1554</t>
+          <t xml:space="preserve">1559</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1555</t>
+          <t xml:space="preserve">1560</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556</t>
+          <t xml:space="preserve">1561</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1557</t>
+          <t xml:space="preserve">1562</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1558</t>
+          <t xml:space="preserve">1563</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1559</t>
+          <t xml:space="preserve">1564</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1560</t>
+          <t xml:space="preserve">1565</t>
         </is>
       </c>
     </row>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561</t>
+          <t xml:space="preserve">1566</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1562</t>
+          <t xml:space="preserve">1567</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1563</t>
+          <t xml:space="preserve">1568</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1564</t>
+          <t xml:space="preserve">1569</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1565</t>
+          <t xml:space="preserve">1570</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566</t>
+          <t xml:space="preserve">1571</t>
         </is>
       </c>
     </row>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1567</t>
+          <t xml:space="preserve">1572</t>
         </is>
       </c>
     </row>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1568</t>
+          <t xml:space="preserve">1573</t>
         </is>
       </c>
     </row>
@@ -10281,7 +10281,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1569</t>
+          <t xml:space="preserve">1574</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1570</t>
+          <t xml:space="preserve">1575</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1571</t>
+          <t xml:space="preserve">1576</t>
         </is>
       </c>
     </row>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1572</t>
+          <t xml:space="preserve">1577</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1573</t>
+          <t xml:space="preserve">1578</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1574</t>
+          <t xml:space="preserve">1579</t>
         </is>
       </c>
     </row>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575</t>
+          <t xml:space="preserve">1580</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1576</t>
+          <t xml:space="preserve">1581</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10577,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1577</t>
+          <t xml:space="preserve">1582</t>
         </is>
       </c>
     </row>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1578</t>
+          <t xml:space="preserve">1583</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1579</t>
+          <t xml:space="preserve">1584</t>
         </is>
       </c>
     </row>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580</t>
+          <t xml:space="preserve">1585</t>
         </is>
       </c>
     </row>
@@ -10725,7 +10725,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1581</t>
+          <t xml:space="preserve">1586</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1582</t>
+          <t xml:space="preserve">1587</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1583</t>
+          <t xml:space="preserve">1588</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1584</t>
+          <t xml:space="preserve">1589</t>
         </is>
       </c>
     </row>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1585</t>
+          <t xml:space="preserve">1590</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1586</t>
+          <t xml:space="preserve">1591</t>
         </is>
       </c>
     </row>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1587</t>
+          <t xml:space="preserve">1592</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1588</t>
+          <t xml:space="preserve">1593</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1589</t>
+          <t xml:space="preserve">1594</t>
         </is>
       </c>
     </row>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1590</t>
+          <t xml:space="preserve">1595</t>
         </is>
       </c>
     </row>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1591</t>
+          <t xml:space="preserve">1596</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1592</t>
+          <t xml:space="preserve">1597</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1593</t>
+          <t xml:space="preserve">1598</t>
         </is>
       </c>
     </row>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1594</t>
+          <t xml:space="preserve">1599</t>
         </is>
       </c>
     </row>
@@ -11243,7 +11243,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1595</t>
+          <t xml:space="preserve">1600</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1596</t>
+          <t xml:space="preserve">1601</t>
         </is>
       </c>
     </row>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1597</t>
+          <t xml:space="preserve">1602</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1598</t>
+          <t xml:space="preserve">1603</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1599</t>
+          <t xml:space="preserve">1604</t>
         </is>
       </c>
     </row>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600</t>
+          <t xml:space="preserve">1605</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1601</t>
+          <t xml:space="preserve">1606</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602</t>
+          <t xml:space="preserve">1607</t>
         </is>
       </c>
     </row>
@@ -11539,7 +11539,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603</t>
+          <t xml:space="preserve">1608</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1604</t>
+          <t xml:space="preserve">1609</t>
         </is>
       </c>
     </row>
@@ -11613,7 +11613,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605</t>
+          <t xml:space="preserve">1610</t>
         </is>
       </c>
     </row>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1606</t>
+          <t xml:space="preserve">1611</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1607</t>
+          <t xml:space="preserve">1612</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1608</t>
+          <t xml:space="preserve">1613</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1609</t>
+          <t xml:space="preserve">1614</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610</t>
+          <t xml:space="preserve">1615</t>
         </is>
       </c>
     </row>
@@ -11835,7 +11835,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1611</t>
+          <t xml:space="preserve">1616</t>
         </is>
       </c>
     </row>
@@ -11872,7 +11872,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612</t>
+          <t xml:space="preserve">1617</t>
         </is>
       </c>
     </row>
@@ -11909,7 +11909,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1613</t>
+          <t xml:space="preserve">1618</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614</t>
+          <t xml:space="preserve">1619</t>
         </is>
       </c>
     </row>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615</t>
+          <t xml:space="preserve">1620</t>
         </is>
       </c>
     </row>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616</t>
+          <t xml:space="preserve">1621</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1617</t>
+          <t xml:space="preserve">1622</t>
         </is>
       </c>
     </row>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618</t>
+          <t xml:space="preserve">1623</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619</t>
+          <t xml:space="preserve">1624</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620</t>
+          <t xml:space="preserve">1625</t>
         </is>
       </c>
     </row>
@@ -12205,7 +12205,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1621</t>
+          <t xml:space="preserve">1626</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1622</t>
+          <t xml:space="preserve">1627</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623</t>
+          <t xml:space="preserve">1628</t>
         </is>
       </c>
     </row>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1624</t>
+          <t xml:space="preserve">1629</t>
         </is>
       </c>
     </row>
@@ -12353,7 +12353,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625</t>
+          <t xml:space="preserve">1630</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1626</t>
+          <t xml:space="preserve">1631</t>
         </is>
       </c>
     </row>
@@ -12464,7 +12464,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2020/02/NSF_4-Color_bitmap_Logo-298x300.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/nsf-logo.png</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1635</t>
+          <t xml:space="preserve">1640</t>
         </is>
       </c>
     </row>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">http://www.tri-c.edu/programs/engineering-technology/manufacturing-engineering/3d-digital-design-and-manufacturing-technology/images/america-makes.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/america-makes.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1636</t>
+          <t xml:space="preserve">1641</t>
         </is>
       </c>
     </row>
@@ -12538,7 +12538,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://media.defense.gov/2012/Nov/01/2000100887/-1/-1/0/121101-F-JZ008-240.JPG</t>
+          <t xml:space="preserve">assets/sponsors-partners/air-force-research-laboratory.png</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1637</t>
+          <t xml:space="preserve">1642</t>
         </is>
       </c>
     </row>
@@ -12575,7 +12575,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2017/03/Office_of_Naval_Research_Official_Logo-1q0s65d-300x137.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/office-of-naval-research.png</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1638</t>
+          <t xml:space="preserve">1643</t>
         </is>
       </c>
     </row>
@@ -12612,7 +12612,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2020/06/image-153x300.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/pennsylvania-manufacturing-sponsor.png</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640</t>
+          <t xml:space="preserve">1644</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2017/03/PA-DCED-Logo-RACP-1q5i7zw-300x76.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/pa-dced-logo.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1641</t>
+          <t xml:space="preserve">1645</t>
         </is>
       </c>
     </row>
@@ -12686,7 +12686,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2017/03/nistlogo_centerexcellence-1cjege7-300x143.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/nist-center-of-excellence.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642</t>
+          <t xml:space="preserve">1646</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2025/02/images-300x136.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/defense-manufacturing-sponsor.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644</t>
+          <t xml:space="preserve">1647</t>
         </is>
       </c>
     </row>
@@ -12760,7 +12760,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2025/02/IACMI_logo-300x154.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/iacmi-logo.png</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645</t>
+          <t xml:space="preserve">1648</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors/ascent-flextech.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/ascent-flextech.png</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1646</t>
+          <t xml:space="preserve">1649</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2025/02/darpa-logo-300x163.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/darpa-logo.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647</t>
+          <t xml:space="preserve">1650</t>
         </is>
       </c>
     </row>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">http://www.mmsonline.com/cdn/showrooms/profile/logo/Methods%20email%20logo.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/methods-machine-tools.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1651</t>
+          <t xml:space="preserve">1654</t>
         </is>
       </c>
     </row>
@@ -12908,7 +12908,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2017/03/logo-21lo2vj.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/industrial-collaboration-partner.png</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653</t>
+          <t xml:space="preserve">1655</t>
         </is>
       </c>
     </row>
@@ -12945,7 +12945,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://d2q79iu7y748jz.cloudfront.net/s/_logo/7e176f6b8f69ff34570ace1c3853f668</t>
+          <t xml:space="preserve">assets/sponsors-partners/technical-collaboration-partner.png</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655</t>
+          <t xml:space="preserve">1656</t>
         </is>
       </c>
     </row>
@@ -12982,7 +12982,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2017/03/hcclogo-2c6kfxy.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/hagerstown-community-college.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656</t>
+          <t xml:space="preserve">1657</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2017/03/MastercamBlackRed_RGB-1pobr8g.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/mastercam-logo.png</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657</t>
+          <t xml:space="preserve">1658</t>
         </is>
       </c>
     </row>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263</t>
+          <t xml:space="preserve">1268</t>
         </is>
       </c>
     </row>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285</t>
+          <t xml:space="preserve">1290</t>
         </is>
       </c>
     </row>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288</t>
+          <t xml:space="preserve">1293</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1317</t>
+          <t xml:space="preserve">1322</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1325</t>
+          <t xml:space="preserve">1330</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1333</t>
+          <t xml:space="preserve">1338</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1347</t>
+          <t xml:space="preserve">1352</t>
         </is>
       </c>
     </row>
@@ -13445,7 +13445,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1355</t>
+          <t xml:space="preserve">1360</t>
         </is>
       </c>
     </row>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1363</t>
+          <t xml:space="preserve">1368</t>
         </is>
       </c>
     </row>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1382</t>
+          <t xml:space="preserve">1387</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1386</t>
+          <t xml:space="preserve">1391</t>
         </is>
       </c>
     </row>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1399</t>
+          <t xml:space="preserve">1404</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406</t>
+          <t xml:space="preserve">1411</t>
         </is>
       </c>
     </row>
@@ -13607,7 +13607,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1407</t>
+          <t xml:space="preserve">1412</t>
         </is>
       </c>
     </row>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408</t>
+          <t xml:space="preserve">1413</t>
         </is>
       </c>
     </row>
@@ -13661,7 +13661,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409</t>
+          <t xml:space="preserve">1414</t>
         </is>
       </c>
     </row>
@@ -13688,7 +13688,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1410</t>
+          <t xml:space="preserve">1415</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411</t>
+          <t xml:space="preserve">1416</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412</t>
+          <t xml:space="preserve">1417</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413</t>
+          <t xml:space="preserve">1418</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1414</t>
+          <t xml:space="preserve">1419</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1415</t>
+          <t xml:space="preserve">1420</t>
         </is>
       </c>
     </row>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416</t>
+          <t xml:space="preserve">1421</t>
         </is>
       </c>
     </row>
@@ -13877,7 +13877,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1423</t>
+          <t xml:space="preserve">1428</t>
         </is>
       </c>
     </row>
@@ -13904,7 +13904,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1430</t>
+          <t xml:space="preserve">1435</t>
         </is>
       </c>
     </row>
@@ -13931,7 +13931,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437</t>
+          <t xml:space="preserve">1442</t>
         </is>
       </c>
     </row>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1438</t>
+          <t xml:space="preserve">1443</t>
         </is>
       </c>
     </row>
@@ -13985,7 +13985,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1439</t>
+          <t xml:space="preserve">1444</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440</t>
+          <t xml:space="preserve">1445</t>
         </is>
       </c>
     </row>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1441</t>
+          <t xml:space="preserve">1446</t>
         </is>
       </c>
     </row>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442</t>
+          <t xml:space="preserve">1447</t>
         </is>
       </c>
     </row>
@@ -14093,7 +14093,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1443</t>
+          <t xml:space="preserve">1448</t>
         </is>
       </c>
     </row>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1525</t>
+          <t xml:space="preserve">1530</t>
         </is>
       </c>
     </row>
@@ -14147,7 +14147,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1529</t>
+          <t xml:space="preserve">1534</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1533</t>
+          <t xml:space="preserve">1538</t>
         </is>
       </c>
     </row>
@@ -14201,14 +14201,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1537</t>
+          <t xml:space="preserve">1542</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2020/02/NSF_4-Color_bitmap_Logo-298x300.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/nsf-logo.png</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -14218,7 +14218,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -14228,14 +14228,14 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1635</t>
+          <t xml:space="preserve">1640</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">http://www.tri-c.edu/programs/engineering-technology/manufacturing-engineering/3d-digital-design-and-manufacturing-technology/images/america-makes.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/america-makes.jpg</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -14255,14 +14255,14 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1636</t>
+          <t xml:space="preserve">1641</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://media.defense.gov/2012/Nov/01/2000100887/-1/-1/0/121101-F-JZ008-240.JPG</t>
+          <t xml:space="preserve">assets/sponsors-partners/air-force-research-laboratory.png</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -14272,7 +14272,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -14282,14 +14282,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1637</t>
+          <t xml:space="preserve">1642</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2017/03/Office_of_Naval_Research_Official_Logo-1q0s65d-300x137.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/office-of-naval-research.png</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -14309,14 +14309,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1638</t>
+          <t xml:space="preserve">1643</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2020/06/image-153x300.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/pennsylvania-manufacturing-sponsor.png</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -14336,14 +14336,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640</t>
+          <t xml:space="preserve">1644</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2017/03/PA-DCED-Logo-RACP-1q5i7zw-300x76.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/pa-dced-logo.jpg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -14363,14 +14363,14 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1641</t>
+          <t xml:space="preserve">1645</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2017/03/nistlogo_centerexcellence-1cjege7-300x143.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/nist-center-of-excellence.jpg</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -14390,14 +14390,14 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642</t>
+          <t xml:space="preserve">1646</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2025/02/images-300x136.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/defense-manufacturing-sponsor.jpg</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -14417,14 +14417,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644</t>
+          <t xml:space="preserve">1647</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2025/02/IACMI_logo-300x154.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/iacmi-logo.png</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -14444,14 +14444,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645</t>
+          <t xml:space="preserve">1648</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors/ascent-flextech.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/ascent-flextech.png</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -14471,14 +14471,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1646</t>
+          <t xml:space="preserve">1649</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2025/02/darpa-logo-300x163.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/darpa-logo.jpg</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -14498,14 +14498,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647</t>
+          <t xml:space="preserve">1650</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">http://www.mmsonline.com/cdn/showrooms/profile/logo/Methods%20email%20logo.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/methods-machine-tools.jpg</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -14525,14 +14525,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1651</t>
+          <t xml:space="preserve">1654</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2017/03/logo-21lo2vj.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/industrial-collaboration-partner.png</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -14552,14 +14552,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653</t>
+          <t xml:space="preserve">1655</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://d2q79iu7y748jz.cloudfront.net/s/_logo/7e176f6b8f69ff34570ace1c3853f668</t>
+          <t xml:space="preserve">assets/sponsors-partners/technical-collaboration-partner.png</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -14579,14 +14579,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655</t>
+          <t xml:space="preserve">1656</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2017/03/hcclogo-2c6kfxy.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/hagerstown-community-college.jpg</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -14606,14 +14606,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656</t>
+          <t xml:space="preserve">1657</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2017/03/MastercamBlackRed_RGB-1pobr8g.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/mastercam-logo.png</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657</t>
+          <t xml:space="preserve">1658</t>
         </is>
       </c>
     </row>
@@ -14660,7 +14660,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2887</t>
+          <t xml:space="preserve">2888</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2888</t>
+          <t xml:space="preserve">2889</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889</t>
+          <t xml:space="preserve">2890</t>
         </is>
       </c>
     </row>
@@ -14741,7 +14741,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890</t>
+          <t xml:space="preserve">2891</t>
         </is>
       </c>
     </row>
@@ -14768,7 +14768,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891</t>
+          <t xml:space="preserve">2892</t>
         </is>
       </c>
     </row>
@@ -14795,7 +14795,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2892</t>
+          <t xml:space="preserve">2893</t>
         </is>
       </c>
     </row>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2893</t>
+          <t xml:space="preserve">2894</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2894</t>
+          <t xml:space="preserve">2895</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2895</t>
+          <t xml:space="preserve">2896</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2896</t>
+          <t xml:space="preserve">2897</t>
         </is>
       </c>
     </row>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2897</t>
+          <t xml:space="preserve">2898</t>
         </is>
       </c>
     </row>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898</t>
+          <t xml:space="preserve">2899</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2899</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
     </row>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2901</t>
         </is>
       </c>
     </row>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2901</t>
+          <t xml:space="preserve">2902</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2902</t>
+          <t xml:space="preserve">2903</t>
         </is>
       </c>
     </row>
@@ -15092,7 +15092,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2903</t>
+          <t xml:space="preserve">2904</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2904</t>
+          <t xml:space="preserve">2905</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2905</t>
+          <t xml:space="preserve">2906</t>
         </is>
       </c>
     </row>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2906</t>
+          <t xml:space="preserve">2907</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907</t>
+          <t xml:space="preserve">2908</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2908</t>
+          <t xml:space="preserve">2909</t>
         </is>
       </c>
     </row>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2909</t>
+          <t xml:space="preserve">2910</t>
         </is>
       </c>
     </row>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2910</t>
+          <t xml:space="preserve">2911</t>
         </is>
       </c>
     </row>
@@ -15308,7 +15308,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2964</t>
+          <t xml:space="preserve">2965</t>
         </is>
       </c>
     </row>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262</t>
+          <t xml:space="preserve">1267</t>
         </is>
       </c>
     </row>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270</t>
+          <t xml:space="preserve">1275</t>
         </is>
       </c>
     </row>
@@ -15406,7 +15406,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271</t>
+          <t xml:space="preserve">1276</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272</t>
+          <t xml:space="preserve">1277</t>
         </is>
       </c>
     </row>
@@ -15450,7 +15450,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273</t>
+          <t xml:space="preserve">1278</t>
         </is>
       </c>
     </row>
@@ -15472,7 +15472,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274</t>
+          <t xml:space="preserve">1279</t>
         </is>
       </c>
     </row>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275</t>
+          <t xml:space="preserve">1280</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15516,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276</t>
+          <t xml:space="preserve">1281</t>
         </is>
       </c>
     </row>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277</t>
+          <t xml:space="preserve">1282</t>
         </is>
       </c>
     </row>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1392</t>
+          <t xml:space="preserve">1397</t>
         </is>
       </c>
     </row>
@@ -15582,7 +15582,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1392</t>
+          <t xml:space="preserve">1397</t>
         </is>
       </c>
     </row>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1399</t>
+          <t xml:space="preserve">1404</t>
         </is>
       </c>
     </row>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1399</t>
+          <t xml:space="preserve">1404</t>
         </is>
       </c>
     </row>
@@ -15648,7 +15648,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1399</t>
+          <t xml:space="preserve">1404</t>
         </is>
       </c>
     </row>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406</t>
+          <t xml:space="preserve">1411</t>
         </is>
       </c>
     </row>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406</t>
+          <t xml:space="preserve">1411</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406</t>
+          <t xml:space="preserve">1411</t>
         </is>
       </c>
     </row>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1407</t>
+          <t xml:space="preserve">1412</t>
         </is>
       </c>
     </row>
@@ -15758,7 +15758,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1407</t>
+          <t xml:space="preserve">1412</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15780,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1407</t>
+          <t xml:space="preserve">1412</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408</t>
+          <t xml:space="preserve">1413</t>
         </is>
       </c>
     </row>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408</t>
+          <t xml:space="preserve">1413</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15846,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408</t>
+          <t xml:space="preserve">1413</t>
         </is>
       </c>
     </row>
@@ -15868,7 +15868,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409</t>
+          <t xml:space="preserve">1414</t>
         </is>
       </c>
     </row>
@@ -15890,7 +15890,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409</t>
+          <t xml:space="preserve">1414</t>
         </is>
       </c>
     </row>
@@ -15912,7 +15912,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409</t>
+          <t xml:space="preserve">1414</t>
         </is>
       </c>
     </row>
@@ -15934,7 +15934,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1410</t>
+          <t xml:space="preserve">1415</t>
         </is>
       </c>
     </row>
@@ -15956,7 +15956,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1410</t>
+          <t xml:space="preserve">1415</t>
         </is>
       </c>
     </row>
@@ -15978,7 +15978,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411</t>
+          <t xml:space="preserve">1416</t>
         </is>
       </c>
     </row>
@@ -16000,7 +16000,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411</t>
+          <t xml:space="preserve">1416</t>
         </is>
       </c>
     </row>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412</t>
+          <t xml:space="preserve">1417</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412</t>
+          <t xml:space="preserve">1417</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413</t>
+          <t xml:space="preserve">1418</t>
         </is>
       </c>
     </row>
@@ -16088,7 +16088,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1414</t>
+          <t xml:space="preserve">1419</t>
         </is>
       </c>
     </row>
@@ -16110,7 +16110,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1414</t>
+          <t xml:space="preserve">1419</t>
         </is>
       </c>
     </row>
@@ -16132,7 +16132,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1414</t>
+          <t xml:space="preserve">1419</t>
         </is>
       </c>
     </row>
@@ -16154,7 +16154,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1415</t>
+          <t xml:space="preserve">1420</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1415</t>
+          <t xml:space="preserve">1420</t>
         </is>
       </c>
     </row>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416</t>
+          <t xml:space="preserve">1421</t>
         </is>
       </c>
     </row>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416</t>
+          <t xml:space="preserve">1421</t>
         </is>
       </c>
     </row>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1430</t>
+          <t xml:space="preserve">1435</t>
         </is>
       </c>
     </row>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1430</t>
+          <t xml:space="preserve">1435</t>
         </is>
       </c>
     </row>
@@ -16286,7 +16286,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437</t>
+          <t xml:space="preserve">1442</t>
         </is>
       </c>
     </row>
@@ -16308,7 +16308,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437</t>
+          <t xml:space="preserve">1442</t>
         </is>
       </c>
     </row>
@@ -16330,7 +16330,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1438</t>
+          <t xml:space="preserve">1443</t>
         </is>
       </c>
     </row>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1438</t>
+          <t xml:space="preserve">1443</t>
         </is>
       </c>
     </row>
@@ -16374,7 +16374,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1439</t>
+          <t xml:space="preserve">1444</t>
         </is>
       </c>
     </row>
@@ -16396,7 +16396,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440</t>
+          <t xml:space="preserve">1445</t>
         </is>
       </c>
     </row>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440</t>
+          <t xml:space="preserve">1445</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1441</t>
+          <t xml:space="preserve">1446</t>
         </is>
       </c>
     </row>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1441</t>
+          <t xml:space="preserve">1446</t>
         </is>
       </c>
     </row>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442</t>
+          <t xml:space="preserve">1447</t>
         </is>
       </c>
     </row>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442</t>
+          <t xml:space="preserve">1447</t>
         </is>
       </c>
     </row>
@@ -16528,7 +16528,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1443</t>
+          <t xml:space="preserve">1448</t>
         </is>
       </c>
     </row>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1443</t>
+          <t xml:space="preserve">1448</t>
         </is>
       </c>
     </row>
@@ -16572,7 +16572,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1526</t>
+          <t xml:space="preserve">1531</t>
         </is>
       </c>
     </row>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544</t>
+          <t xml:space="preserve">1549</t>
         </is>
       </c>
     </row>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1545</t>
+          <t xml:space="preserve">1550</t>
         </is>
       </c>
     </row>
@@ -16638,7 +16638,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1548</t>
+          <t xml:space="preserve">1553</t>
         </is>
       </c>
     </row>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1550</t>
+          <t xml:space="preserve">1555</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551</t>
+          <t xml:space="preserve">1556</t>
         </is>
       </c>
     </row>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1552</t>
+          <t xml:space="preserve">1557</t>
         </is>
       </c>
     </row>
@@ -16726,7 +16726,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1554</t>
+          <t xml:space="preserve">1559</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620</t>
+          <t xml:space="preserve">1625</t>
         </is>
       </c>
     </row>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1624</t>
+          <t xml:space="preserve">1629</t>
         </is>
       </c>
     </row>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625</t>
+          <t xml:space="preserve">1630</t>
         </is>
       </c>
     </row>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1626</t>
+          <t xml:space="preserve">1631</t>
         </is>
       </c>
     </row>
@@ -16836,7 +16836,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1635</t>
+          <t xml:space="preserve">1640</t>
         </is>
       </c>
     </row>
@@ -16858,7 +16858,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1636</t>
+          <t xml:space="preserve">1641</t>
         </is>
       </c>
     </row>
@@ -16880,7 +16880,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1637</t>
+          <t xml:space="preserve">1642</t>
         </is>
       </c>
     </row>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1638</t>
+          <t xml:space="preserve">1643</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640</t>
+          <t xml:space="preserve">1644</t>
         </is>
       </c>
     </row>
@@ -16946,7 +16946,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1641</t>
+          <t xml:space="preserve">1645</t>
         </is>
       </c>
     </row>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642</t>
+          <t xml:space="preserve">1646</t>
         </is>
       </c>
     </row>
@@ -16990,7 +16990,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644</t>
+          <t xml:space="preserve">1647</t>
         </is>
       </c>
     </row>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645</t>
+          <t xml:space="preserve">1648</t>
         </is>
       </c>
     </row>
@@ -17034,7 +17034,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1646</t>
+          <t xml:space="preserve">1649</t>
         </is>
       </c>
     </row>
@@ -17056,7 +17056,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647</t>
+          <t xml:space="preserve">1650</t>
         </is>
       </c>
     </row>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1651</t>
+          <t xml:space="preserve">1654</t>
         </is>
       </c>
     </row>
@@ -17100,7 +17100,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653</t>
+          <t xml:space="preserve">1655</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655</t>
+          <t xml:space="preserve">1656</t>
         </is>
       </c>
     </row>
@@ -17144,7 +17144,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656</t>
+          <t xml:space="preserve">1657</t>
         </is>
       </c>
     </row>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657</t>
+          <t xml:space="preserve">1658</t>
         </is>
       </c>
     </row>
@@ -17188,7 +17188,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680</t>
+          <t xml:space="preserve">1681</t>
         </is>
       </c>
     </row>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690</t>
+          <t xml:space="preserve">1691</t>
         </is>
       </c>
     </row>
@@ -17232,7 +17232,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1700</t>
+          <t xml:space="preserve">1701</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1715</t>
+          <t xml:space="preserve">1716</t>
         </is>
       </c>
     </row>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1725</t>
+          <t xml:space="preserve">1726</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1735</t>
+          <t xml:space="preserve">1736</t>
         </is>
       </c>
     </row>
@@ -17320,7 +17320,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1745</t>
+          <t xml:space="preserve">1746</t>
         </is>
       </c>
     </row>
@@ -17342,7 +17342,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1755</t>
+          <t xml:space="preserve">1756</t>
         </is>
       </c>
     </row>
@@ -17364,7 +17364,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1765</t>
+          <t xml:space="preserve">1766</t>
         </is>
       </c>
     </row>
@@ -17386,7 +17386,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1775</t>
+          <t xml:space="preserve">1776</t>
         </is>
       </c>
     </row>
@@ -17408,7 +17408,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1785</t>
+          <t xml:space="preserve">1786</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1795</t>
+          <t xml:space="preserve">1796</t>
         </is>
       </c>
     </row>
@@ -17452,7 +17452,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805</t>
+          <t xml:space="preserve">1806</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815</t>
+          <t xml:space="preserve">1816</t>
         </is>
       </c>
     </row>
@@ -17496,7 +17496,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825</t>
+          <t xml:space="preserve">1826</t>
         </is>
       </c>
     </row>
@@ -17518,7 +17518,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1835</t>
+          <t xml:space="preserve">1836</t>
         </is>
       </c>
     </row>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1845</t>
+          <t xml:space="preserve">1846</t>
         </is>
       </c>
     </row>
@@ -17562,7 +17562,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855</t>
+          <t xml:space="preserve">1856</t>
         </is>
       </c>
     </row>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870</t>
+          <t xml:space="preserve">1871</t>
         </is>
       </c>
     </row>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880</t>
+          <t xml:space="preserve">1881</t>
         </is>
       </c>
     </row>
@@ -17628,7 +17628,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890</t>
+          <t xml:space="preserve">1891</t>
         </is>
       </c>
     </row>
@@ -17650,7 +17650,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900</t>
+          <t xml:space="preserve">1901</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910</t>
+          <t xml:space="preserve">1911</t>
         </is>
       </c>
     </row>
@@ -17694,7 +17694,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920</t>
+          <t xml:space="preserve">1921</t>
         </is>
       </c>
     </row>
@@ -17716,7 +17716,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930</t>
+          <t xml:space="preserve">1931</t>
         </is>
       </c>
     </row>
@@ -17738,7 +17738,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940</t>
+          <t xml:space="preserve">1941</t>
         </is>
       </c>
     </row>
@@ -17760,7 +17760,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950</t>
+          <t xml:space="preserve">1951</t>
         </is>
       </c>
     </row>
@@ -17782,7 +17782,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965</t>
+          <t xml:space="preserve">1966</t>
         </is>
       </c>
     </row>
@@ -17804,7 +17804,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1975</t>
+          <t xml:space="preserve">1976</t>
         </is>
       </c>
     </row>
@@ -17826,7 +17826,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1985</t>
+          <t xml:space="preserve">1986</t>
         </is>
       </c>
     </row>
@@ -17848,7 +17848,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1995</t>
+          <t xml:space="preserve">1996</t>
         </is>
       </c>
     </row>
@@ -17870,7 +17870,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005</t>
+          <t xml:space="preserve">2006</t>
         </is>
       </c>
     </row>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2015</t>
+          <t xml:space="preserve">2016</t>
         </is>
       </c>
     </row>
@@ -17914,7 +17914,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025</t>
+          <t xml:space="preserve">2026</t>
         </is>
       </c>
     </row>
@@ -17936,7 +17936,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035</t>
+          <t xml:space="preserve">2036</t>
         </is>
       </c>
     </row>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2045</t>
+          <t xml:space="preserve">2046</t>
         </is>
       </c>
     </row>
@@ -17980,7 +17980,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2055</t>
+          <t xml:space="preserve">2056</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2065</t>
+          <t xml:space="preserve">2066</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18024,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2075</t>
+          <t xml:space="preserve">2076</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085</t>
+          <t xml:space="preserve">2086</t>
         </is>
       </c>
     </row>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2100</t>
+          <t xml:space="preserve">2101</t>
         </is>
       </c>
     </row>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110</t>
+          <t xml:space="preserve">2111</t>
         </is>
       </c>
     </row>
@@ -18112,7 +18112,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120</t>
+          <t xml:space="preserve">2121</t>
         </is>
       </c>
     </row>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2130</t>
+          <t xml:space="preserve">2131</t>
         </is>
       </c>
     </row>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2140</t>
+          <t xml:space="preserve">2141</t>
         </is>
       </c>
     </row>
@@ -18178,7 +18178,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2150</t>
+          <t xml:space="preserve">2151</t>
         </is>
       </c>
     </row>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160</t>
+          <t xml:space="preserve">2161</t>
         </is>
       </c>
     </row>
@@ -18222,7 +18222,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170</t>
+          <t xml:space="preserve">2171</t>
         </is>
       </c>
     </row>
@@ -18244,7 +18244,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180</t>
+          <t xml:space="preserve">2181</t>
         </is>
       </c>
     </row>
@@ -18266,7 +18266,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190</t>
+          <t xml:space="preserve">2191</t>
         </is>
       </c>
     </row>
@@ -18288,7 +18288,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2200</t>
+          <t xml:space="preserve">2201</t>
         </is>
       </c>
     </row>
@@ -18310,7 +18310,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2210</t>
+          <t xml:space="preserve">2211</t>
         </is>
       </c>
     </row>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220</t>
+          <t xml:space="preserve">2221</t>
         </is>
       </c>
     </row>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2230</t>
+          <t xml:space="preserve">2231</t>
         </is>
       </c>
     </row>
@@ -18376,7 +18376,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2240</t>
+          <t xml:space="preserve">2241</t>
         </is>
       </c>
     </row>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2250</t>
+          <t xml:space="preserve">2251</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2260</t>
+          <t xml:space="preserve">2261</t>
         </is>
       </c>
     </row>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270</t>
+          <t xml:space="preserve">2271</t>
         </is>
       </c>
     </row>
@@ -18464,7 +18464,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2280</t>
+          <t xml:space="preserve">2281</t>
         </is>
       </c>
     </row>
@@ -18486,7 +18486,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290</t>
+          <t xml:space="preserve">2291</t>
         </is>
       </c>
     </row>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2300</t>
+          <t xml:space="preserve">2301</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2310</t>
+          <t xml:space="preserve">2311</t>
         </is>
       </c>
     </row>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2320</t>
+          <t xml:space="preserve">2321</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2330</t>
+          <t xml:space="preserve">2331</t>
         </is>
       </c>
     </row>
@@ -18596,7 +18596,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2340</t>
+          <t xml:space="preserve">2341</t>
         </is>
       </c>
     </row>
@@ -18618,7 +18618,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2350</t>
+          <t xml:space="preserve">2351</t>
         </is>
       </c>
     </row>
@@ -18640,7 +18640,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2365</t>
+          <t xml:space="preserve">2366</t>
         </is>
       </c>
     </row>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380</t>
+          <t xml:space="preserve">2381</t>
         </is>
       </c>
     </row>
@@ -18684,7 +18684,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390</t>
+          <t xml:space="preserve">2391</t>
         </is>
       </c>
     </row>
@@ -18706,7 +18706,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400</t>
+          <t xml:space="preserve">2401</t>
         </is>
       </c>
     </row>
@@ -18728,7 +18728,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410</t>
+          <t xml:space="preserve">2411</t>
         </is>
       </c>
     </row>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2420</t>
+          <t xml:space="preserve">2421</t>
         </is>
       </c>
     </row>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2430</t>
+          <t xml:space="preserve">2431</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2440</t>
+          <t xml:space="preserve">2441</t>
         </is>
       </c>
     </row>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2459</t>
+          <t xml:space="preserve">2460</t>
         </is>
       </c>
     </row>
@@ -18838,7 +18838,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2469</t>
+          <t xml:space="preserve">2470</t>
         </is>
       </c>
     </row>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479</t>
+          <t xml:space="preserve">2480</t>
         </is>
       </c>
     </row>
@@ -18882,7 +18882,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2489</t>
+          <t xml:space="preserve">2490</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499</t>
+          <t xml:space="preserve">2500</t>
         </is>
       </c>
     </row>
@@ -18926,7 +18926,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2509</t>
+          <t xml:space="preserve">2510</t>
         </is>
       </c>
     </row>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2519</t>
+          <t xml:space="preserve">2520</t>
         </is>
       </c>
     </row>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2529</t>
+          <t xml:space="preserve">2530</t>
         </is>
       </c>
     </row>
@@ -18992,7 +18992,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539</t>
+          <t xml:space="preserve">2540</t>
         </is>
       </c>
     </row>
@@ -19014,7 +19014,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2991</t>
+          <t xml:space="preserve">2992</t>
         </is>
       </c>
     </row>
@@ -19036,7 +19036,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2992</t>
+          <t xml:space="preserve">2993</t>
         </is>
       </c>
     </row>
@@ -19058,7 +19058,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2993</t>
+          <t xml:space="preserve">2994</t>
         </is>
       </c>
     </row>
@@ -19080,7 +19080,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2994</t>
+          <t xml:space="preserve">2995</t>
         </is>
       </c>
     </row>
@@ -19102,7 +19102,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2995</t>
+          <t xml:space="preserve">2996</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2996</t>
+          <t xml:space="preserve">2997</t>
         </is>
       </c>
     </row>
@@ -19146,7 +19146,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2997</t>
+          <t xml:space="preserve">2998</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2998</t>
+          <t xml:space="preserve">2999</t>
         </is>
       </c>
     </row>

--- a/SHAPE-Lab-Website-Content.xlsx
+++ b/SHAPE-Lab-Website-Content.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310</t>
+          <t xml:space="preserve">1129</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310</t>
+          <t xml:space="preserve">1129</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1380</t>
+          <t xml:space="preserve">1199</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1523</t>
+          <t xml:space="preserve">1346</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1636</t>
+          <t xml:space="preserve">1459</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1636</t>
+          <t xml:space="preserve">1459</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1663</t>
+          <t xml:space="preserve">1486</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1663</t>
+          <t xml:space="preserve">1486</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2642</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2642</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2921</t>
+          <t xml:space="preserve">2683</t>
         </is>
       </c>
     </row>
@@ -1009,81 +1009,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2921</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">visitors</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Section Title</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Where the world tunes in from.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2942</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">visitors</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Section Lede</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A privacy-preserving snapshot of visitor locations. GitHub Pages displays fallback totals unless an external analytics feed is connected.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2942</t>
+          <t xml:space="preserve">2683</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1048,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\1000009313-fd20a745478509a4.jpg</t>
+          <t xml:space="preserve">shapelab_photos\shapelab_photos\20250625_125103-1024x768.jpg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1132,7 +1058,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198393</t>
+          <t xml:space="preserve">95351</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1144,7 +1070,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\1575779114043-300x300.jpg</t>
+          <t xml:space="preserve">shapelab_photos\shapelab_photos\250096-psn-tpms_blueorange-300x225.jpg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1154,7 +1080,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20506</t>
+          <t xml:space="preserve">12462</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1166,7 +1092,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\1670433046839-300x300.jpg</t>
+          <t xml:space="preserve">shapelab_photos\shapelab_photos\Additive_Manufacturing-G.Manogharan.jpg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1176,7 +1102,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">13655</t>
+          <t xml:space="preserve">37358</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1188,7 +1114,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\1740781076730-300x300.jpg</t>
+          <t xml:space="preserve">shapelab_photos\shapelab_photos\daghir-joseph-240x300.jpg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1198,7 +1124,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">17285</t>
+          <t xml:space="preserve">11904</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1210,29 +1136,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\20191221_1814591-e1587059674952.jpg</t>
+          <t xml:space="preserve">shapelab_photos\shapelab_photos\Group photo - Shape Lab.jpeg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">jpg</t>
+          <t xml:space="preserve">jpeg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">166566</t>
+          <t xml:space="preserve">6138195</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
+          <t xml:space="preserve">2026-05-22 12:14:43</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\20250625_125103-1024x768.jpg</t>
+          <t xml:space="preserve">shapelab_photos\shapelab_photos\IMG_5766.jpg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1242,7 +1168,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">95351</t>
+          <t xml:space="preserve">481041</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1254,17 +1180,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\20251115_142725-300x225.jpg</t>
+          <t xml:space="preserve">shapelab_photos\shapelab_photos\penn-state-news-lg1.png</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">jpg</t>
+          <t xml:space="preserve">png</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">18063</t>
+          <t xml:space="preserve">358336</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1276,7 +1202,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\250096-psn-tpms_blueorange-300x225.jpg</t>
+          <t xml:space="preserve">shapelab_photos\shapelab_photos\SHAPE-Lab-2018.jpg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1286,7 +1212,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">12462</t>
+          <t xml:space="preserve">157665</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1298,17 +1224,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\5f7aab06-.jpg</t>
+          <t xml:space="preserve">shapelab_photos\shapelab_photos\trans-logo.png</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">jpg</t>
+          <t xml:space="preserve">png</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">248832</t>
+          <t xml:space="preserve">6927</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1320,1142 +1246,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\78A8608-211x300.jpg</t>
+          <t xml:space="preserve">shapelab_photos\shapelab_photos_manifest.txt</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">jpg</t>
+          <t xml:space="preserve">txt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">11077</t>
+          <t xml:space="preserve">2444</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Additive_Manufacturing-G.Manogharan.jpg</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37358</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\ashish-ad60a0810bc29cdc-240x300.jpg</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10798</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\BestSophmorePhoto-e1761688087220-236x300.jpg</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10031</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\bryan-300x300.jpg</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13657</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\cropped-PSU-Shape-1024x211.png</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">png</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33564</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\daghir-joseph-240x300.jpg</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11904</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\daniel2.jpg</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153770</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\DSC_0136-e1665517373923-265x300.jpg</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10280</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\eric-aaa2219df26cd818.png</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">png</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29409</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Group photo - Shape Lab.jpeg</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpeg</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6138195</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-22 12:14:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\guha.jpg</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">301848</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Hanlon-Headshot-c8f1b3c9a0932a06-274x300.jpg</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10087</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\headshot-e1761687933679-255x300.jpg</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9305</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Headshot-e1775499920484-236x300.png</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">png</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37808</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Image-from-iOS-1.jpg</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">747545</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\IMG_0063-300x225.jpg</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18494</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\IMG_1473-225x300.jpg</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12532</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\IMG_20160522_193907_1463971177473.jpg</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182346</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\IMG_2276.jpg</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88436</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\IMG_3044.jpg</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">807334</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\IMG_3693-2.jpg</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97338</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\IMG_4077.jpg</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">363384</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\IMG_4585-e1668446043331-202x300.jpg</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13727</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\IMG_4917-1-300x225.jpg</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14839</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\IMG_5766.jpg</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">481041</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\img_6277_52048265114_o.jpg</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">469000</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\IMG_70541-225x300.jpg</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17627</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\IMG_7093.jpg</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">329080</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\james_sprague.jpg</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27750</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-22 12:14:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Julian-Kim-241x300.jpg</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21014</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Kazi-4x5-1-240x300.jpg</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9088</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\LinkedIn-1-200x300.jpg</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9834</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\luis-rod-300x247.jpg</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10119</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Oreoluwa-Adegbite-Headshot-240x300.jpg</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9085</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Paula-1024x768.jpg</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80472</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\penn-state-news-lg1.png</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">png</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">358336</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Picture1-300x300.png</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">png</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51317</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Professional_Headshot_Linkedin-240x300.png</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">png</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39230</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Resized_20220430_170127003.jpeg</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpeg</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">323617</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Santosh_Graduation.jpg</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283900</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Screen-Shot-2021-09-28-at-8.08.44-AM-240x300.png</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">png</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33004</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\SHAPE-Lab-2018.jpg</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157665</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\SHAPE-LAB-2019.jpg</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">538337</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\shape-parallax-background.png</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">png</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1540431</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\springawardcollage_02-300x225.jpg</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27538</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Taiki-Headshot-266x300.jpg</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21222</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\thumbnail_IMG_5714-245x300.jpg</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17682</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\trans-logo.png</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">png</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6927</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Willem.jpg</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56823</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos\Xi_graduation.jpg</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jpg</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65758</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos\shapelab_photos_manifest.txt</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">txt</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2444</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-20 20:36:14</t>
         </is>
@@ -2541,7 +1345,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321</t>
+          <t xml:space="preserve">1140</t>
         </is>
       </c>
     </row>
@@ -2578,7 +1382,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329</t>
+          <t xml:space="preserve">1148</t>
         </is>
       </c>
     </row>
@@ -2615,7 +1419,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1337</t>
+          <t xml:space="preserve">1156</t>
         </is>
       </c>
     </row>
@@ -2652,7 +1456,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1351</t>
+          <t xml:space="preserve">1170</t>
         </is>
       </c>
     </row>
@@ -2689,7 +1493,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1359</t>
+          <t xml:space="preserve">1178</t>
         </is>
       </c>
     </row>
@@ -2726,7 +1530,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1367</t>
+          <t xml:space="preserve">1186</t>
         </is>
       </c>
     </row>
@@ -3261,7 +2065,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Engineer</t>
+          <t xml:space="preserve">Research Engineers</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3710,12 +2514,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sagar Jalui</t>
+          <t xml:space="preserve">Rose Torielli</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ph.D., Mechanical Engineering, 2024</t>
+          <t xml:space="preserve">Ph.D., Industrial &amp; Manufacturing Engineering, 2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3725,7 +2529,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">AM-driven design innovation: DfAM constraints in adjoint shape optimization for gas turbine applications</t>
+          <t xml:space="preserve">Using Lean Methodologies for Economically and Environmentally Sustainable Foundries</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3747,7 +2551,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankit Saxena</t>
+          <t xml:space="preserve">Sagar Jalui</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3762,7 +2566,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Systematic design of pressure-actuated adaptive structural cells enabling adaptive mechanical properties in mechanical structures</t>
+          <t xml:space="preserve">AM-driven design innovation: DfAM constraints in adjoint shape optimization for gas turbine applications</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3784,12 +2588,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philip King</t>
+          <t xml:space="preserve">Ankit Saxena</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ph.D., Mechanical Engineering, 2023</t>
+          <t xml:space="preserve">Ph.D., Mechanical Engineering, 2024</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3799,7 +2603,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bridging the oldest and newest manufacturing technologies: Additive Manufacturing, Metal Casting, and Internet of Things.</t>
+          <t xml:space="preserve">Systematic design of pressure-actuated adaptive structural cells enabling adaptive mechanical properties in mechanical structures</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3821,12 +2625,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foxian Fan</t>
+          <t xml:space="preserve">Philip King</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ph.D., Industrial &amp; Manufacturing Engineering, 2023</t>
+          <t xml:space="preserve">Ph.D., Mechanical Engineering, 2023</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3836,7 +2640,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evolution of Additive Manufacturing surface morphology during Centrifugal Disc Finishing.</t>
+          <t xml:space="preserve">Bridging the oldest and newest manufacturing technologies: Additive Manufacturing, Metal Casting, and Internet of Things.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3858,12 +2662,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Md Moinuddin Shuvo</t>
+          <t xml:space="preserve">Foxian Fan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ph.D., Mechanical Engineering, 2023</t>
+          <t xml:space="preserve">Ph.D., Industrial &amp; Manufacturing Engineering, 2023</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3873,7 +2677,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Improving sustainability of Sand-Casting Processes via novel 3D Mold Designs.</t>
+          <t xml:space="preserve">Evolution of Additive Manufacturing surface morphology during Centrifugal Disc Finishing.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3895,12 +2699,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xi Gong</t>
+          <t xml:space="preserve">Md Moinuddin Shuvo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ph.D., Mechanical Engineering, 2020</t>
+          <t xml:space="preserve">Ph.D., Mechanical Engineering, 2023</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3910,7 +2714,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machining Behavior and Material Properties in Additive Manufacturing of TI-6AL-4V Parts</t>
+          <t xml:space="preserve">Improving sustainability of Sand-Casting Processes via novel 3D Mold Designs.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3932,7 +2736,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maryam Tilton</t>
+          <t xml:space="preserve">Xi Gong</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3947,7 +2751,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-Objective Design and Characterization of Orthopaedic Implants and Meta-Biomaterials Fabricated via Additive Manufacturing</t>
+          <t xml:space="preserve">Machining Behavior and Material Properties in Additive Manufacturing of TI-6AL-4V Parts</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3964,17 +2768,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alumni - Masters</t>
+          <t xml:space="preserve">Alumni - Ph.D.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaitlyn Hartman</t>
+          <t xml:space="preserve">Maryam Tilton</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">M.S. Mechanical Engineering, 2025</t>
+          <t xml:space="preserve">Ph.D., Mechanical Engineering, 2020</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3984,7 +2788,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Functionally Graded TPMS Lattice Structures Optimized to Improve Mechanical Strength</t>
+          <t xml:space="preserve">Multi-Objective Design and Characterization of Orthopaedic Implants and Meta-Biomaterials Fabricated via Additive Manufacturing</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4006,12 +2810,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mychal Taylor</t>
+          <t xml:space="preserve">Kaitlyn Hartman</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">M.S. Mechanical Engineering, 2024</t>
+          <t xml:space="preserve">M.S. Mechanical Engineering, 2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4021,7 +2825,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power cell packaging using a structural electronics approach</t>
+          <t xml:space="preserve">Functionally Graded TPMS Lattice Structures Optimized to Improve Mechanical Strength</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4043,7 +2847,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buket Yilmaz</t>
+          <t xml:space="preserve">Mychal Taylor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4058,7 +2862,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">A review of the interface design in multi-material laser powder bed fusion of metals</t>
+          <t xml:space="preserve">Power cell packaging using a structural electronics approach</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4080,7 +2884,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Williams</t>
+          <t xml:space="preserve">Buket Yilmaz</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4095,7 +2899,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-axis routing of syringe deposited conductive traces over topology-optimized multi-functional structures</t>
+          <t xml:space="preserve">A review of the interface design in multi-material laser powder bed fusion of metals</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4117,7 +2921,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serah Hatch</t>
+          <t xml:space="preserve">Matthew Williams</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4132,7 +2936,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">A microstructure based machine learning model to predict mechanical properties of LPBF-manufactured 15-5PH stainless steel.</t>
+          <t xml:space="preserve">Multi-axis routing of syringe deposited conductive traces over topology-optimized multi-functional structures</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4154,7 +2958,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carson Vath</t>
+          <t xml:space="preserve">Serah Hatch</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4169,7 +2973,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Development and testing of novel multi-material additive manufacturing systems for embedding wire electronic.</t>
+          <t xml:space="preserve">A microstructure based machine learning model to predict mechanical properties of LPBF-manufactured 15-5PH stainless steel.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4191,12 +2995,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandy Karam</t>
+          <t xml:space="preserve">Carson Vath</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">M.S. Mechanical Engineering, 2023</t>
+          <t xml:space="preserve">M.S. Mechanical Engineering, 2024</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4206,7 +3010,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Additive Manufacturing of patient-specific high-fidelity and thickness-controlled cerebral aneurysm geometries</t>
+          <t xml:space="preserve">Development and testing of novel multi-material additive manufacturing systems for embedding wire electronic.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4228,7 +3032,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willem Groeneveld-Meijer</t>
+          <t xml:space="preserve">Sandy Karam</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4243,7 +3047,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Does Finer Powder get deposited first in Powder Bed? A Comparative Study using Simulation and Experimental Techniques.</t>
+          <t xml:space="preserve">Additive Manufacturing of patient-specific high-fidelity and thickness-controlled cerebral aneurysm geometries</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4265,12 +3069,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryan Stebbins</t>
+          <t xml:space="preserve">Willem Groeneveld-Meijer</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">M.S. Mechanical Engineering, 2022</t>
+          <t xml:space="preserve">M.S. Mechanical Engineering, 2023</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4280,7 +3084,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Novel Runner Extension Designs via 3D Sand-printing to Improve Casting Performance</t>
+          <t xml:space="preserve">Does Finer Powder get deposited first in Powder Bed? A Comparative Study using Simulation and Experimental Techniques.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4302,12 +3106,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paula Clares</t>
+          <t xml:space="preserve">Ryan Stebbins</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">M.S. Additive Manufacturing &amp; Design, 2022</t>
+          <t xml:space="preserve">M.S. Mechanical Engineering, 2022</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4317,7 +3121,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fundamental Understanding into Bimodal Powder Size Distributions in Binder Jetting Additive Manufacturing Process</t>
+          <t xml:space="preserve">Novel Runner Extension Designs via 3D Sand-printing to Improve Casting Performance</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4339,12 +3143,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Jacobs</t>
+          <t xml:space="preserve">Paula Clares</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">M.S. Additive Manufacturing &amp; Design, 2021</t>
+          <t xml:space="preserve">M.S. Additive Manufacturing &amp; Design, 2022</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4354,7 +3158,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Influence of Anti-Counterfeiting Taggants on the Tensile Properties of STEP Additively Manufactured Polymer</t>
+          <t xml:space="preserve">Fundamental Understanding into Bimodal Powder Size Distributions in Binder Jetting Additive Manufacturing Process</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4376,12 +3180,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicholas Soares</t>
+          <t xml:space="preserve">Erik Jacobs</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">M.S. Mechanical Engineering, 2021</t>
+          <t xml:space="preserve">M.S. Additive Manufacturing &amp; Design, 2021</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4391,7 +3195,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incorporating Novel Sprue Design and Additive Manufacturing Techniques to Improve Nickel Aluminum Bronze Castings</t>
+          <t xml:space="preserve">Influence of Anti-Counterfeiting Taggants on the Tensile Properties of STEP Additively Manufactured Polymer</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4413,12 +3217,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Martinez</t>
+          <t xml:space="preserve">Nicholas Soares</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">M.S. Additive Manufacturing, 2019</t>
+          <t xml:space="preserve">M.S. Mechanical Engineering, 2021</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4428,7 +3232,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indirect Hybrid Manufacturing - Integrating 3D Sand-Printing for Metal Casting</t>
+          <t xml:space="preserve">Incorporating Novel Sprue Design and Additive Manufacturing Techniques to Improve Nickel Aluminum Bronze Castings</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4450,12 +3254,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casey Bate</t>
+          <t xml:space="preserve">Daniel Martinez</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">M.S. Mechanical Engineering, 2019</t>
+          <t xml:space="preserve">M.S. Additive Manufacturing, 2019</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4465,7 +3269,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fundamental Study on 3D Sand-Printed Molds: Metal Flow and Thermal Properties</t>
+          <t xml:space="preserve">Indirect Hybrid Manufacturing - Integrating 3D Sand-Printing for Metal Casting</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4487,7 +3291,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gregory Bicknell</t>
+          <t xml:space="preserve">Casey Bate</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4502,7 +3306,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical Discharge Machining Process Design for Post-Processing Stainless Steel 316L Additively Manufactured Parts</t>
+          <t xml:space="preserve">Fundamental Study on 3D Sand-Printed Molds: Metal Flow and Thermal Properties</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4524,12 +3328,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santosh Reddy Sama</t>
+          <t xml:space="preserve">Gregory Bicknell</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">M.S. Mechanical Engineering, 2018</t>
+          <t xml:space="preserve">M.S. Mechanical Engineering, 2019</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4539,7 +3343,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Investigation into Non-Conventional Mold Design Using 3D Sand-Printing in Castings</t>
+          <t xml:space="preserve">Electrical Discharge Machining Process Design for Post-Processing Stainless Steel 316L Additively Manufactured Parts</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4561,12 +3365,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jiayi Wang</t>
+          <t xml:space="preserve">Santosh Reddy Sama</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">M.S. Engineering Design, 2017</t>
+          <t xml:space="preserve">M.S. Mechanical Engineering, 2018</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4576,7 +3380,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part Design and Topology Optimization for Rapid Sand and Investment Casting</t>
+          <t xml:space="preserve">Investigation into Non-Conventional Mold Design Using 3D Sand-Printing in Castings</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4593,17 +3397,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alumni - Undergraduate</t>
+          <t xml:space="preserve">Alumni - Masters</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Borst, Visiting student from Clarkson University</t>
+          <t xml:space="preserve">Jiayi Wang</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Mechanical Engineering, 2026</t>
+          <t xml:space="preserve">M.S. Engineering Design, 2017</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4613,7 +3417,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Part Design and Topology Optimization for Rapid Sand and Investment Casting</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4635,12 +3439,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joseph Daghir</t>
+          <t xml:space="preserve">Julian Kim</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Mechanical Engineering, 2025</t>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4672,12 +3476,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Molnar</t>
+          <t xml:space="preserve">Paige Cole</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Mechanical Engineering, 2024</t>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4709,12 +3513,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avah Cherry, Visiting student from University of Tennessee</t>
+          <t xml:space="preserve">Mackenzie Cherry</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.E. Aerospace Engineering, 2026</t>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4746,12 +3550,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rachel Bonfini</t>
+          <t xml:space="preserve">Joe Borst, Visiting student from Clarkson University</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Biomedical and Mechanical Engineering, 2024</t>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4783,12 +3587,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valerie Fu</t>
+          <t xml:space="preserve">Joseph Daghir</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Mechanical Engineering, 2023</t>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4820,12 +3624,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christine Gabriele</t>
+          <t xml:space="preserve">Thomas Molnar</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Mechanical Engineering, 2023</t>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2024</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4857,12 +3661,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jay Sim</t>
+          <t xml:space="preserve">Avah Cherry, Visiting student from University of Tennessee</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Mechanical Engineering, 2022</t>
+          <t xml:space="preserve">B.E. Aerospace Engineering, 2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4894,12 +3698,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shelby Bauer</t>
+          <t xml:space="preserve">Rachel Bonfini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Mechanical Engineering, 2022</t>
+          <t xml:space="preserve">B.S. Biomedical and Mechanical Engineering, 2024</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4931,12 +3735,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nick Vitagliano</t>
+          <t xml:space="preserve">Valerie Fu</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Mechanical Engineering, 2021</t>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2023</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4968,12 +3772,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alex Cayley</t>
+          <t xml:space="preserve">Christine Gabriele</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Mechanical Engineering, 2021</t>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2023</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5005,12 +3809,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brianna Wilson</t>
+          <t xml:space="preserve">Jay Sim</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Industrial and Manufacturing Engineering, 2021</t>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2022</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5042,12 +3846,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Israel Monroy</t>
+          <t xml:space="preserve">Shelby Bauer</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Mechanical Engineering, 2021</t>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2022</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5079,12 +3883,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hunter Snyder</t>
+          <t xml:space="preserve">Nick Vitagliano</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Mechanical Engineering, 2019</t>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2021</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5116,12 +3920,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Szczesniak</t>
+          <t xml:space="preserve">Alex Cayley</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.S. Mechanical Engineering, 2018</t>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2021</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5153,30 +3957,178 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brianna Wilson</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B.S. Industrial and Manufacturing Engineering, 2021</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alumni - Undergraduate</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Israel Monroy</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2021</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alumni - Undergraduate</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hunter Snyder</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2019</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alumni - Undergraduate</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Michael Szczesniak</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B.S. Mechanical Engineering, 2018</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alumni - Undergraduate</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t xml:space="preserve">James Lauer</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t xml:space="preserve">B.S. Mechanical Engineering, 2018</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5252,7 +4204,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1674</t>
+          <t xml:space="preserve">1497</t>
         </is>
       </c>
     </row>
@@ -5284,7 +4236,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684</t>
+          <t xml:space="preserve">1507</t>
         </is>
       </c>
     </row>
@@ -5316,7 +4268,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694</t>
+          <t xml:space="preserve">1517</t>
         </is>
       </c>
     </row>
@@ -5348,7 +4300,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1709</t>
+          <t xml:space="preserve">1532</t>
         </is>
       </c>
     </row>
@@ -5380,7 +4332,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719</t>
+          <t xml:space="preserve">1542</t>
         </is>
       </c>
     </row>
@@ -5412,7 +4364,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1729</t>
+          <t xml:space="preserve">1552</t>
         </is>
       </c>
     </row>
@@ -5444,7 +4396,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739</t>
+          <t xml:space="preserve">1562</t>
         </is>
       </c>
     </row>
@@ -5476,7 +4428,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1749</t>
+          <t xml:space="preserve">1572</t>
         </is>
       </c>
     </row>
@@ -5508,7 +4460,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1759</t>
+          <t xml:space="preserve">1582</t>
         </is>
       </c>
     </row>
@@ -5540,7 +4492,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1769</t>
+          <t xml:space="preserve">1592</t>
         </is>
       </c>
     </row>
@@ -5572,7 +4524,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1779</t>
+          <t xml:space="preserve">1602</t>
         </is>
       </c>
     </row>
@@ -5604,7 +4556,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1789</t>
+          <t xml:space="preserve">1612</t>
         </is>
       </c>
     </row>
@@ -5636,7 +4588,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1799</t>
+          <t xml:space="preserve">1622</t>
         </is>
       </c>
     </row>
@@ -5668,7 +4620,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809</t>
+          <t xml:space="preserve">1632</t>
         </is>
       </c>
     </row>
@@ -5700,7 +4652,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819</t>
+          <t xml:space="preserve">1642</t>
         </is>
       </c>
     </row>
@@ -5732,7 +4684,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829</t>
+          <t xml:space="preserve">1652</t>
         </is>
       </c>
     </row>
@@ -5764,7 +4716,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839</t>
+          <t xml:space="preserve">1662</t>
         </is>
       </c>
     </row>
@@ -5796,7 +4748,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849</t>
+          <t xml:space="preserve">1672</t>
         </is>
       </c>
     </row>
@@ -5828,7 +4780,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864</t>
+          <t xml:space="preserve">1687</t>
         </is>
       </c>
     </row>
@@ -5860,7 +4812,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874</t>
+          <t xml:space="preserve">1697</t>
         </is>
       </c>
     </row>
@@ -5892,7 +4844,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884</t>
+          <t xml:space="preserve">1707</t>
         </is>
       </c>
     </row>
@@ -5924,7 +4876,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894</t>
+          <t xml:space="preserve">1717</t>
         </is>
       </c>
     </row>
@@ -5956,7 +4908,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1904</t>
+          <t xml:space="preserve">1727</t>
         </is>
       </c>
     </row>
@@ -5988,7 +4940,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1914</t>
+          <t xml:space="preserve">1737</t>
         </is>
       </c>
     </row>
@@ -6020,7 +4972,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924</t>
+          <t xml:space="preserve">1747</t>
         </is>
       </c>
     </row>
@@ -6052,7 +5004,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1934</t>
+          <t xml:space="preserve">1757</t>
         </is>
       </c>
     </row>
@@ -6084,7 +5036,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944</t>
+          <t xml:space="preserve">1767</t>
         </is>
       </c>
     </row>
@@ -6116,7 +5068,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1959</t>
+          <t xml:space="preserve">1782</t>
         </is>
       </c>
     </row>
@@ -6148,7 +5100,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1969</t>
+          <t xml:space="preserve">1792</t>
         </is>
       </c>
     </row>
@@ -6180,7 +5132,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1979</t>
+          <t xml:space="preserve">1802</t>
         </is>
       </c>
     </row>
@@ -6212,7 +5164,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1989</t>
+          <t xml:space="preserve">1812</t>
         </is>
       </c>
     </row>
@@ -6244,7 +5196,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1999</t>
+          <t xml:space="preserve">1822</t>
         </is>
       </c>
     </row>
@@ -6276,7 +5228,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009</t>
+          <t xml:space="preserve">1832</t>
         </is>
       </c>
     </row>
@@ -6308,7 +5260,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019</t>
+          <t xml:space="preserve">1842</t>
         </is>
       </c>
     </row>
@@ -6340,7 +5292,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029</t>
+          <t xml:space="preserve">1852</t>
         </is>
       </c>
     </row>
@@ -6372,7 +5324,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2039</t>
+          <t xml:space="preserve">1862</t>
         </is>
       </c>
     </row>
@@ -6404,7 +5356,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2049</t>
+          <t xml:space="preserve">1872</t>
         </is>
       </c>
     </row>
@@ -6436,7 +5388,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2059</t>
+          <t xml:space="preserve">1882</t>
         </is>
       </c>
     </row>
@@ -6468,7 +5420,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069</t>
+          <t xml:space="preserve">1892</t>
         </is>
       </c>
     </row>
@@ -6500,7 +5452,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079</t>
+          <t xml:space="preserve">1902</t>
         </is>
       </c>
     </row>
@@ -6532,7 +5484,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2094</t>
+          <t xml:space="preserve">1917</t>
         </is>
       </c>
     </row>
@@ -6564,7 +5516,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2104</t>
+          <t xml:space="preserve">1927</t>
         </is>
       </c>
     </row>
@@ -6596,7 +5548,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114</t>
+          <t xml:space="preserve">1937</t>
         </is>
       </c>
     </row>
@@ -6628,7 +5580,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2124</t>
+          <t xml:space="preserve">1947</t>
         </is>
       </c>
     </row>
@@ -6660,7 +5612,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134</t>
+          <t xml:space="preserve">1957</t>
         </is>
       </c>
     </row>
@@ -6692,7 +5644,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2144</t>
+          <t xml:space="preserve">1967</t>
         </is>
       </c>
     </row>
@@ -6724,7 +5676,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2154</t>
+          <t xml:space="preserve">1977</t>
         </is>
       </c>
     </row>
@@ -6756,7 +5708,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164</t>
+          <t xml:space="preserve">1987</t>
         </is>
       </c>
     </row>
@@ -6788,7 +5740,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174</t>
+          <t xml:space="preserve">1997</t>
         </is>
       </c>
     </row>
@@ -6820,7 +5772,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
     </row>
@@ -6852,7 +5804,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2194</t>
+          <t xml:space="preserve">2017</t>
         </is>
       </c>
     </row>
@@ -6884,7 +5836,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204</t>
+          <t xml:space="preserve">2027</t>
         </is>
       </c>
     </row>
@@ -6916,7 +5868,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214</t>
+          <t xml:space="preserve">2037</t>
         </is>
       </c>
     </row>
@@ -6948,7 +5900,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224</t>
+          <t xml:space="preserve">2047</t>
         </is>
       </c>
     </row>
@@ -6980,7 +5932,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2234</t>
+          <t xml:space="preserve">2057</t>
         </is>
       </c>
     </row>
@@ -7012,7 +5964,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2244</t>
+          <t xml:space="preserve">2067</t>
         </is>
       </c>
     </row>
@@ -7044,7 +5996,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2254</t>
+          <t xml:space="preserve">2077</t>
         </is>
       </c>
     </row>
@@ -7076,7 +6028,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2264</t>
+          <t xml:space="preserve">2087</t>
         </is>
       </c>
     </row>
@@ -7108,7 +6060,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2274</t>
+          <t xml:space="preserve">2097</t>
         </is>
       </c>
     </row>
@@ -7140,7 +6092,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2284</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
     </row>
@@ -7172,7 +6124,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2294</t>
+          <t xml:space="preserve">2117</t>
         </is>
       </c>
     </row>
@@ -7204,7 +6156,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304</t>
+          <t xml:space="preserve">2127</t>
         </is>
       </c>
     </row>
@@ -7236,7 +6188,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2314</t>
+          <t xml:space="preserve">2137</t>
         </is>
       </c>
     </row>
@@ -7268,7 +6220,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2324</t>
+          <t xml:space="preserve">2147</t>
         </is>
       </c>
     </row>
@@ -7300,7 +6252,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2334</t>
+          <t xml:space="preserve">2157</t>
         </is>
       </c>
     </row>
@@ -7332,7 +6284,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2344</t>
+          <t xml:space="preserve">2167</t>
         </is>
       </c>
     </row>
@@ -7364,7 +6316,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2359</t>
+          <t xml:space="preserve">2182</t>
         </is>
       </c>
     </row>
@@ -7396,7 +6348,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2374</t>
+          <t xml:space="preserve">2197</t>
         </is>
       </c>
     </row>
@@ -7428,7 +6380,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384</t>
+          <t xml:space="preserve">2207</t>
         </is>
       </c>
     </row>
@@ -7460,7 +6412,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2394</t>
+          <t xml:space="preserve">2217</t>
         </is>
       </c>
     </row>
@@ -7492,7 +6444,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404</t>
+          <t xml:space="preserve">2227</t>
         </is>
       </c>
     </row>
@@ -7524,7 +6476,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2414</t>
+          <t xml:space="preserve">2237</t>
         </is>
       </c>
     </row>
@@ -7556,7 +6508,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2424</t>
+          <t xml:space="preserve">2247</t>
         </is>
       </c>
     </row>
@@ -7588,7 +6540,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2434</t>
+          <t xml:space="preserve">2257</t>
         </is>
       </c>
     </row>
@@ -7620,7 +6572,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2444</t>
+          <t xml:space="preserve">2267</t>
         </is>
       </c>
     </row>
@@ -7652,7 +6604,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2453</t>
+          <t xml:space="preserve">2274</t>
         </is>
       </c>
     </row>
@@ -7684,7 +6636,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2463</t>
+          <t xml:space="preserve">2284</t>
         </is>
       </c>
     </row>
@@ -7716,7 +6668,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2473</t>
+          <t xml:space="preserve">2294</t>
         </is>
       </c>
     </row>
@@ -7748,7 +6700,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2483</t>
+          <t xml:space="preserve">2304</t>
         </is>
       </c>
     </row>
@@ -7780,7 +6732,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2493</t>
+          <t xml:space="preserve">2314</t>
         </is>
       </c>
     </row>
@@ -7812,7 +6764,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2503</t>
+          <t xml:space="preserve">2324</t>
         </is>
       </c>
     </row>
@@ -7844,7 +6796,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2513</t>
+          <t xml:space="preserve">2334</t>
         </is>
       </c>
     </row>
@@ -7876,7 +6828,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2523</t>
+          <t xml:space="preserve">2344</t>
         </is>
       </c>
     </row>
@@ -7908,7 +6860,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2533</t>
+          <t xml:space="preserve">2354</t>
         </is>
       </c>
     </row>
@@ -7940,7 +6892,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2543</t>
+          <t xml:space="preserve">2364</t>
         </is>
       </c>
     </row>
@@ -7972,7 +6924,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552</t>
+          <t xml:space="preserve">2371</t>
         </is>
       </c>
     </row>
@@ -8004,7 +6956,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2561</t>
+          <t xml:space="preserve">2378</t>
         </is>
       </c>
     </row>
@@ -8036,7 +6988,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2570</t>
+          <t xml:space="preserve">2385</t>
         </is>
       </c>
     </row>
@@ -8068,7 +7020,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579</t>
+          <t xml:space="preserve">2392</t>
         </is>
       </c>
     </row>
@@ -8100,7 +7052,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2588</t>
+          <t xml:space="preserve">2399</t>
         </is>
       </c>
     </row>
@@ -8132,7 +7084,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2597</t>
+          <t xml:space="preserve">2406</t>
         </is>
       </c>
     </row>
@@ -8164,7 +7116,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2606</t>
+          <t xml:space="preserve">2413</t>
         </is>
       </c>
     </row>
@@ -8196,7 +7148,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2615</t>
+          <t xml:space="preserve">2420</t>
         </is>
       </c>
     </row>
@@ -8228,7 +7180,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2624</t>
+          <t xml:space="preserve">2427</t>
         </is>
       </c>
     </row>
@@ -8260,7 +7212,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2633</t>
+          <t xml:space="preserve">2434</t>
         </is>
       </c>
     </row>
@@ -8292,7 +7244,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2642</t>
+          <t xml:space="preserve">2441</t>
         </is>
       </c>
     </row>
@@ -8324,7 +7276,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2651</t>
+          <t xml:space="preserve">2448</t>
         </is>
       </c>
     </row>
@@ -8356,7 +7308,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2455</t>
         </is>
       </c>
     </row>
@@ -8388,7 +7340,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2669</t>
+          <t xml:space="preserve">2462</t>
         </is>
       </c>
     </row>
@@ -8420,7 +7372,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2678</t>
+          <t xml:space="preserve">2469</t>
         </is>
       </c>
     </row>
@@ -8452,7 +7404,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2687</t>
+          <t xml:space="preserve">2476</t>
         </is>
       </c>
     </row>
@@ -8484,7 +7436,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2696</t>
+          <t xml:space="preserve">2483</t>
         </is>
       </c>
     </row>
@@ -8516,7 +7468,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2705</t>
+          <t xml:space="preserve">2490</t>
         </is>
       </c>
     </row>
@@ -8548,7 +7500,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2714</t>
+          <t xml:space="preserve">2497</t>
         </is>
       </c>
     </row>
@@ -8580,7 +7532,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2723</t>
+          <t xml:space="preserve">2504</t>
         </is>
       </c>
     </row>
@@ -8612,7 +7564,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2737</t>
+          <t xml:space="preserve">2516</t>
         </is>
       </c>
     </row>
@@ -8644,7 +7596,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2745</t>
+          <t xml:space="preserve">2523</t>
         </is>
       </c>
     </row>
@@ -8676,7 +7628,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2753</t>
+          <t xml:space="preserve">2530</t>
         </is>
       </c>
     </row>
@@ -8708,7 +7660,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2761</t>
+          <t xml:space="preserve">2537</t>
         </is>
       </c>
     </row>
@@ -8740,7 +7692,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2769</t>
+          <t xml:space="preserve">2544</t>
         </is>
       </c>
     </row>
@@ -8772,7 +7724,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2777</t>
+          <t xml:space="preserve">2551</t>
         </is>
       </c>
     </row>
@@ -8804,7 +7756,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2785</t>
+          <t xml:space="preserve">2558</t>
         </is>
       </c>
     </row>
@@ -8836,7 +7788,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2793</t>
+          <t xml:space="preserve">2565</t>
         </is>
       </c>
     </row>
@@ -8868,7 +7820,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2801</t>
+          <t xml:space="preserve">2572</t>
         </is>
       </c>
     </row>
@@ -8900,7 +7852,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2809</t>
+          <t xml:space="preserve">2579</t>
         </is>
       </c>
     </row>
@@ -8932,7 +7884,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2817</t>
+          <t xml:space="preserve">2586</t>
         </is>
       </c>
     </row>
@@ -8964,7 +7916,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2825</t>
+          <t xml:space="preserve">2593</t>
         </is>
       </c>
     </row>
@@ -8996,7 +7948,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2833</t>
+          <t xml:space="preserve">2600</t>
         </is>
       </c>
     </row>
@@ -9028,7 +7980,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2841</t>
+          <t xml:space="preserve">2607</t>
         </is>
       </c>
     </row>
@@ -9060,7 +8012,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2849</t>
+          <t xml:space="preserve">2614</t>
         </is>
       </c>
     </row>
@@ -9092,7 +8044,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2857</t>
+          <t xml:space="preserve">2621</t>
         </is>
       </c>
     </row>
@@ -9124,7 +8076,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2865</t>
+          <t xml:space="preserve">2628</t>
         </is>
       </c>
     </row>
@@ -9208,7 +8160,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1529</t>
+          <t xml:space="preserve">1352</t>
         </is>
       </c>
     </row>
@@ -9245,7 +8197,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1533</t>
+          <t xml:space="preserve">1356</t>
         </is>
       </c>
     </row>
@@ -9282,7 +8234,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1537</t>
+          <t xml:space="preserve">1360</t>
         </is>
       </c>
     </row>
@@ -9319,7 +8271,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1541</t>
+          <t xml:space="preserve">1364</t>
         </is>
       </c>
     </row>
@@ -9356,7 +8308,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1549</t>
+          <t xml:space="preserve">1372</t>
         </is>
       </c>
     </row>
@@ -9393,7 +8345,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1550</t>
+          <t xml:space="preserve">1373</t>
         </is>
       </c>
     </row>
@@ -9430,7 +8382,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551</t>
+          <t xml:space="preserve">1374</t>
         </is>
       </c>
     </row>
@@ -9467,7 +8419,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1552</t>
+          <t xml:space="preserve">1375</t>
         </is>
       </c>
     </row>
@@ -9504,7 +8456,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553</t>
+          <t xml:space="preserve">1376</t>
         </is>
       </c>
     </row>
@@ -9541,7 +8493,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1554</t>
+          <t xml:space="preserve">1377</t>
         </is>
       </c>
     </row>
@@ -9578,7 +8530,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1555</t>
+          <t xml:space="preserve">1378</t>
         </is>
       </c>
     </row>
@@ -9615,7 +8567,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556</t>
+          <t xml:space="preserve">1379</t>
         </is>
       </c>
     </row>
@@ -9652,7 +8604,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1557</t>
+          <t xml:space="preserve">1380</t>
         </is>
       </c>
     </row>
@@ -9689,7 +8641,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1558</t>
+          <t xml:space="preserve">1381</t>
         </is>
       </c>
     </row>
@@ -9726,7 +8678,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1559</t>
+          <t xml:space="preserve">1382</t>
         </is>
       </c>
     </row>
@@ -9763,7 +8715,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1560</t>
+          <t xml:space="preserve">1383</t>
         </is>
       </c>
     </row>
@@ -9800,7 +8752,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561</t>
+          <t xml:space="preserve">1384</t>
         </is>
       </c>
     </row>
@@ -9837,7 +8789,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1562</t>
+          <t xml:space="preserve">1385</t>
         </is>
       </c>
     </row>
@@ -9874,7 +8826,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1563</t>
+          <t xml:space="preserve">1386</t>
         </is>
       </c>
     </row>
@@ -9911,7 +8863,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1564</t>
+          <t xml:space="preserve">1387</t>
         </is>
       </c>
     </row>
@@ -9948,7 +8900,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1565</t>
+          <t xml:space="preserve">1388</t>
         </is>
       </c>
     </row>
@@ -9985,7 +8937,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566</t>
+          <t xml:space="preserve">1389</t>
         </is>
       </c>
     </row>
@@ -10022,7 +8974,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1567</t>
+          <t xml:space="preserve">1390</t>
         </is>
       </c>
     </row>
@@ -10059,7 +9011,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1568</t>
+          <t xml:space="preserve">1391</t>
         </is>
       </c>
     </row>
@@ -10096,7 +9048,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1569</t>
+          <t xml:space="preserve">1392</t>
         </is>
       </c>
     </row>
@@ -10133,7 +9085,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1570</t>
+          <t xml:space="preserve">1393</t>
         </is>
       </c>
     </row>
@@ -10170,7 +9122,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1571</t>
+          <t xml:space="preserve">1394</t>
         </is>
       </c>
     </row>
@@ -10207,7 +9159,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1572</t>
+          <t xml:space="preserve">1395</t>
         </is>
       </c>
     </row>
@@ -10244,7 +9196,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1573</t>
+          <t xml:space="preserve">1396</t>
         </is>
       </c>
     </row>
@@ -10281,7 +9233,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1574</t>
+          <t xml:space="preserve">1397</t>
         </is>
       </c>
     </row>
@@ -10318,7 +9270,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575</t>
+          <t xml:space="preserve">1398</t>
         </is>
       </c>
     </row>
@@ -10355,7 +9307,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1576</t>
+          <t xml:space="preserve">1399</t>
         </is>
       </c>
     </row>
@@ -10392,7 +9344,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1577</t>
+          <t xml:space="preserve">1400</t>
         </is>
       </c>
     </row>
@@ -10429,7 +9381,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1578</t>
+          <t xml:space="preserve">1401</t>
         </is>
       </c>
     </row>
@@ -10466,7 +9418,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1579</t>
+          <t xml:space="preserve">1402</t>
         </is>
       </c>
     </row>
@@ -10503,7 +9455,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580</t>
+          <t xml:space="preserve">1403</t>
         </is>
       </c>
     </row>
@@ -10540,7 +9492,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1581</t>
+          <t xml:space="preserve">1404</t>
         </is>
       </c>
     </row>
@@ -10577,7 +9529,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1582</t>
+          <t xml:space="preserve">1405</t>
         </is>
       </c>
     </row>
@@ -10614,7 +9566,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1583</t>
+          <t xml:space="preserve">1406</t>
         </is>
       </c>
     </row>
@@ -10651,7 +9603,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1584</t>
+          <t xml:space="preserve">1407</t>
         </is>
       </c>
     </row>
@@ -10688,7 +9640,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1585</t>
+          <t xml:space="preserve">1408</t>
         </is>
       </c>
     </row>
@@ -10725,7 +9677,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1586</t>
+          <t xml:space="preserve">1409</t>
         </is>
       </c>
     </row>
@@ -10762,7 +9714,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1587</t>
+          <t xml:space="preserve">1410</t>
         </is>
       </c>
     </row>
@@ -10799,7 +9751,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1588</t>
+          <t xml:space="preserve">1411</t>
         </is>
       </c>
     </row>
@@ -10836,7 +9788,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1589</t>
+          <t xml:space="preserve">1412</t>
         </is>
       </c>
     </row>
@@ -10873,7 +9825,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1590</t>
+          <t xml:space="preserve">1413</t>
         </is>
       </c>
     </row>
@@ -10910,7 +9862,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1591</t>
+          <t xml:space="preserve">1414</t>
         </is>
       </c>
     </row>
@@ -10947,7 +9899,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1592</t>
+          <t xml:space="preserve">1415</t>
         </is>
       </c>
     </row>
@@ -10984,7 +9936,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1593</t>
+          <t xml:space="preserve">1416</t>
         </is>
       </c>
     </row>
@@ -11021,7 +9973,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1594</t>
+          <t xml:space="preserve">1417</t>
         </is>
       </c>
     </row>
@@ -11058,7 +10010,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1595</t>
+          <t xml:space="preserve">1418</t>
         </is>
       </c>
     </row>
@@ -11095,7 +10047,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1596</t>
+          <t xml:space="preserve">1419</t>
         </is>
       </c>
     </row>
@@ -11132,7 +10084,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1597</t>
+          <t xml:space="preserve">1420</t>
         </is>
       </c>
     </row>
@@ -11169,7 +10121,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1598</t>
+          <t xml:space="preserve">1421</t>
         </is>
       </c>
     </row>
@@ -11206,7 +10158,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1599</t>
+          <t xml:space="preserve">1422</t>
         </is>
       </c>
     </row>
@@ -11243,7 +10195,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600</t>
+          <t xml:space="preserve">1423</t>
         </is>
       </c>
     </row>
@@ -11280,7 +10232,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1601</t>
+          <t xml:space="preserve">1424</t>
         </is>
       </c>
     </row>
@@ -11317,7 +10269,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602</t>
+          <t xml:space="preserve">1425</t>
         </is>
       </c>
     </row>
@@ -11354,7 +10306,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603</t>
+          <t xml:space="preserve">1426</t>
         </is>
       </c>
     </row>
@@ -11391,7 +10343,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1604</t>
+          <t xml:space="preserve">1427</t>
         </is>
       </c>
     </row>
@@ -11428,7 +10380,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605</t>
+          <t xml:space="preserve">1428</t>
         </is>
       </c>
     </row>
@@ -11465,7 +10417,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1606</t>
+          <t xml:space="preserve">1429</t>
         </is>
       </c>
     </row>
@@ -11502,7 +10454,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1607</t>
+          <t xml:space="preserve">1430</t>
         </is>
       </c>
     </row>
@@ -11539,7 +10491,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1608</t>
+          <t xml:space="preserve">1431</t>
         </is>
       </c>
     </row>
@@ -11576,7 +10528,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1609</t>
+          <t xml:space="preserve">1432</t>
         </is>
       </c>
     </row>
@@ -11613,7 +10565,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610</t>
+          <t xml:space="preserve">1433</t>
         </is>
       </c>
     </row>
@@ -11650,7 +10602,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1611</t>
+          <t xml:space="preserve">1434</t>
         </is>
       </c>
     </row>
@@ -11687,7 +10639,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612</t>
+          <t xml:space="preserve">1435</t>
         </is>
       </c>
     </row>
@@ -11724,7 +10676,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1613</t>
+          <t xml:space="preserve">1436</t>
         </is>
       </c>
     </row>
@@ -11761,7 +10713,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614</t>
+          <t xml:space="preserve">1437</t>
         </is>
       </c>
     </row>
@@ -11798,7 +10750,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615</t>
+          <t xml:space="preserve">1438</t>
         </is>
       </c>
     </row>
@@ -11835,7 +10787,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616</t>
+          <t xml:space="preserve">1439</t>
         </is>
       </c>
     </row>
@@ -11872,7 +10824,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1617</t>
+          <t xml:space="preserve">1440</t>
         </is>
       </c>
     </row>
@@ -11909,7 +10861,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618</t>
+          <t xml:space="preserve">1441</t>
         </is>
       </c>
     </row>
@@ -11946,7 +10898,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619</t>
+          <t xml:space="preserve">1442</t>
         </is>
       </c>
     </row>
@@ -11983,7 +10935,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620</t>
+          <t xml:space="preserve">1443</t>
         </is>
       </c>
     </row>
@@ -12020,7 +10972,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1621</t>
+          <t xml:space="preserve">1444</t>
         </is>
       </c>
     </row>
@@ -12057,7 +11009,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1622</t>
+          <t xml:space="preserve">1445</t>
         </is>
       </c>
     </row>
@@ -12094,7 +11046,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623</t>
+          <t xml:space="preserve">1446</t>
         </is>
       </c>
     </row>
@@ -12131,7 +11083,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1624</t>
+          <t xml:space="preserve">1447</t>
         </is>
       </c>
     </row>
@@ -12168,7 +11120,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625</t>
+          <t xml:space="preserve">1448</t>
         </is>
       </c>
     </row>
@@ -12205,7 +11157,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1626</t>
+          <t xml:space="preserve">1449</t>
         </is>
       </c>
     </row>
@@ -12242,7 +11194,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1627</t>
+          <t xml:space="preserve">1450</t>
         </is>
       </c>
     </row>
@@ -12279,7 +11231,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628</t>
+          <t xml:space="preserve">1451</t>
         </is>
       </c>
     </row>
@@ -12316,7 +11268,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1629</t>
+          <t xml:space="preserve">1452</t>
         </is>
       </c>
     </row>
@@ -12353,7 +11305,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1630</t>
+          <t xml:space="preserve">1453</t>
         </is>
       </c>
     </row>
@@ -12390,7 +11342,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631</t>
+          <t xml:space="preserve">1454</t>
         </is>
       </c>
     </row>
@@ -12474,7 +11426,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640</t>
+          <t xml:space="preserve">1463</t>
         </is>
       </c>
     </row>
@@ -12511,7 +11463,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1641</t>
+          <t xml:space="preserve">1464</t>
         </is>
       </c>
     </row>
@@ -12548,7 +11500,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642</t>
+          <t xml:space="preserve">1465</t>
         </is>
       </c>
     </row>
@@ -12585,7 +11537,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1643</t>
+          <t xml:space="preserve">1466</t>
         </is>
       </c>
     </row>
@@ -12622,7 +11574,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644</t>
+          <t xml:space="preserve">1467</t>
         </is>
       </c>
     </row>
@@ -12659,7 +11611,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645</t>
+          <t xml:space="preserve">1468</t>
         </is>
       </c>
     </row>
@@ -12696,7 +11648,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1646</t>
+          <t xml:space="preserve">1469</t>
         </is>
       </c>
     </row>
@@ -12733,7 +11685,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647</t>
+          <t xml:space="preserve">1470</t>
         </is>
       </c>
     </row>
@@ -12770,7 +11722,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648</t>
+          <t xml:space="preserve">1471</t>
         </is>
       </c>
     </row>
@@ -12807,7 +11759,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649</t>
+          <t xml:space="preserve">1472</t>
         </is>
       </c>
     </row>
@@ -12844,7 +11796,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650</t>
+          <t xml:space="preserve">1473</t>
         </is>
       </c>
     </row>
@@ -12881,7 +11833,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654</t>
+          <t xml:space="preserve">1477</t>
         </is>
       </c>
     </row>
@@ -12918,7 +11870,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655</t>
+          <t xml:space="preserve">1478</t>
         </is>
       </c>
     </row>
@@ -12955,7 +11907,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656</t>
+          <t xml:space="preserve">1479</t>
         </is>
       </c>
     </row>
@@ -12992,7 +11944,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657</t>
+          <t xml:space="preserve">1480</t>
         </is>
       </c>
     </row>
@@ -13029,7 +11981,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658</t>
+          <t xml:space="preserve">1481</t>
         </is>
       </c>
     </row>
@@ -13162,40 +12114,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Awaiting analytics</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Awaiting analytics</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Awaiting analytics</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Awaiting analytics</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:Z1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13256,7 +12174,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268</t>
+          <t xml:space="preserve">1087</t>
         </is>
       </c>
     </row>
@@ -13283,7 +12201,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290</t>
+          <t xml:space="preserve">1109</t>
         </is>
       </c>
     </row>
@@ -13310,7 +12228,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293</t>
+          <t xml:space="preserve">1112</t>
         </is>
       </c>
     </row>
@@ -13337,7 +12255,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1322</t>
+          <t xml:space="preserve">1141</t>
         </is>
       </c>
     </row>
@@ -13364,7 +12282,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1330</t>
+          <t xml:space="preserve">1149</t>
         </is>
       </c>
     </row>
@@ -13391,7 +12309,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1338</t>
+          <t xml:space="preserve">1157</t>
         </is>
       </c>
     </row>
@@ -13418,7 +12336,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352</t>
+          <t xml:space="preserve">1171</t>
         </is>
       </c>
     </row>
@@ -13445,7 +12363,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1360</t>
+          <t xml:space="preserve">1179</t>
         </is>
       </c>
     </row>
@@ -13472,7 +12390,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1368</t>
+          <t xml:space="preserve">1187</t>
         </is>
       </c>
     </row>
@@ -13499,7 +12417,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1387</t>
+          <t xml:space="preserve">1206</t>
         </is>
       </c>
     </row>
@@ -13526,7 +12444,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1391</t>
+          <t xml:space="preserve">1210</t>
         </is>
       </c>
     </row>
@@ -13553,7 +12471,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404</t>
+          <t xml:space="preserve">1223</t>
         </is>
       </c>
     </row>
@@ -13580,7 +12498,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411</t>
+          <t xml:space="preserve">1230</t>
         </is>
       </c>
     </row>
@@ -13607,7 +12525,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412</t>
+          <t xml:space="preserve">1231</t>
         </is>
       </c>
     </row>
@@ -13634,7 +12552,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413</t>
+          <t xml:space="preserve">1232</t>
         </is>
       </c>
     </row>
@@ -13661,7 +12579,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1414</t>
+          <t xml:space="preserve">1233</t>
         </is>
       </c>
     </row>
@@ -13688,7 +12606,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1415</t>
+          <t xml:space="preserve">1234</t>
         </is>
       </c>
     </row>
@@ -13715,7 +12633,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416</t>
+          <t xml:space="preserve">1235</t>
         </is>
       </c>
     </row>
@@ -13742,7 +12660,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1417</t>
+          <t xml:space="preserve">1236</t>
         </is>
       </c>
     </row>
@@ -13769,7 +12687,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418</t>
+          <t xml:space="preserve">1237</t>
         </is>
       </c>
     </row>
@@ -13796,7 +12714,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1419</t>
+          <t xml:space="preserve">1238</t>
         </is>
       </c>
     </row>
@@ -13823,7 +12741,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420</t>
+          <t xml:space="preserve">1239</t>
         </is>
       </c>
     </row>
@@ -13850,7 +12768,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1421</t>
+          <t xml:space="preserve">1240</t>
         </is>
       </c>
     </row>
@@ -13877,7 +12795,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428</t>
+          <t xml:space="preserve">1247</t>
         </is>
       </c>
     </row>
@@ -13904,7 +12822,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1435</t>
+          <t xml:space="preserve">1254</t>
         </is>
       </c>
     </row>
@@ -13931,7 +12849,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442</t>
+          <t xml:space="preserve">1261</t>
         </is>
       </c>
     </row>
@@ -13958,7 +12876,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1443</t>
+          <t xml:space="preserve">1262</t>
         </is>
       </c>
     </row>
@@ -13985,7 +12903,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1444</t>
+          <t xml:space="preserve">1263</t>
         </is>
       </c>
     </row>
@@ -14012,7 +12930,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1445</t>
+          <t xml:space="preserve">1264</t>
         </is>
       </c>
     </row>
@@ -14039,7 +12957,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1446</t>
+          <t xml:space="preserve">1265</t>
         </is>
       </c>
     </row>
@@ -14066,7 +12984,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1447</t>
+          <t xml:space="preserve">1266</t>
         </is>
       </c>
     </row>
@@ -14093,7 +13011,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1448</t>
+          <t xml:space="preserve">1267</t>
         </is>
       </c>
     </row>
@@ -14120,7 +13038,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530</t>
+          <t xml:space="preserve">1353</t>
         </is>
       </c>
     </row>
@@ -14147,7 +13065,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1534</t>
+          <t xml:space="preserve">1357</t>
         </is>
       </c>
     </row>
@@ -14174,7 +13092,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1538</t>
+          <t xml:space="preserve">1361</t>
         </is>
       </c>
     </row>
@@ -14201,7 +13119,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1542</t>
+          <t xml:space="preserve">1365</t>
         </is>
       </c>
     </row>
@@ -14228,7 +13146,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640</t>
+          <t xml:space="preserve">1463</t>
         </is>
       </c>
     </row>
@@ -14255,7 +13173,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1641</t>
+          <t xml:space="preserve">1464</t>
         </is>
       </c>
     </row>
@@ -14282,7 +13200,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642</t>
+          <t xml:space="preserve">1465</t>
         </is>
       </c>
     </row>
@@ -14309,7 +13227,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1643</t>
+          <t xml:space="preserve">1466</t>
         </is>
       </c>
     </row>
@@ -14336,7 +13254,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644</t>
+          <t xml:space="preserve">1467</t>
         </is>
       </c>
     </row>
@@ -14363,7 +13281,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645</t>
+          <t xml:space="preserve">1468</t>
         </is>
       </c>
     </row>
@@ -14390,7 +13308,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1646</t>
+          <t xml:space="preserve">1469</t>
         </is>
       </c>
     </row>
@@ -14417,7 +13335,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647</t>
+          <t xml:space="preserve">1470</t>
         </is>
       </c>
     </row>
@@ -14444,7 +13362,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648</t>
+          <t xml:space="preserve">1471</t>
         </is>
       </c>
     </row>
@@ -14471,7 +13389,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649</t>
+          <t xml:space="preserve">1472</t>
         </is>
       </c>
     </row>
@@ -14498,7 +13416,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650</t>
+          <t xml:space="preserve">1473</t>
         </is>
       </c>
     </row>
@@ -14525,7 +13443,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654</t>
+          <t xml:space="preserve">1477</t>
         </is>
       </c>
     </row>
@@ -14552,7 +13470,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655</t>
+          <t xml:space="preserve">1478</t>
         </is>
       </c>
     </row>
@@ -14579,7 +13497,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656</t>
+          <t xml:space="preserve">1479</t>
         </is>
       </c>
     </row>
@@ -14606,7 +13524,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657</t>
+          <t xml:space="preserve">1480</t>
         </is>
       </c>
     </row>
@@ -14633,7 +13551,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658</t>
+          <t xml:space="preserve">1481</t>
         </is>
       </c>
     </row>
@@ -14660,7 +13578,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2888</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
     </row>
@@ -14687,7 +13605,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889</t>
+          <t xml:space="preserve">2651</t>
         </is>
       </c>
     </row>
@@ -14714,7 +13632,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890</t>
+          <t xml:space="preserve">2652</t>
         </is>
       </c>
     </row>
@@ -14741,7 +13659,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891</t>
+          <t xml:space="preserve">2653</t>
         </is>
       </c>
     </row>
@@ -14768,7 +13686,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2892</t>
+          <t xml:space="preserve">2654</t>
         </is>
       </c>
     </row>
@@ -14795,7 +13713,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2893</t>
+          <t xml:space="preserve">2655</t>
         </is>
       </c>
     </row>
@@ -14822,7 +13740,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2894</t>
+          <t xml:space="preserve">2656</t>
         </is>
       </c>
     </row>
@@ -14849,7 +13767,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2895</t>
+          <t xml:space="preserve">2657</t>
         </is>
       </c>
     </row>
@@ -14876,7 +13794,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2896</t>
+          <t xml:space="preserve">2658</t>
         </is>
       </c>
     </row>
@@ -14903,7 +13821,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2897</t>
+          <t xml:space="preserve">2659</t>
         </is>
       </c>
     </row>
@@ -14930,7 +13848,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
     </row>
@@ -14957,7 +13875,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2899</t>
+          <t xml:space="preserve">2661</t>
         </is>
       </c>
     </row>
@@ -14984,7 +13902,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2662</t>
         </is>
       </c>
     </row>
@@ -15011,7 +13929,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2901</t>
+          <t xml:space="preserve">2663</t>
         </is>
       </c>
     </row>
@@ -15038,7 +13956,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2902</t>
+          <t xml:space="preserve">2664</t>
         </is>
       </c>
     </row>
@@ -15065,7 +13983,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2903</t>
+          <t xml:space="preserve">2665</t>
         </is>
       </c>
     </row>
@@ -15092,7 +14010,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2904</t>
+          <t xml:space="preserve">2666</t>
         </is>
       </c>
     </row>
@@ -15119,7 +14037,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2905</t>
+          <t xml:space="preserve">2667</t>
         </is>
       </c>
     </row>
@@ -15146,7 +14064,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2906</t>
+          <t xml:space="preserve">2668</t>
         </is>
       </c>
     </row>
@@ -15173,7 +14091,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907</t>
+          <t xml:space="preserve">2669</t>
         </is>
       </c>
     </row>
@@ -15200,7 +14118,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2908</t>
+          <t xml:space="preserve">2670</t>
         </is>
       </c>
     </row>
@@ -15227,7 +14145,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2909</t>
+          <t xml:space="preserve">2671</t>
         </is>
       </c>
     </row>
@@ -15254,7 +14172,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2910</t>
+          <t xml:space="preserve">2672</t>
         </is>
       </c>
     </row>
@@ -15281,34 +14199,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2911</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">assets/world-map.png</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Local</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lazy</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2965</t>
+          <t xml:space="preserve">2673</t>
         </is>
       </c>
     </row>
@@ -15362,7 +14253,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267</t>
+          <t xml:space="preserve">1086</t>
         </is>
       </c>
     </row>
@@ -15384,7 +14275,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275</t>
+          <t xml:space="preserve">1094</t>
         </is>
       </c>
     </row>
@@ -15406,7 +14297,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276</t>
+          <t xml:space="preserve">1095</t>
         </is>
       </c>
     </row>
@@ -15428,7 +14319,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277</t>
+          <t xml:space="preserve">1096</t>
         </is>
       </c>
     </row>
@@ -15450,7 +14341,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278</t>
+          <t xml:space="preserve">1097</t>
         </is>
       </c>
     </row>
@@ -15472,7 +14363,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279</t>
+          <t xml:space="preserve">1098</t>
         </is>
       </c>
     </row>
@@ -15494,7 +14385,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280</t>
+          <t xml:space="preserve">1099</t>
         </is>
       </c>
     </row>
@@ -15516,7 +14407,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281</t>
+          <t xml:space="preserve">1100</t>
         </is>
       </c>
     </row>
@@ -15538,7 +14429,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282</t>
+          <t xml:space="preserve">1101</t>
         </is>
       </c>
     </row>
@@ -15560,7 +14451,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397</t>
+          <t xml:space="preserve">1216</t>
         </is>
       </c>
     </row>
@@ -15582,7 +14473,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397</t>
+          <t xml:space="preserve">1216</t>
         </is>
       </c>
     </row>
@@ -15604,7 +14495,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404</t>
+          <t xml:space="preserve">1223</t>
         </is>
       </c>
     </row>
@@ -15626,7 +14517,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404</t>
+          <t xml:space="preserve">1223</t>
         </is>
       </c>
     </row>
@@ -15648,7 +14539,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404</t>
+          <t xml:space="preserve">1223</t>
         </is>
       </c>
     </row>
@@ -15670,7 +14561,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411</t>
+          <t xml:space="preserve">1230</t>
         </is>
       </c>
     </row>
@@ -15692,7 +14583,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411</t>
+          <t xml:space="preserve">1230</t>
         </is>
       </c>
     </row>
@@ -15714,7 +14605,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411</t>
+          <t xml:space="preserve">1230</t>
         </is>
       </c>
     </row>
@@ -15736,7 +14627,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412</t>
+          <t xml:space="preserve">1231</t>
         </is>
       </c>
     </row>
@@ -15758,7 +14649,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412</t>
+          <t xml:space="preserve">1231</t>
         </is>
       </c>
     </row>
@@ -15780,7 +14671,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412</t>
+          <t xml:space="preserve">1231</t>
         </is>
       </c>
     </row>
@@ -15802,7 +14693,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413</t>
+          <t xml:space="preserve">1232</t>
         </is>
       </c>
     </row>
@@ -15824,7 +14715,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413</t>
+          <t xml:space="preserve">1232</t>
         </is>
       </c>
     </row>
@@ -15846,7 +14737,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413</t>
+          <t xml:space="preserve">1232</t>
         </is>
       </c>
     </row>
@@ -15868,7 +14759,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1414</t>
+          <t xml:space="preserve">1233</t>
         </is>
       </c>
     </row>
@@ -15890,7 +14781,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1414</t>
+          <t xml:space="preserve">1233</t>
         </is>
       </c>
     </row>
@@ -15912,7 +14803,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1414</t>
+          <t xml:space="preserve">1233</t>
         </is>
       </c>
     </row>
@@ -15934,7 +14825,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1415</t>
+          <t xml:space="preserve">1234</t>
         </is>
       </c>
     </row>
@@ -15956,7 +14847,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1415</t>
+          <t xml:space="preserve">1234</t>
         </is>
       </c>
     </row>
@@ -15978,7 +14869,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416</t>
+          <t xml:space="preserve">1235</t>
         </is>
       </c>
     </row>
@@ -16000,7 +14891,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416</t>
+          <t xml:space="preserve">1235</t>
         </is>
       </c>
     </row>
@@ -16022,7 +14913,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1417</t>
+          <t xml:space="preserve">1236</t>
         </is>
       </c>
     </row>
@@ -16044,7 +14935,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1417</t>
+          <t xml:space="preserve">1236</t>
         </is>
       </c>
     </row>
@@ -16066,7 +14957,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418</t>
+          <t xml:space="preserve">1237</t>
         </is>
       </c>
     </row>
@@ -16088,7 +14979,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1419</t>
+          <t xml:space="preserve">1238</t>
         </is>
       </c>
     </row>
@@ -16110,7 +15001,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1419</t>
+          <t xml:space="preserve">1238</t>
         </is>
       </c>
     </row>
@@ -16132,7 +15023,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1419</t>
+          <t xml:space="preserve">1238</t>
         </is>
       </c>
     </row>
@@ -16154,7 +15045,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420</t>
+          <t xml:space="preserve">1239</t>
         </is>
       </c>
     </row>
@@ -16176,7 +15067,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420</t>
+          <t xml:space="preserve">1239</t>
         </is>
       </c>
     </row>
@@ -16198,7 +15089,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1421</t>
+          <t xml:space="preserve">1240</t>
         </is>
       </c>
     </row>
@@ -16220,7 +15111,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1421</t>
+          <t xml:space="preserve">1240</t>
         </is>
       </c>
     </row>
@@ -16242,7 +15133,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1435</t>
+          <t xml:space="preserve">1254</t>
         </is>
       </c>
     </row>
@@ -16264,7 +15155,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1435</t>
+          <t xml:space="preserve">1254</t>
         </is>
       </c>
     </row>
@@ -16286,7 +15177,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442</t>
+          <t xml:space="preserve">1261</t>
         </is>
       </c>
     </row>
@@ -16308,7 +15199,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442</t>
+          <t xml:space="preserve">1261</t>
         </is>
       </c>
     </row>
@@ -16330,7 +15221,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1443</t>
+          <t xml:space="preserve">1262</t>
         </is>
       </c>
     </row>
@@ -16352,7 +15243,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1443</t>
+          <t xml:space="preserve">1262</t>
         </is>
       </c>
     </row>
@@ -16374,7 +15265,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1444</t>
+          <t xml:space="preserve">1263</t>
         </is>
       </c>
     </row>
@@ -16396,7 +15287,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1445</t>
+          <t xml:space="preserve">1264</t>
         </is>
       </c>
     </row>
@@ -16418,7 +15309,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1445</t>
+          <t xml:space="preserve">1264</t>
         </is>
       </c>
     </row>
@@ -16440,7 +15331,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1446</t>
+          <t xml:space="preserve">1265</t>
         </is>
       </c>
     </row>
@@ -16462,7 +15353,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1446</t>
+          <t xml:space="preserve">1265</t>
         </is>
       </c>
     </row>
@@ -16484,7 +15375,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1447</t>
+          <t xml:space="preserve">1266</t>
         </is>
       </c>
     </row>
@@ -16506,7 +15397,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1447</t>
+          <t xml:space="preserve">1266</t>
         </is>
       </c>
     </row>
@@ -16528,7 +15419,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1448</t>
+          <t xml:space="preserve">1267</t>
         </is>
       </c>
     </row>
@@ -16550,7 +15441,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1448</t>
+          <t xml:space="preserve">1267</t>
         </is>
       </c>
     </row>
@@ -16572,7 +15463,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531</t>
+          <t xml:space="preserve">1354</t>
         </is>
       </c>
     </row>
@@ -16594,7 +15485,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1549</t>
+          <t xml:space="preserve">1372</t>
         </is>
       </c>
     </row>
@@ -16616,7 +15507,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1550</t>
+          <t xml:space="preserve">1373</t>
         </is>
       </c>
     </row>
@@ -16638,7 +15529,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553</t>
+          <t xml:space="preserve">1376</t>
         </is>
       </c>
     </row>
@@ -16660,7 +15551,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1555</t>
+          <t xml:space="preserve">1378</t>
         </is>
       </c>
     </row>
@@ -16682,7 +15573,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556</t>
+          <t xml:space="preserve">1379</t>
         </is>
       </c>
     </row>
@@ -16704,7 +15595,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1557</t>
+          <t xml:space="preserve">1380</t>
         </is>
       </c>
     </row>
@@ -16726,7 +15617,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1559</t>
+          <t xml:space="preserve">1382</t>
         </is>
       </c>
     </row>
@@ -16748,7 +15639,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625</t>
+          <t xml:space="preserve">1448</t>
         </is>
       </c>
     </row>
@@ -16770,7 +15661,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1629</t>
+          <t xml:space="preserve">1452</t>
         </is>
       </c>
     </row>
@@ -16792,7 +15683,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1630</t>
+          <t xml:space="preserve">1453</t>
         </is>
       </c>
     </row>
@@ -16814,7 +15705,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631</t>
+          <t xml:space="preserve">1454</t>
         </is>
       </c>
     </row>
@@ -16836,7 +15727,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640</t>
+          <t xml:space="preserve">1463</t>
         </is>
       </c>
     </row>
@@ -16858,7 +15749,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1641</t>
+          <t xml:space="preserve">1464</t>
         </is>
       </c>
     </row>
@@ -16880,7 +15771,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642</t>
+          <t xml:space="preserve">1465</t>
         </is>
       </c>
     </row>
@@ -16902,7 +15793,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1643</t>
+          <t xml:space="preserve">1466</t>
         </is>
       </c>
     </row>
@@ -16924,7 +15815,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644</t>
+          <t xml:space="preserve">1467</t>
         </is>
       </c>
     </row>
@@ -16946,7 +15837,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645</t>
+          <t xml:space="preserve">1468</t>
         </is>
       </c>
     </row>
@@ -16968,7 +15859,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1646</t>
+          <t xml:space="preserve">1469</t>
         </is>
       </c>
     </row>
@@ -16990,7 +15881,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647</t>
+          <t xml:space="preserve">1470</t>
         </is>
       </c>
     </row>
@@ -17012,7 +15903,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648</t>
+          <t xml:space="preserve">1471</t>
         </is>
       </c>
     </row>
@@ -17034,7 +15925,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649</t>
+          <t xml:space="preserve">1472</t>
         </is>
       </c>
     </row>
@@ -17056,7 +15947,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650</t>
+          <t xml:space="preserve">1473</t>
         </is>
       </c>
     </row>
@@ -17078,7 +15969,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654</t>
+          <t xml:space="preserve">1477</t>
         </is>
       </c>
     </row>
@@ -17100,7 +15991,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655</t>
+          <t xml:space="preserve">1478</t>
         </is>
       </c>
     </row>
@@ -17122,7 +16013,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656</t>
+          <t xml:space="preserve">1479</t>
         </is>
       </c>
     </row>
@@ -17144,7 +16035,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657</t>
+          <t xml:space="preserve">1480</t>
         </is>
       </c>
     </row>
@@ -17166,7 +16057,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658</t>
+          <t xml:space="preserve">1481</t>
         </is>
       </c>
     </row>
@@ -17188,7 +16079,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1681</t>
+          <t xml:space="preserve">1504</t>
         </is>
       </c>
     </row>
@@ -17210,7 +16101,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691</t>
+          <t xml:space="preserve">1514</t>
         </is>
       </c>
     </row>
@@ -17232,7 +16123,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1701</t>
+          <t xml:space="preserve">1524</t>
         </is>
       </c>
     </row>
@@ -17254,7 +16145,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1716</t>
+          <t xml:space="preserve">1539</t>
         </is>
       </c>
     </row>
@@ -17276,7 +16167,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1726</t>
+          <t xml:space="preserve">1549</t>
         </is>
       </c>
     </row>
@@ -17298,7 +16189,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1736</t>
+          <t xml:space="preserve">1559</t>
         </is>
       </c>
     </row>
@@ -17320,7 +16211,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1746</t>
+          <t xml:space="preserve">1569</t>
         </is>
       </c>
     </row>
@@ -17342,7 +16233,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1756</t>
+          <t xml:space="preserve">1579</t>
         </is>
       </c>
     </row>
@@ -17364,7 +16255,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1766</t>
+          <t xml:space="preserve">1589</t>
         </is>
       </c>
     </row>
@@ -17386,7 +16277,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1776</t>
+          <t xml:space="preserve">1599</t>
         </is>
       </c>
     </row>
@@ -17408,7 +16299,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1786</t>
+          <t xml:space="preserve">1609</t>
         </is>
       </c>
     </row>
@@ -17430,7 +16321,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1796</t>
+          <t xml:space="preserve">1619</t>
         </is>
       </c>
     </row>
@@ -17452,7 +16343,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806</t>
+          <t xml:space="preserve">1629</t>
         </is>
       </c>
     </row>
@@ -17474,7 +16365,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1816</t>
+          <t xml:space="preserve">1639</t>
         </is>
       </c>
     </row>
@@ -17496,7 +16387,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826</t>
+          <t xml:space="preserve">1649</t>
         </is>
       </c>
     </row>
@@ -17518,7 +16409,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1836</t>
+          <t xml:space="preserve">1659</t>
         </is>
       </c>
     </row>
@@ -17540,7 +16431,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846</t>
+          <t xml:space="preserve">1669</t>
         </is>
       </c>
     </row>
@@ -17562,7 +16453,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856</t>
+          <t xml:space="preserve">1679</t>
         </is>
       </c>
     </row>
@@ -17584,7 +16475,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871</t>
+          <t xml:space="preserve">1694</t>
         </is>
       </c>
     </row>
@@ -17606,7 +16497,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881</t>
+          <t xml:space="preserve">1704</t>
         </is>
       </c>
     </row>
@@ -17628,7 +16519,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891</t>
+          <t xml:space="preserve">1714</t>
         </is>
       </c>
     </row>
@@ -17650,7 +16541,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901</t>
+          <t xml:space="preserve">1724</t>
         </is>
       </c>
     </row>
@@ -17672,7 +16563,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1911</t>
+          <t xml:space="preserve">1734</t>
         </is>
       </c>
     </row>
@@ -17694,7 +16585,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921</t>
+          <t xml:space="preserve">1744</t>
         </is>
       </c>
     </row>
@@ -17716,7 +16607,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1931</t>
+          <t xml:space="preserve">1754</t>
         </is>
       </c>
     </row>
@@ -17738,7 +16629,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941</t>
+          <t xml:space="preserve">1764</t>
         </is>
       </c>
     </row>
@@ -17760,7 +16651,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1951</t>
+          <t xml:space="preserve">1774</t>
         </is>
       </c>
     </row>
@@ -17782,7 +16673,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">1789</t>
         </is>
       </c>
     </row>
@@ -17804,7 +16695,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1976</t>
+          <t xml:space="preserve">1799</t>
         </is>
       </c>
     </row>
@@ -17826,7 +16717,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1986</t>
+          <t xml:space="preserve">1809</t>
         </is>
       </c>
     </row>
@@ -17848,7 +16739,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996</t>
+          <t xml:space="preserve">1819</t>
         </is>
       </c>
     </row>
@@ -17870,7 +16761,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006</t>
+          <t xml:space="preserve">1829</t>
         </is>
       </c>
     </row>
@@ -17892,7 +16783,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016</t>
+          <t xml:space="preserve">1839</t>
         </is>
       </c>
     </row>
@@ -17914,7 +16805,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026</t>
+          <t xml:space="preserve">1849</t>
         </is>
       </c>
     </row>
@@ -17936,7 +16827,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036</t>
+          <t xml:space="preserve">1859</t>
         </is>
       </c>
     </row>
@@ -17958,7 +16849,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2046</t>
+          <t xml:space="preserve">1869</t>
         </is>
       </c>
     </row>
@@ -17980,7 +16871,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2056</t>
+          <t xml:space="preserve">1879</t>
         </is>
       </c>
     </row>
@@ -18002,7 +16893,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2066</t>
+          <t xml:space="preserve">1889</t>
         </is>
       </c>
     </row>
@@ -18024,7 +16915,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2076</t>
+          <t xml:space="preserve">1899</t>
         </is>
       </c>
     </row>
@@ -18046,7 +16937,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086</t>
+          <t xml:space="preserve">1909</t>
         </is>
       </c>
     </row>
@@ -18068,7 +16959,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2101</t>
+          <t xml:space="preserve">1924</t>
         </is>
       </c>
     </row>
@@ -18090,7 +16981,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2111</t>
+          <t xml:space="preserve">1934</t>
         </is>
       </c>
     </row>
@@ -18112,7 +17003,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121</t>
+          <t xml:space="preserve">1944</t>
         </is>
       </c>
     </row>
@@ -18134,7 +17025,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2131</t>
+          <t xml:space="preserve">1954</t>
         </is>
       </c>
     </row>
@@ -18156,7 +17047,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141</t>
+          <t xml:space="preserve">1964</t>
         </is>
       </c>
     </row>
@@ -18178,7 +17069,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2151</t>
+          <t xml:space="preserve">1974</t>
         </is>
       </c>
     </row>
@@ -18200,7 +17091,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161</t>
+          <t xml:space="preserve">1984</t>
         </is>
       </c>
     </row>
@@ -18222,7 +17113,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171</t>
+          <t xml:space="preserve">1994</t>
         </is>
       </c>
     </row>
@@ -18244,7 +17135,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181</t>
+          <t xml:space="preserve">2004</t>
         </is>
       </c>
     </row>
@@ -18266,7 +17157,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191</t>
+          <t xml:space="preserve">2014</t>
         </is>
       </c>
     </row>
@@ -18288,7 +17179,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201</t>
+          <t xml:space="preserve">2024</t>
         </is>
       </c>
     </row>
@@ -18310,7 +17201,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211</t>
+          <t xml:space="preserve">2034</t>
         </is>
       </c>
     </row>
@@ -18332,7 +17223,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221</t>
+          <t xml:space="preserve">2044</t>
         </is>
       </c>
     </row>
@@ -18354,7 +17245,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231</t>
+          <t xml:space="preserve">2054</t>
         </is>
       </c>
     </row>
@@ -18376,7 +17267,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241</t>
+          <t xml:space="preserve">2064</t>
         </is>
       </c>
     </row>
@@ -18398,7 +17289,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2251</t>
+          <t xml:space="preserve">2074</t>
         </is>
       </c>
     </row>
@@ -18420,7 +17311,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261</t>
+          <t xml:space="preserve">2084</t>
         </is>
       </c>
     </row>
@@ -18442,7 +17333,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2271</t>
+          <t xml:space="preserve">2094</t>
         </is>
       </c>
     </row>
@@ -18464,7 +17355,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2281</t>
+          <t xml:space="preserve">2104</t>
         </is>
       </c>
     </row>
@@ -18486,7 +17377,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2291</t>
+          <t xml:space="preserve">2114</t>
         </is>
       </c>
     </row>
@@ -18508,7 +17399,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301</t>
+          <t xml:space="preserve">2124</t>
         </is>
       </c>
     </row>
@@ -18530,7 +17421,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2311</t>
+          <t xml:space="preserve">2134</t>
         </is>
       </c>
     </row>
@@ -18552,7 +17443,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2321</t>
+          <t xml:space="preserve">2144</t>
         </is>
       </c>
     </row>
@@ -18574,7 +17465,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2331</t>
+          <t xml:space="preserve">2154</t>
         </is>
       </c>
     </row>
@@ -18596,7 +17487,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2341</t>
+          <t xml:space="preserve">2164</t>
         </is>
       </c>
     </row>
@@ -18618,7 +17509,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2351</t>
+          <t xml:space="preserve">2174</t>
         </is>
       </c>
     </row>
@@ -18640,7 +17531,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366</t>
+          <t xml:space="preserve">2189</t>
         </is>
       </c>
     </row>
@@ -18662,7 +17553,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381</t>
+          <t xml:space="preserve">2204</t>
         </is>
       </c>
     </row>
@@ -18684,7 +17575,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391</t>
+          <t xml:space="preserve">2214</t>
         </is>
       </c>
     </row>
@@ -18706,7 +17597,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401</t>
+          <t xml:space="preserve">2224</t>
         </is>
       </c>
     </row>
@@ -18728,7 +17619,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411</t>
+          <t xml:space="preserve">2234</t>
         </is>
       </c>
     </row>
@@ -18750,7 +17641,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2421</t>
+          <t xml:space="preserve">2244</t>
         </is>
       </c>
     </row>
@@ -18772,7 +17663,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2431</t>
+          <t xml:space="preserve">2254</t>
         </is>
       </c>
     </row>
@@ -18794,7 +17685,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2441</t>
+          <t xml:space="preserve">2264</t>
         </is>
       </c>
     </row>
@@ -18816,7 +17707,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2460</t>
+          <t xml:space="preserve">2281</t>
         </is>
       </c>
     </row>
@@ -18838,7 +17729,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2470</t>
+          <t xml:space="preserve">2291</t>
         </is>
       </c>
     </row>
@@ -18860,7 +17751,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2480</t>
+          <t xml:space="preserve">2301</t>
         </is>
       </c>
     </row>
@@ -18882,7 +17773,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2490</t>
+          <t xml:space="preserve">2311</t>
         </is>
       </c>
     </row>
@@ -18904,7 +17795,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2500</t>
+          <t xml:space="preserve">2321</t>
         </is>
       </c>
     </row>
@@ -18926,7 +17817,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2510</t>
+          <t xml:space="preserve">2331</t>
         </is>
       </c>
     </row>
@@ -18948,7 +17839,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2520</t>
+          <t xml:space="preserve">2341</t>
         </is>
       </c>
     </row>
@@ -18970,7 +17861,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2530</t>
+          <t xml:space="preserve">2351</t>
         </is>
       </c>
     </row>
@@ -18992,7 +17883,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2540</t>
+          <t xml:space="preserve">2361</t>
         </is>
       </c>
     </row>
@@ -19014,7 +17905,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2992</t>
+          <t xml:space="preserve">2710</t>
         </is>
       </c>
     </row>
@@ -19036,7 +17927,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2993</t>
+          <t xml:space="preserve">2711</t>
         </is>
       </c>
     </row>
@@ -19058,7 +17949,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2994</t>
+          <t xml:space="preserve">2712</t>
         </is>
       </c>
     </row>
@@ -19080,7 +17971,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2995</t>
+          <t xml:space="preserve">2713</t>
         </is>
       </c>
     </row>
@@ -19102,7 +17993,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2996</t>
+          <t xml:space="preserve">2714</t>
         </is>
       </c>
     </row>
@@ -19124,7 +18015,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2997</t>
+          <t xml:space="preserve">2715</t>
         </is>
       </c>
     </row>
@@ -19146,7 +18037,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2998</t>
+          <t xml:space="preserve">2716</t>
         </is>
       </c>
     </row>
@@ -19168,7 +18059,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2999</t>
+          <t xml:space="preserve">2717</t>
         </is>
       </c>
     </row>

--- a/SHAPE-Lab-Website-Content.xlsx
+++ b/SHAPE-Lab-Website-Content.xlsx
@@ -750,7 +750,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1459</t>
+          <t xml:space="preserve">1461</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1459</t>
+          <t xml:space="preserve">1461</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1486</t>
+          <t xml:space="preserve">1488</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1486</t>
+          <t xml:space="preserve">1488</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2642</t>
+          <t xml:space="preserve">2644</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2642</t>
+          <t xml:space="preserve">2644</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2683</t>
+          <t xml:space="preserve">2685</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2683</t>
+          <t xml:space="preserve">2685</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1497</t>
+          <t xml:space="preserve">1499</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507</t>
+          <t xml:space="preserve">1509</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1517</t>
+          <t xml:space="preserve">1519</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1532</t>
+          <t xml:space="preserve">1534</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1542</t>
+          <t xml:space="preserve">1544</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1552</t>
+          <t xml:space="preserve">1554</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1562</t>
+          <t xml:space="preserve">1564</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1572</t>
+          <t xml:space="preserve">1574</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1582</t>
+          <t xml:space="preserve">1584</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1592</t>
+          <t xml:space="preserve">1594</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602</t>
+          <t xml:space="preserve">1604</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612</t>
+          <t xml:space="preserve">1614</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1622</t>
+          <t xml:space="preserve">1624</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1632</t>
+          <t xml:space="preserve">1634</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642</t>
+          <t xml:space="preserve">1644</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1652</t>
+          <t xml:space="preserve">1654</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662</t>
+          <t xml:space="preserve">1664</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672</t>
+          <t xml:space="preserve">1674</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1687</t>
+          <t xml:space="preserve">1689</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697</t>
+          <t xml:space="preserve">1699</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1707</t>
+          <t xml:space="preserve">1709</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1717</t>
+          <t xml:space="preserve">1719</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1727</t>
+          <t xml:space="preserve">1729</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737</t>
+          <t xml:space="preserve">1739</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1747</t>
+          <t xml:space="preserve">1749</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1757</t>
+          <t xml:space="preserve">1759</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1767</t>
+          <t xml:space="preserve">1769</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1782</t>
+          <t xml:space="preserve">1784</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1792</t>
+          <t xml:space="preserve">1794</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802</t>
+          <t xml:space="preserve">1804</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812</t>
+          <t xml:space="preserve">1814</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822</t>
+          <t xml:space="preserve">1824</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832</t>
+          <t xml:space="preserve">1834</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842</t>
+          <t xml:space="preserve">1844</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852</t>
+          <t xml:space="preserve">1854</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862</t>
+          <t xml:space="preserve">1864</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872</t>
+          <t xml:space="preserve">1874</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882</t>
+          <t xml:space="preserve">1884</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1892</t>
+          <t xml:space="preserve">1894</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1902</t>
+          <t xml:space="preserve">1904</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917</t>
+          <t xml:space="preserve">1919</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1927</t>
+          <t xml:space="preserve">1929</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1937</t>
+          <t xml:space="preserve">1939</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1947</t>
+          <t xml:space="preserve">1949</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1957</t>
+          <t xml:space="preserve">1959</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1967</t>
+          <t xml:space="preserve">1969</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977</t>
+          <t xml:space="preserve">1979</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1987</t>
+          <t xml:space="preserve">1989</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1997</t>
+          <t xml:space="preserve">1999</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2007</t>
+          <t xml:space="preserve">2009</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017</t>
+          <t xml:space="preserve">2019</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027</t>
+          <t xml:space="preserve">2029</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037</t>
+          <t xml:space="preserve">2039</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047</t>
+          <t xml:space="preserve">2049</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2057</t>
+          <t xml:space="preserve">2059</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067</t>
+          <t xml:space="preserve">2069</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2077</t>
+          <t xml:space="preserve">2079</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087</t>
+          <t xml:space="preserve">2089</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2097</t>
+          <t xml:space="preserve">2099</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2107</t>
+          <t xml:space="preserve">2109</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117</t>
+          <t xml:space="preserve">2119</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2127</t>
+          <t xml:space="preserve">2129</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2137</t>
+          <t xml:space="preserve">2139</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147</t>
+          <t xml:space="preserve">2149</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157</t>
+          <t xml:space="preserve">2159</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167</t>
+          <t xml:space="preserve">2169</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2182</t>
+          <t xml:space="preserve">2184</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2197</t>
+          <t xml:space="preserve">2199</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2207</t>
+          <t xml:space="preserve">2209</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217</t>
+          <t xml:space="preserve">2219</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2227</t>
+          <t xml:space="preserve">2229</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2237</t>
+          <t xml:space="preserve">2239</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2247</t>
+          <t xml:space="preserve">2249</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2257</t>
+          <t xml:space="preserve">2259</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2267</t>
+          <t xml:space="preserve">2269</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2274</t>
+          <t xml:space="preserve">2276</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2284</t>
+          <t xml:space="preserve">2286</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2294</t>
+          <t xml:space="preserve">2296</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304</t>
+          <t xml:space="preserve">2306</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2314</t>
+          <t xml:space="preserve">2316</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2324</t>
+          <t xml:space="preserve">2326</t>
         </is>
       </c>
     </row>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2334</t>
+          <t xml:space="preserve">2336</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2344</t>
+          <t xml:space="preserve">2346</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2354</t>
+          <t xml:space="preserve">2356</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364</t>
+          <t xml:space="preserve">2366</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2371</t>
+          <t xml:space="preserve">2373</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2378</t>
+          <t xml:space="preserve">2380</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2385</t>
+          <t xml:space="preserve">2387</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392</t>
+          <t xml:space="preserve">2394</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399</t>
+          <t xml:space="preserve">2401</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2406</t>
+          <t xml:space="preserve">2408</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2413</t>
+          <t xml:space="preserve">2415</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2420</t>
+          <t xml:space="preserve">2422</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2427</t>
+          <t xml:space="preserve">2429</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2434</t>
+          <t xml:space="preserve">2436</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2441</t>
+          <t xml:space="preserve">2443</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448</t>
+          <t xml:space="preserve">2450</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7308,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2455</t>
+          <t xml:space="preserve">2457</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2462</t>
+          <t xml:space="preserve">2464</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2469</t>
+          <t xml:space="preserve">2471</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2476</t>
+          <t xml:space="preserve">2478</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2483</t>
+          <t xml:space="preserve">2485</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2490</t>
+          <t xml:space="preserve">2492</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2497</t>
+          <t xml:space="preserve">2499</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2504</t>
+          <t xml:space="preserve">2506</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2516</t>
+          <t xml:space="preserve">2518</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2523</t>
+          <t xml:space="preserve">2525</t>
         </is>
       </c>
     </row>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2530</t>
+          <t xml:space="preserve">2532</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2537</t>
+          <t xml:space="preserve">2539</t>
         </is>
       </c>
     </row>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2544</t>
+          <t xml:space="preserve">2546</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2551</t>
+          <t xml:space="preserve">2553</t>
         </is>
       </c>
     </row>
@@ -7756,7 +7756,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2558</t>
+          <t xml:space="preserve">2560</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2565</t>
+          <t xml:space="preserve">2567</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2572</t>
+          <t xml:space="preserve">2574</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579</t>
+          <t xml:space="preserve">2581</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2586</t>
+          <t xml:space="preserve">2588</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593</t>
+          <t xml:space="preserve">2595</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600</t>
+          <t xml:space="preserve">2602</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2607</t>
+          <t xml:space="preserve">2609</t>
         </is>
       </c>
     </row>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2614</t>
+          <t xml:space="preserve">2616</t>
         </is>
       </c>
     </row>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2621</t>
+          <t xml:space="preserve">2623</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8076,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2628</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
     </row>
@@ -8278,12 +8278,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spring 2025</t>
+          <t xml:space="preserve">Spring 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Ashish Jacob for being recognized with the 2025 Harold F. Martin Graduate Assistant Outstanding Teaching Award .</t>
+          <t xml:space="preserve">Congratulations to Kazi Shahed for being awarded the Marcus-Neibel-Schall Graduate Student Scholarship.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.psu.edu/news/graduate-school/story/graduate-school-honors-40-graduate-students-teaching-excellence</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -8315,12 +8315,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current Events</t>
+          <t xml:space="preserve">Fall 2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyond welding: researchers 3D print two metals in a single complex structure .</t>
+          <t xml:space="preserve">Congratulations to Bryan Gong for being awarded the University Graduate Fellowship.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.psu.edu/news/engineering/story/beyond-welding-researchers-3d-print-two-metals-single-complex-structure</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -8352,12 +8352,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current Events</t>
+          <t xml:space="preserve">Spring 2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab's multi-material laser powder bed fusion capabilities were featured by Additive Manufacturing Media.</t>
+          <t xml:space="preserve">Congratulations to Ashish Jacob for being recognized with the 2025 Harold F. Martin Graduate Assistant Outstanding Teaching Award .</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.psu.edu/news/graduate-school/story/graduate-school-honors-40-graduate-students-teaching-excellence</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Guha Manogharan gave a Computational Design Symposium keynote on design optimization for multi-material laser powder bed fusion.</t>
+          <t xml:space="preserve">Beyond welding: researchers 3D print two metals in a single complex structure .</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.psu.edu/news/engineering/story/beyond-welding-researchers-3d-print-two-metals-single-complex-structure</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Guha Manogharan was named co-director of Penn State's additive manufacturing center. Read more .</t>
+          <t xml:space="preserve">SHAPE Lab's multi-material laser powder bed fusion capabilities were featured by Additive Manufacturing Media.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.psu.edu/news/engineering</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Georgia Tech's Manufacturing Institute lecture series featured "Hybrid Additive Manufacturing: Role of AM in advancing traditional manufacturing methods" by Dr. Guha Manogharan.</t>
+          <t xml:space="preserve">Dr. Guha Manogharan gave a Computational Design Symposium keynote on design optimization for multi-material laser powder bed fusion.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3D-Printing Grad Student Helps Optimize Emerging Technology by Paula Clares.</t>
+          <t xml:space="preserve">Dr. Guha Manogharan was named co-director of Penn State's additive manufacturing center. Read more .</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.psu.edu/news/engineering/story/3d-printing-grad-student-helps-optimize-emerging-technology</t>
+          <t xml:space="preserve">https://www.psu.edu/news/engineering</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3D-Printing Surgical Implants Inspires Engineering Graduate Student by Lauren Judkins.</t>
+          <t xml:space="preserve">Georgia Tech's Manufacturing Institute lecture series featured "Hybrid Additive Manufacturing: Role of AM in advancing traditional manufacturing methods" by Dr. Guha Manogharan.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.psu.edu/news/engineering/story/3d-printing-surgical-implants-inspires-engineering-graduate-student</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3D Printing for Better Flame From a Gas Turbine Swirler: The Cool Parts Show #42 from Additive Manufacturing Media.</t>
+          <t xml:space="preserve">3D-Printing Grad Student Helps Optimize Emerging Technology by Paula Clares.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.additivemanufacturing.media/articles/3d-printing-for-better-flame-from-a-gas-turbine-swirler-the-cool-parts-show-42</t>
+          <t xml:space="preserve">https://www.psu.edu/news/engineering/story/3d-printing-grad-student-helps-optimize-emerging-technology</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -8611,12 +8611,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Summer 2025</t>
+          <t xml:space="preserve">Current Events</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Kaitlyn Hartman for being awarded 2nd place in the MSEC 2025 student poster competition for her research poster titled "Functionally graded TPMS lattices structures for biomedical applications."</t>
+          <t xml:space="preserve">3D-Printing Surgical Implants Inspires Engineering Graduate Student by Lauren Judkins.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.psu.edu/news/engineering/story/3d-printing-surgical-implants-inspires-engineering-graduate-student</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -8648,12 +8648,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spring 2025</t>
+          <t xml:space="preserve">Current Events</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab undergraduate honors researcher Joseph Daghir has been honored as a Spring 2025 Student Marshal .</t>
+          <t xml:space="preserve">3D Printing for Better Flame From a Gas Turbine Swirler: The Cool Parts Show #42 from Additive Manufacturing Media.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.engr.psu.edu/academics/student-marshals.aspx</t>
+          <t xml:space="preserve">https://www.additivemanufacturing.media/articles/3d-printing-for-better-flame-from-a-gas-turbine-swirler-the-cool-parts-show-42</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -8685,12 +8685,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spring 2025</t>
+          <t xml:space="preserve">Summer 2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Dr. Foxian Fan, who is starting as tenure-track assistant professor at Eastern Kentucky University.</t>
+          <t xml:space="preserve">Congratulations to Kaitlyn Hartman for being awarded 2nd place in the MSEC 2025 student poster competition for her research poster titled "Functionally graded TPMS lattices structures for biomedical applications."</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8722,12 +8722,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">July 2024</t>
+          <t xml:space="preserve">Spring 2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Dr. Ankit Saxena, who is starting as tenure-track assistant professor at the University of Wyoming.</t>
+          <t xml:space="preserve">SHAPE Lab undergraduate honors researcher Joseph Daghir has been honored as a Spring 2025 Student Marshal .</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.engr.psu.edu/academics/student-marshals.aspx</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8759,12 +8759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">July 2024</t>
+          <t xml:space="preserve">Spring 2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Dr. Sagar Jalui, who successfully defended his dissertation titled "AM-Driven Design Innovation: DfAM Constraints in Adjoint Shape Optimization for Gas Turbine Applications."</t>
+          <t xml:space="preserve">Congratulations to Dr. Foxian Fan, who is starting as tenure-track assistant professor at Eastern Kentucky University.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Dr. Ankit Saxena, who successfully defended his dissertation titled "Systematic Design of Pressure-Actuated Adaptive Structural Cells Enabling Adaptive Mechanical Properties in Mechanical Structures."</t>
+          <t xml:space="preserve">Congratulations to Dr. Ankit Saxena, who is starting as tenure-track assistant professor at the University of Wyoming.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8833,12 +8833,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 2024</t>
+          <t xml:space="preserve">July 2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jacklyn Griffis for being selected for the Naval Research Enterprise Internship Program 2024 at Naval Surface Warfare Center, Carderock Division.</t>
+          <t xml:space="preserve">Congratulations to Dr. Sagar Jalui, who successfully defended his dissertation titled "AM-Driven Design Innovation: DfAM Constraints in Adjoint Shape Optimization for Gas Turbine Applications."</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8870,12 +8870,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">August 2023</t>
+          <t xml:space="preserve">July 2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Carson Vath, who successfully defended his master's thesis titled "Development and Testing of Novel Multi-Material Additive Manufacturing Systems for Embedding Wire Electronics."</t>
+          <t xml:space="preserve">Congratulations to Dr. Ankit Saxena, who successfully defended his dissertation titled "Systematic Design of Pressure-Actuated Adaptive Structural Cells Enabling Adaptive Mechanical Properties in Mechanical Structures."</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8907,12 +8907,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">August 2023</t>
+          <t xml:space="preserve">May 2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Dr. Maryam Tilton, who is starting as tenure-track assistant professor at the University of Texas, Austin.</t>
+          <t xml:space="preserve">Congratulations to Jacklyn Griffis for being selected for the Naval Research Enterprise Internship Program 2024 at Naval Surface Warfare Center, Carderock Division.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Dr. Philip King, who is starting as tenure-track assistant professor at the University of Maine.</t>
+          <t xml:space="preserve">Congratulations to Carson Vath, who successfully defended his master's thesis titled "Development and Testing of Novel Multi-Material Additive Manufacturing Systems for Embedding Wire Electronics."</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Dr. Md Moinuddin Shuvo, who successfully defended his dissertation titled "Improving sustainability of Sand-Casting Processes via novel 3D Mold Designs."</t>
+          <t xml:space="preserve">Congratulations to Dr. Maryam Tilton, who is starting as tenure-track assistant professor at the University of Texas, Austin.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Dr. Foxian Fan, who successfully defended his dissertation titled "Evolution of Additive Manufacturing surface morphology during Centrifugal Disc Finishing."</t>
+          <t xml:space="preserve">Congratulations to Dr. Philip King, who is starting as tenure-track assistant professor at the University of Maine.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Dr. Philip King, who successfully defended his dissertation titled "Bridging the oldest and newest manufacturing technologies: Additive Manufacturing, Metal Casting, and Internet of Things."</t>
+          <t xml:space="preserve">Congratulations to Dr. Md Moinuddin Shuvo, who successfully defended his dissertation titled "Improving sustainability of Sand-Casting Processes via novel 3D Mold Designs."</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Sandy Karam, who successfully defended her master's paper titled "Additive Manufacturing of patient-specific high-fidelity and thickness-controlled cerebral aneurysm geometries."</t>
+          <t xml:space="preserve">Congratulations to Dr. Foxian Fan, who successfully defended his dissertation titled "Evolution of Additive Manufacturing surface morphology during Centrifugal Disc Finishing."</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Willem Groeneveld-Meijer, who successfully defended his master's thesis titled "Does Finer Powder get deposited first in Powder Bed? - A Comparative Study using Simulation and Experimental Techniques."</t>
+          <t xml:space="preserve">Congratulations to Dr. Philip King, who successfully defended his dissertation titled "Bridging the oldest and newest manufacturing technologies: Additive Manufacturing, Metal Casting, and Internet of Things."</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jacklyn Griffis, who was awarded the Walker Graduate Assistantship with ARL.</t>
+          <t xml:space="preserve">Congratulations to Sandy Karam, who successfully defended her master's paper titled "Additive Manufacturing of patient-specific high-fidelity and thickness-controlled cerebral aneurysm geometries."</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9203,12 +9203,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 2023</t>
+          <t xml:space="preserve">August 2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Foxian Fan, who was awarded the IISE Best Track Paper Award - Engineering Economy Division for "Cost Analysis of Mass Finishing Additively Manufactured Ti6Al4V Parts" at IISE 2023 in New Orleans, LA.</t>
+          <t xml:space="preserve">Congratulations to Willem Groeneveld-Meijer, who successfully defended his master's thesis titled "Does Finer Powder get deposited first in Powder Bed? - A Comparative Study using Simulation and Experimental Techniques."</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9240,12 +9240,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">March 2023</t>
+          <t xml:space="preserve">August 2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jacklyn Griffis for being selected for the Naval Research Enterprise Internship Program 2023.</t>
+          <t xml:space="preserve">Congratulations to Jacklyn Griffis, who was awarded the Walker Graduate Assistantship with ARL.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9277,12 +9277,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">January 2023</t>
+          <t xml:space="preserve">May 2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Ankit Saxena for being recognized with the 2022-23 Harold F. Martin Graduate Assistant Outstanding Teaching Award.</t>
+          <t xml:space="preserve">Congratulations to Foxian Fan, who was awarded the IISE Best Track Paper Award - Engineering Economy Division for "Cost Analysis of Mass Finishing Additively Manufactured Ti6Al4V Parts" at IISE 2023 in New Orleans, LA.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9314,12 +9314,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">October 2022</t>
+          <t xml:space="preserve">March 2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Philip King for being awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
+          <t xml:space="preserve">Congratulations to Jacklyn Griffis for being selected for the Naval Research Enterprise Internship Program 2023.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9351,12 +9351,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">October 2022</t>
+          <t xml:space="preserve">January 2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Shuvo for being awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
+          <t xml:space="preserve">Congratulations to Ankit Saxena for being recognized with the 2022-23 Harold F. Martin Graduate Assistant Outstanding Teaching Award.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Shuvo for being awarded the Steel Founders Society of America award for research in metal casting.</t>
+          <t xml:space="preserve">Congratulations to Philip King for being awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -9425,12 +9425,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">June 2022</t>
+          <t xml:space="preserve">October 2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Philip King for being awarded NSF student support for the Solid Freeform Fabrication Symposium 2022.</t>
+          <t xml:space="preserve">Congratulations to Shuvo for being awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -9462,12 +9462,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">June 2022</t>
+          <t xml:space="preserve">October 2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Shuvo for being awarded the Graduate Fellowship for research in metal casting.</t>
+          <t xml:space="preserve">Congratulations to Shuvo for being awarded the Steel Founders Society of America award for research in metal casting.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -9499,12 +9499,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 2022</t>
+          <t xml:space="preserve">June 2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Ankit Saxena for being awarded the part-time graduate teaching excellence liaison by the Schreyer Institute for Teaching Excellence.</t>
+          <t xml:space="preserve">Congratulations to Philip King for being awarded NSF student support for the Solid Freeform Fabrication Symposium 2022.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -9536,12 +9536,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 2022</t>
+          <t xml:space="preserve">June 2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Ankit Saxena for being awarded the 2022 ASME Graduate Teaching Fellowship.</t>
+          <t xml:space="preserve">Congratulations to Shuvo for being awarded the Graduate Fellowship for research in metal casting.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Paula Clares, who successfully defended her M.S. thesis in Additive Manufacturing &amp; Design titled "Fundamental Understanding into Bimodal Powder Size Distributions in Binder Jetting Additive Manufacturing Process."</t>
+          <t xml:space="preserve">Congratulations to Ankit Saxena for being awarded the part-time graduate teaching excellence liaison by the Schreyer Institute for Teaching Excellence.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Ryan Stebbins, who successfully defended his M.S. thesis in Mechanical Engineering titled "Novel Runner Extension Designs via 3D Sand-printing to Improve Casting Performance."</t>
+          <t xml:space="preserve">Congratulations to Ankit Saxena for being awarded the 2022 ASME Graduate Teaching Fellowship.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9647,12 +9647,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">April 2022</t>
+          <t xml:space="preserve">May 2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jay Sim for being awarded the Outstanding Undergraduate Research Achievement.</t>
+          <t xml:space="preserve">Congratulations to Paula Clares, who successfully defended her M.S. thesis in Additive Manufacturing &amp; Design titled "Fundamental Understanding into Bimodal Powder Size Distributions in Binder Jetting Additive Manufacturing Process."</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -9684,12 +9684,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">April 2022</t>
+          <t xml:space="preserve">May 2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Foxian Fan for the 2021-22 Harold F. Martin Graduate Assistant Outstanding Teaching Award.</t>
+          <t xml:space="preserve">Congratulations to Ryan Stebbins, who successfully defended his M.S. thesis in Mechanical Engineering titled "Novel Runner Extension Designs via 3D Sand-printing to Improve Casting Performance."</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Paula Clares for the 2021-22 Distinguished Master's Thesis Award.</t>
+          <t xml:space="preserve">Congratulations to Jay Sim for being awarded the Outstanding Undergraduate Research Achievement.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -9758,12 +9758,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">March 2022</t>
+          <t xml:space="preserve">April 2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Willem Groeneveld-Meijer for being awarded the Naval Research Enterprise Internship Program 2022.</t>
+          <t xml:space="preserve">Congratulations to Foxian Fan for the 2021-22 Harold F. Martin Graduate Assistant Outstanding Teaching Award.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -9795,12 +9795,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">August 2021</t>
+          <t xml:space="preserve">April 2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
+          <t xml:space="preserve">Congratulations to Paula Clares for the 2021-22 Distinguished Master's Thesis Award.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -9832,12 +9832,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">August 2021</t>
+          <t xml:space="preserve">March 2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Philip King, who was awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
+          <t xml:space="preserve">Congratulations to Willem Groeneveld-Meijer for being awarded the Naval Research Enterprise Internship Program 2022.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -9869,12 +9869,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">June 2021</t>
+          <t xml:space="preserve">August 2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Sagar Jalui for being awarded NSF student support for the Solid Freeform Fabrication Symposium 2021.</t>
+          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9906,12 +9906,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">June 2021</t>
+          <t xml:space="preserve">August 2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Ankit Saxena for being awarded NSF student support for the Solid Freeform Fabrication Symposium 2021.</t>
+          <t xml:space="preserve">Congratulations to Philip King, who was awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Nicholas Vitagliano for being awarded NSF student support for the Solid Freeform Fabrication Symposium 2021.</t>
+          <t xml:space="preserve">Congratulations to Sagar Jalui for being awarded NSF student support for the Solid Freeform Fabrication Symposium 2021.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Willem Groeneveld-Meijer for being awarded NSF student support for the Solid Freeform Fabrication Symposium 2021.</t>
+          <t xml:space="preserve">Congratulations to Ankit Saxena for being awarded NSF student support for the Solid Freeform Fabrication Symposium 2021.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -10017,12 +10017,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 2021</t>
+          <t xml:space="preserve">June 2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the H. H. Harris Foundation scholarship for research in metal casting.</t>
+          <t xml:space="preserve">Congratulations to Nicholas Vitagliano for being awarded NSF student support for the Solid Freeform Fabrication Symposium 2021.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -10054,12 +10054,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">April 2021</t>
+          <t xml:space="preserve">June 2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jay Sim for being awarded Second Best Presenter at the Undergraduate Research Exhibition.</t>
+          <t xml:space="preserve">Congratulations to Willem Groeneveld-Meijer for being awarded NSF student support for the Solid Freeform Fabrication Symposium 2021.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -10091,12 +10091,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">August 2020</t>
+          <t xml:space="preserve">May 2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Philip King for winning the Penn State Energy and Environmental Sustainability Green Dollars Grant.</t>
+          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the H. H. Harris Foundation scholarship for research in metal casting.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -10128,12 +10128,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">June 2020</t>
+          <t xml:space="preserve">April 2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Dr. Maryam Tilton on defending her dissertation titled "Multi-Objective Design and Characterization of Orthopaedic Implants and Meta-Biomaterials Fabricated via Additive Manufacturing."</t>
+          <t xml:space="preserve">Congratulations to Jay Sim for being awarded Second Best Presenter at the Undergraduate Research Exhibition.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -10165,12 +10165,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 2020</t>
+          <t xml:space="preserve">August 2020</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Dr. Xi Gong, who successfully defended his dissertation titled "Machining Behavior and Material Properties in Additive Manufacturing of TI-6AL-4V Parts."</t>
+          <t xml:space="preserve">Congratulations to Philip King for winning the Penn State Energy and Environmental Sustainability Green Dollars Grant.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -10202,12 +10202,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 2020</t>
+          <t xml:space="preserve">June 2020</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the H. H. Harris Foundation scholarship for research in metal casting.</t>
+          <t xml:space="preserve">Congratulations to Dr. Maryam Tilton on defending her dissertation titled "Multi-Objective Design and Characterization of Orthopaedic Implants and Meta-Biomaterials Fabricated via Additive Manufacturing."</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -10239,12 +10239,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">April 2020</t>
+          <t xml:space="preserve">May 2020</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jay Sim for being awarded Third Best Presenter at the Undergraduate Research Exhibition for work on Reinventing Foundry in a Box for the 21st Century.</t>
+          <t xml:space="preserve">Congratulations to Dr. Xi Gong, who successfully defended his dissertation titled "Machining Behavior and Material Properties in Additive Manufacturing of TI-6AL-4V Parts."</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -10276,12 +10276,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">March 2020</t>
+          <t xml:space="preserve">May 2020</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to SHAPE Lab member Phil King, who was awarded the NSF Graduate Research Fellowship for work on numerical modeling and experimentation with novel 3D runner geometries.</t>
+          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the H. H. Harris Foundation scholarship for research in metal casting.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -10313,12 +10313,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">March 2020</t>
+          <t xml:space="preserve">April 2020</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jay Sim, who was selected for a 2020 PSU Erickson Discovery Grant for research in casting science.</t>
+          <t xml:space="preserve">Congratulations to Jay Sim for being awarded Third Best Presenter at the Undergraduate Research Exhibition for work on Reinventing Foundry in a Box for the 21st Century.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -10350,12 +10350,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">January 2020</t>
+          <t xml:space="preserve">March 2020</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
+          <t xml:space="preserve">Congratulations to SHAPE Lab member Phil King, who was awarded the NSF Graduate Research Fellowship for work on numerical modeling and experimentation with novel 3D runner geometries.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -10387,12 +10387,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">January 2020</t>
+          <t xml:space="preserve">March 2020</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the Spring 2020 Equity REU Grant to continue research redesigning AFS Foundry-in-a-Box.</t>
+          <t xml:space="preserve">Congratulations to Jay Sim, who was selected for a 2020 PSU Erickson Discovery Grant for research in casting science.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -10424,12 +10424,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">December 2019</t>
+          <t xml:space="preserve">January 2020</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab member Israel Monroy presented research work and findings at the Fall 2019 Design Showcase at University Park.</t>
+          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -10461,12 +10461,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">August 2019</t>
+          <t xml:space="preserve">January 2020</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Philip King, who was awarded the PA Manufacturing Fellowship for research in metal casting.</t>
+          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the Spring 2020 Equity REU Grant to continue research redesigning AFS Foundry-in-a-Box.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -10498,12 +10498,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">August 2019</t>
+          <t xml:space="preserve">December 2019</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Philip King, who was awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
+          <t xml:space="preserve">SHAPE Lab member Israel Monroy presented research work and findings at the Fall 2019 Design Showcase at University Park.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
+          <t xml:space="preserve">Congratulations to Philip King, who was awarded the PA Manufacturing Fellowship for research in metal casting.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the Fall 2019 Equity REU Grant to begin research on redesigning AFS Foundry-in-a-Box.</t>
+          <t xml:space="preserve">Congratulations to Philip King, who was awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Israel Monroy, who was awarded a scholarship from the College of Engineering for acceptance into the 2019 Fall REU program.</t>
+          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the Foundry Education Foundation scholarship for research in metal casting.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab member Daniel Martinez gave two technical presentations on "In-Direct Hybrid AM: Advancing Metal Castings via 3D Sand-Printing" and "Influence of 3D Sand-Printing Processing Conditions on Thermo-Mechanical Properties of Molds" at SFF 2019 in Austin, TX.</t>
+          <t xml:space="preserve">Congratulations to Jay Sim, who was awarded the Fall 2019 Equity REU Grant to begin research on redesigning AFS Foundry-in-a-Box.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -10683,12 +10683,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">June 2019</t>
+          <t xml:space="preserve">August 2019</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab member Daniel Martinez gave a poster presentation on "Improving mechanical properties of metal castings using novel sprue designs via 3D sand-printing" at ASME MSEC 2019 in Erie, PA.</t>
+          <t xml:space="preserve">Congratulations to Israel Monroy, who was awarded a scholarship from the College of Engineering for acceptance into the 2019 Fall REU program.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10720,12 +10720,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">April 2019</t>
+          <t xml:space="preserve">August 2019</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Maryam Tilton, who was awarded the DAAD RISE Professional 2019 Award and joined Zeiss 3D ManuFact in Germany for a three-month study and training program.</t>
+          <t xml:space="preserve">SHAPE Lab member Daniel Martinez gave two technical presentations on "In-Direct Hybrid AM: Advancing Metal Castings via 3D Sand-Printing" and "Influence of 3D Sand-Printing Processing Conditions on Thermo-Mechanical Properties of Molds" at SFF 2019 in Austin, TX.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10757,12 +10757,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">April 2019</t>
+          <t xml:space="preserve">June 2019</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Greg Bicknell, who successfully defended his M.S. thesis in Mechanical Engineering titled "Electrical Discharge Machining Process for Post-Processing Stainless Steel 316L Additively Manufactured Parts."</t>
+          <t xml:space="preserve">SHAPE Lab member Daniel Martinez gave a poster presentation on "Improving mechanical properties of metal castings using novel sprue designs via 3D sand-printing" at ASME MSEC 2019 in Erie, PA.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10794,12 +10794,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">March 2019</t>
+          <t xml:space="preserve">April 2019</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Daniel Martinez, who was awarded the EESL Green Dollars grant for his project titled "Image Analysis of Pore Networks in 3D-Sand Printed Specimens Using Computer Tomography Scanning."</t>
+          <t xml:space="preserve">Congratulations to Maryam Tilton, who was awarded the DAAD RISE Professional 2019 Award and joined Zeiss 3D ManuFact in Germany for a three-month study and training program.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10831,12 +10831,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">February 2019</t>
+          <t xml:space="preserve">April 2019</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maryam Tilton presented work at the Orthopaedic Research Society Annual Meeting 2019 in Austin, TX on additively manufactured proximal humerus fracture fixation plates and patient-specific prostheses.</t>
+          <t xml:space="preserve">Congratulations to Greg Bicknell, who successfully defended his M.S. thesis in Mechanical Engineering titled "Electrical Discharge Machining Process for Post-Processing Stainless Steel 316L Additively Manufactured Parts."</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10868,12 +10868,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">December 2018</t>
+          <t xml:space="preserve">March 2019</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Santosh Reddy Sama, who graduated with dual M.S. thesis degrees in Mechanical Engineering and Additive Manufacturing and Design.</t>
+          <t xml:space="preserve">Congratulations to Daniel Martinez, who was awarded the EESL Green Dollars grant for his project titled "Image Analysis of Pore Networks in 3D-Sand Printed Specimens Using Computer Tomography Scanning."</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10905,12 +10905,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">December 2018</t>
+          <t xml:space="preserve">February 2019</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Santosh Reddy Sama, who published "Novel Sprue Design in Metal Casting via 3D Sand-Printing" in Additive Manufacturing .</t>
+          <t xml:space="preserve">Maryam Tilton presented work at the Orthopaedic Research Society Annual Meeting 2019 in Austin, TX on additively manufactured proximal humerus fracture fixation plates and patient-specific prostheses.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10942,12 +10942,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">August 2018</t>
+          <t xml:space="preserve">December 2018</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Santosh Reddy Sama, who published "Non-conventional mold design for metal casting using 3D sand-printing" in the Journal of Manufacturing Processes .</t>
+          <t xml:space="preserve">Congratulations to Santosh Reddy Sama, who graduated with dual M.S. thesis degrees in Mechanical Engineering and Additive Manufacturing and Design.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10979,12 +10979,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">June 2018</t>
+          <t xml:space="preserve">December 2018</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab member Santosh Reddy Sama gave a technical presentation on "Non-Conventional Mold Design for Metal Casting using 3D Sand-Printing" at NAMRC in College Station, TX.</t>
+          <t xml:space="preserve">Congratulations to Santosh Reddy Sama, who published "Novel Sprue Design in Metal Casting via 3D Sand-Printing" in Additive Manufacturing .</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -11016,12 +11016,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 2018</t>
+          <t xml:space="preserve">August 2018</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab member Santosh Reddy Sama gave a technical presentation on "Topology Optimization for Metal Castings using 3D Sand-Printing including Manufacturing Constraints" at IISE 2018 in Orlando, FL.</t>
+          <t xml:space="preserve">Congratulations to Santosh Reddy Sama, who published "Non-conventional mold design for metal casting using 3D sand-printing" in the Journal of Manufacturing Processes .</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11053,12 +11053,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 2018</t>
+          <t xml:space="preserve">June 2018</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab member Jiayi Wang gave a technical presentation on "Topology Optimization for Rapid Investment Casting of AM Patterns via Material Extrusion" at IISE 2018 in Orlando, FL.</t>
+          <t xml:space="preserve">SHAPE Lab member Santosh Reddy Sama gave a technical presentation on "Non-Conventional Mold Design for Metal Casting using 3D Sand-Printing" at NAMRC in College Station, TX.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11090,12 +11090,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">April 2018</t>
+          <t xml:space="preserve">May 2018</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab member Maryam Jahanzad gave a technical presentation on "How Can Additive Manufacturing Improve Fatigue Life in Fracture Fixations: An Experimental Study in Proximal Humerus Fractures" at RAPID 2018 in Fort Worth, TX.</t>
+          <t xml:space="preserve">SHAPE Lab member Santosh Reddy Sama gave a technical presentation on "Topology Optimization for Metal Castings using 3D Sand-Printing including Manufacturing Constraints" at IISE 2018 in Orlando, FL.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.rapid3devent.com/</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -11127,12 +11127,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">April 2018</t>
+          <t xml:space="preserve">May 2018</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to Jiayi Wang, who published "Re-Thinking Design Methodology for Castings: 3D Sand-Printing And Topology Optimization" in the International Journal of Metalcasting .</t>
+          <t xml:space="preserve">SHAPE Lab member Jiayi Wang gave a technical presentation on "Topology Optimization for Rapid Investment Casting of AM Patterns via Material Extrusion" at IISE 2018 in Orlando, FL.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Congratulations to undergraduate honors lab member Michael Szczesniak, who won the 2nd best presentation at the 2018 Undergraduate Research Exhibition for his thesis project, "Wire Arc Additive Manufacturing (WAAM) Utilizing a Low Cost, Closed Loop Current Control System."</t>
+          <t xml:space="preserve">SHAPE Lab member Maryam Jahanzad gave a technical presentation on "How Can Additive Manufacturing Improve Fatigue Life in Fracture Fixations: An Experimental Study in Proximal Humerus Fractures" at RAPID 2018 in Fort Worth, TX.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.rapid3devent.com/</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -11201,12 +11201,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">December 2017</t>
+          <t xml:space="preserve">April 2018</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jiayi Wang successfully defended his thesis on "Part Design and Topology Optimization for Rapid Sand and Investment Casting" and graduated with a master's in Engineering Design.</t>
+          <t xml:space="preserve">Congratulations to Jiayi Wang, who published "Re-Thinking Design Methodology for Castings: 3D Sand-Printing And Topology Optimization" in the International Journal of Metalcasting .</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11238,12 +11238,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">October 2017</t>
+          <t xml:space="preserve">April 2018</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">An invited talk on "Advanced Hybrid Manufacturing: Roadmap of Technological Challenges" was presented at the 2017 Annual International Solid Freeform Fabrication Symposium.</t>
+          <t xml:space="preserve">Congratulations to undergraduate honors lab member Michael Szczesniak, who won the 2nd best presentation at the 2018 Undergraduate Research Exhibition for his thesis project, "Wire Arc Additive Manufacturing (WAAM) Utilizing a Low Cost, Closed Loop Current Control System."</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.programmaster.org/</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -11275,12 +11275,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">October 2017</t>
+          <t xml:space="preserve">December 2017</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">An invited talk on "Hybrid Manufacturing - Integrating Additive Manufacturing with Traditional Technologies" was presented at MetalStorm 2017.</t>
+          <t xml:space="preserve">Jiayi Wang successfully defended his thesis on "Part Design and Topology Optimization for Rapid Sand and Investment Casting" and graduated with a master's in Engineering Design.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.methodsmachine.com/</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -11312,37 +11312,111 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t xml:space="preserve">October 2017</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An invited talk on "Advanced Hybrid Manufacturing: Roadmap of Technological Challenges" was presented at the 2017 Annual International Solid Freeform Fabrication Symposium.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.programmaster.org/</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1454</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2017</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An invited talk on "Hybrid Manufacturing - Integrating Additive Manufacturing with Traditional Technologies" was presented at MetalStorm 2017.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.methodsmachine.com/</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1455</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t xml:space="preserve">May 2017</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t xml:space="preserve">SHAPE Lab member Maryam Jahanzad gave a technical presentation on "Addressing Challenges in Custom Orthopedic Implants Using Additive Manufacturing" at RAPID 2017 in Pittsburgh, PA.</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.rapid3devent.com/</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1454</t>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1456</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11500,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463</t>
+          <t xml:space="preserve">1465</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11537,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1464</t>
+          <t xml:space="preserve">1466</t>
         </is>
       </c>
     </row>
@@ -11500,7 +11574,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1465</t>
+          <t xml:space="preserve">1467</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11611,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466</t>
+          <t xml:space="preserve">1468</t>
         </is>
       </c>
     </row>
@@ -11574,7 +11648,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1467</t>
+          <t xml:space="preserve">1469</t>
         </is>
       </c>
     </row>
@@ -11611,7 +11685,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468</t>
+          <t xml:space="preserve">1470</t>
         </is>
       </c>
     </row>
@@ -11648,7 +11722,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469</t>
+          <t xml:space="preserve">1471</t>
         </is>
       </c>
     </row>
@@ -11685,7 +11759,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1470</t>
+          <t xml:space="preserve">1472</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11796,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1471</t>
+          <t xml:space="preserve">1473</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11833,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1472</t>
+          <t xml:space="preserve">1474</t>
         </is>
       </c>
     </row>
@@ -11796,7 +11870,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1473</t>
+          <t xml:space="preserve">1475</t>
         </is>
       </c>
     </row>
@@ -11833,7 +11907,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477</t>
+          <t xml:space="preserve">1479</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11944,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478</t>
+          <t xml:space="preserve">1480</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11981,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1479</t>
+          <t xml:space="preserve">1481</t>
         </is>
       </c>
     </row>
@@ -11944,7 +12018,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1480</t>
+          <t xml:space="preserve">1482</t>
         </is>
       </c>
     </row>
@@ -11981,7 +12055,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1481</t>
+          <t xml:space="preserve">1483</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13220,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463</t>
+          <t xml:space="preserve">1465</t>
         </is>
       </c>
     </row>
@@ -13173,7 +13247,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1464</t>
+          <t xml:space="preserve">1466</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13274,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1465</t>
+          <t xml:space="preserve">1467</t>
         </is>
       </c>
     </row>
@@ -13227,7 +13301,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466</t>
+          <t xml:space="preserve">1468</t>
         </is>
       </c>
     </row>
@@ -13254,7 +13328,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1467</t>
+          <t xml:space="preserve">1469</t>
         </is>
       </c>
     </row>
@@ -13281,7 +13355,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468</t>
+          <t xml:space="preserve">1470</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13382,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469</t>
+          <t xml:space="preserve">1471</t>
         </is>
       </c>
     </row>
@@ -13335,7 +13409,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1470</t>
+          <t xml:space="preserve">1472</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13436,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1471</t>
+          <t xml:space="preserve">1473</t>
         </is>
       </c>
     </row>
@@ -13389,7 +13463,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1472</t>
+          <t xml:space="preserve">1474</t>
         </is>
       </c>
     </row>
@@ -13416,7 +13490,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1473</t>
+          <t xml:space="preserve">1475</t>
         </is>
       </c>
     </row>
@@ -13443,7 +13517,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477</t>
+          <t xml:space="preserve">1479</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13544,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478</t>
+          <t xml:space="preserve">1480</t>
         </is>
       </c>
     </row>
@@ -13497,7 +13571,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1479</t>
+          <t xml:space="preserve">1481</t>
         </is>
       </c>
     </row>
@@ -13524,7 +13598,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1480</t>
+          <t xml:space="preserve">1482</t>
         </is>
       </c>
     </row>
@@ -13551,7 +13625,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1481</t>
+          <t xml:space="preserve">1483</t>
         </is>
       </c>
     </row>
@@ -13578,7 +13652,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">2652</t>
         </is>
       </c>
     </row>
@@ -13605,7 +13679,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2651</t>
+          <t xml:space="preserve">2653</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13706,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2652</t>
+          <t xml:space="preserve">2654</t>
         </is>
       </c>
     </row>
@@ -13659,7 +13733,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2653</t>
+          <t xml:space="preserve">2655</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13760,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2654</t>
+          <t xml:space="preserve">2656</t>
         </is>
       </c>
     </row>
@@ -13713,7 +13787,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2655</t>
+          <t xml:space="preserve">2657</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13814,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656</t>
+          <t xml:space="preserve">2658</t>
         </is>
       </c>
     </row>
@@ -13767,7 +13841,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657</t>
+          <t xml:space="preserve">2659</t>
         </is>
       </c>
     </row>
@@ -13794,7 +13868,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2658</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
     </row>
@@ -13821,7 +13895,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2659</t>
+          <t xml:space="preserve">2661</t>
         </is>
       </c>
     </row>
@@ -13848,7 +13922,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2662</t>
         </is>
       </c>
     </row>
@@ -13875,7 +13949,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2661</t>
+          <t xml:space="preserve">2663</t>
         </is>
       </c>
     </row>
@@ -13902,7 +13976,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662</t>
+          <t xml:space="preserve">2664</t>
         </is>
       </c>
     </row>
@@ -13929,7 +14003,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2663</t>
+          <t xml:space="preserve">2665</t>
         </is>
       </c>
     </row>
@@ -13956,7 +14030,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2664</t>
+          <t xml:space="preserve">2666</t>
         </is>
       </c>
     </row>
@@ -13983,7 +14057,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2665</t>
+          <t xml:space="preserve">2667</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14084,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666</t>
+          <t xml:space="preserve">2668</t>
         </is>
       </c>
     </row>
@@ -14037,7 +14111,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2667</t>
+          <t xml:space="preserve">2669</t>
         </is>
       </c>
     </row>
@@ -14064,7 +14138,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2668</t>
+          <t xml:space="preserve">2670</t>
         </is>
       </c>
     </row>
@@ -14091,7 +14165,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2669</t>
+          <t xml:space="preserve">2671</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14192,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2670</t>
+          <t xml:space="preserve">2672</t>
         </is>
       </c>
     </row>
@@ -14145,7 +14219,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2671</t>
+          <t xml:space="preserve">2673</t>
         </is>
       </c>
     </row>
@@ -14172,7 +14246,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2672</t>
+          <t xml:space="preserve">2674</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14273,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2673</t>
+          <t xml:space="preserve">2675</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15559,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1372</t>
+          <t xml:space="preserve">1374</t>
         </is>
       </c>
     </row>
@@ -15507,7 +15581,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1373</t>
+          <t xml:space="preserve">1375</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15603,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1376</t>
+          <t xml:space="preserve">1378</t>
         </is>
       </c>
     </row>
@@ -15551,7 +15625,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1378</t>
+          <t xml:space="preserve">1380</t>
         </is>
       </c>
     </row>
@@ -15573,7 +15647,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1379</t>
+          <t xml:space="preserve">1381</t>
         </is>
       </c>
     </row>
@@ -15595,7 +15669,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1380</t>
+          <t xml:space="preserve">1382</t>
         </is>
       </c>
     </row>
@@ -15617,7 +15691,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1382</t>
+          <t xml:space="preserve">1384</t>
         </is>
       </c>
     </row>
@@ -15639,7 +15713,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1448</t>
+          <t xml:space="preserve">1450</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15735,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452</t>
+          <t xml:space="preserve">1454</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15757,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1453</t>
+          <t xml:space="preserve">1455</t>
         </is>
       </c>
     </row>
@@ -15705,7 +15779,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1454</t>
+          <t xml:space="preserve">1456</t>
         </is>
       </c>
     </row>
@@ -15727,7 +15801,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463</t>
+          <t xml:space="preserve">1465</t>
         </is>
       </c>
     </row>
@@ -15749,7 +15823,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1464</t>
+          <t xml:space="preserve">1466</t>
         </is>
       </c>
     </row>
@@ -15771,7 +15845,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1465</t>
+          <t xml:space="preserve">1467</t>
         </is>
       </c>
     </row>
@@ -15793,7 +15867,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466</t>
+          <t xml:space="preserve">1468</t>
         </is>
       </c>
     </row>
@@ -15815,7 +15889,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1467</t>
+          <t xml:space="preserve">1469</t>
         </is>
       </c>
     </row>
@@ -15837,7 +15911,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468</t>
+          <t xml:space="preserve">1470</t>
         </is>
       </c>
     </row>
@@ -15859,7 +15933,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469</t>
+          <t xml:space="preserve">1471</t>
         </is>
       </c>
     </row>
@@ -15881,7 +15955,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1470</t>
+          <t xml:space="preserve">1472</t>
         </is>
       </c>
     </row>
@@ -15903,7 +15977,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1471</t>
+          <t xml:space="preserve">1473</t>
         </is>
       </c>
     </row>
@@ -15925,7 +15999,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1472</t>
+          <t xml:space="preserve">1474</t>
         </is>
       </c>
     </row>
@@ -15947,7 +16021,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1473</t>
+          <t xml:space="preserve">1475</t>
         </is>
       </c>
     </row>
@@ -15969,7 +16043,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477</t>
+          <t xml:space="preserve">1479</t>
         </is>
       </c>
     </row>
@@ -15991,7 +16065,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478</t>
+          <t xml:space="preserve">1480</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16087,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1479</t>
+          <t xml:space="preserve">1481</t>
         </is>
       </c>
     </row>
@@ -16035,7 +16109,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1480</t>
+          <t xml:space="preserve">1482</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16131,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1481</t>
+          <t xml:space="preserve">1483</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16153,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1504</t>
+          <t xml:space="preserve">1506</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16175,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1514</t>
+          <t xml:space="preserve">1516</t>
         </is>
       </c>
     </row>
@@ -16123,7 +16197,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1524</t>
+          <t xml:space="preserve">1526</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16219,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1539</t>
+          <t xml:space="preserve">1541</t>
         </is>
       </c>
     </row>
@@ -16167,7 +16241,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1549</t>
+          <t xml:space="preserve">1551</t>
         </is>
       </c>
     </row>
@@ -16189,7 +16263,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1559</t>
+          <t xml:space="preserve">1561</t>
         </is>
       </c>
     </row>
@@ -16211,7 +16285,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1569</t>
+          <t xml:space="preserve">1571</t>
         </is>
       </c>
     </row>
@@ -16233,7 +16307,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1579</t>
+          <t xml:space="preserve">1581</t>
         </is>
       </c>
     </row>
@@ -16255,7 +16329,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1589</t>
+          <t xml:space="preserve">1591</t>
         </is>
       </c>
     </row>
@@ -16277,7 +16351,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1599</t>
+          <t xml:space="preserve">1601</t>
         </is>
       </c>
     </row>
@@ -16299,7 +16373,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1609</t>
+          <t xml:space="preserve">1611</t>
         </is>
       </c>
     </row>
@@ -16321,7 +16395,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619</t>
+          <t xml:space="preserve">1621</t>
         </is>
       </c>
     </row>
@@ -16343,7 +16417,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1629</t>
+          <t xml:space="preserve">1631</t>
         </is>
       </c>
     </row>
@@ -16365,7 +16439,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1639</t>
+          <t xml:space="preserve">1641</t>
         </is>
       </c>
     </row>
@@ -16387,7 +16461,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649</t>
+          <t xml:space="preserve">1651</t>
         </is>
       </c>
     </row>
@@ -16409,7 +16483,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1659</t>
+          <t xml:space="preserve">1661</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16505,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1669</t>
+          <t xml:space="preserve">1671</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16527,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679</t>
+          <t xml:space="preserve">1681</t>
         </is>
       </c>
     </row>
@@ -16475,7 +16549,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694</t>
+          <t xml:space="preserve">1696</t>
         </is>
       </c>
     </row>
@@ -16497,7 +16571,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1704</t>
+          <t xml:space="preserve">1706</t>
         </is>
       </c>
     </row>
@@ -16519,7 +16593,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1714</t>
+          <t xml:space="preserve">1716</t>
         </is>
       </c>
     </row>
@@ -16541,7 +16615,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1724</t>
+          <t xml:space="preserve">1726</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16637,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1734</t>
+          <t xml:space="preserve">1736</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16659,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1744</t>
+          <t xml:space="preserve">1746</t>
         </is>
       </c>
     </row>
@@ -16607,7 +16681,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1754</t>
+          <t xml:space="preserve">1756</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16703,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1764</t>
+          <t xml:space="preserve">1766</t>
         </is>
       </c>
     </row>
@@ -16651,7 +16725,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1774</t>
+          <t xml:space="preserve">1776</t>
         </is>
       </c>
     </row>
@@ -16673,7 +16747,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1789</t>
+          <t xml:space="preserve">1791</t>
         </is>
       </c>
     </row>
@@ -16695,7 +16769,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1799</t>
+          <t xml:space="preserve">1801</t>
         </is>
       </c>
     </row>
@@ -16717,7 +16791,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809</t>
+          <t xml:space="preserve">1811</t>
         </is>
       </c>
     </row>
@@ -16739,7 +16813,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819</t>
+          <t xml:space="preserve">1821</t>
         </is>
       </c>
     </row>
@@ -16761,7 +16835,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829</t>
+          <t xml:space="preserve">1831</t>
         </is>
       </c>
     </row>
@@ -16783,7 +16857,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839</t>
+          <t xml:space="preserve">1841</t>
         </is>
       </c>
     </row>
@@ -16805,7 +16879,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849</t>
+          <t xml:space="preserve">1851</t>
         </is>
       </c>
     </row>
@@ -16827,7 +16901,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859</t>
+          <t xml:space="preserve">1861</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16923,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1869</t>
+          <t xml:space="preserve">1871</t>
         </is>
       </c>
     </row>
@@ -16871,7 +16945,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879</t>
+          <t xml:space="preserve">1881</t>
         </is>
       </c>
     </row>
@@ -16893,7 +16967,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1889</t>
+          <t xml:space="preserve">1891</t>
         </is>
       </c>
     </row>
@@ -16915,7 +16989,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899</t>
+          <t xml:space="preserve">1901</t>
         </is>
       </c>
     </row>
@@ -16937,7 +17011,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909</t>
+          <t xml:space="preserve">1911</t>
         </is>
       </c>
     </row>
@@ -16959,7 +17033,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924</t>
+          <t xml:space="preserve">1926</t>
         </is>
       </c>
     </row>
@@ -16981,7 +17055,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1934</t>
+          <t xml:space="preserve">1936</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17077,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944</t>
+          <t xml:space="preserve">1946</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17099,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1954</t>
+          <t xml:space="preserve">1956</t>
         </is>
       </c>
     </row>
@@ -17047,7 +17121,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1964</t>
+          <t xml:space="preserve">1966</t>
         </is>
       </c>
     </row>
@@ -17069,7 +17143,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974</t>
+          <t xml:space="preserve">1976</t>
         </is>
       </c>
     </row>
@@ -17091,7 +17165,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1984</t>
+          <t xml:space="preserve">1986</t>
         </is>
       </c>
     </row>
@@ -17113,7 +17187,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1994</t>
+          <t xml:space="preserve">1996</t>
         </is>
       </c>
     </row>
@@ -17135,7 +17209,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004</t>
+          <t xml:space="preserve">2006</t>
         </is>
       </c>
     </row>
@@ -17157,7 +17231,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014</t>
+          <t xml:space="preserve">2016</t>
         </is>
       </c>
     </row>
@@ -17179,7 +17253,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024</t>
+          <t xml:space="preserve">2026</t>
         </is>
       </c>
     </row>
@@ -17201,7 +17275,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034</t>
+          <t xml:space="preserve">2036</t>
         </is>
       </c>
     </row>
@@ -17223,7 +17297,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2044</t>
+          <t xml:space="preserve">2046</t>
         </is>
       </c>
     </row>
@@ -17245,7 +17319,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2054</t>
+          <t xml:space="preserve">2056</t>
         </is>
       </c>
     </row>
@@ -17267,7 +17341,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064</t>
+          <t xml:space="preserve">2066</t>
         </is>
       </c>
     </row>
@@ -17289,7 +17363,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2074</t>
+          <t xml:space="preserve">2076</t>
         </is>
       </c>
     </row>
@@ -17311,7 +17385,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2084</t>
+          <t xml:space="preserve">2086</t>
         </is>
       </c>
     </row>
@@ -17333,7 +17407,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2094</t>
+          <t xml:space="preserve">2096</t>
         </is>
       </c>
     </row>
@@ -17355,7 +17429,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2104</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
     </row>
@@ -17377,7 +17451,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114</t>
+          <t xml:space="preserve">2116</t>
         </is>
       </c>
     </row>
@@ -17399,7 +17473,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2124</t>
+          <t xml:space="preserve">2126</t>
         </is>
       </c>
     </row>
@@ -17421,7 +17495,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134</t>
+          <t xml:space="preserve">2136</t>
         </is>
       </c>
     </row>
@@ -17443,7 +17517,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2144</t>
+          <t xml:space="preserve">2146</t>
         </is>
       </c>
     </row>
@@ -17465,7 +17539,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2154</t>
+          <t xml:space="preserve">2156</t>
         </is>
       </c>
     </row>
@@ -17487,7 +17561,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164</t>
+          <t xml:space="preserve">2166</t>
         </is>
       </c>
     </row>
@@ -17509,7 +17583,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174</t>
+          <t xml:space="preserve">2176</t>
         </is>
       </c>
     </row>
@@ -17531,7 +17605,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189</t>
+          <t xml:space="preserve">2191</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17627,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204</t>
+          <t xml:space="preserve">2206</t>
         </is>
       </c>
     </row>
@@ -17575,7 +17649,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214</t>
+          <t xml:space="preserve">2216</t>
         </is>
       </c>
     </row>
@@ -17597,7 +17671,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224</t>
+          <t xml:space="preserve">2226</t>
         </is>
       </c>
     </row>
@@ -17619,7 +17693,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2234</t>
+          <t xml:space="preserve">2236</t>
         </is>
       </c>
     </row>
@@ -17641,7 +17715,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2244</t>
+          <t xml:space="preserve">2246</t>
         </is>
       </c>
     </row>
@@ -17663,7 +17737,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2254</t>
+          <t xml:space="preserve">2256</t>
         </is>
       </c>
     </row>
@@ -17685,7 +17759,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2264</t>
+          <t xml:space="preserve">2266</t>
         </is>
       </c>
     </row>
@@ -17707,7 +17781,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2281</t>
+          <t xml:space="preserve">2283</t>
         </is>
       </c>
     </row>
@@ -17729,7 +17803,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2291</t>
+          <t xml:space="preserve">2293</t>
         </is>
       </c>
     </row>
@@ -17751,7 +17825,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301</t>
+          <t xml:space="preserve">2303</t>
         </is>
       </c>
     </row>
@@ -17773,7 +17847,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2311</t>
+          <t xml:space="preserve">2313</t>
         </is>
       </c>
     </row>
@@ -17795,7 +17869,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2321</t>
+          <t xml:space="preserve">2323</t>
         </is>
       </c>
     </row>
@@ -17817,7 +17891,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2331</t>
+          <t xml:space="preserve">2333</t>
         </is>
       </c>
     </row>
@@ -17839,7 +17913,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2341</t>
+          <t xml:space="preserve">2343</t>
         </is>
       </c>
     </row>
@@ -17861,7 +17935,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2351</t>
+          <t xml:space="preserve">2353</t>
         </is>
       </c>
     </row>
@@ -17883,7 +17957,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2361</t>
+          <t xml:space="preserve">2363</t>
         </is>
       </c>
     </row>
@@ -17905,7 +17979,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2710</t>
+          <t xml:space="preserve">2712</t>
         </is>
       </c>
     </row>
@@ -17927,7 +18001,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2711</t>
+          <t xml:space="preserve">2713</t>
         </is>
       </c>
     </row>
@@ -17949,7 +18023,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2712</t>
+          <t xml:space="preserve">2714</t>
         </is>
       </c>
     </row>
@@ -17971,7 +18045,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2713</t>
+          <t xml:space="preserve">2715</t>
         </is>
       </c>
     </row>
@@ -17993,7 +18067,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2714</t>
+          <t xml:space="preserve">2716</t>
         </is>
       </c>
     </row>
@@ -18015,7 +18089,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2715</t>
+          <t xml:space="preserve">2717</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18111,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2716</t>
+          <t xml:space="preserve">2718</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18133,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2717</t>
+          <t xml:space="preserve">2719</t>
         </is>
       </c>
     </row>

--- a/SHAPE-Lab-Website-Content.xlsx
+++ b/SHAPE-Lab-Website-Content.xlsx
@@ -461,12 +461,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mission</t>
+          <t xml:space="preserve">research</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mission Item</t>
+          <t xml:space="preserve">Section Title</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -476,7 +476,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Additive Manufacturing: Design, Material Development and Biomedical Applications</t>
+          <t xml:space="preserve">Projects across the additive manufacturing landscape.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -491,19 +491,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1262</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mission</t>
+          <t xml:space="preserve">research</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mission Item</t>
+          <t xml:space="preserve">Section Lede</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybrid Manufacturing</t>
+          <t xml:space="preserve">Research highlights connect students, tools, manufacturing equipment, and publications across additive manufacturing, hybrid manufacturing, binder jetting, biomedical AM, and sand printing for casting.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -528,19 +528,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1262</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mission</t>
+          <t xml:space="preserve">team</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mission Item</t>
+          <t xml:space="preserve">Section Title</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sand-Printing for Metal Casting</t>
+          <t xml:space="preserve">Team</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -565,14 +565,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1393</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">research</t>
+          <t xml:space="preserve">news</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projects across the additive manufacturing landscape.</t>
+          <t xml:space="preserve">What's happening at SHAPE.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -602,19 +602,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129</t>
+          <t xml:space="preserve">1540</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">research</t>
+          <t xml:space="preserve">sponsors</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Lede</t>
+          <t xml:space="preserve">Section Title</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research highlights connect students, tools, manufacturing equipment, and publications across additive manufacturing, hybrid manufacturing, binder jetting, biomedical AM, and sand printing for casting.</t>
+          <t xml:space="preserve">Sponsors and partners.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -639,19 +639,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129</t>
+          <t xml:space="preserve">1655</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">team</t>
+          <t xml:space="preserve">sponsors</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Title</t>
+          <t xml:space="preserve">Section Lede</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Team</t>
+          <t xml:space="preserve">SHAPE Lab research is built around collaborations that connect manufacturing science to real application needs.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -676,14 +676,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199</t>
+          <t xml:space="preserve">1655</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">news</t>
+          <t xml:space="preserve">publications</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">What's happening at SHAPE.</t>
+          <t xml:space="preserve">Manufacturing research outputs.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -713,19 +713,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1346</t>
+          <t xml:space="preserve">1682</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">sponsors</t>
+          <t xml:space="preserve">publications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Title</t>
+          <t xml:space="preserve">Section Lede</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sponsors and partners.</t>
+          <t xml:space="preserve">Papers from the official S.H.A.P.E. Lab publication list, grouped by research area and publication type.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -750,19 +750,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1461</t>
+          <t xml:space="preserve">1682</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">sponsors</t>
+          <t xml:space="preserve">gallery</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Lede</t>
+          <t xml:space="preserve">Section Title</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab research is built around collaborations that connect manufacturing science to real application needs.</t>
+          <t xml:space="preserve">Snapshots from SHAPE Lab.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -787,19 +787,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1461</t>
+          <t xml:space="preserve">2838</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">publications</t>
+          <t xml:space="preserve">gallery</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Title</t>
+          <t xml:space="preserve">Section Lede</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing research outputs.</t>
+          <t xml:space="preserve">Photos from lab events, student milestones, and research moments.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -824,19 +824,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488</t>
+          <t xml:space="preserve">2838</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">publications</t>
+          <t xml:space="preserve">contact</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Lede</t>
+          <t xml:space="preserve">Section Title</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papers from the official S.H.A.P.E. Lab publication list, grouped by research area and publication type.</t>
+          <t xml:space="preserve">Connect with S.H.A.P.E. Lab.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -861,19 +861,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488</t>
+          <t xml:space="preserve">2879</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery</t>
+          <t xml:space="preserve">contact</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Title</t>
+          <t xml:space="preserve">Section Lede</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snapshots from SHAPE Lab.</t>
+          <t xml:space="preserve">The lab works across additive manufacturing, hybrid process engineering, 3D sand printing, biomedical AM, and multi-material metal systems.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -898,118 +898,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2644</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gallery</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Section Lede</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Photos from lab events, student milestones, and research moments.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2644</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">contact</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Section Title</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Connect with S.H.A.P.E. Lab.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2685</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">contact</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Section Lede</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The lab works across additive manufacturing, hybrid process engineering, 3D sand printing, biomedical AM, and multi-material metal systems.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2685</t>
+          <t xml:space="preserve">2879</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1209,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sand Casting</t>
+          <t xml:space="preserve">3D Sand Printing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1330,207 +1219,170 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Increases casting design complexity, improves mechanical properties, and enables earlier defect identification.</t>
+          <t xml:space="preserve">3D sand printing expands casting design complexity, improves mechanical properties, and supports earlier identification of defects.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/20250625_125103-1024x768.jpg</t>
+          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/Sand-Casting-1.png</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3D sand printing research</t>
+          <t xml:space="preserve">Advancing metal casting process via 3D sand printing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140</t>
+          <t xml:space="preserve">1279</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sand Casting</t>
+          <t xml:space="preserve">Hybrid Manufacturing</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metal Casting</t>
+          <t xml:space="preserve">AM + Mass Finishing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Printed molds, cores, and process design</t>
+          <t xml:space="preserve">Additive Manufacturing + Mass Finishing Hybrid Manufacturing System</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Printed sand tooling supports complex thermal, geometric, and production-aware casting workflows.</t>
+          <t xml:space="preserve">AM+MF research improves metal AM surface finish and cost efficiency through mass finishing technologies and surface characterization.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/IMG_5766.jpg</t>
+          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/CDF.png</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casting process equipment</t>
+          <t xml:space="preserve">Additive Manufacturing plus Mass Finishing Hybrid Manufacturing System</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148</t>
+          <t xml:space="preserve">1303</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sand Casting</t>
+          <t xml:space="preserve">Multi-Material Additive Manufacturing</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Process Systems</t>
+          <t xml:space="preserve">Laser Powder Bed Fusion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing-centered research environments</t>
+          <t xml:space="preserve">Multi-Material Laser Powder Bed Fusion of Complex Structures</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Students connect design, simulation, lab equipment, and inspection in complete research loops.</t>
+          <t xml:space="preserve">Multi-material L-PBF research develops complex structures with reduced material use and characterized microstructure.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/SHAPE-Lab-2018.jpg</t>
+          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/TPMS1.png</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab group</t>
+          <t xml:space="preserve">Multi-material laser powder bed fusion of complex structures</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156</t>
+          <t xml:space="preserve">1328</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybrid Manufacturing</t>
+          <t xml:space="preserve">Multi-Material Additive Manufacturing</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybrid Manufacturing</t>
+          <t xml:space="preserve">TPMS Structures</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Additive Manufacturing + Mass Finishing Hybrid Manufacturing System</t>
+          <t xml:space="preserve">Design of Non-Pneumatic Tires (NPT) using TPMS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Improving metal AM surface finish and cost efficiency through post-processing and characterization.</t>
+          <t xml:space="preserve">TPMS-based non-pneumatic tire research develops localized stiffness through lattice design and mechanical testing.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/Additive_Manufacturing-G.Manogharan.jpg</t>
+          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/TPMS2-e1681999465376.png</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Additive manufacturing equipment</t>
+          <t xml:space="preserve">Design of non-pneumatic tires using TPMS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170</t>
+          <t xml:space="preserve">1345</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybrid Manufacturing</t>
+          <t xml:space="preserve">Binder Jet Additive Manufacturing</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DfAM</t>
+          <t xml:space="preserve">Binder Jetting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Design for Additive Manufacturing</t>
+          <t xml:space="preserve">Study of multimodal powder-binder interaction in binder jetting process</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Novel design rules, lattice structures, and optimization methods for process-aware parts.</t>
+          <t xml:space="preserve">Binder jetting research examines how powder packing and droplet velocity affect binder penetration, spreading, and processing behavior.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/250096-psn-tpms_blueorange-300x225.jpg</t>
+          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/BJAM2.png</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TPMS structure</t>
+          <t xml:space="preserve">Study of multimodal powder-binder interaction in binder jetting process</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hybrid Manufacturing</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Biomedical AM</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Patient-specific and orthopedic additive manufacturing</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High-fidelity biomedical geometries, biodegradable implants, and controlled scaffold structures.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/penn-state-news-lg1.png</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Penn State engineering feature</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1186</t>
+          <t xml:space="preserve">1370</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4056,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499</t>
+          <t xml:space="preserve">1693</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4088,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1509</t>
+          <t xml:space="preserve">1703</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4120,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1519</t>
+          <t xml:space="preserve">1713</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4152,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1534</t>
+          <t xml:space="preserve">1728</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4184,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544</t>
+          <t xml:space="preserve">1738</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4216,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1554</t>
+          <t xml:space="preserve">1748</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4248,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1564</t>
+          <t xml:space="preserve">1758</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4280,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1574</t>
+          <t xml:space="preserve">1768</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4312,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1584</t>
+          <t xml:space="preserve">1778</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4344,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1594</t>
+          <t xml:space="preserve">1788</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4376,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1604</t>
+          <t xml:space="preserve">1798</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4408,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614</t>
+          <t xml:space="preserve">1808</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4440,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1624</t>
+          <t xml:space="preserve">1818</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4472,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1634</t>
+          <t xml:space="preserve">1828</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4504,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644</t>
+          <t xml:space="preserve">1838</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4536,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654</t>
+          <t xml:space="preserve">1848</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4568,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664</t>
+          <t xml:space="preserve">1858</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4600,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1674</t>
+          <t xml:space="preserve">1868</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4632,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689</t>
+          <t xml:space="preserve">1883</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4664,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1699</t>
+          <t xml:space="preserve">1893</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4696,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1709</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4728,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719</t>
+          <t xml:space="preserve">1913</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4760,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1729</t>
+          <t xml:space="preserve">1923</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4792,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1739</t>
+          <t xml:space="preserve">1933</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4824,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1749</t>
+          <t xml:space="preserve">1943</t>
         </is>
       </c>
     </row>
@@ -5004,7 +4856,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1759</t>
+          <t xml:space="preserve">1953</t>
         </is>
       </c>
     </row>
@@ -5036,7 +4888,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1769</t>
+          <t xml:space="preserve">1963</t>
         </is>
       </c>
     </row>
@@ -5068,7 +4920,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1784</t>
+          <t xml:space="preserve">1978</t>
         </is>
       </c>
     </row>
@@ -5100,7 +4952,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794</t>
+          <t xml:space="preserve">1988</t>
         </is>
       </c>
     </row>
@@ -5132,7 +4984,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804</t>
+          <t xml:space="preserve">1998</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5016,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814</t>
+          <t xml:space="preserve">2008</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5048,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1824</t>
+          <t xml:space="preserve">2018</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5080,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834</t>
+          <t xml:space="preserve">2028</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5112,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844</t>
+          <t xml:space="preserve">2038</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5144,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854</t>
+          <t xml:space="preserve">2048</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5176,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864</t>
+          <t xml:space="preserve">2058</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5208,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874</t>
+          <t xml:space="preserve">2068</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5240,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884</t>
+          <t xml:space="preserve">2078</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5272,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894</t>
+          <t xml:space="preserve">2088</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5304,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1904</t>
+          <t xml:space="preserve">2098</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5336,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919</t>
+          <t xml:space="preserve">2113</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5368,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929</t>
+          <t xml:space="preserve">2123</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5400,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1939</t>
+          <t xml:space="preserve">2133</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5432,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1949</t>
+          <t xml:space="preserve">2143</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5464,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1959</t>
+          <t xml:space="preserve">2153</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5496,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1969</t>
+          <t xml:space="preserve">2163</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5528,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1979</t>
+          <t xml:space="preserve">2173</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5560,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1989</t>
+          <t xml:space="preserve">2183</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5592,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1999</t>
+          <t xml:space="preserve">2193</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5624,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009</t>
+          <t xml:space="preserve">2203</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5656,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019</t>
+          <t xml:space="preserve">2213</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5688,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029</t>
+          <t xml:space="preserve">2223</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5720,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2039</t>
+          <t xml:space="preserve">2233</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5752,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2049</t>
+          <t xml:space="preserve">2243</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5784,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2059</t>
+          <t xml:space="preserve">2253</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5816,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069</t>
+          <t xml:space="preserve">2263</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5848,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079</t>
+          <t xml:space="preserve">2273</t>
         </is>
       </c>
     </row>
@@ -6028,7 +5880,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089</t>
+          <t xml:space="preserve">2283</t>
         </is>
       </c>
     </row>
@@ -6060,7 +5912,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099</t>
+          <t xml:space="preserve">2293</t>
         </is>
       </c>
     </row>
@@ -6092,7 +5944,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2109</t>
+          <t xml:space="preserve">2303</t>
         </is>
       </c>
     </row>
@@ -6124,7 +5976,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119</t>
+          <t xml:space="preserve">2313</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6008,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2129</t>
+          <t xml:space="preserve">2323</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6040,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2139</t>
+          <t xml:space="preserve">2333</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6072,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2149</t>
+          <t xml:space="preserve">2343</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6104,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159</t>
+          <t xml:space="preserve">2353</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6136,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169</t>
+          <t xml:space="preserve">2363</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6168,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184</t>
+          <t xml:space="preserve">2378</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6200,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2199</t>
+          <t xml:space="preserve">2393</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6232,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209</t>
+          <t xml:space="preserve">2403</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6264,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219</t>
+          <t xml:space="preserve">2413</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6296,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229</t>
+          <t xml:space="preserve">2423</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6328,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239</t>
+          <t xml:space="preserve">2433</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6360,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2249</t>
+          <t xml:space="preserve">2443</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6392,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2259</t>
+          <t xml:space="preserve">2453</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6424,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2269</t>
+          <t xml:space="preserve">2463</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6456,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2276</t>
+          <t xml:space="preserve">2470</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6488,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2286</t>
+          <t xml:space="preserve">2480</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6520,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2296</t>
+          <t xml:space="preserve">2490</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6552,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2306</t>
+          <t xml:space="preserve">2500</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6584,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2316</t>
+          <t xml:space="preserve">2510</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6616,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2326</t>
+          <t xml:space="preserve">2520</t>
         </is>
       </c>
     </row>
@@ -6796,7 +6648,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2336</t>
+          <t xml:space="preserve">2530</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6680,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2346</t>
+          <t xml:space="preserve">2540</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6712,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356</t>
+          <t xml:space="preserve">2550</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6744,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366</t>
+          <t xml:space="preserve">2560</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6776,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2373</t>
+          <t xml:space="preserve">2567</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6808,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380</t>
+          <t xml:space="preserve">2574</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6840,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2387</t>
+          <t xml:space="preserve">2581</t>
         </is>
       </c>
     </row>
@@ -7020,7 +6872,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2394</t>
+          <t xml:space="preserve">2588</t>
         </is>
       </c>
     </row>
@@ -7052,7 +6904,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401</t>
+          <t xml:space="preserve">2595</t>
         </is>
       </c>
     </row>
@@ -7084,7 +6936,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408</t>
+          <t xml:space="preserve">2602</t>
         </is>
       </c>
     </row>
@@ -7116,7 +6968,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2415</t>
+          <t xml:space="preserve">2609</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7000,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2422</t>
+          <t xml:space="preserve">2616</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7032,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2429</t>
+          <t xml:space="preserve">2623</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7064,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2436</t>
+          <t xml:space="preserve">2630</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7096,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2443</t>
+          <t xml:space="preserve">2637</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7128,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2450</t>
+          <t xml:space="preserve">2644</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7160,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2457</t>
+          <t xml:space="preserve">2651</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7192,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2464</t>
+          <t xml:space="preserve">2658</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7224,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2471</t>
+          <t xml:space="preserve">2665</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7256,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2478</t>
+          <t xml:space="preserve">2672</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7288,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2485</t>
+          <t xml:space="preserve">2679</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7320,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492</t>
+          <t xml:space="preserve">2686</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7352,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2499</t>
+          <t xml:space="preserve">2693</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7384,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2506</t>
+          <t xml:space="preserve">2700</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7416,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518</t>
+          <t xml:space="preserve">2712</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7448,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2525</t>
+          <t xml:space="preserve">2719</t>
         </is>
       </c>
     </row>
@@ -7628,7 +7480,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2532</t>
+          <t xml:space="preserve">2726</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7512,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539</t>
+          <t xml:space="preserve">2733</t>
         </is>
       </c>
     </row>
@@ -7692,7 +7544,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2546</t>
+          <t xml:space="preserve">2740</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7576,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2553</t>
+          <t xml:space="preserve">2747</t>
         </is>
       </c>
     </row>
@@ -7756,7 +7608,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2560</t>
+          <t xml:space="preserve">2754</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7640,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2567</t>
+          <t xml:space="preserve">2761</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7672,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2574</t>
+          <t xml:space="preserve">2768</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7704,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2581</t>
+          <t xml:space="preserve">2775</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7736,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2588</t>
+          <t xml:space="preserve">2782</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7768,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2595</t>
+          <t xml:space="preserve">2789</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7800,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2602</t>
+          <t xml:space="preserve">2796</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7832,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2609</t>
+          <t xml:space="preserve">2803</t>
         </is>
       </c>
     </row>
@@ -8012,7 +7864,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2616</t>
+          <t xml:space="preserve">2810</t>
         </is>
       </c>
     </row>
@@ -8044,7 +7896,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2623</t>
+          <t xml:space="preserve">2817</t>
         </is>
       </c>
     </row>
@@ -8076,7 +7928,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630</t>
+          <t xml:space="preserve">2824</t>
         </is>
       </c>
     </row>
@@ -8160,7 +8012,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352</t>
+          <t xml:space="preserve">1546</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8049,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1356</t>
+          <t xml:space="preserve">1550</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8086,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1360</t>
+          <t xml:space="preserve">1554</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8123,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1364</t>
+          <t xml:space="preserve">1558</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8160,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1372</t>
+          <t xml:space="preserve">1566</t>
         </is>
       </c>
     </row>
@@ -8345,7 +8197,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1373</t>
+          <t xml:space="preserve">1567</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8234,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1374</t>
+          <t xml:space="preserve">1568</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8271,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375</t>
+          <t xml:space="preserve">1569</t>
         </is>
       </c>
     </row>
@@ -8456,7 +8308,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1376</t>
+          <t xml:space="preserve">1570</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8345,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1377</t>
+          <t xml:space="preserve">1571</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8382,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1378</t>
+          <t xml:space="preserve">1572</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8419,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1379</t>
+          <t xml:space="preserve">1573</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8456,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1380</t>
+          <t xml:space="preserve">1574</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8493,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1381</t>
+          <t xml:space="preserve">1575</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8530,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1382</t>
+          <t xml:space="preserve">1576</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8567,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1383</t>
+          <t xml:space="preserve">1577</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8604,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1384</t>
+          <t xml:space="preserve">1578</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8641,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385</t>
+          <t xml:space="preserve">1579</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8678,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1386</t>
+          <t xml:space="preserve">1580</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8715,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1387</t>
+          <t xml:space="preserve">1581</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8752,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388</t>
+          <t xml:space="preserve">1582</t>
         </is>
       </c>
     </row>
@@ -8937,7 +8789,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1389</t>
+          <t xml:space="preserve">1583</t>
         </is>
       </c>
     </row>
@@ -8974,7 +8826,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1390</t>
+          <t xml:space="preserve">1584</t>
         </is>
       </c>
     </row>
@@ -9011,7 +8863,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1391</t>
+          <t xml:space="preserve">1585</t>
         </is>
       </c>
     </row>
@@ -9048,7 +8900,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1392</t>
+          <t xml:space="preserve">1586</t>
         </is>
       </c>
     </row>
@@ -9085,7 +8937,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1393</t>
+          <t xml:space="preserve">1587</t>
         </is>
       </c>
     </row>
@@ -9122,7 +8974,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1394</t>
+          <t xml:space="preserve">1588</t>
         </is>
       </c>
     </row>
@@ -9159,7 +9011,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1395</t>
+          <t xml:space="preserve">1589</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9048,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1396</t>
+          <t xml:space="preserve">1590</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9085,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397</t>
+          <t xml:space="preserve">1591</t>
         </is>
       </c>
     </row>
@@ -9270,7 +9122,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398</t>
+          <t xml:space="preserve">1592</t>
         </is>
       </c>
     </row>
@@ -9307,7 +9159,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1399</t>
+          <t xml:space="preserve">1593</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9196,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400</t>
+          <t xml:space="preserve">1594</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9233,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1401</t>
+          <t xml:space="preserve">1595</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9270,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1402</t>
+          <t xml:space="preserve">1596</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9307,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403</t>
+          <t xml:space="preserve">1597</t>
         </is>
       </c>
     </row>
@@ -9492,7 +9344,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404</t>
+          <t xml:space="preserve">1598</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9381,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405</t>
+          <t xml:space="preserve">1599</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9418,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406</t>
+          <t xml:space="preserve">1600</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9455,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1407</t>
+          <t xml:space="preserve">1601</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9492,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408</t>
+          <t xml:space="preserve">1602</t>
         </is>
       </c>
     </row>
@@ -9677,7 +9529,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409</t>
+          <t xml:space="preserve">1603</t>
         </is>
       </c>
     </row>
@@ -9714,7 +9566,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1410</t>
+          <t xml:space="preserve">1604</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9603,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411</t>
+          <t xml:space="preserve">1605</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9640,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412</t>
+          <t xml:space="preserve">1606</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9677,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413</t>
+          <t xml:space="preserve">1607</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9714,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1414</t>
+          <t xml:space="preserve">1608</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9751,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1415</t>
+          <t xml:space="preserve">1609</t>
         </is>
       </c>
     </row>
@@ -9936,7 +9788,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416</t>
+          <t xml:space="preserve">1610</t>
         </is>
       </c>
     </row>
@@ -9973,7 +9825,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1417</t>
+          <t xml:space="preserve">1611</t>
         </is>
       </c>
     </row>
@@ -10010,7 +9862,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418</t>
+          <t xml:space="preserve">1612</t>
         </is>
       </c>
     </row>
@@ -10047,7 +9899,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1419</t>
+          <t xml:space="preserve">1613</t>
         </is>
       </c>
     </row>
@@ -10084,7 +9936,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420</t>
+          <t xml:space="preserve">1614</t>
         </is>
       </c>
     </row>
@@ -10121,7 +9973,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1421</t>
+          <t xml:space="preserve">1615</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10010,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1422</t>
+          <t xml:space="preserve">1616</t>
         </is>
       </c>
     </row>
@@ -10195,7 +10047,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1423</t>
+          <t xml:space="preserve">1617</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10084,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424</t>
+          <t xml:space="preserve">1618</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10121,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425</t>
+          <t xml:space="preserve">1619</t>
         </is>
       </c>
     </row>
@@ -10306,7 +10158,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426</t>
+          <t xml:space="preserve">1620</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10195,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427</t>
+          <t xml:space="preserve">1621</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10232,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428</t>
+          <t xml:space="preserve">1622</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10269,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429</t>
+          <t xml:space="preserve">1623</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10306,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1430</t>
+          <t xml:space="preserve">1624</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10343,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1431</t>
+          <t xml:space="preserve">1625</t>
         </is>
       </c>
     </row>
@@ -10528,7 +10380,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1432</t>
+          <t xml:space="preserve">1626</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10417,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1433</t>
+          <t xml:space="preserve">1627</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10454,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1434</t>
+          <t xml:space="preserve">1628</t>
         </is>
       </c>
     </row>
@@ -10639,7 +10491,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1435</t>
+          <t xml:space="preserve">1629</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10528,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1436</t>
+          <t xml:space="preserve">1630</t>
         </is>
       </c>
     </row>
@@ -10713,7 +10565,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437</t>
+          <t xml:space="preserve">1631</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10602,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1438</t>
+          <t xml:space="preserve">1632</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10639,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1439</t>
+          <t xml:space="preserve">1633</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10676,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440</t>
+          <t xml:space="preserve">1634</t>
         </is>
       </c>
     </row>
@@ -10861,7 +10713,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1441</t>
+          <t xml:space="preserve">1635</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10750,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442</t>
+          <t xml:space="preserve">1636</t>
         </is>
       </c>
     </row>
@@ -10935,7 +10787,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1443</t>
+          <t xml:space="preserve">1637</t>
         </is>
       </c>
     </row>
@@ -10972,7 +10824,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1444</t>
+          <t xml:space="preserve">1638</t>
         </is>
       </c>
     </row>
@@ -11009,7 +10861,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1445</t>
+          <t xml:space="preserve">1639</t>
         </is>
       </c>
     </row>
@@ -11046,7 +10898,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1446</t>
+          <t xml:space="preserve">1640</t>
         </is>
       </c>
     </row>
@@ -11083,7 +10935,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1447</t>
+          <t xml:space="preserve">1641</t>
         </is>
       </c>
     </row>
@@ -11120,7 +10972,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1448</t>
+          <t xml:space="preserve">1642</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11009,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1449</t>
+          <t xml:space="preserve">1643</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11046,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1450</t>
+          <t xml:space="preserve">1644</t>
         </is>
       </c>
     </row>
@@ -11231,7 +11083,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1451</t>
+          <t xml:space="preserve">1645</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11120,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452</t>
+          <t xml:space="preserve">1646</t>
         </is>
       </c>
     </row>
@@ -11305,7 +11157,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1453</t>
+          <t xml:space="preserve">1647</t>
         </is>
       </c>
     </row>
@@ -11342,7 +11194,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1454</t>
+          <t xml:space="preserve">1648</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11231,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455</t>
+          <t xml:space="preserve">1649</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11268,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1456</t>
+          <t xml:space="preserve">1650</t>
         </is>
       </c>
     </row>
@@ -11500,7 +11352,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1465</t>
+          <t xml:space="preserve">1659</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11389,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466</t>
+          <t xml:space="preserve">1660</t>
         </is>
       </c>
     </row>
@@ -11574,7 +11426,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1467</t>
+          <t xml:space="preserve">1661</t>
         </is>
       </c>
     </row>
@@ -11611,7 +11463,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468</t>
+          <t xml:space="preserve">1662</t>
         </is>
       </c>
     </row>
@@ -11648,7 +11500,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469</t>
+          <t xml:space="preserve">1663</t>
         </is>
       </c>
     </row>
@@ -11685,7 +11537,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1470</t>
+          <t xml:space="preserve">1664</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11574,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1471</t>
+          <t xml:space="preserve">1665</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11611,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1472</t>
+          <t xml:space="preserve">1666</t>
         </is>
       </c>
     </row>
@@ -11796,7 +11648,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1473</t>
+          <t xml:space="preserve">1667</t>
         </is>
       </c>
     </row>
@@ -11833,7 +11685,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474</t>
+          <t xml:space="preserve">1668</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11722,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1475</t>
+          <t xml:space="preserve">1669</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11759,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1479</t>
+          <t xml:space="preserve">1673</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11796,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1480</t>
+          <t xml:space="preserve">1674</t>
         </is>
       </c>
     </row>
@@ -11981,7 +11833,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1481</t>
+          <t xml:space="preserve">1675</t>
         </is>
       </c>
     </row>
@@ -12018,7 +11870,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1482</t>
+          <t xml:space="preserve">1676</t>
         </is>
       </c>
     </row>
@@ -12055,7 +11907,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1483</t>
+          <t xml:space="preserve">1677</t>
         </is>
       </c>
     </row>
@@ -12248,14 +12100,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1087</t>
+          <t xml:space="preserve">1231</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/250096-psn-tpms_blueorange-300x225.jpg</t>
+          <t xml:space="preserve">assets/backgrounds/shape-lab-hero-tpms-enhanced.png</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12275,7 +12127,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109</t>
+          <t xml:space="preserve">1253</t>
         </is>
       </c>
     </row>
@@ -12302,24 +12154,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112</t>
+          <t xml:space="preserve">1256</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/20250625_125103-1024x768.jpg</t>
+          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/Sand-Casting-1.png</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3D sand printing research</t>
+          <t xml:space="preserve">Advancing metal casting process via 3D sand printing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Local</t>
+          <t xml:space="preserve">Remote</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -12329,24 +12181,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141</t>
+          <t xml:space="preserve">1280</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/IMG_5766.jpg</t>
+          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/CDF.png</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casting process equipment</t>
+          <t xml:space="preserve">Additive Manufacturing plus Mass Finishing Hybrid Manufacturing System</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Local</t>
+          <t xml:space="preserve">Remote</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -12356,24 +12208,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149</t>
+          <t xml:space="preserve">1304</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/SHAPE-Lab-2018.jpg</t>
+          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/TPMS1.png</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab group</t>
+          <t xml:space="preserve">Multi-material laser powder bed fusion of complex structures</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Local</t>
+          <t xml:space="preserve">Remote</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12383,24 +12235,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157</t>
+          <t xml:space="preserve">1329</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/Additive_Manufacturing-G.Manogharan.jpg</t>
+          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/TPMS2-e1681999465376.png</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Additive manufacturing equipment</t>
+          <t xml:space="preserve">Design of non-pneumatic tires using TPMS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Local</t>
+          <t xml:space="preserve">Remote</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -12410,24 +12262,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171</t>
+          <t xml:space="preserve">1346</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/250096-psn-tpms_blueorange-300x225.jpg</t>
+          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/BJAM2.png</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TPMS structure</t>
+          <t xml:space="preserve">Study of multimodal powder-binder interaction in binder jetting process</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Local</t>
+          <t xml:space="preserve">Remote</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12437,19 +12289,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179</t>
+          <t xml:space="preserve">1371</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/penn-state-news-lg1.png</t>
+          <t xml:space="preserve">shapelab_photos/shapelab_photos/Group photo - Shape Lab.jpeg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penn State engineering feature</t>
+          <t xml:space="preserve">SHAPE Lab group photo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -12464,19 +12316,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187</t>
+          <t xml:space="preserve">1400</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/Group photo - Shape Lab.jpeg</t>
+          <t xml:space="preserve">profile_photos/Guha.png</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab group photo</t>
+          <t xml:space="preserve">Guha Manogharan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -12491,19 +12343,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206</t>
+          <t xml:space="preserve">1404</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Guha.png</t>
+          <t xml:space="preserve">profile_photos/Aish.jpg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guha Manogharan</t>
+          <t xml:space="preserve">Aishwarya Deshpande</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -12518,19 +12370,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210</t>
+          <t xml:space="preserve">1417</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Aish.jpg</t>
+          <t xml:space="preserve">profile_photos/Kazi.jpg</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aishwarya Deshpande</t>
+          <t xml:space="preserve">Kazi Safowan Shahed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -12545,19 +12397,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223</t>
+          <t xml:space="preserve">1424</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Kazi.jpg</t>
+          <t xml:space="preserve">profile_photos/Avez.png</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kazi Safowan Shahed</t>
+          <t xml:space="preserve">Avez Shaikh</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -12572,19 +12424,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230</t>
+          <t xml:space="preserve">1425</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Avez.png</t>
+          <t xml:space="preserve">profile_photos/Ashish.jpg</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avez Shaikh</t>
+          <t xml:space="preserve">Ashish Jacob</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -12599,19 +12451,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231</t>
+          <t xml:space="preserve">1426</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Ashish.jpg</t>
+          <t xml:space="preserve">profile_photos/Bryan.jpg</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ashish Jacob</t>
+          <t xml:space="preserve">Bryan Gong</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -12626,19 +12478,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232</t>
+          <t xml:space="preserve">1427</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Bryan.jpg</t>
+          <t xml:space="preserve">profile_photos/Thomas.jpg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryan Gong</t>
+          <t xml:space="preserve">Thomas Hanlon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -12653,19 +12505,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233</t>
+          <t xml:space="preserve">1428</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Thomas.jpg</t>
+          <t xml:space="preserve">profile_photos/Luis.jpg</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Hanlon</t>
+          <t xml:space="preserve">Luis Rodriguez</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -12680,19 +12532,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234</t>
+          <t xml:space="preserve">1429</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Luis.jpg</t>
+          <t xml:space="preserve">profile_photos/KC Majewski.jpg</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luis Rodriguez</t>
+          <t xml:space="preserve">KC Majewski</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -12707,19 +12559,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235</t>
+          <t xml:space="preserve">1430</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/KC Majewski.jpg</t>
+          <t xml:space="preserve">profile_photos/Andres.jpg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC Majewski</t>
+          <t xml:space="preserve">Andres Bujanda</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -12734,19 +12586,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236</t>
+          <t xml:space="preserve">1431</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Andres.jpg</t>
+          <t xml:space="preserve">profile_photos/Krishna.jpg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andres Bujanda</t>
+          <t xml:space="preserve">Kirshna Vistarakula</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -12761,19 +12613,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237</t>
+          <t xml:space="preserve">1432</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Krishna.jpg</t>
+          <t xml:space="preserve">profile_photos/Eric.png</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirshna Vistarakula</t>
+          <t xml:space="preserve">Eklou Eric Hiheglo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -12788,19 +12640,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238</t>
+          <t xml:space="preserve">1433</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Eric.png</t>
+          <t xml:space="preserve">profile_photos/James.jpg</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eklou Eric Hiheglo</t>
+          <t xml:space="preserve">James Sprague IV</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -12815,19 +12667,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239</t>
+          <t xml:space="preserve">1434</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/James.jpg</t>
+          <t xml:space="preserve">profile_photos/Chris Carson.jpg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">James Sprague IV</t>
+          <t xml:space="preserve">Chris Carson</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -12842,19 +12694,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240</t>
+          <t xml:space="preserve">1441</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Chris Carson.jpg</t>
+          <t xml:space="preserve">profile_photos/Timothy.jpg</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Carson</t>
+          <t xml:space="preserve">Timothy Sheffield</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12869,19 +12721,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247</t>
+          <t xml:space="preserve">1448</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Timothy.jpg</t>
+          <t xml:space="preserve">profile_photos/Ore.jpg</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timothy Sheffield</t>
+          <t xml:space="preserve">Oreoluwa Adegbite</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -12896,19 +12748,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254</t>
+          <t xml:space="preserve">1455</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Ore.jpg</t>
+          <t xml:space="preserve">profile_photos/Max.jpg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oreoluwa Adegbite</t>
+          <t xml:space="preserve">Maxwell Bacon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12923,19 +12775,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261</t>
+          <t xml:space="preserve">1456</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Max.jpg</t>
+          <t xml:space="preserve">profile_photos/Taiki.jpg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maxwell Bacon</t>
+          <t xml:space="preserve">Taiki Murakami</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -12950,19 +12802,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262</t>
+          <t xml:space="preserve">1457</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Taiki.jpg</t>
+          <t xml:space="preserve">profile_photos/Ella.png</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiki Murakami</t>
+          <t xml:space="preserve">Ella Fuener</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -12977,19 +12829,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263</t>
+          <t xml:space="preserve">1458</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Ella.png</t>
+          <t xml:space="preserve">profile_photos/Joe.jpg</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ella Fuener</t>
+          <t xml:space="preserve">Joseph Northcote</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -13004,19 +12856,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264</t>
+          <t xml:space="preserve">1459</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Joe.jpg</t>
+          <t xml:space="preserve">profile_photos/George.jpg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joseph Northcote</t>
+          <t xml:space="preserve">George Kuney</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -13031,19 +12883,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265</t>
+          <t xml:space="preserve">1460</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/George.jpg</t>
+          <t xml:space="preserve">profile_photos/Ahmed.png</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Kuney</t>
+          <t xml:space="preserve">Ahmed Elmanzalawi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -13058,24 +12910,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266</t>
+          <t xml:space="preserve">1461</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">profile_photos/Ahmed.png</t>
+          <t xml:space="preserve">https://psu-gatsby-files-prod.s3.amazonaws.com/s3fs-public/styles/4_3_1500w/public/2025/11/250469-psn-guha-manogharan.jpg?h=19ad3fdd&amp;itok=IvZXhMmJ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahmed Elmanzalawi</t>
+          <t xml:space="preserve">Penn State digital casting research team</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Local</t>
+          <t xml:space="preserve">Remote</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -13085,24 +12937,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267</t>
+          <t xml:space="preserve">1547</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://psu-gatsby-files-prod.s3.amazonaws.com/s3fs-public/styles/4_3_1500w/public/2025/11/250469-psn-guha-manogharan.jpg?h=19ad3fdd&amp;itok=IvZXhMmJ</t>
+          <t xml:space="preserve">shapelab_photos/shapelab_photos/Additive_Manufacturing-G.Manogharan.jpg</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penn State digital casting research team</t>
+          <t xml:space="preserve">Additive manufacturing project</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -13112,19 +12964,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1353</t>
+          <t xml:space="preserve">1551</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/Additive_Manufacturing-G.Manogharan.jpg</t>
+          <t xml:space="preserve">shapelab_photos/shapelab_photos/20250625_125103-1024x768.jpg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Additive manufacturing project</t>
+          <t xml:space="preserve">Student poster recognition</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -13139,19 +12991,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357</t>
+          <t xml:space="preserve">1555</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/20250625_125103-1024x768.jpg</t>
+          <t xml:space="preserve">shapelab_photos/shapelab_photos/daghir-joseph-240x300.jpg</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student poster recognition</t>
+          <t xml:space="preserve">Joseph Daghir</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -13166,19 +13018,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1361</t>
+          <t xml:space="preserve">1559</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">shapelab_photos/shapelab_photos/daghir-joseph-240x300.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/nsf-logo.png</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joseph Daghir</t>
+          <t xml:space="preserve">National Science Foundation logo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -13193,19 +13045,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1365</t>
+          <t xml:space="preserve">1659</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/nsf-logo.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/america-makes.jpg</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">National Science Foundation logo</t>
+          <t xml:space="preserve">America Makes logo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -13220,19 +13072,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1465</t>
+          <t xml:space="preserve">1660</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/america-makes.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/air-force-research-laboratory.png</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">America Makes logo</t>
+          <t xml:space="preserve">Air Force Research Laboratory logo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -13247,19 +13099,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466</t>
+          <t xml:space="preserve">1661</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/air-force-research-laboratory.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/office-of-naval-research.png</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Air Force Research Laboratory logo</t>
+          <t xml:space="preserve">Office of Naval Research logo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -13274,19 +13126,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1467</t>
+          <t xml:space="preserve">1662</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/office-of-naval-research.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/pennsylvania-manufacturing-sponsor.png</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Office of Naval Research logo</t>
+          <t xml:space="preserve">Pennsylvania manufacturing sponsor logo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -13301,19 +13153,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468</t>
+          <t xml:space="preserve">1663</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/pennsylvania-manufacturing-sponsor.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/pa-dced-logo.jpg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pennsylvania manufacturing sponsor logo</t>
+          <t xml:space="preserve">Pennsylvania Department of Community and Economic Development logo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -13328,19 +13180,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469</t>
+          <t xml:space="preserve">1664</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/pa-dced-logo.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/nist-center-of-excellence.jpg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pennsylvania Department of Community and Economic Development logo</t>
+          <t xml:space="preserve">NIST Center of Excellence logo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -13355,19 +13207,19 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1470</t>
+          <t xml:space="preserve">1665</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/nist-center-of-excellence.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/defense-manufacturing-sponsor.jpg</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">NIST Center of Excellence logo</t>
+          <t xml:space="preserve">Defense manufacturing sponsor logo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -13382,19 +13234,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1471</t>
+          <t xml:space="preserve">1666</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/defense-manufacturing-sponsor.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/iacmi-logo.png</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Defense manufacturing sponsor logo</t>
+          <t xml:space="preserve">IACMI The Composites Institute logo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -13409,19 +13261,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1472</t>
+          <t xml:space="preserve">1667</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/iacmi-logo.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/ascent-flextech.png</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">IACMI The Composites Institute logo</t>
+          <t xml:space="preserve">Ascent FlexTech logo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -13436,19 +13288,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1473</t>
+          <t xml:space="preserve">1668</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/ascent-flextech.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/darpa-logo.jpg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ascent FlexTech logo</t>
+          <t xml:space="preserve">DARPA logo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -13463,19 +13315,19 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474</t>
+          <t xml:space="preserve">1669</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/darpa-logo.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/methods-machine-tools.jpg</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">DARPA logo</t>
+          <t xml:space="preserve">Methods Machine Tools logo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -13490,19 +13342,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1475</t>
+          <t xml:space="preserve">1673</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/methods-machine-tools.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/industrial-collaboration-partner.png</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Methods Machine Tools logo</t>
+          <t xml:space="preserve">SHAPE Lab partner logo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -13517,14 +13369,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1479</t>
+          <t xml:space="preserve">1674</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/industrial-collaboration-partner.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/technical-collaboration-partner.png</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -13544,19 +13396,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1480</t>
+          <t xml:space="preserve">1675</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/technical-collaboration-partner.png</t>
+          <t xml:space="preserve">assets/sponsors-partners/hagerstown-community-college.jpg</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab partner logo</t>
+          <t xml:space="preserve">Hagerstown Community College logo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -13571,19 +13423,19 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1481</t>
+          <t xml:space="preserve">1676</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/hagerstown-community-college.jpg</t>
+          <t xml:space="preserve">assets/sponsors-partners/mastercam-logo.png</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hagerstown Community College logo</t>
+          <t xml:space="preserve">Mastercam logo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -13598,19 +13450,19 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1482</t>
+          <t xml:space="preserve">1677</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/mastercam-logo.png</t>
+          <t xml:space="preserve">scrolling_photos/1000009313-fd20a745478509a4.jpg</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mastercam logo</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -13620,24 +13472,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">lazy</t>
+          <t xml:space="preserve">eager</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1483</t>
+          <t xml:space="preserve">2846</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/1000009313-fd20a745478509a4.jpg</t>
+          <t xml:space="preserve">scrolling_photos/1000014064.jpg</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 1</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -13647,24 +13499,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">eager</t>
+          <t xml:space="preserve">lazy</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2652</t>
+          <t xml:space="preserve">2847</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/1000014064.jpg</t>
+          <t xml:space="preserve">scrolling_photos/20191221_1814591-e1587059674952-138x300.jpg</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 2</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -13679,19 +13531,19 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2653</t>
+          <t xml:space="preserve">2848</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/20191221_1814591-e1587059674952-138x300.jpg</t>
+          <t xml:space="preserve">scrolling_photos/20251115_142725-768x576.jpg</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 3</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 4</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -13706,19 +13558,19 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2654</t>
+          <t xml:space="preserve">2849</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/20251115_142725-768x576.jpg</t>
+          <t xml:space="preserve">scrolling_photos/20260503_144210(0).jpg</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 4</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 5</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -13733,19 +13585,19 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2655</t>
+          <t xml:space="preserve">2850</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/20260503_144210(0).jpg</t>
+          <t xml:space="preserve">scrolling_photos/5f7aab06-.jpg</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 5</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 6</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -13760,19 +13612,19 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656</t>
+          <t xml:space="preserve">2851</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/5f7aab06-.jpg</t>
+          <t xml:space="preserve">scrolling_photos/Image-from-iOS-1-300x225.jpg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 6</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 7</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -13787,19 +13639,19 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657</t>
+          <t xml:space="preserve">2852</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/Image-from-iOS-1-300x225.jpg</t>
+          <t xml:space="preserve">scrolling_photos/IMG_0063-768x576.jpg</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 7</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 8</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -13814,19 +13666,19 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2658</t>
+          <t xml:space="preserve">2853</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/IMG_0063-768x576.jpg</t>
+          <t xml:space="preserve">scrolling_photos/IMG_20160522_193907_1463971177473-768x749.jpg</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 8</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 9</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -13841,19 +13693,19 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2659</t>
+          <t xml:space="preserve">2854</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/IMG_20160522_193907_1463971177473-768x749.jpg</t>
+          <t xml:space="preserve">scrolling_photos/IMG_2276.jpg</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 9</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -13868,19 +13720,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2855</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/IMG_2276.jpg</t>
+          <t xml:space="preserve">scrolling_photos/IMG_3044-768x576.jpg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 10</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 11</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -13895,19 +13747,19 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2661</t>
+          <t xml:space="preserve">2856</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/IMG_3044-768x576.jpg</t>
+          <t xml:space="preserve">scrolling_photos/IMG_3693-2-577x1024.jpg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 11</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 12</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -13922,19 +13774,19 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662</t>
+          <t xml:space="preserve">2857</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/IMG_3693-2-577x1024.jpg</t>
+          <t xml:space="preserve">scrolling_photos/IMG_4077-768x1024.jpg</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 12</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 13</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -13949,19 +13801,19 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2663</t>
+          <t xml:space="preserve">2858</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/IMG_4077-768x1024.jpg</t>
+          <t xml:space="preserve">scrolling_photos/IMG_4917-1-300x225.jpg</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 13</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 14</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -13976,19 +13828,19 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2664</t>
+          <t xml:space="preserve">2859</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/IMG_4917-1-300x225.jpg</t>
+          <t xml:space="preserve">scrolling_photos/IMG_5619.jpg</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 14</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -14003,19 +13855,19 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2665</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/IMG_5619.jpg</t>
+          <t xml:space="preserve">scrolling_photos/IMG_5766-768x576.jpg</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 15</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -14030,19 +13882,19 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666</t>
+          <t xml:space="preserve">2861</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/IMG_5766-768x576.jpg</t>
+          <t xml:space="preserve">scrolling_photos/img_6277_52048265114_o-768x511.jpg</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 16</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 17</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -14057,19 +13909,19 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2667</t>
+          <t xml:space="preserve">2862</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/img_6277_52048265114_o-768x511.jpg</t>
+          <t xml:space="preserve">scrolling_photos/IMG_7093.jpg</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 17</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 18</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -14084,19 +13936,19 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2668</t>
+          <t xml:space="preserve">2863</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/IMG_7093.jpg</t>
+          <t xml:space="preserve">scrolling_photos/Resized_20220430_170127003-768x1024.jpeg</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 18</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 19</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -14111,19 +13963,19 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2669</t>
+          <t xml:space="preserve">2864</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/Resized_20220430_170127003-768x1024.jpeg</t>
+          <t xml:space="preserve">scrolling_photos/Santosh_Graduation-300x225.jpg</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 19</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 20</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -14138,19 +13990,19 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2670</t>
+          <t xml:space="preserve">2865</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/Santosh_Graduation-300x225.jpg</t>
+          <t xml:space="preserve">scrolling_photos/SHAPE-Lab-2018-300x200.jpg</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 20</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 21</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -14165,19 +14017,19 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2671</t>
+          <t xml:space="preserve">2866</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/SHAPE-Lab-2018-300x200.jpg</t>
+          <t xml:space="preserve">scrolling_photos/SHAPE-LAB-2019-300x200.jpg</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 21</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 22</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -14192,19 +14044,19 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2672</t>
+          <t xml:space="preserve">2867</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/SHAPE-LAB-2019-300x200.jpg</t>
+          <t xml:space="preserve">scrolling_photos/Willem.jpg</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 22</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 23</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -14219,19 +14071,19 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2673</t>
+          <t xml:space="preserve">2868</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrolling_photos/Willem.jpg</t>
+          <t xml:space="preserve">scrolling_photos/Xi_graduation.jpg</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 23</t>
+          <t xml:space="preserve">SHAPE Lab gallery photo 24</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -14246,34 +14098,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2674</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">scrolling_photos/Xi_graduation.jpg</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SHAPE Lab gallery photo 24</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Local</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lazy</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2675</t>
+          <t xml:space="preserve">2869</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14152,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086</t>
+          <t xml:space="preserve">1230</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14174,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094</t>
+          <t xml:space="preserve">1238</t>
         </is>
       </c>
     </row>
@@ -14371,7 +14196,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1095</t>
+          <t xml:space="preserve">1239</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14218,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096</t>
+          <t xml:space="preserve">1240</t>
         </is>
       </c>
     </row>
@@ -14415,7 +14240,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097</t>
+          <t xml:space="preserve">1241</t>
         </is>
       </c>
     </row>
@@ -14437,7 +14262,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098</t>
+          <t xml:space="preserve">1242</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14284,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1099</t>
+          <t xml:space="preserve">1243</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14306,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100</t>
+          <t xml:space="preserve">1244</t>
         </is>
       </c>
     </row>
@@ -14503,7 +14328,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101</t>
+          <t xml:space="preserve">1245</t>
         </is>
       </c>
     </row>
@@ -14525,7 +14350,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216</t>
+          <t xml:space="preserve">1410</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14372,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216</t>
+          <t xml:space="preserve">1410</t>
         </is>
       </c>
     </row>
@@ -14569,7 +14394,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223</t>
+          <t xml:space="preserve">1417</t>
         </is>
       </c>
     </row>
@@ -14591,7 +14416,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223</t>
+          <t xml:space="preserve">1417</t>
         </is>
       </c>
     </row>
@@ -14613,7 +14438,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223</t>
+          <t xml:space="preserve">1417</t>
         </is>
       </c>
     </row>
@@ -14635,7 +14460,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230</t>
+          <t xml:space="preserve">1424</t>
         </is>
       </c>
     </row>
@@ -14657,7 +14482,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230</t>
+          <t xml:space="preserve">1424</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14504,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230</t>
+          <t xml:space="preserve">1424</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14526,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231</t>
+          <t xml:space="preserve">1425</t>
         </is>
       </c>
     </row>
@@ -14723,7 +14548,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231</t>
+          <t xml:space="preserve">1425</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14570,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231</t>
+          <t xml:space="preserve">1425</t>
         </is>
       </c>
     </row>
@@ -14767,7 +14592,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232</t>
+          <t xml:space="preserve">1426</t>
         </is>
       </c>
     </row>
@@ -14789,7 +14614,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232</t>
+          <t xml:space="preserve">1426</t>
         </is>
       </c>
     </row>
@@ -14811,7 +14636,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232</t>
+          <t xml:space="preserve">1426</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14658,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233</t>
+          <t xml:space="preserve">1427</t>
         </is>
       </c>
     </row>
@@ -14855,7 +14680,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233</t>
+          <t xml:space="preserve">1427</t>
         </is>
       </c>
     </row>
@@ -14877,7 +14702,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233</t>
+          <t xml:space="preserve">1427</t>
         </is>
       </c>
     </row>
@@ -14899,7 +14724,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234</t>
+          <t xml:space="preserve">1428</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14746,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234</t>
+          <t xml:space="preserve">1428</t>
         </is>
       </c>
     </row>
@@ -14943,7 +14768,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235</t>
+          <t xml:space="preserve">1429</t>
         </is>
       </c>
     </row>
@@ -14965,7 +14790,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235</t>
+          <t xml:space="preserve">1429</t>
         </is>
       </c>
     </row>
@@ -14987,7 +14812,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236</t>
+          <t xml:space="preserve">1430</t>
         </is>
       </c>
     </row>
@@ -15009,7 +14834,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236</t>
+          <t xml:space="preserve">1430</t>
         </is>
       </c>
     </row>
@@ -15031,7 +14856,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237</t>
+          <t xml:space="preserve">1431</t>
         </is>
       </c>
     </row>
@@ -15053,7 +14878,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238</t>
+          <t xml:space="preserve">1432</t>
         </is>
       </c>
     </row>
@@ -15075,7 +14900,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238</t>
+          <t xml:space="preserve">1432</t>
         </is>
       </c>
     </row>
@@ -15097,7 +14922,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238</t>
+          <t xml:space="preserve">1432</t>
         </is>
       </c>
     </row>
@@ -15119,7 +14944,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239</t>
+          <t xml:space="preserve">1433</t>
         </is>
       </c>
     </row>
@@ -15141,7 +14966,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239</t>
+          <t xml:space="preserve">1433</t>
         </is>
       </c>
     </row>
@@ -15163,7 +14988,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240</t>
+          <t xml:space="preserve">1434</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15010,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240</t>
+          <t xml:space="preserve">1434</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15032,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254</t>
+          <t xml:space="preserve">1448</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15054,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254</t>
+          <t xml:space="preserve">1448</t>
         </is>
       </c>
     </row>
@@ -15251,7 +15076,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261</t>
+          <t xml:space="preserve">1455</t>
         </is>
       </c>
     </row>
@@ -15273,7 +15098,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261</t>
+          <t xml:space="preserve">1455</t>
         </is>
       </c>
     </row>
@@ -15295,7 +15120,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262</t>
+          <t xml:space="preserve">1456</t>
         </is>
       </c>
     </row>
@@ -15317,7 +15142,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262</t>
+          <t xml:space="preserve">1456</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15164,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263</t>
+          <t xml:space="preserve">1457</t>
         </is>
       </c>
     </row>
@@ -15361,7 +15186,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264</t>
+          <t xml:space="preserve">1458</t>
         </is>
       </c>
     </row>
@@ -15383,7 +15208,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264</t>
+          <t xml:space="preserve">1458</t>
         </is>
       </c>
     </row>
@@ -15405,7 +15230,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265</t>
+          <t xml:space="preserve">1459</t>
         </is>
       </c>
     </row>
@@ -15427,7 +15252,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265</t>
+          <t xml:space="preserve">1459</t>
         </is>
       </c>
     </row>
@@ -15449,7 +15274,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266</t>
+          <t xml:space="preserve">1460</t>
         </is>
       </c>
     </row>
@@ -15471,7 +15296,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266</t>
+          <t xml:space="preserve">1460</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15318,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267</t>
+          <t xml:space="preserve">1461</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15340,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267</t>
+          <t xml:space="preserve">1461</t>
         </is>
       </c>
     </row>
@@ -15537,7 +15362,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1354</t>
+          <t xml:space="preserve">1548</t>
         </is>
       </c>
     </row>
@@ -15559,7 +15384,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1374</t>
+          <t xml:space="preserve">1568</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15406,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375</t>
+          <t xml:space="preserve">1569</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15428,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1378</t>
+          <t xml:space="preserve">1572</t>
         </is>
       </c>
     </row>
@@ -15625,7 +15450,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1380</t>
+          <t xml:space="preserve">1574</t>
         </is>
       </c>
     </row>
@@ -15647,7 +15472,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1381</t>
+          <t xml:space="preserve">1575</t>
         </is>
       </c>
     </row>
@@ -15669,7 +15494,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1382</t>
+          <t xml:space="preserve">1576</t>
         </is>
       </c>
     </row>
@@ -15691,7 +15516,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1384</t>
+          <t xml:space="preserve">1578</t>
         </is>
       </c>
     </row>
@@ -15713,7 +15538,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1450</t>
+          <t xml:space="preserve">1644</t>
         </is>
       </c>
     </row>
@@ -15735,7 +15560,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1454</t>
+          <t xml:space="preserve">1648</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15582,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455</t>
+          <t xml:space="preserve">1649</t>
         </is>
       </c>
     </row>
@@ -15779,7 +15604,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1456</t>
+          <t xml:space="preserve">1650</t>
         </is>
       </c>
     </row>
@@ -15801,7 +15626,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1465</t>
+          <t xml:space="preserve">1659</t>
         </is>
       </c>
     </row>
@@ -15823,7 +15648,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466</t>
+          <t xml:space="preserve">1660</t>
         </is>
       </c>
     </row>
@@ -15845,7 +15670,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1467</t>
+          <t xml:space="preserve">1661</t>
         </is>
       </c>
     </row>
@@ -15867,7 +15692,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468</t>
+          <t xml:space="preserve">1662</t>
         </is>
       </c>
     </row>
@@ -15889,7 +15714,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469</t>
+          <t xml:space="preserve">1663</t>
         </is>
       </c>
     </row>
@@ -15911,7 +15736,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1470</t>
+          <t xml:space="preserve">1664</t>
         </is>
       </c>
     </row>
@@ -15933,7 +15758,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1471</t>
+          <t xml:space="preserve">1665</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15780,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1472</t>
+          <t xml:space="preserve">1666</t>
         </is>
       </c>
     </row>
@@ -15977,7 +15802,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1473</t>
+          <t xml:space="preserve">1667</t>
         </is>
       </c>
     </row>
@@ -15999,7 +15824,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474</t>
+          <t xml:space="preserve">1668</t>
         </is>
       </c>
     </row>
@@ -16021,7 +15846,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1475</t>
+          <t xml:space="preserve">1669</t>
         </is>
       </c>
     </row>
@@ -16043,7 +15868,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1479</t>
+          <t xml:space="preserve">1673</t>
         </is>
       </c>
     </row>
@@ -16065,7 +15890,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1480</t>
+          <t xml:space="preserve">1674</t>
         </is>
       </c>
     </row>
@@ -16087,7 +15912,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1481</t>
+          <t xml:space="preserve">1675</t>
         </is>
       </c>
     </row>
@@ -16109,7 +15934,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1482</t>
+          <t xml:space="preserve">1676</t>
         </is>
       </c>
     </row>
@@ -16131,7 +15956,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1483</t>
+          <t xml:space="preserve">1677</t>
         </is>
       </c>
     </row>
@@ -16153,7 +15978,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1506</t>
+          <t xml:space="preserve">1700</t>
         </is>
       </c>
     </row>
@@ -16175,7 +16000,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1516</t>
+          <t xml:space="preserve">1710</t>
         </is>
       </c>
     </row>
@@ -16197,7 +16022,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1526</t>
+          <t xml:space="preserve">1720</t>
         </is>
       </c>
     </row>
@@ -16219,7 +16044,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1541</t>
+          <t xml:space="preserve">1735</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16066,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551</t>
+          <t xml:space="preserve">1745</t>
         </is>
       </c>
     </row>
@@ -16263,7 +16088,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561</t>
+          <t xml:space="preserve">1755</t>
         </is>
       </c>
     </row>
@@ -16285,7 +16110,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1571</t>
+          <t xml:space="preserve">1765</t>
         </is>
       </c>
     </row>
@@ -16307,7 +16132,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1581</t>
+          <t xml:space="preserve">1775</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16154,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1591</t>
+          <t xml:space="preserve">1785</t>
         </is>
       </c>
     </row>
@@ -16351,7 +16176,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1601</t>
+          <t xml:space="preserve">1795</t>
         </is>
       </c>
     </row>
@@ -16373,7 +16198,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1611</t>
+          <t xml:space="preserve">1805</t>
         </is>
       </c>
     </row>
@@ -16395,7 +16220,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1621</t>
+          <t xml:space="preserve">1815</t>
         </is>
       </c>
     </row>
@@ -16417,7 +16242,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631</t>
+          <t xml:space="preserve">1825</t>
         </is>
       </c>
     </row>
@@ -16439,7 +16264,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1641</t>
+          <t xml:space="preserve">1835</t>
         </is>
       </c>
     </row>
@@ -16461,7 +16286,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1651</t>
+          <t xml:space="preserve">1845</t>
         </is>
       </c>
     </row>
@@ -16483,7 +16308,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1661</t>
+          <t xml:space="preserve">1855</t>
         </is>
       </c>
     </row>
@@ -16505,7 +16330,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671</t>
+          <t xml:space="preserve">1865</t>
         </is>
       </c>
     </row>
@@ -16527,7 +16352,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1681</t>
+          <t xml:space="preserve">1875</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16374,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1696</t>
+          <t xml:space="preserve">1890</t>
         </is>
       </c>
     </row>
@@ -16571,7 +16396,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1706</t>
+          <t xml:space="preserve">1900</t>
         </is>
       </c>
     </row>
@@ -16593,7 +16418,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1716</t>
+          <t xml:space="preserve">1910</t>
         </is>
       </c>
     </row>
@@ -16615,7 +16440,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1726</t>
+          <t xml:space="preserve">1920</t>
         </is>
       </c>
     </row>
@@ -16637,7 +16462,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1736</t>
+          <t xml:space="preserve">1930</t>
         </is>
       </c>
     </row>
@@ -16659,7 +16484,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1746</t>
+          <t xml:space="preserve">1940</t>
         </is>
       </c>
     </row>
@@ -16681,7 +16506,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1756</t>
+          <t xml:space="preserve">1950</t>
         </is>
       </c>
     </row>
@@ -16703,7 +16528,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1766</t>
+          <t xml:space="preserve">1960</t>
         </is>
       </c>
     </row>
@@ -16725,7 +16550,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1776</t>
+          <t xml:space="preserve">1970</t>
         </is>
       </c>
     </row>
@@ -16747,7 +16572,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1791</t>
+          <t xml:space="preserve">1985</t>
         </is>
       </c>
     </row>
@@ -16769,7 +16594,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801</t>
+          <t xml:space="preserve">1995</t>
         </is>
       </c>
     </row>
@@ -16791,7 +16616,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811</t>
+          <t xml:space="preserve">2005</t>
         </is>
       </c>
     </row>
@@ -16813,7 +16638,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1821</t>
+          <t xml:space="preserve">2015</t>
         </is>
       </c>
     </row>
@@ -16835,7 +16660,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1831</t>
+          <t xml:space="preserve">2025</t>
         </is>
       </c>
     </row>
@@ -16857,7 +16682,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841</t>
+          <t xml:space="preserve">2035</t>
         </is>
       </c>
     </row>
@@ -16879,7 +16704,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851</t>
+          <t xml:space="preserve">2045</t>
         </is>
       </c>
     </row>
@@ -16901,7 +16726,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1861</t>
+          <t xml:space="preserve">2055</t>
         </is>
       </c>
     </row>
@@ -16923,7 +16748,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871</t>
+          <t xml:space="preserve">2065</t>
         </is>
       </c>
     </row>
@@ -16945,7 +16770,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881</t>
+          <t xml:space="preserve">2075</t>
         </is>
       </c>
     </row>
@@ -16967,7 +16792,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891</t>
+          <t xml:space="preserve">2085</t>
         </is>
       </c>
     </row>
@@ -16989,7 +16814,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901</t>
+          <t xml:space="preserve">2095</t>
         </is>
       </c>
     </row>
@@ -17011,7 +16836,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1911</t>
+          <t xml:space="preserve">2105</t>
         </is>
       </c>
     </row>
@@ -17033,7 +16858,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926</t>
+          <t xml:space="preserve">2120</t>
         </is>
       </c>
     </row>
@@ -17055,7 +16880,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1936</t>
+          <t xml:space="preserve">2130</t>
         </is>
       </c>
     </row>
@@ -17077,7 +16902,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946</t>
+          <t xml:space="preserve">2140</t>
         </is>
       </c>
     </row>
@@ -17099,7 +16924,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956</t>
+          <t xml:space="preserve">2150</t>
         </is>
       </c>
     </row>
@@ -17121,7 +16946,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">2160</t>
         </is>
       </c>
     </row>
@@ -17143,7 +16968,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1976</t>
+          <t xml:space="preserve">2170</t>
         </is>
       </c>
     </row>
@@ -17165,7 +16990,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1986</t>
+          <t xml:space="preserve">2180</t>
         </is>
       </c>
     </row>
@@ -17187,7 +17012,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996</t>
+          <t xml:space="preserve">2190</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17034,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006</t>
+          <t xml:space="preserve">2200</t>
         </is>
       </c>
     </row>
@@ -17231,7 +17056,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016</t>
+          <t xml:space="preserve">2210</t>
         </is>
       </c>
     </row>
@@ -17253,7 +17078,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026</t>
+          <t xml:space="preserve">2220</t>
         </is>
       </c>
     </row>
@@ -17275,7 +17100,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036</t>
+          <t xml:space="preserve">2230</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17122,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2046</t>
+          <t xml:space="preserve">2240</t>
         </is>
       </c>
     </row>
@@ -17319,7 +17144,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2056</t>
+          <t xml:space="preserve">2250</t>
         </is>
       </c>
     </row>
@@ -17341,7 +17166,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2066</t>
+          <t xml:space="preserve">2260</t>
         </is>
       </c>
     </row>
@@ -17363,7 +17188,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2076</t>
+          <t xml:space="preserve">2270</t>
         </is>
       </c>
     </row>
@@ -17385,7 +17210,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086</t>
+          <t xml:space="preserve">2280</t>
         </is>
       </c>
     </row>
@@ -17407,7 +17232,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2096</t>
+          <t xml:space="preserve">2290</t>
         </is>
       </c>
     </row>
@@ -17429,7 +17254,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2106</t>
+          <t xml:space="preserve">2300</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17276,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2116</t>
+          <t xml:space="preserve">2310</t>
         </is>
       </c>
     </row>
@@ -17473,7 +17298,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126</t>
+          <t xml:space="preserve">2320</t>
         </is>
       </c>
     </row>
@@ -17495,7 +17320,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136</t>
+          <t xml:space="preserve">2330</t>
         </is>
       </c>
     </row>
@@ -17517,7 +17342,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146</t>
+          <t xml:space="preserve">2340</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17364,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2156</t>
+          <t xml:space="preserve">2350</t>
         </is>
       </c>
     </row>
@@ -17561,7 +17386,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2166</t>
+          <t xml:space="preserve">2360</t>
         </is>
       </c>
     </row>
@@ -17583,7 +17408,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176</t>
+          <t xml:space="preserve">2370</t>
         </is>
       </c>
     </row>
@@ -17605,7 +17430,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191</t>
+          <t xml:space="preserve">2385</t>
         </is>
       </c>
     </row>
@@ -17627,7 +17452,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2206</t>
+          <t xml:space="preserve">2400</t>
         </is>
       </c>
     </row>
@@ -17649,7 +17474,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216</t>
+          <t xml:space="preserve">2410</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17496,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226</t>
+          <t xml:space="preserve">2420</t>
         </is>
       </c>
     </row>
@@ -17693,7 +17518,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236</t>
+          <t xml:space="preserve">2430</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17540,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2246</t>
+          <t xml:space="preserve">2440</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17562,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2256</t>
+          <t xml:space="preserve">2450</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17584,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266</t>
+          <t xml:space="preserve">2460</t>
         </is>
       </c>
     </row>
@@ -17781,7 +17606,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2283</t>
+          <t xml:space="preserve">2477</t>
         </is>
       </c>
     </row>
@@ -17803,7 +17628,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2293</t>
+          <t xml:space="preserve">2487</t>
         </is>
       </c>
     </row>
@@ -17825,7 +17650,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303</t>
+          <t xml:space="preserve">2497</t>
         </is>
       </c>
     </row>
@@ -17847,7 +17672,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2313</t>
+          <t xml:space="preserve">2507</t>
         </is>
       </c>
     </row>
@@ -17869,7 +17694,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323</t>
+          <t xml:space="preserve">2517</t>
         </is>
       </c>
     </row>
@@ -17891,7 +17716,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2333</t>
+          <t xml:space="preserve">2527</t>
         </is>
       </c>
     </row>
@@ -17913,7 +17738,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2343</t>
+          <t xml:space="preserve">2537</t>
         </is>
       </c>
     </row>
@@ -17935,7 +17760,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2353</t>
+          <t xml:space="preserve">2547</t>
         </is>
       </c>
     </row>
@@ -17957,7 +17782,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2363</t>
+          <t xml:space="preserve">2557</t>
         </is>
       </c>
     </row>
@@ -17979,7 +17804,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2712</t>
+          <t xml:space="preserve">2906</t>
         </is>
       </c>
     </row>
@@ -18001,7 +17826,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2713</t>
+          <t xml:space="preserve">2907</t>
         </is>
       </c>
     </row>
@@ -18023,7 +17848,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2714</t>
+          <t xml:space="preserve">2908</t>
         </is>
       </c>
     </row>
@@ -18045,7 +17870,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2715</t>
+          <t xml:space="preserve">2909</t>
         </is>
       </c>
     </row>
@@ -18067,7 +17892,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2716</t>
+          <t xml:space="preserve">2910</t>
         </is>
       </c>
     </row>
@@ -18089,7 +17914,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2717</t>
+          <t xml:space="preserve">2911</t>
         </is>
       </c>
     </row>
@@ -18111,7 +17936,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2718</t>
+          <t xml:space="preserve">2912</t>
         </is>
       </c>
     </row>
@@ -18133,7 +17958,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2719</t>
+          <t xml:space="preserve">2913</t>
         </is>
       </c>
     </row>

--- a/SHAPE-Lab-Website-Content.xlsx
+++ b/SHAPE-Lab-Website-Content.xlsx
@@ -88,7 +88,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -547,12 +547,12 @@
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">team</t>
+          <t xml:space="preserve">research</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Title</t>
+          <t xml:space="preserve">Section Lede</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Team</t>
+          <t xml:space="preserve">Research highlights connect students, tools, manufacturing equipment, and publications across additive manufacturing, hybrid manufacturing, binder jetting, biomedical AM, and sand printing for casting.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -577,14 +577,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1391</t>
+          <t xml:space="preserve">1262</t>
         </is>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">news</t>
+          <t xml:space="preserve">team</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">What's happening at SHAPE.</t>
+          <t xml:space="preserve">Team</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -614,14 +614,14 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1538</t>
+          <t xml:space="preserve">1387</t>
         </is>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sponsors</t>
+          <t xml:space="preserve">news</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sponsors and partners.</t>
+          <t xml:space="preserve">What's happening at SHAPE.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653</t>
+          <t xml:space="preserve">1534</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Lede</t>
+          <t xml:space="preserve">Section Title</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHAPE Lab research is built around collaborations that connect manufacturing science to real application needs.</t>
+          <t xml:space="preserve">Sponsors and partners.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -688,19 +688,19 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653</t>
+          <t xml:space="preserve">1649</t>
         </is>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">publications</t>
+          <t xml:space="preserve">sponsors</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Title</t>
+          <t xml:space="preserve">Section Lede</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing research outputs.</t>
+          <t xml:space="preserve">SHAPE Lab research is built around collaborations that connect manufacturing science to real application needs.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680</t>
+          <t xml:space="preserve">1649</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Lede</t>
+          <t xml:space="preserve">Section Title</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papers from the official S.H.A.P.E. Lab publication list, grouped by research area and publication type.</t>
+          <t xml:space="preserve">Manufacturing research outputs.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -762,19 +762,19 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680</t>
+          <t xml:space="preserve">1676</t>
         </is>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery</t>
+          <t xml:space="preserve">publications</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Title</t>
+          <t xml:space="preserve">Section Lede</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snapshots from SHAPE Lab.</t>
+          <t xml:space="preserve">Papers from the official S.H.A.P.E. Lab publication list, grouped by research area and publication type.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2836</t>
+          <t xml:space="preserve">1676</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Lede</t>
+          <t xml:space="preserve">Section Title</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Photos from lab events, student milestones, and research moments.</t>
+          <t xml:space="preserve">Snapshots from SHAPE Lab.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -836,19 +836,19 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2836</t>
+          <t xml:space="preserve">2832</t>
         </is>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">contact</t>
+          <t xml:space="preserve">gallery</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section Title</t>
+          <t xml:space="preserve">Section Lede</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect with S.H.A.P.E. Lab.</t>
+          <t xml:space="preserve">Photos from lab events, student milestones, and research moments.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2877</t>
+          <t xml:space="preserve">2832</t>
         </is>
       </c>
     </row>
@@ -885,37 +885,74 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Section Title</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connect with S.H.A.P.E. Lab.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2873</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contact</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Section Lede</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The lab works across additive manufacturing, hybrid process engineering, 3D sand printing, biomedical AM, and multi-material metal systems.</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2877</t>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2873</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:G23"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -971,7 +1008,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
+          <t xml:space="preserve">2026-05-28 13:21:39</t>
         </is>
       </c>
     </row>
@@ -993,7 +1030,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
+          <t xml:space="preserve">2026-05-28 13:21:39</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1052,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
+          <t xml:space="preserve">2026-05-28 13:21:39</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1074,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
+          <t xml:space="preserve">2026-05-28 13:21:39</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1096,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-22 12:14:43</t>
+          <t xml:space="preserve">2026-05-28 13:21:39</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1118,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
+          <t xml:space="preserve">2026-05-28 13:21:39</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1140,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
+          <t xml:space="preserve">2026-05-28 13:21:39</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1162,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
+          <t xml:space="preserve">2026-05-28 13:21:39</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1184,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
+          <t xml:space="preserve">2026-05-28 13:21:39</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1206,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-20 20:36:14</t>
+          <t xml:space="preserve">2026-05-28 13:21:39</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1290,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/Sand-Casting-1.png</t>
+          <t xml:space="preserve">research%20photos/sand-casting.png</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1263,7 +1300,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277</t>
+          <t xml:space="preserve">1273</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1327,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/CDF.png</t>
+          <t xml:space="preserve">research%20photos/mass-finishing-cdf.png</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1300,7 +1337,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301</t>
+          <t xml:space="preserve">1297</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1364,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/TPMS1.png</t>
+          <t xml:space="preserve">research%20photos/multi-material-lpbf-tpms.png</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1337,7 +1374,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326</t>
+          <t xml:space="preserve">1322</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1401,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/TPMS2-e1681999465376.png</t>
+          <t xml:space="preserve">research%20photos/non-pneumatic-tires-tpms.png</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1374,7 +1411,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1343</t>
+          <t xml:space="preserve">1339</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1438,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/BJAM2.png</t>
+          <t xml:space="preserve">research%20photos/binder-jetting.png</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1411,7 +1448,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1368</t>
+          <t xml:space="preserve">1364</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4141,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691</t>
+          <t xml:space="preserve">1687</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4173,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1701</t>
+          <t xml:space="preserve">1697</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4205,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711</t>
+          <t xml:space="preserve">1707</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4237,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1726</t>
+          <t xml:space="preserve">1722</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4269,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1736</t>
+          <t xml:space="preserve">1732</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4301,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1746</t>
+          <t xml:space="preserve">1742</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4333,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1756</t>
+          <t xml:space="preserve">1752</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4365,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1766</t>
+          <t xml:space="preserve">1762</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4397,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1776</t>
+          <t xml:space="preserve">1772</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4429,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1786</t>
+          <t xml:space="preserve">1782</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4461,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1796</t>
+          <t xml:space="preserve">1792</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4493,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806</t>
+          <t xml:space="preserve">1802</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4525,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1816</t>
+          <t xml:space="preserve">1812</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4557,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826</t>
+          <t xml:space="preserve">1822</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4589,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1836</t>
+          <t xml:space="preserve">1832</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4621,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846</t>
+          <t xml:space="preserve">1842</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4653,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856</t>
+          <t xml:space="preserve">1852</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4685,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866</t>
+          <t xml:space="preserve">1862</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4717,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881</t>
+          <t xml:space="preserve">1877</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4749,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891</t>
+          <t xml:space="preserve">1887</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901</t>
+          <t xml:space="preserve">1897</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4813,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1911</t>
+          <t xml:space="preserve">1907</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4845,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921</t>
+          <t xml:space="preserve">1917</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4877,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1931</t>
+          <t xml:space="preserve">1927</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4909,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941</t>
+          <t xml:space="preserve">1937</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4941,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1951</t>
+          <t xml:space="preserve">1947</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4973,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1961</t>
+          <t xml:space="preserve">1957</t>
         </is>
       </c>
     </row>
@@ -4968,7 +5005,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1976</t>
+          <t xml:space="preserve">1972</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5037,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1986</t>
+          <t xml:space="preserve">1982</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5069,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996</t>
+          <t xml:space="preserve">1992</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5101,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006</t>
+          <t xml:space="preserve">2002</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5133,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016</t>
+          <t xml:space="preserve">2012</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5165,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026</t>
+          <t xml:space="preserve">2022</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5197,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036</t>
+          <t xml:space="preserve">2032</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5229,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2046</t>
+          <t xml:space="preserve">2042</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5261,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2056</t>
+          <t xml:space="preserve">2052</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5293,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2066</t>
+          <t xml:space="preserve">2062</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5325,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2076</t>
+          <t xml:space="preserve">2072</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5357,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086</t>
+          <t xml:space="preserve">2082</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5389,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2096</t>
+          <t xml:space="preserve">2092</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5421,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2111</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5453,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121</t>
+          <t xml:space="preserve">2117</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5485,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2131</t>
+          <t xml:space="preserve">2127</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5517,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141</t>
+          <t xml:space="preserve">2137</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5549,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2151</t>
+          <t xml:space="preserve">2147</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5581,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161</t>
+          <t xml:space="preserve">2157</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5613,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171</t>
+          <t xml:space="preserve">2167</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5645,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181</t>
+          <t xml:space="preserve">2177</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5677,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191</t>
+          <t xml:space="preserve">2187</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5709,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201</t>
+          <t xml:space="preserve">2197</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5741,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211</t>
+          <t xml:space="preserve">2207</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5773,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221</t>
+          <t xml:space="preserve">2217</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5805,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231</t>
+          <t xml:space="preserve">2227</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5837,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241</t>
+          <t xml:space="preserve">2237</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5869,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2251</t>
+          <t xml:space="preserve">2247</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5901,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261</t>
+          <t xml:space="preserve">2257</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5933,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2271</t>
+          <t xml:space="preserve">2267</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5965,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2281</t>
+          <t xml:space="preserve">2277</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5997,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2291</t>
+          <t xml:space="preserve">2287</t>
         </is>
       </c>
     </row>
@@ -5992,7 +6029,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301</t>
+          <t xml:space="preserve">2297</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6061,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2311</t>
+          <t xml:space="preserve">2307</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6093,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2321</t>
+          <t xml:space="preserve">2317</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6125,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2331</t>
+          <t xml:space="preserve">2327</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6157,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2341</t>
+          <t xml:space="preserve">2337</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6189,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2351</t>
+          <t xml:space="preserve">2347</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6221,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2361</t>
+          <t xml:space="preserve">2357</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6253,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2376</t>
+          <t xml:space="preserve">2372</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6285,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391</t>
+          <t xml:space="preserve">2387</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6317,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401</t>
+          <t xml:space="preserve">2397</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6349,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411</t>
+          <t xml:space="preserve">2407</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6381,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2421</t>
+          <t xml:space="preserve">2417</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6413,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2431</t>
+          <t xml:space="preserve">2427</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6445,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2441</t>
+          <t xml:space="preserve">2437</t>
         </is>
       </c>
     </row>
@@ -6440,7 +6477,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2451</t>
+          <t xml:space="preserve">2447</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6509,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2461</t>
+          <t xml:space="preserve">2457</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6541,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2468</t>
+          <t xml:space="preserve">2464</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6573,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2478</t>
+          <t xml:space="preserve">2474</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6605,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2488</t>
+          <t xml:space="preserve">2484</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6637,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2498</t>
+          <t xml:space="preserve">2494</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6669,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2508</t>
+          <t xml:space="preserve">2504</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6701,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2518</t>
+          <t xml:space="preserve">2514</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6733,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2528</t>
+          <t xml:space="preserve">2524</t>
         </is>
       </c>
     </row>
@@ -6728,7 +6765,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2538</t>
+          <t xml:space="preserve">2534</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6797,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2548</t>
+          <t xml:space="preserve">2544</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6829,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2558</t>
+          <t xml:space="preserve">2554</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6861,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2565</t>
+          <t xml:space="preserve">2561</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6893,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2572</t>
+          <t xml:space="preserve">2568</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6925,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579</t>
+          <t xml:space="preserve">2575</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6957,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2586</t>
+          <t xml:space="preserve">2582</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6989,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2593</t>
+          <t xml:space="preserve">2589</t>
         </is>
       </c>
     </row>
@@ -6984,7 +7021,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600</t>
+          <t xml:space="preserve">2596</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7053,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2607</t>
+          <t xml:space="preserve">2603</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7085,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2614</t>
+          <t xml:space="preserve">2610</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7117,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2621</t>
+          <t xml:space="preserve">2617</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7149,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2628</t>
+          <t xml:space="preserve">2624</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7181,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635</t>
+          <t xml:space="preserve">2631</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7213,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2642</t>
+          <t xml:space="preserve">2638</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7245,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2649</t>
+          <t xml:space="preserve">2645</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7277,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656</t>
+          <t xml:space="preserve">2652</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7309,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2663</t>
+          <t xml:space="preserve">2659</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7341,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2670</t>
+          <t xml:space="preserve">2666</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7373,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2677</t>
+          <t xml:space="preserve">2673</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7405,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2684</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7437,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2691</t>
+          <t xml:space="preserve">2687</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7469,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2698</t>
+          <t xml:space="preserve">2694</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7501,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2710</t>
+          <t xml:space="preserve">2706</t>
         </is>
       </c>
     </row>
@@ -7496,7 +7533,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2717</t>
+          <t xml:space="preserve">2713</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7565,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2724</t>
+          <t xml:space="preserve">2720</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7597,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2731</t>
+          <t xml:space="preserve">2727</t>
         </is>
       </c>
     </row>
@@ -7592,7 +7629,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2738</t>
+          <t xml:space="preserve">2734</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7661,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2745</t>
+          <t xml:space="preserve">2741</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7693,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2752</t>
+          <t xml:space="preserve">2748</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7725,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2759</t>
+          <t xml:space="preserve">2755</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7757,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2766</t>
+          <t xml:space="preserve">2762</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7789,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2773</t>
+          <t xml:space="preserve">2769</t>
         </is>
       </c>
     </row>
@@ -7784,7 +7821,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2780</t>
+          <t xml:space="preserve">2776</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7853,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2787</t>
+          <t xml:space="preserve">2783</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7885,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2794</t>
+          <t xml:space="preserve">2790</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7917,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2801</t>
+          <t xml:space="preserve">2797</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7949,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2808</t>
+          <t xml:space="preserve">2804</t>
         </is>
       </c>
     </row>
@@ -7944,7 +7981,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2815</t>
+          <t xml:space="preserve">2811</t>
         </is>
       </c>
     </row>
@@ -7976,7 +8013,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2822</t>
+          <t xml:space="preserve">2818</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8107,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544</t>
+          <t xml:space="preserve">1540</t>
         </is>
       </c>
     </row>
@@ -8107,7 +8144,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1548</t>
+          <t xml:space="preserve">1544</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8181,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1552</t>
+          <t xml:space="preserve">1548</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8218,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556</t>
+          <t xml:space="preserve">1552</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8255,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1564</t>
+          <t xml:space="preserve">1560</t>
         </is>
       </c>
     </row>
@@ -8255,7 +8292,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1565</t>
+          <t xml:space="preserve">1561</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8329,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566</t>
+          <t xml:space="preserve">1562</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8366,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1567</t>
+          <t xml:space="preserve">1563</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8403,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1568</t>
+          <t xml:space="preserve">1564</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8440,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1569</t>
+          <t xml:space="preserve">1565</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8477,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1570</t>
+          <t xml:space="preserve">1566</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8514,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1571</t>
+          <t xml:space="preserve">1567</t>
         </is>
       </c>
     </row>
@@ -8514,7 +8551,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1572</t>
+          <t xml:space="preserve">1568</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8588,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1573</t>
+          <t xml:space="preserve">1569</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8625,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1574</t>
+          <t xml:space="preserve">1570</t>
         </is>
       </c>
     </row>
@@ -8625,7 +8662,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575</t>
+          <t xml:space="preserve">1571</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8699,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1576</t>
+          <t xml:space="preserve">1572</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8736,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1577</t>
+          <t xml:space="preserve">1573</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8773,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1578</t>
+          <t xml:space="preserve">1574</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8810,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1579</t>
+          <t xml:space="preserve">1575</t>
         </is>
       </c>
     </row>
@@ -8810,7 +8847,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580</t>
+          <t xml:space="preserve">1576</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8884,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1581</t>
+          <t xml:space="preserve">1577</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8921,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1582</t>
+          <t xml:space="preserve">1578</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8958,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1583</t>
+          <t xml:space="preserve">1579</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8995,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1584</t>
+          <t xml:space="preserve">1580</t>
         </is>
       </c>
     </row>
@@ -8995,7 +9032,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1585</t>
+          <t xml:space="preserve">1581</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9069,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1586</t>
+          <t xml:space="preserve">1582</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9106,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1587</t>
+          <t xml:space="preserve">1583</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9143,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1588</t>
+          <t xml:space="preserve">1584</t>
         </is>
       </c>
     </row>
@@ -9143,7 +9180,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1589</t>
+          <t xml:space="preserve">1585</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9217,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1590</t>
+          <t xml:space="preserve">1586</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9254,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1591</t>
+          <t xml:space="preserve">1587</t>
         </is>
       </c>
     </row>
@@ -9254,7 +9291,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1592</t>
+          <t xml:space="preserve">1588</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9328,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1593</t>
+          <t xml:space="preserve">1589</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9365,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1594</t>
+          <t xml:space="preserve">1590</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9402,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1595</t>
+          <t xml:space="preserve">1591</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9439,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1596</t>
+          <t xml:space="preserve">1592</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9476,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1597</t>
+          <t xml:space="preserve">1593</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9513,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1598</t>
+          <t xml:space="preserve">1594</t>
         </is>
       </c>
     </row>
@@ -9513,7 +9550,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1599</t>
+          <t xml:space="preserve">1595</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9587,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600</t>
+          <t xml:space="preserve">1596</t>
         </is>
       </c>
     </row>
@@ -9587,7 +9624,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1601</t>
+          <t xml:space="preserve">1597</t>
         </is>
       </c>
     </row>
@@ -9624,7 +9661,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602</t>
+          <t xml:space="preserve">1598</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9698,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603</t>
+          <t xml:space="preserve">1599</t>
         </is>
       </c>
     </row>
@@ -9698,7 +9735,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1604</t>
+          <t xml:space="preserve">1600</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9772,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605</t>
+          <t xml:space="preserve">1601</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9809,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1606</t>
+          <t xml:space="preserve">1602</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9846,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1607</t>
+          <t xml:space="preserve">1603</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9883,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1608</t>
+          <t xml:space="preserve">1604</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9920,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1609</t>
+          <t xml:space="preserve">1605</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9957,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610</t>
+          <t xml:space="preserve">1606</t>
         </is>
       </c>
     </row>
@@ -9957,7 +9994,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1611</t>
+          <t xml:space="preserve">1607</t>
         </is>
       </c>
     </row>
@@ -9994,7 +10031,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612</t>
+          <t xml:space="preserve">1608</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10068,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1613</t>
+          <t xml:space="preserve">1609</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10105,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614</t>
+          <t xml:space="preserve">1610</t>
         </is>
       </c>
     </row>
@@ -10105,7 +10142,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615</t>
+          <t xml:space="preserve">1611</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10179,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616</t>
+          <t xml:space="preserve">1612</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10216,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1617</t>
+          <t xml:space="preserve">1613</t>
         </is>
       </c>
     </row>
@@ -10216,7 +10253,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618</t>
+          <t xml:space="preserve">1614</t>
         </is>
       </c>
     </row>
@@ -10253,7 +10290,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619</t>
+          <t xml:space="preserve">1615</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10327,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620</t>
+          <t xml:space="preserve">1616</t>
         </is>
       </c>
     </row>
@@ -10327,7 +10364,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1621</t>
+          <t xml:space="preserve">1617</t>
         </is>
       </c>
     </row>
@@ -10364,7 +10401,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1622</t>
+          <t xml:space="preserve">1618</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10438,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623</t>
+          <t xml:space="preserve">1619</t>
         </is>
       </c>
     </row>
@@ -10438,7 +10475,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1624</t>
+          <t xml:space="preserve">1620</t>
         </is>
       </c>
     </row>
@@ -10475,7 +10512,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625</t>
+          <t xml:space="preserve">1621</t>
         </is>
       </c>
     </row>
@@ -10512,7 +10549,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1626</t>
+          <t xml:space="preserve">1622</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10586,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1627</t>
+          <t xml:space="preserve">1623</t>
         </is>
       </c>
     </row>
@@ -10586,7 +10623,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628</t>
+          <t xml:space="preserve">1624</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10660,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1629</t>
+          <t xml:space="preserve">1625</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10697,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1630</t>
+          <t xml:space="preserve">1626</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10734,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631</t>
+          <t xml:space="preserve">1627</t>
         </is>
       </c>
     </row>
@@ -10734,7 +10771,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1632</t>
+          <t xml:space="preserve">1628</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10808,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1633</t>
+          <t xml:space="preserve">1629</t>
         </is>
       </c>
     </row>
@@ -10808,7 +10845,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1634</t>
+          <t xml:space="preserve">1630</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10882,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1635</t>
+          <t xml:space="preserve">1631</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10919,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1636</t>
+          <t xml:space="preserve">1632</t>
         </is>
       </c>
     </row>
@@ -10919,7 +10956,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1637</t>
+          <t xml:space="preserve">1633</t>
         </is>
       </c>
     </row>
@@ -10956,7 +10993,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1638</t>
+          <t xml:space="preserve">1634</t>
         </is>
       </c>
     </row>
@@ -10993,7 +11030,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1639</t>
+          <t xml:space="preserve">1635</t>
         </is>
       </c>
     </row>
@@ -11030,7 +11067,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640</t>
+          <t xml:space="preserve">1636</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11104,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1641</t>
+          <t xml:space="preserve">1637</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11141,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642</t>
+          <t xml:space="preserve">1638</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11178,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1643</t>
+          <t xml:space="preserve">1639</t>
         </is>
       </c>
     </row>
@@ -11178,7 +11215,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644</t>
+          <t xml:space="preserve">1640</t>
         </is>
       </c>
     </row>
@@ -11215,7 +11252,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645</t>
+          <t xml:space="preserve">1641</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11289,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1646</t>
+          <t xml:space="preserve">1642</t>
         </is>
       </c>
     </row>
@@ -11289,7 +11326,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647</t>
+          <t xml:space="preserve">1643</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11363,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648</t>
+          <t xml:space="preserve">1644</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11447,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/nsf-logo.png</t>
+          <t xml:space="preserve">sponsors-partners/nsf-logo.png</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -11420,7 +11457,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657</t>
+          <t xml:space="preserve">1653</t>
         </is>
       </c>
     </row>
@@ -11447,7 +11484,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/america-makes.jpg</t>
+          <t xml:space="preserve">sponsors-partners/america-makes.jpg</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -11457,7 +11494,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658</t>
+          <t xml:space="preserve">1654</t>
         </is>
       </c>
     </row>
@@ -11484,7 +11521,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/air-force-research-laboratory.png</t>
+          <t xml:space="preserve">sponsors-partners/air-force-research-laboratory.png</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -11494,7 +11531,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1659</t>
+          <t xml:space="preserve">1655</t>
         </is>
       </c>
     </row>
@@ -11521,7 +11558,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/office-of-naval-research.png</t>
+          <t xml:space="preserve">sponsors-partners/office-of-naval-research.png</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -11531,7 +11568,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660</t>
+          <t xml:space="preserve">1656</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11595,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/pennsylvania-manufacturing-sponsor.png</t>
+          <t xml:space="preserve">sponsors-partners/pennsylvania-manufacturing-sponsor.png</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -11568,7 +11605,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1661</t>
+          <t xml:space="preserve">1657</t>
         </is>
       </c>
     </row>
@@ -11595,7 +11632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/pa-dced-logo.jpg</t>
+          <t xml:space="preserve">sponsors-partners/pa-dced-logo.jpg</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -11605,7 +11642,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662</t>
+          <t xml:space="preserve">1658</t>
         </is>
       </c>
     </row>
@@ -11632,7 +11669,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/nist-center-of-excellence.jpg</t>
+          <t xml:space="preserve">sponsors-partners/nist-center-of-excellence.jpg</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -11642,7 +11679,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1663</t>
+          <t xml:space="preserve">1659</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11706,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/defense-manufacturing-sponsor.jpg</t>
+          <t xml:space="preserve">sponsors-partners/defense-manufacturing-sponsor.jpg</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -11679,7 +11716,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664</t>
+          <t xml:space="preserve">1660</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11743,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/iacmi-logo.png</t>
+          <t xml:space="preserve">sponsors-partners/iacmi-logo.png</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -11716,7 +11753,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665</t>
+          <t xml:space="preserve">1661</t>
         </is>
       </c>
     </row>
@@ -11743,7 +11780,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/ascent-flextech.png</t>
+          <t xml:space="preserve">sponsors-partners/ascent-flextech.png</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11753,7 +11790,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666</t>
+          <t xml:space="preserve">1662</t>
         </is>
       </c>
     </row>
@@ -11780,7 +11817,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/darpa-logo.jpg</t>
+          <t xml:space="preserve">sponsors-partners/darpa-logo.jpg</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11790,7 +11827,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1667</t>
+          <t xml:space="preserve">1663</t>
         </is>
       </c>
     </row>
@@ -11817,7 +11854,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/methods-machine-tools.jpg</t>
+          <t xml:space="preserve">sponsors-partners/methods-machine-tools.jpg</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -11827,7 +11864,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671</t>
+          <t xml:space="preserve">1667</t>
         </is>
       </c>
     </row>
@@ -11854,7 +11891,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/industrial-collaboration-partner.png</t>
+          <t xml:space="preserve">sponsors-partners/industrial-collaboration-partner.png</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11864,7 +11901,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672</t>
+          <t xml:space="preserve">1668</t>
         </is>
       </c>
     </row>
@@ -11891,7 +11928,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/technical-collaboration-partner.png</t>
+          <t xml:space="preserve">sponsors-partners/technical-collaboration-partner.png</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -11901,7 +11938,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1673</t>
+          <t xml:space="preserve">1669</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11965,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/hagerstown-community-college.jpg</t>
+          <t xml:space="preserve">sponsors-partners/hagerstown-community-college.jpg</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -11938,7 +11975,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1674</t>
+          <t xml:space="preserve">1670</t>
         </is>
       </c>
     </row>
@@ -11965,7 +12002,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/mastercam-logo.png</t>
+          <t xml:space="preserve">sponsors-partners/mastercam-logo.png</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -11975,7 +12012,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1675</t>
+          <t xml:space="preserve">1671</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12280,7 @@
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/Sand-Casting-1.png</t>
+          <t xml:space="preserve">research%20photos/sand-casting.png</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -12253,7 +12290,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -12263,14 +12300,14 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278</t>
+          <t xml:space="preserve">1274</t>
         </is>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/CDF.png</t>
+          <t xml:space="preserve">research%20photos/mass-finishing-cdf.png</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -12280,7 +12317,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -12290,14 +12327,14 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302</t>
+          <t xml:space="preserve">1298</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/TPMS1.png</t>
+          <t xml:space="preserve">research%20photos/multi-material-lpbf-tpms.png</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -12307,7 +12344,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -12317,14 +12354,14 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1327</t>
+          <t xml:space="preserve">1323</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/TPMS2-e1681999465376.png</t>
+          <t xml:space="preserve">research%20photos/non-pneumatic-tires-tpms.png</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -12334,7 +12371,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -12344,14 +12381,14 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344</t>
+          <t xml:space="preserve">1340</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sites.psu.edu/shapelab/files/2023/04/BJAM2.png</t>
+          <t xml:space="preserve">research%20photos/binder-jetting.png</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -12361,7 +12398,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote</t>
+          <t xml:space="preserve">Local</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -12371,7 +12408,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1369</t>
+          <t xml:space="preserve">1365</t>
         </is>
       </c>
     </row>
@@ -12398,7 +12435,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398</t>
+          <t xml:space="preserve">1394</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12462,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1402</t>
+          <t xml:space="preserve">1398</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12489,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1415</t>
+          <t xml:space="preserve">1411</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12516,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1422</t>
+          <t xml:space="preserve">1418</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12543,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1423</t>
+          <t xml:space="preserve">1419</t>
         </is>
       </c>
     </row>
@@ -12533,7 +12570,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424</t>
+          <t xml:space="preserve">1420</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12597,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425</t>
+          <t xml:space="preserve">1421</t>
         </is>
       </c>
     </row>
@@ -12587,7 +12624,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426</t>
+          <t xml:space="preserve">1422</t>
         </is>
       </c>
     </row>
@@ -12614,7 +12651,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427</t>
+          <t xml:space="preserve">1423</t>
         </is>
       </c>
     </row>
@@ -12641,7 +12678,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428</t>
+          <t xml:space="preserve">1424</t>
         </is>
       </c>
     </row>
@@ -12668,7 +12705,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429</t>
+          <t xml:space="preserve">1425</t>
         </is>
       </c>
     </row>
@@ -12695,7 +12732,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1430</t>
+          <t xml:space="preserve">1426</t>
         </is>
       </c>
     </row>
@@ -12722,7 +12759,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1431</t>
+          <t xml:space="preserve">1427</t>
         </is>
       </c>
     </row>
@@ -12749,7 +12786,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1432</t>
+          <t xml:space="preserve">1428</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12813,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1439</t>
+          <t xml:space="preserve">1435</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12840,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1446</t>
+          <t xml:space="preserve">1442</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12867,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1453</t>
+          <t xml:space="preserve">1449</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12894,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1454</t>
+          <t xml:space="preserve">1450</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12921,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455</t>
+          <t xml:space="preserve">1451</t>
         </is>
       </c>
     </row>
@@ -12911,7 +12948,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1456</t>
+          <t xml:space="preserve">1452</t>
         </is>
       </c>
     </row>
@@ -12938,7 +12975,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1457</t>
+          <t xml:space="preserve">1453</t>
         </is>
       </c>
     </row>
@@ -12965,7 +13002,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1458</t>
+          <t xml:space="preserve">1454</t>
         </is>
       </c>
     </row>
@@ -12992,7 +13029,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1459</t>
+          <t xml:space="preserve">1455</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13056,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1545</t>
+          <t xml:space="preserve">1541</t>
         </is>
       </c>
     </row>
@@ -13046,7 +13083,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1549</t>
+          <t xml:space="preserve">1545</t>
         </is>
       </c>
     </row>
@@ -13073,7 +13110,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553</t>
+          <t xml:space="preserve">1549</t>
         </is>
       </c>
     </row>
@@ -13100,14 +13137,14 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1557</t>
+          <t xml:space="preserve">1553</t>
         </is>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/nsf-logo.png</t>
+          <t xml:space="preserve">sponsors-partners/nsf-logo.png</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -13127,14 +13164,14 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657</t>
+          <t xml:space="preserve">1653</t>
         </is>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/america-makes.jpg</t>
+          <t xml:space="preserve">sponsors-partners/america-makes.jpg</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -13154,14 +13191,14 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658</t>
+          <t xml:space="preserve">1654</t>
         </is>
       </c>
     </row>
     <row r="39" ht="48" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/air-force-research-laboratory.png</t>
+          <t xml:space="preserve">sponsors-partners/air-force-research-laboratory.png</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -13181,14 +13218,14 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1659</t>
+          <t xml:space="preserve">1655</t>
         </is>
       </c>
     </row>
     <row r="40" ht="48" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/office-of-naval-research.png</t>
+          <t xml:space="preserve">sponsors-partners/office-of-naval-research.png</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -13208,14 +13245,14 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660</t>
+          <t xml:space="preserve">1656</t>
         </is>
       </c>
     </row>
     <row r="41" ht="48" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/pennsylvania-manufacturing-sponsor.png</t>
+          <t xml:space="preserve">sponsors-partners/pennsylvania-manufacturing-sponsor.png</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -13235,14 +13272,14 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1661</t>
+          <t xml:space="preserve">1657</t>
         </is>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/pa-dced-logo.jpg</t>
+          <t xml:space="preserve">sponsors-partners/pa-dced-logo.jpg</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -13262,14 +13299,14 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662</t>
+          <t xml:space="preserve">1658</t>
         </is>
       </c>
     </row>
     <row r="43" ht="48" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/nist-center-of-excellence.jpg</t>
+          <t xml:space="preserve">sponsors-partners/nist-center-of-excellence.jpg</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -13289,14 +13326,14 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1663</t>
+          <t xml:space="preserve">1659</t>
         </is>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/defense-manufacturing-sponsor.jpg</t>
+          <t xml:space="preserve">sponsors-partners/defense-manufacturing-sponsor.jpg</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -13316,14 +13353,14 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664</t>
+          <t xml:space="preserve">1660</t>
         </is>
       </c>
     </row>
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/iacmi-logo.png</t>
+          <t xml:space="preserve">sponsors-partners/iacmi-logo.png</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -13343,14 +13380,14 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665</t>
+          <t xml:space="preserve">1661</t>
         </is>
       </c>
     </row>
     <row r="46" ht="48" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/ascent-flextech.png</t>
+          <t xml:space="preserve">sponsors-partners/ascent-flextech.png</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -13370,14 +13407,14 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666</t>
+          <t xml:space="preserve">1662</t>
         </is>
       </c>
     </row>
     <row r="47" ht="48" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/darpa-logo.jpg</t>
+          <t xml:space="preserve">sponsors-partners/darpa-logo.jpg</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -13397,14 +13434,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1667</t>
+          <t xml:space="preserve">1663</t>
         </is>
       </c>
     </row>
     <row r="48" ht="48" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/methods-machine-tools.jpg</t>
+          <t xml:space="preserve">sponsors-partners/methods-machine-tools.jpg</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -13424,14 +13461,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671</t>
+          <t xml:space="preserve">1667</t>
         </is>
       </c>
     </row>
     <row r="49" ht="48" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/industrial-collaboration-partner.png</t>
+          <t xml:space="preserve">sponsors-partners/industrial-collaboration-partner.png</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -13451,14 +13488,14 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672</t>
+          <t xml:space="preserve">1668</t>
         </is>
       </c>
     </row>
     <row r="50" ht="48" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/technical-collaboration-partner.png</t>
+          <t xml:space="preserve">sponsors-partners/technical-collaboration-partner.png</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -13478,14 +13515,14 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1673</t>
+          <t xml:space="preserve">1669</t>
         </is>
       </c>
     </row>
     <row r="51" ht="48" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/hagerstown-community-college.jpg</t>
+          <t xml:space="preserve">sponsors-partners/hagerstown-community-college.jpg</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -13505,14 +13542,14 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1674</t>
+          <t xml:space="preserve">1670</t>
         </is>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets/sponsors-partners/mastercam-logo.png</t>
+          <t xml:space="preserve">sponsors-partners/mastercam-logo.png</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -13532,7 +13569,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1675</t>
+          <t xml:space="preserve">1671</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13596,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2844</t>
+          <t xml:space="preserve">2840</t>
         </is>
       </c>
     </row>
@@ -13586,7 +13623,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2845</t>
+          <t xml:space="preserve">2841</t>
         </is>
       </c>
     </row>
@@ -13613,7 +13650,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2846</t>
+          <t xml:space="preserve">2842</t>
         </is>
       </c>
     </row>
@@ -13640,7 +13677,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2847</t>
+          <t xml:space="preserve">2843</t>
         </is>
       </c>
     </row>
@@ -13667,7 +13704,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2848</t>
+          <t xml:space="preserve">2844</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13731,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2849</t>
+          <t xml:space="preserve">2845</t>
         </is>
       </c>
     </row>
@@ -13721,7 +13758,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2850</t>
+          <t xml:space="preserve">2846</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13785,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2851</t>
+          <t xml:space="preserve">2847</t>
         </is>
       </c>
     </row>
@@ -13775,7 +13812,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2852</t>
+          <t xml:space="preserve">2848</t>
         </is>
       </c>
     </row>
@@ -13802,7 +13839,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2853</t>
+          <t xml:space="preserve">2849</t>
         </is>
       </c>
     </row>
@@ -13829,7 +13866,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2854</t>
+          <t xml:space="preserve">2850</t>
         </is>
       </c>
     </row>
@@ -13856,7 +13893,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2855</t>
+          <t xml:space="preserve">2851</t>
         </is>
       </c>
     </row>
@@ -13883,7 +13920,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2856</t>
+          <t xml:space="preserve">2852</t>
         </is>
       </c>
     </row>
@@ -13910,7 +13947,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2857</t>
+          <t xml:space="preserve">2853</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13974,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2858</t>
+          <t xml:space="preserve">2854</t>
         </is>
       </c>
     </row>
@@ -13964,7 +14001,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2859</t>
+          <t xml:space="preserve">2855</t>
         </is>
       </c>
     </row>
@@ -13991,7 +14028,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2856</t>
         </is>
       </c>
     </row>
@@ -14018,7 +14055,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861</t>
+          <t xml:space="preserve">2857</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14082,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2862</t>
+          <t xml:space="preserve">2858</t>
         </is>
       </c>
     </row>
@@ -14072,7 +14109,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2863</t>
+          <t xml:space="preserve">2859</t>
         </is>
       </c>
     </row>
@@ -14099,7 +14136,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2864</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
     </row>
@@ -14126,7 +14163,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2865</t>
+          <t xml:space="preserve">2861</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14190,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2866</t>
+          <t xml:space="preserve">2862</t>
         </is>
       </c>
     </row>
@@ -14180,7 +14217,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2867</t>
+          <t xml:space="preserve">2863</t>
         </is>
       </c>
     </row>
@@ -14439,7 +14476,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408</t>
+          <t xml:space="preserve">1404</t>
         </is>
       </c>
     </row>
@@ -14461,7 +14498,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408</t>
+          <t xml:space="preserve">1404</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14520,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1415</t>
+          <t xml:space="preserve">1411</t>
         </is>
       </c>
     </row>
@@ -14505,7 +14542,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1415</t>
+          <t xml:space="preserve">1411</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14564,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1415</t>
+          <t xml:space="preserve">1411</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14586,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1422</t>
+          <t xml:space="preserve">1418</t>
         </is>
       </c>
     </row>
@@ -14571,7 +14608,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1422</t>
+          <t xml:space="preserve">1418</t>
         </is>
       </c>
     </row>
@@ -14593,7 +14630,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1422</t>
+          <t xml:space="preserve">1418</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14652,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1423</t>
+          <t xml:space="preserve">1419</t>
         </is>
       </c>
     </row>
@@ -14637,7 +14674,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1423</t>
+          <t xml:space="preserve">1419</t>
         </is>
       </c>
     </row>
@@ -14659,7 +14696,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1423</t>
+          <t xml:space="preserve">1419</t>
         </is>
       </c>
     </row>
@@ -14681,7 +14718,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424</t>
+          <t xml:space="preserve">1420</t>
         </is>
       </c>
     </row>
@@ -14703,7 +14740,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424</t>
+          <t xml:space="preserve">1420</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14762,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424</t>
+          <t xml:space="preserve">1420</t>
         </is>
       </c>
     </row>
@@ -14747,7 +14784,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425</t>
+          <t xml:space="preserve">1421</t>
         </is>
       </c>
     </row>
@@ -14769,7 +14806,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425</t>
+          <t xml:space="preserve">1421</t>
         </is>
       </c>
     </row>
@@ -14791,7 +14828,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425</t>
+          <t xml:space="preserve">1421</t>
         </is>
       </c>
     </row>
@@ -14813,7 +14850,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426</t>
+          <t xml:space="preserve">1422</t>
         </is>
       </c>
     </row>
@@ -14835,7 +14872,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426</t>
+          <t xml:space="preserve">1422</t>
         </is>
       </c>
     </row>
@@ -14857,7 +14894,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427</t>
+          <t xml:space="preserve">1423</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14916,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427</t>
+          <t xml:space="preserve">1423</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14938,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428</t>
+          <t xml:space="preserve">1424</t>
         </is>
       </c>
     </row>
@@ -14923,7 +14960,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428</t>
+          <t xml:space="preserve">1424</t>
         </is>
       </c>
     </row>
@@ -14945,7 +14982,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429</t>
+          <t xml:space="preserve">1425</t>
         </is>
       </c>
     </row>
@@ -14967,7 +15004,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1430</t>
+          <t xml:space="preserve">1426</t>
         </is>
       </c>
     </row>
@@ -14989,7 +15026,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1430</t>
+          <t xml:space="preserve">1426</t>
         </is>
       </c>
     </row>
@@ -15011,7 +15048,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1430</t>
+          <t xml:space="preserve">1426</t>
         </is>
       </c>
     </row>
@@ -15033,7 +15070,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1431</t>
+          <t xml:space="preserve">1427</t>
         </is>
       </c>
     </row>
@@ -15055,7 +15092,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1431</t>
+          <t xml:space="preserve">1427</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15114,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1432</t>
+          <t xml:space="preserve">1428</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15136,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1432</t>
+          <t xml:space="preserve">1428</t>
         </is>
       </c>
     </row>
@@ -15121,7 +15158,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1446</t>
+          <t xml:space="preserve">1442</t>
         </is>
       </c>
     </row>
@@ -15143,7 +15180,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1446</t>
+          <t xml:space="preserve">1442</t>
         </is>
       </c>
     </row>
@@ -15165,7 +15202,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1453</t>
+          <t xml:space="preserve">1449</t>
         </is>
       </c>
     </row>
@@ -15187,7 +15224,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1453</t>
+          <t xml:space="preserve">1449</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15246,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1454</t>
+          <t xml:space="preserve">1450</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15268,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1454</t>
+          <t xml:space="preserve">1450</t>
         </is>
       </c>
     </row>
@@ -15253,7 +15290,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455</t>
+          <t xml:space="preserve">1451</t>
         </is>
       </c>
     </row>
@@ -15275,7 +15312,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1456</t>
+          <t xml:space="preserve">1452</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15334,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1456</t>
+          <t xml:space="preserve">1452</t>
         </is>
       </c>
     </row>
@@ -15319,7 +15356,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1457</t>
+          <t xml:space="preserve">1453</t>
         </is>
       </c>
     </row>
@@ -15341,7 +15378,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1457</t>
+          <t xml:space="preserve">1453</t>
         </is>
       </c>
     </row>
@@ -15363,7 +15400,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1458</t>
+          <t xml:space="preserve">1454</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15422,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1458</t>
+          <t xml:space="preserve">1454</t>
         </is>
       </c>
     </row>
@@ -15407,7 +15444,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1459</t>
+          <t xml:space="preserve">1455</t>
         </is>
       </c>
     </row>
@@ -15429,7 +15466,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1459</t>
+          <t xml:space="preserve">1455</t>
         </is>
       </c>
     </row>
@@ -15451,7 +15488,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1546</t>
+          <t xml:space="preserve">1542</t>
         </is>
       </c>
     </row>
@@ -15473,7 +15510,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566</t>
+          <t xml:space="preserve">1562</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15532,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1567</t>
+          <t xml:space="preserve">1563</t>
         </is>
       </c>
     </row>
@@ -15517,7 +15554,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1570</t>
+          <t xml:space="preserve">1566</t>
         </is>
       </c>
     </row>
@@ -15539,7 +15576,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1572</t>
+          <t xml:space="preserve">1568</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15598,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1573</t>
+          <t xml:space="preserve">1569</t>
         </is>
       </c>
     </row>
@@ -15583,7 +15620,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1574</t>
+          <t xml:space="preserve">1570</t>
         </is>
       </c>
     </row>
@@ -15605,7 +15642,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1576</t>
+          <t xml:space="preserve">1572</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15664,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642</t>
+          <t xml:space="preserve">1638</t>
         </is>
       </c>
     </row>
@@ -15649,7 +15686,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1646</t>
+          <t xml:space="preserve">1642</t>
         </is>
       </c>
     </row>
@@ -15671,7 +15708,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647</t>
+          <t xml:space="preserve">1643</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15730,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648</t>
+          <t xml:space="preserve">1644</t>
         </is>
       </c>
     </row>
@@ -15715,7 +15752,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657</t>
+          <t xml:space="preserve">1653</t>
         </is>
       </c>
     </row>
@@ -15737,7 +15774,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658</t>
+          <t xml:space="preserve">1654</t>
         </is>
       </c>
     </row>
@@ -15759,7 +15796,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1659</t>
+          <t xml:space="preserve">1655</t>
         </is>
       </c>
     </row>
@@ -15781,7 +15818,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660</t>
+          <t xml:space="preserve">1656</t>
         </is>
       </c>
     </row>
@@ -15803,7 +15840,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1661</t>
+          <t xml:space="preserve">1657</t>
         </is>
       </c>
     </row>
@@ -15825,7 +15862,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662</t>
+          <t xml:space="preserve">1658</t>
         </is>
       </c>
     </row>
@@ -15847,7 +15884,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1663</t>
+          <t xml:space="preserve">1659</t>
         </is>
       </c>
     </row>
@@ -15869,7 +15906,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664</t>
+          <t xml:space="preserve">1660</t>
         </is>
       </c>
     </row>
@@ -15891,7 +15928,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665</t>
+          <t xml:space="preserve">1661</t>
         </is>
       </c>
     </row>
@@ -15913,7 +15950,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666</t>
+          <t xml:space="preserve">1662</t>
         </is>
       </c>
     </row>
@@ -15935,7 +15972,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1667</t>
+          <t xml:space="preserve">1663</t>
         </is>
       </c>
     </row>
@@ -15957,7 +15994,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671</t>
+          <t xml:space="preserve">1667</t>
         </is>
       </c>
     </row>
@@ -15979,7 +16016,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672</t>
+          <t xml:space="preserve">1668</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16038,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1673</t>
+          <t xml:space="preserve">1669</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16060,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1674</t>
+          <t xml:space="preserve">1670</t>
         </is>
       </c>
     </row>
@@ -16045,7 +16082,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1675</t>
+          <t xml:space="preserve">1671</t>
         </is>
       </c>
     </row>
@@ -16067,7 +16104,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1698</t>
+          <t xml:space="preserve">1694</t>
         </is>
       </c>
     </row>
@@ -16089,7 +16126,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1708</t>
+          <t xml:space="preserve">1704</t>
         </is>
       </c>
     </row>
@@ -16111,7 +16148,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718</t>
+          <t xml:space="preserve">1714</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16170,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1733</t>
+          <t xml:space="preserve">1729</t>
         </is>
       </c>
     </row>
@@ -16155,7 +16192,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1743</t>
+          <t xml:space="preserve">1739</t>
         </is>
       </c>
     </row>
@@ -16177,7 +16214,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1753</t>
+          <t xml:space="preserve">1749</t>
         </is>
       </c>
     </row>
@@ -16199,7 +16236,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1763</t>
+          <t xml:space="preserve">1759</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16258,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1773</t>
+          <t xml:space="preserve">1769</t>
         </is>
       </c>
     </row>
@@ -16243,7 +16280,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1783</t>
+          <t xml:space="preserve">1779</t>
         </is>
       </c>
     </row>
@@ -16265,7 +16302,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1793</t>
+          <t xml:space="preserve">1789</t>
         </is>
       </c>
     </row>
@@ -16287,7 +16324,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1803</t>
+          <t xml:space="preserve">1799</t>
         </is>
       </c>
     </row>
@@ -16309,7 +16346,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1813</t>
+          <t xml:space="preserve">1809</t>
         </is>
       </c>
     </row>
@@ -16331,7 +16368,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1823</t>
+          <t xml:space="preserve">1819</t>
         </is>
       </c>
     </row>
@@ -16353,7 +16390,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1833</t>
+          <t xml:space="preserve">1829</t>
         </is>
       </c>
     </row>
@@ -16375,7 +16412,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1843</t>
+          <t xml:space="preserve">1839</t>
         </is>
       </c>
     </row>
@@ -16397,7 +16434,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853</t>
+          <t xml:space="preserve">1849</t>
         </is>
       </c>
     </row>
@@ -16419,7 +16456,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1863</t>
+          <t xml:space="preserve">1859</t>
         </is>
       </c>
     </row>
@@ -16441,7 +16478,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1873</t>
+          <t xml:space="preserve">1869</t>
         </is>
       </c>
     </row>
@@ -16463,7 +16500,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888</t>
+          <t xml:space="preserve">1884</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16522,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898</t>
+          <t xml:space="preserve">1894</t>
         </is>
       </c>
     </row>
@@ -16507,7 +16544,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1908</t>
+          <t xml:space="preserve">1904</t>
         </is>
       </c>
     </row>
@@ -16529,7 +16566,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918</t>
+          <t xml:space="preserve">1914</t>
         </is>
       </c>
     </row>
@@ -16551,7 +16588,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928</t>
+          <t xml:space="preserve">1924</t>
         </is>
       </c>
     </row>
@@ -16573,7 +16610,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1938</t>
+          <t xml:space="preserve">1934</t>
         </is>
       </c>
     </row>
@@ -16595,7 +16632,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948</t>
+          <t xml:space="preserve">1944</t>
         </is>
       </c>
     </row>
@@ -16617,7 +16654,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1958</t>
+          <t xml:space="preserve">1954</t>
         </is>
       </c>
     </row>
@@ -16639,7 +16676,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1968</t>
+          <t xml:space="preserve">1964</t>
         </is>
       </c>
     </row>
@@ -16661,7 +16698,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1983</t>
+          <t xml:space="preserve">1979</t>
         </is>
       </c>
     </row>
@@ -16683,7 +16720,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1993</t>
+          <t xml:space="preserve">1989</t>
         </is>
       </c>
     </row>
@@ -16705,7 +16742,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003</t>
+          <t xml:space="preserve">1999</t>
         </is>
       </c>
     </row>
@@ -16727,7 +16764,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013</t>
+          <t xml:space="preserve">2009</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16786,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023</t>
+          <t xml:space="preserve">2019</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16808,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033</t>
+          <t xml:space="preserve">2029</t>
         </is>
       </c>
     </row>
@@ -16793,7 +16830,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2043</t>
+          <t xml:space="preserve">2039</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16852,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2053</t>
+          <t xml:space="preserve">2049</t>
         </is>
       </c>
     </row>
@@ -16837,7 +16874,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2063</t>
+          <t xml:space="preserve">2059</t>
         </is>
       </c>
     </row>
@@ -16859,7 +16896,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2073</t>
+          <t xml:space="preserve">2069</t>
         </is>
       </c>
     </row>
@@ -16881,7 +16918,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2083</t>
+          <t xml:space="preserve">2079</t>
         </is>
       </c>
     </row>
@@ -16903,7 +16940,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2093</t>
+          <t xml:space="preserve">2089</t>
         </is>
       </c>
     </row>
@@ -16925,7 +16962,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103</t>
+          <t xml:space="preserve">2099</t>
         </is>
       </c>
     </row>
@@ -16947,7 +16984,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118</t>
+          <t xml:space="preserve">2114</t>
         </is>
       </c>
     </row>
@@ -16969,7 +17006,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128</t>
+          <t xml:space="preserve">2124</t>
         </is>
       </c>
     </row>
@@ -16991,7 +17028,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138</t>
+          <t xml:space="preserve">2134</t>
         </is>
       </c>
     </row>
@@ -17013,7 +17050,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148</t>
+          <t xml:space="preserve">2144</t>
         </is>
       </c>
     </row>
@@ -17035,7 +17072,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2158</t>
+          <t xml:space="preserve">2154</t>
         </is>
       </c>
     </row>
@@ -17057,7 +17094,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2168</t>
+          <t xml:space="preserve">2164</t>
         </is>
       </c>
     </row>
@@ -17079,7 +17116,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178</t>
+          <t xml:space="preserve">2174</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17138,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188</t>
+          <t xml:space="preserve">2184</t>
         </is>
       </c>
     </row>
@@ -17123,7 +17160,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198</t>
+          <t xml:space="preserve">2194</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17182,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208</t>
+          <t xml:space="preserve">2204</t>
         </is>
       </c>
     </row>
@@ -17167,7 +17204,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218</t>
+          <t xml:space="preserve">2214</t>
         </is>
       </c>
     </row>
@@ -17189,7 +17226,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228</t>
+          <t xml:space="preserve">2224</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17248,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2238</t>
+          <t xml:space="preserve">2234</t>
         </is>
       </c>
     </row>
@@ -17233,7 +17270,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2248</t>
+          <t xml:space="preserve">2244</t>
         </is>
       </c>
     </row>
@@ -17255,7 +17292,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258</t>
+          <t xml:space="preserve">2254</t>
         </is>
       </c>
     </row>
@@ -17277,7 +17314,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2268</t>
+          <t xml:space="preserve">2264</t>
         </is>
       </c>
     </row>
@@ -17299,7 +17336,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2278</t>
+          <t xml:space="preserve">2274</t>
         </is>
       </c>
     </row>
@@ -17321,7 +17358,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2288</t>
+          <t xml:space="preserve">2284</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17380,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298</t>
+          <t xml:space="preserve">2294</t>
         </is>
       </c>
     </row>
@@ -17365,7 +17402,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2308</t>
+          <t xml:space="preserve">2304</t>
         </is>
       </c>
     </row>
@@ -17387,7 +17424,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2318</t>
+          <t xml:space="preserve">2314</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17446,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328</t>
+          <t xml:space="preserve">2324</t>
         </is>
       </c>
     </row>
@@ -17431,7 +17468,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2338</t>
+          <t xml:space="preserve">2334</t>
         </is>
       </c>
     </row>
@@ -17453,7 +17490,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348</t>
+          <t xml:space="preserve">2344</t>
         </is>
       </c>
     </row>
@@ -17475,7 +17512,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2358</t>
+          <t xml:space="preserve">2354</t>
         </is>
       </c>
     </row>
@@ -17497,7 +17534,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2368</t>
+          <t xml:space="preserve">2364</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17556,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2383</t>
+          <t xml:space="preserve">2379</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17578,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2398</t>
+          <t xml:space="preserve">2394</t>
         </is>
       </c>
     </row>
@@ -17563,7 +17600,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408</t>
+          <t xml:space="preserve">2404</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17622,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2418</t>
+          <t xml:space="preserve">2414</t>
         </is>
       </c>
     </row>
@@ -17607,7 +17644,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2428</t>
+          <t xml:space="preserve">2424</t>
         </is>
       </c>
     </row>
@@ -17629,7 +17666,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2438</t>
+          <t xml:space="preserve">2434</t>
         </is>
       </c>
     </row>
@@ -17651,7 +17688,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448</t>
+          <t xml:space="preserve">2444</t>
         </is>
       </c>
     </row>
@@ -17673,7 +17710,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2458</t>
+          <t xml:space="preserve">2454</t>
         </is>
       </c>
     </row>
@@ -17695,7 +17732,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2475</t>
+          <t xml:space="preserve">2471</t>
         </is>
       </c>
     </row>
@@ -17717,7 +17754,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2485</t>
+          <t xml:space="preserve">2481</t>
         </is>
       </c>
     </row>
@@ -17739,7 +17776,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2495</t>
+          <t xml:space="preserve">2491</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17798,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505</t>
+          <t xml:space="preserve">2501</t>
         </is>
       </c>
     </row>
@@ -17783,7 +17820,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515</t>
+          <t xml:space="preserve">2511</t>
         </is>
       </c>
     </row>
@@ -17805,7 +17842,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2525</t>
+          <t xml:space="preserve">2521</t>
         </is>
       </c>
     </row>
@@ -17827,7 +17864,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2535</t>
+          <t xml:space="preserve">2531</t>
         </is>
       </c>
     </row>
@@ -17849,7 +17886,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2545</t>
+          <t xml:space="preserve">2541</t>
         </is>
       </c>
     </row>
@@ -17871,7 +17908,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2555</t>
+          <t xml:space="preserve">2551</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17930,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2904</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
     </row>
@@ -17915,7 +17952,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2905</t>
+          <t xml:space="preserve">2901</t>
         </is>
       </c>
     </row>
@@ -17937,7 +17974,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2906</t>
+          <t xml:space="preserve">2902</t>
         </is>
       </c>
     </row>
@@ -17959,7 +17996,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907</t>
+          <t xml:space="preserve">2903</t>
         </is>
       </c>
     </row>
@@ -17981,7 +18018,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2908</t>
+          <t xml:space="preserve">2904</t>
         </is>
       </c>
     </row>
@@ -18003,7 +18040,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2909</t>
+          <t xml:space="preserve">2905</t>
         </is>
       </c>
     </row>
@@ -18025,7 +18062,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2910</t>
+          <t xml:space="preserve">2906</t>
         </is>
       </c>
     </row>
@@ -18047,7 +18084,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2911</t>
+          <t xml:space="preserve">2907</t>
         </is>
       </c>
     </row>

--- a/SHAPE-Lab-Website-Content.xlsx
+++ b/SHAPE-Lab-Website-Content.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3378" uniqueCount="1612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="1616">
   <si>
     <t>Section</t>
   </si>
@@ -4865,6 +4865,18 @@
   </si>
   <si>
     <t>Bryan Gong, Aishwarya Deshpande, Chris Carson</t>
+  </si>
+  <si>
+    <t>mailto:kvd25@psu.edu</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=e4NY0-cAAAAJ&amp;hl=en&amp;authuser=3</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kaustub-deshmukh</t>
+  </si>
+  <si>
+    <t>1463</t>
   </si>
 </sst>
 </file>
@@ -14396,7 +14408,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D178"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -16855,8 +16867,50 @@
         <v>1555</v>
       </c>
     </row>
+    <row r="176" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>1615</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D175" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <autoFilter ref="A1:D178" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/SHAPE-Lab-Website-Content.xlsx
+++ b/SHAPE-Lab-Website-Content.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="1616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="1618">
   <si>
     <t>Section</t>
   </si>
@@ -4877,6 +4877,12 @@
   </si>
   <si>
     <t>1463</t>
+  </si>
+  <si>
+    <t>mailto:cfc5052@psu.edu</t>
+  </si>
+  <si>
+    <t>1487</t>
   </si>
 </sst>
 </file>
@@ -14408,7 +14414,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:D178"/>
+  <dimension ref="A1:D179"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -16909,8 +16915,22 @@
         <v>1615</v>
       </c>
     </row>
+    <row r="179" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A179" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>1617</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D178" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <autoFilter ref="A1:D179" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>